--- a/forms/app/covid_education.xlsx
+++ b/forms/app/covid_education.xlsx
@@ -13,30 +13,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="266">
-  <si>
-    <t>form_title</t>
-  </si>
-  <si>
-    <t>form_id</t>
-  </si>
-  <si>
-    <t>version</t>
-  </si>
-  <si>
-    <t>style</t>
-  </si>
-  <si>
-    <t>path</t>
-  </si>
-  <si>
-    <t>instance_name</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="269">
   <si>
     <t>type</t>
-  </si>
-  <si>
-    <t>list_name</t>
   </si>
   <si>
     <t>name</t>
@@ -48,19 +27,100 @@
     <t>label::sw</t>
   </si>
   <si>
-    <t xml:space="preserve">Covid Education </t>
+    <t>required</t>
   </si>
   <si>
-    <t>covid_education</t>
+    <t>relevant</t>
   </si>
   <si>
-    <t>pages</t>
+    <t>appearance</t>
+  </si>
+  <si>
+    <t>read_only</t>
+  </si>
+  <si>
+    <t>constraint</t>
+  </si>
+  <si>
+    <t>constraint_message::en</t>
+  </si>
+  <si>
+    <t>constraint_message::sw</t>
+  </si>
+  <si>
+    <t>calculation</t>
+  </si>
+  <si>
+    <t>choice_filter</t>
+  </si>
+  <si>
+    <t>hint::en</t>
+  </si>
+  <si>
+    <t>hint::sw</t>
+  </si>
+  <si>
+    <t>default</t>
+  </si>
+  <si>
+    <t>repeat_count</t>
+  </si>
+  <si>
+    <t>media::image::en</t>
+  </si>
+  <si>
+    <t>media::image::sw</t>
+  </si>
+  <si>
+    <t>begin group</t>
+  </si>
+  <si>
+    <t>inputs</t>
+  </si>
+  <si>
+    <t>NO_LABEL</t>
+  </si>
+  <si>
+    <t>user</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>contact_id</t>
+  </si>
+  <si>
+    <t>Contact ID of the logged in user</t>
+  </si>
+  <si>
+    <t>facility_id</t>
+  </si>
+  <si>
+    <t>Facility ID for the parent user</t>
+  </si>
+  <si>
+    <t>Name of the logged in user</t>
+  </si>
+  <si>
+    <t>end group</t>
+  </si>
+  <si>
+    <t>calculate</t>
+  </si>
+  <si>
+    <t>created_by</t>
+  </si>
+  <si>
+    <t>hidden</t>
+  </si>
+  <si>
+    <t>../inputs/user/name</t>
+  </si>
+  <si>
+    <t>list_name</t>
   </si>
   <si>
     <t>yes_no</t>
-  </si>
-  <si>
-    <t>data</t>
   </si>
   <si>
     <t>yes</t>
@@ -207,96 +267,6 @@
     <t xml:space="preserve">Hakuna moja wapo </t>
   </si>
   <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>relevant</t>
-  </si>
-  <si>
-    <t>appearance</t>
-  </si>
-  <si>
-    <t>read_only</t>
-  </si>
-  <si>
-    <t>constraint</t>
-  </si>
-  <si>
-    <t>constraint_message::en</t>
-  </si>
-  <si>
-    <t>constraint_message::sw</t>
-  </si>
-  <si>
-    <t>calculation</t>
-  </si>
-  <si>
-    <t>choice_filter</t>
-  </si>
-  <si>
-    <t>hint::en</t>
-  </si>
-  <si>
-    <t>hint::sw</t>
-  </si>
-  <si>
-    <t>default</t>
-  </si>
-  <si>
-    <t>repeat_count</t>
-  </si>
-  <si>
-    <t>media::image::en</t>
-  </si>
-  <si>
-    <t>media::image::sw</t>
-  </si>
-  <si>
-    <t>begin group</t>
-  </si>
-  <si>
-    <t>inputs</t>
-  </si>
-  <si>
-    <t>NO_LABEL</t>
-  </si>
-  <si>
-    <t>user</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>contact_id</t>
-  </si>
-  <si>
-    <t>Contact ID of the logged in user</t>
-  </si>
-  <si>
-    <t>facility_id</t>
-  </si>
-  <si>
-    <t>Facility ID for the parent user</t>
-  </si>
-  <si>
-    <t>Name of the logged in user</t>
-  </si>
-  <si>
-    <t>end group</t>
-  </si>
-  <si>
-    <t>calculate</t>
-  </si>
-  <si>
-    <t>created_by</t>
-  </si>
-  <si>
-    <t>hidden</t>
-  </si>
-  <si>
-    <t>../inputs/user/name</t>
-  </si>
-  <si>
     <t>created_by_person_uuid</t>
   </si>
   <si>
@@ -331,21 +301,24 @@
   </si>
   <si>
     <t xml:space="preserve">&lt;span style="color:#f58a1f"&gt;As a CHV, you are responsible for making sure that you are providing the community with health education and services while trying to take precautions to stop the transmission of Coronavirus to one another. Therefore, make sure you consider the following while you conduct the visits:  
+•       All visits must be conducted outside the home in open space, where there is air flow and risk of spread of disease is less.
+•       You must wear a cloth mask when conducting home visits and moving through the community. If you do not have a mask, please do not make the household visit.
 •        Wash your hands with soap/sanitizer as many time as you can while at home, once you are at the client’s house and when you leave.
 •        Keep a 2 meters distance while talking to your clients.
 •        Don’t shake hands with your clients. 
 •        Avoid group gatherings.
-•        Provide the service at the open space and if it should be inside, make sure the windows and doors are open. 
 •        Cover your mouth with a towel or elbow when you sneeze or cough. 
-•        Do not go for a visit if you have symptoms of fever, cough or frequent sneezing.&lt;/span&gt; </t>
+•        Do not go for a visit if you have symptoms of fever, cough or frequent sneezing.&lt;/span&gt; 
+</t>
   </si>
   <si>
     <t xml:space="preserve">&lt;span style="color:#f58a1f"&gt;Kama mhudumu wa afya ya jamii, una jukumu la kuhakikisha unatoa elimu ya afya ya jamii na huduma huku ukijikinga ili kuepusha kusambaa kwa maambukizi ya korona kutoka kwa mtu mmoja kwenda kwa mwengine. Hivyo hakikisha unazingatia yafuatayo wakati ukiwa unatoa huduma:
+•         Matembeleo yote yafanye nje ya nyumba kwenye eneo la wazi, ambapo kuna mzunguko wa hewa kwa kupunguza athari za kuenea kwa maambukizi.
+•         Ni Lazima kuvaa barakoa yako muda wote unafanya matembeleo au kutembea kwenye jamii. Kama huna barakoa, tafadhali acha kufanya matembeleo.
 •        Osha mikono yako kwa maji na sabuni au kutumia vitakasa mikono mara nyingi kadiri unavyoweza ukiwa nyumbani kwako,nyumbani kwa mteja wako na pindi ukimaliza kutoa huduma. 
 •        Hakikisha kuna umbali wa mita mbili kati yako na mteja wako unayeenda kumtembelea 
 •        Pindi ukiongea na wateja wako , usishikane mikono. 
 •        Epuka mikusanyiko. 
-•        Toa huduma katika maeneo yaliyo wazi na ikitokea ukafanya ndani hakikisha milango na madirisha yanakuwa wazi.  
 •        Funika mdomo wako kwa kitambaa au kiwiko unavyooenda chafya au kukohoa. 
 •        Tafadhali usiende kutoa huduma ukijihisi na dalili za homa na kukohoa na kwenda chafya kwa wingi.&lt;/span&gt; 
 </t>
@@ -360,7 +333,7 @@
     <t xml:space="preserve">Introduction to COVID </t>
   </si>
   <si>
-    <t xml:space="preserve">Muhtasari </t>
+    <t>Muhtasari</t>
   </si>
   <si>
     <t>field-list</t>
@@ -369,10 +342,10 @@
     <t>introduction</t>
   </si>
   <si>
-    <t>Hi mom, how are you? Today before we start our visit, please let’s talk a little about the coronavirus. As we know the world is now experiencing this tragedy of coronavirus and we as Zanzibarians have the disease here as well and the infection is affecting people, and it is our responsibility to protect ourselves</t>
+    <t>Hi, how are you? Today before we start our visit, please let’s talk a little about the coronavirus. As we know the world is now experiencing this tragedy of coronavirus and we as Zanzibarians have the disease here as well and the infection is affecting people, and it is our responsibility to protect ourselves</t>
   </si>
   <si>
-    <t>Habari mama, leo kabla hatujaanza tembeleo letu naomba tuzungumzie kidogo kuhusu virusi vya Korona. Kama tunavyojua dunia sasa inakabiliwa na janga hili la virusi vya Korona na sisi kama wanzanzibar huu ugonjwa umeshafika na teyari unawaathiri watu, na ni jukumu letu sote kujilinda.</t>
+    <t>Habari yako, leo kabla hatujaanza tembeleo letu naomba tuzungumzie kidogo kuhusu virusi vya Korona. Kama tunavyojua dunia sasa inakabiliwa na janga hili la virusi vya Korona na sisi kama wanzanzibar huu ugonjwa umeshafika na teyari unawaathiri watu, na ni jukumu letu sote kujilinda.</t>
   </si>
   <si>
     <t>select_one yes_no</t>
@@ -405,7 +378,7 @@
     <t xml:space="preserve">Before we start, do the householders have something specific about the Coronavirus they want to know or tell me? </t>
   </si>
   <si>
-    <t xml:space="preserve">Kabla hatujaanza ,Je wanakaya wana jambo mahsusi kuhusu Korona wanalotaka kujua au kuniambia? </t>
+    <t>Kabla hatujaanza ,Je wanakaya wana jambo mahsusi kuhusu Korona wanalotaka kujua au kuniambia?</t>
   </si>
   <si>
     <t>answer_questions</t>
@@ -471,10 +444,10 @@
     <t>what_is_corona</t>
   </si>
   <si>
-    <t>It is a rare viral disease caused by a Coronavirus (COVID-19), which is transmitted from one infected person to another. This disease is also one of the most infectious diseases from animals to humans.</t>
+    <t>It is a viral disease caused by a new kind of Coronavirus, which is transmitted from one infected person to another. There are other coronaviruses that cause the flu, but this one is new and worse than the others.</t>
   </si>
   <si>
-    <t xml:space="preserve">Ni ugonjwa wa homa ya mafua makali unaosababishwa na kirusi aina ya korona (COVID-19), ambao huambukiza kutoka kwa mtu mmoja alie na ugonjwa huo kwenda kwa mtu mwengine. Pia ugonjwa huu ni moja kati ya magonjwa yanayoambukizwa kutoka kwa wanyama kwenda kwa binaadamu. </t>
+    <t>Huu ni ugonjwa unaosababishwa na virusi vipya vya korona, ugonjwa huu unasambaa kutoka kwa mtu mmoja kwenda kwa mwengine, Kuna aina nyengine za virusi vya korona ambavyo husababisha mafua, lakini hibhivi i ni virusi vipya na hatari Zaidi kusambaa.</t>
   </si>
   <si>
     <t>How is Corona disease transmitted?</t>
@@ -658,7 +631,7 @@
   <si>
     <t>• Recognize that a person with a coronavirus infection can infect another person even if they have not begun to show signs and symptoms of the disease.
 •  Report promptly to community health workers (CHV) if there is a resident or you have received a visitor with symptoms of a coronavirus 
-•  Corona virus currently has no cure or vaccine and is rapidly spreading around the world.
+•  Coronavirus currently has no cure or vaccine and is rapidly spreading around the world.
 •  You have a responsibility to protect yourself and others
 •  When you feel any signs or symptoms of severe cold flu stay at home and call by phone. Call at no cost: 190
 •  Also let them know about the Facebook, insta and whats apps of the health education unit of the Ministry of Health so that you can find more factual information and trends and events in the Zanzibar coronavirus epidemic</t>
@@ -719,6 +692,15 @@
     <t>selected(${is_wearing},"no")</t>
   </si>
   <si>
+    <t>self_made_mask_pics</t>
+  </si>
+  <si>
+    <t>This is how you can make your cloth mask at home</t>
+  </si>
+  <si>
+    <t>Jinsi ya kutengeneza barakoa yako nyumbani.</t>
+  </si>
+  <si>
     <t>self_made_mask_pic1</t>
   </si>
   <si>
@@ -770,10 +752,10 @@
     <t>self_made_mask_pic5</t>
   </si>
   <si>
-    <t xml:space="preserve">Mask as seen after sewing </t>
+    <t>Mask as seen after preparing</t>
   </si>
   <si>
-    <t xml:space="preserve">Muonekano wa barakoa baada ya kushona      </t>
+    <t>Muonekano wa barakoa baada ya kuiandaa</t>
   </si>
   <si>
     <t>self_made_mask_pic5.png</t>
@@ -794,12 +776,12 @@
     <t>mask_importance</t>
   </si>
   <si>
-    <t xml:space="preserve">Remember that it is important to wear the mask to make sure they do not spread the virus to others. It is possible to spread the virus to others even if they have no symptoms at all.
-Be careful and do not touch the outside or inside with your hands. Wash your hands with water and soap immediately before putting the mask on, and after taking it off. Wash your mask with soap and water daily after use.
-</t>
+    <t>Remember that it is important to wear the mask to make sure they do not spread the virus to others. It is possible to spread the virus to others even if they have no symptoms at all.
+Wearing this mask will not protect you from getting sick if someone around you is sick, so it is important to maintain distance from other people and wash your hands often.Be careful and do not touch the outside or inside with your hands. Wash your hands with water and soap immediately before putting the mask on, and after taking it off. Wash your mask with soap and water daily after use.</t>
   </si>
   <si>
     <t xml:space="preserve">Kumbuka ni muhimu sana kuvaa barakoa kila mara unapotoka nyumbani ili kuwalinda wengine, inawezekana kabisa kuwa na ugonjwa huu na kutoonesha dalili yeyote.
+Kuvaa barakoa hakukuepushi na kupata ugonjwa endapo utakua karibu sana na mgonjwa, hivyo basi ni muhimu kuendelea kukaa umbali kutoka kwa watu wengine na kuosha mikono yako kila mara.
 Kuwa makini na kushika barakoa yako kwa ndani au nje kwa mikono. Kosha mikono yako kwa maji na sabauni mara baada ya kuvaa au kuvua barakoa, Kosha barakoa yako kwa maji na sabuni kila siku baada ya kutumia.
 </t>
   </si>
@@ -886,6 +868,36 @@
   <si>
     <t>Majibu ya maswali yote mawili ni Ndio.Watu wasioonesha dalili wanaweza kueneza maambukizi. Inawezekana kwa mtu kuathirika kwa kushika sehemu yenye virusi na baadae kushika uso wake. Kwahiyo ni muhimu kuvaa barakoa muda wote unapotoka nyumbani , kuosha mikono mara kwa mara  kwa maji na sabuni.Ahsanteni kwa kunisikilia na kwa ushirikiano wenu.</t>
   </si>
+  <si>
+    <t>form_title</t>
+  </si>
+  <si>
+    <t>form_id</t>
+  </si>
+  <si>
+    <t>version</t>
+  </si>
+  <si>
+    <t>style</t>
+  </si>
+  <si>
+    <t>path</t>
+  </si>
+  <si>
+    <t>instance_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Covid Education </t>
+  </si>
+  <si>
+    <t>covid_education</t>
+  </si>
+  <si>
+    <t>pages</t>
+  </si>
+  <si>
+    <t>data</t>
+  </si>
 </sst>
 </file>
 
@@ -894,10 +906,13 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <name val="Arial"/>
     </font>
     <font>
@@ -905,17 +920,15 @@
       <name val="Arial"/>
     </font>
     <font>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <sz val="12.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
-    <font>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-    </font>
+    <font/>
     <font>
       <color rgb="FF1D1C1D"/>
       <name val="Slack-Lato"/>
@@ -928,8 +941,13 @@
       <sz val="11.0"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FF3C4043"/>
+      <name val="Roboto"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -940,6 +958,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFF8F8F8"/>
         <bgColor rgb="FFF8F8F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -955,9 +979,6 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
     </border>
     <border>
       <left style="thin">
@@ -969,89 +990,104 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="30">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1280,62 +1316,62 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="K1" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="L1" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="M1" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="N1" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="O1" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="P1" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q1" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="S1" s="9" t="s">
-        <v>78</v>
+      <c r="L1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="5" t="s">
+        <v>18</v>
       </c>
       <c r="T1" s="2"/>
       <c r="U1" s="2"/>
@@ -1346,2626 +1382,2638 @@
       <c r="Z1" s="2"/>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="11" t="b">
+      <c r="A2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="6" t="b">
         <f>FALSE()</f>
         <v>0</v>
       </c>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
-      <c r="O2" s="10"/>
-      <c r="P2" s="10"/>
-      <c r="Q2" s="10"/>
-      <c r="R2" s="10"/>
-      <c r="S2" s="10"/>
-      <c r="T2" s="10"/>
-      <c r="U2" s="10"/>
-      <c r="V2" s="10"/>
-      <c r="W2" s="10"/>
-      <c r="X2" s="10"/>
-      <c r="Y2" s="10"/>
-      <c r="Z2" s="10"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2"/>
+      <c r="T2" s="2"/>
+      <c r="U2" s="2"/>
+      <c r="V2" s="2"/>
+      <c r="W2" s="2"/>
+      <c r="X2" s="2"/>
+      <c r="Y2" s="2"/>
+      <c r="Z2" s="2"/>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="10"/>
-      <c r="N3" s="10"/>
-      <c r="O3" s="10"/>
-      <c r="P3" s="10"/>
-      <c r="Q3" s="10"/>
-      <c r="R3" s="10"/>
-      <c r="S3" s="10"/>
-      <c r="T3" s="10"/>
-      <c r="U3" s="10"/>
-      <c r="V3" s="10"/>
-      <c r="W3" s="10"/>
-      <c r="X3" s="10"/>
-      <c r="Y3" s="10"/>
-      <c r="Z3" s="10"/>
+      <c r="A3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2"/>
+      <c r="T3" s="2"/>
+      <c r="U3" s="2"/>
+      <c r="V3" s="2"/>
+      <c r="W3" s="2"/>
+      <c r="X3" s="2"/>
+      <c r="Y3" s="2"/>
+      <c r="Z3" s="2"/>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="B4" s="10" t="s">
+      <c r="A4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+      <c r="T4" s="2"/>
+      <c r="U4" s="2"/>
+      <c r="V4" s="2"/>
+      <c r="W4" s="2"/>
+      <c r="X4" s="2"/>
+      <c r="Y4" s="2"/>
+      <c r="Z4" s="2"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
+      <c r="S5" s="2"/>
+      <c r="T5" s="2"/>
+      <c r="U5" s="2"/>
+      <c r="V5" s="2"/>
+      <c r="W5" s="2"/>
+      <c r="X5" s="2"/>
+      <c r="Y5" s="2"/>
+      <c r="Z5" s="2"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2"/>
+      <c r="S6" s="2"/>
+      <c r="T6" s="2"/>
+      <c r="U6" s="2"/>
+      <c r="V6" s="2"/>
+      <c r="W6" s="2"/>
+      <c r="X6" s="2"/>
+      <c r="Y6" s="2"/>
+      <c r="Z6" s="2"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
+      <c r="S7" s="2"/>
+      <c r="T7" s="2"/>
+      <c r="U7" s="2"/>
+      <c r="V7" s="2"/>
+      <c r="W7" s="2"/>
+      <c r="X7" s="2"/>
+      <c r="Y7" s="2"/>
+      <c r="Z7" s="2"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2"/>
+      <c r="S8" s="2"/>
+      <c r="T8" s="2"/>
+      <c r="U8" s="2"/>
+      <c r="V8" s="2"/>
+      <c r="W8" s="2"/>
+      <c r="X8" s="2"/>
+      <c r="Y8" s="2"/>
+      <c r="Z8" s="2"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
+      <c r="S9" s="2"/>
+      <c r="T9" s="2"/>
+      <c r="U9" s="2"/>
+      <c r="V9" s="2"/>
+      <c r="W9" s="2"/>
+      <c r="X9" s="2"/>
+      <c r="Y9" s="2"/>
+      <c r="Z9" s="2"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10"/>
-      <c r="M4" s="10"/>
-      <c r="N4" s="10"/>
-      <c r="O4" s="10"/>
-      <c r="P4" s="10"/>
-      <c r="Q4" s="10"/>
-      <c r="R4" s="10"/>
-      <c r="S4" s="10"/>
-      <c r="T4" s="10"/>
-      <c r="U4" s="10"/>
-      <c r="V4" s="10"/>
-      <c r="W4" s="10"/>
-      <c r="X4" s="10"/>
-      <c r="Y4" s="10"/>
-      <c r="Z4" s="10"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="B5" s="10" t="s">
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2"/>
+      <c r="S10" s="2"/>
+      <c r="T10" s="2"/>
+      <c r="U10" s="2"/>
+      <c r="V10" s="2"/>
+      <c r="W10" s="2"/>
+      <c r="X10" s="2"/>
+      <c r="Y10" s="2"/>
+      <c r="Z10" s="2"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
-      <c r="L5" s="10"/>
-      <c r="M5" s="10"/>
-      <c r="N5" s="10"/>
-      <c r="O5" s="10"/>
-      <c r="P5" s="10"/>
-      <c r="Q5" s="10"/>
-      <c r="R5" s="10"/>
-      <c r="S5" s="10"/>
-      <c r="T5" s="10"/>
-      <c r="U5" s="10"/>
-      <c r="V5" s="10"/>
-      <c r="W5" s="10"/>
-      <c r="X5" s="10"/>
-      <c r="Y5" s="10"/>
-      <c r="Z5" s="10"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="10" t="s">
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="2"/>
+      <c r="S11" s="2"/>
+      <c r="T11" s="2"/>
+      <c r="U11" s="2"/>
+      <c r="V11" s="2"/>
+      <c r="W11" s="2"/>
+      <c r="X11" s="2"/>
+      <c r="Y11" s="2"/>
+      <c r="Z11" s="2"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
-      <c r="L6" s="10"/>
-      <c r="M6" s="10"/>
-      <c r="N6" s="10"/>
-      <c r="O6" s="10"/>
-      <c r="P6" s="10"/>
-      <c r="Q6" s="10"/>
-      <c r="R6" s="10"/>
-      <c r="S6" s="10"/>
-      <c r="T6" s="10"/>
-      <c r="U6" s="10"/>
-      <c r="V6" s="10"/>
-      <c r="W6" s="10"/>
-      <c r="X6" s="10"/>
-      <c r="Y6" s="10"/>
-      <c r="Z6" s="10"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="10" t="s">
+      <c r="B12" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="B7" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
-      <c r="N7" s="10"/>
-      <c r="O7" s="10"/>
-      <c r="P7" s="10"/>
-      <c r="Q7" s="10"/>
-      <c r="R7" s="10"/>
-      <c r="S7" s="10"/>
-      <c r="T7" s="10"/>
-      <c r="U7" s="10"/>
-      <c r="V7" s="10"/>
-      <c r="W7" s="10"/>
-      <c r="X7" s="10"/>
-      <c r="Y7" s="10"/>
-      <c r="Z7" s="10"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="10" t="s">
+      <c r="C12" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="2"/>
+      <c r="S12" s="2"/>
+      <c r="T12" s="2"/>
+      <c r="U12" s="2"/>
+      <c r="V12" s="2"/>
+      <c r="W12" s="2"/>
+      <c r="X12" s="2"/>
+      <c r="Y12" s="2"/>
+      <c r="Z12" s="2"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="2"/>
+      <c r="R13" s="2"/>
+      <c r="S13" s="2"/>
+      <c r="T13" s="2"/>
+      <c r="U13" s="2"/>
+      <c r="V13" s="2"/>
+      <c r="W13" s="2"/>
+      <c r="X13" s="2"/>
+      <c r="Y13" s="2"/>
+      <c r="Z13" s="2"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="B14" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="B8" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="10"/>
-      <c r="L8" s="10"/>
-      <c r="M8" s="10"/>
-      <c r="N8" s="10"/>
-      <c r="O8" s="10"/>
-      <c r="P8" s="10"/>
-      <c r="Q8" s="10"/>
-      <c r="R8" s="10"/>
-      <c r="S8" s="10"/>
-      <c r="T8" s="10"/>
-      <c r="U8" s="10"/>
-      <c r="V8" s="10"/>
-      <c r="W8" s="10"/>
-      <c r="X8" s="10"/>
-      <c r="Y8" s="10"/>
-      <c r="Z8" s="10"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10"/>
-      <c r="L9" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="M9" s="10"/>
-      <c r="N9" s="10"/>
-      <c r="O9" s="10"/>
-      <c r="P9" s="10"/>
-      <c r="Q9" s="10"/>
-      <c r="R9" s="10"/>
-      <c r="S9" s="10"/>
-      <c r="T9" s="10"/>
-      <c r="U9" s="10"/>
-      <c r="V9" s="10"/>
-      <c r="W9" s="10"/>
-      <c r="X9" s="10"/>
-      <c r="Y9" s="10"/>
-      <c r="Z9" s="10"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10"/>
-      <c r="L10" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="M10" s="10"/>
-      <c r="N10" s="10"/>
-      <c r="O10" s="10"/>
-      <c r="P10" s="10"/>
-      <c r="Q10" s="10"/>
-      <c r="R10" s="10"/>
-      <c r="S10" s="10"/>
-      <c r="T10" s="10"/>
-      <c r="U10" s="10"/>
-      <c r="V10" s="10"/>
-      <c r="W10" s="10"/>
-      <c r="X10" s="10"/>
-      <c r="Y10" s="10"/>
-      <c r="Z10" s="10"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="M11" s="10"/>
-      <c r="N11" s="10"/>
-      <c r="O11" s="10"/>
-      <c r="P11" s="10"/>
-      <c r="Q11" s="10"/>
-      <c r="R11" s="10"/>
-      <c r="S11" s="10"/>
-      <c r="T11" s="10"/>
-      <c r="U11" s="10"/>
-      <c r="V11" s="10"/>
-      <c r="W11" s="10"/>
-      <c r="X11" s="10"/>
-      <c r="Y11" s="10"/>
-      <c r="Z11" s="10"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="13" t="s">
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="2"/>
+      <c r="R14" s="2"/>
+      <c r="S14" s="2"/>
+      <c r="T14" s="2"/>
+      <c r="U14" s="2"/>
+      <c r="V14" s="2"/>
+      <c r="W14" s="2"/>
+      <c r="X14" s="2"/>
+      <c r="Y14" s="2"/>
+      <c r="Z14" s="2"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="C15" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="D15" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="D12" s="14" t="s">
+      <c r="E15" s="17"/>
+      <c r="G15" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="H12" s="10"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10"/>
-      <c r="K12" s="10"/>
-      <c r="L12" s="10"/>
-      <c r="M12" s="10"/>
-      <c r="N12" s="10"/>
-      <c r="O12" s="10"/>
-      <c r="P12" s="10"/>
-      <c r="Q12" s="10"/>
-      <c r="R12" s="10"/>
-      <c r="S12" s="10"/>
-      <c r="T12" s="10"/>
-      <c r="U12" s="10"/>
-      <c r="V12" s="10"/>
-      <c r="W12" s="10"/>
-      <c r="X12" s="10"/>
-      <c r="Y12" s="10"/>
-      <c r="Z12" s="10"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="C13" s="15" t="s">
-        <v>105</v>
-      </c>
-      <c r="D13" s="16" t="s">
-        <v>106</v>
-      </c>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10"/>
-      <c r="K13" s="10"/>
-      <c r="L13" s="10"/>
-      <c r="M13" s="10"/>
-      <c r="N13" s="10"/>
-      <c r="O13" s="10"/>
-      <c r="P13" s="10"/>
-      <c r="Q13" s="10"/>
-      <c r="R13" s="10"/>
-      <c r="S13" s="10"/>
-      <c r="T13" s="10"/>
-      <c r="U13" s="10"/>
-      <c r="V13" s="10"/>
-      <c r="W13" s="10"/>
-      <c r="X13" s="10"/>
-      <c r="Y13" s="10"/>
-      <c r="Z13" s="10"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="B14" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
-      <c r="K14" s="10"/>
-      <c r="L14" s="10"/>
-      <c r="M14" s="10"/>
-      <c r="N14" s="10"/>
-      <c r="O14" s="10"/>
-      <c r="P14" s="10"/>
-      <c r="Q14" s="10"/>
-      <c r="R14" s="10"/>
-      <c r="S14" s="10"/>
-      <c r="T14" s="10"/>
-      <c r="U14" s="10"/>
-      <c r="V14" s="10"/>
-      <c r="W14" s="10"/>
-      <c r="X14" s="10"/>
-      <c r="Y14" s="10"/>
-      <c r="Z14" s="10"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="B15" s="17" t="s">
-        <v>108</v>
-      </c>
-      <c r="C15" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="D15" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="E15" s="17"/>
-      <c r="G15" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
-      <c r="L15" s="10"/>
-      <c r="M15" s="10"/>
-      <c r="N15" s="10"/>
-      <c r="O15" s="10"/>
-      <c r="P15" s="10"/>
-      <c r="Q15" s="10"/>
-      <c r="R15" s="10"/>
-      <c r="S15" s="10"/>
-      <c r="T15" s="10"/>
-      <c r="U15" s="10"/>
-      <c r="V15" s="10"/>
-      <c r="W15" s="10"/>
-      <c r="X15" s="10"/>
-      <c r="Y15" s="10"/>
-      <c r="Z15" s="10"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
+      <c r="S15" s="2"/>
+      <c r="T15" s="2"/>
+      <c r="U15" s="2"/>
+      <c r="V15" s="2"/>
+      <c r="W15" s="2"/>
+      <c r="X15" s="2"/>
+      <c r="Y15" s="2"/>
+      <c r="Z15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="C16" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="B16" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="C16" s="17" t="s">
-        <v>113</v>
-      </c>
       <c r="D16" s="17" t="s">
-        <v>114</v>
-      </c>
-      <c r="E16" s="8"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
+        <v>104</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
       <c r="I16" s="18"/>
-      <c r="J16" s="10"/>
-      <c r="K16" s="12"/>
-      <c r="L16" s="10"/>
-      <c r="M16" s="10"/>
-      <c r="N16" s="10"/>
-      <c r="O16" s="10"/>
-      <c r="P16" s="10"/>
-      <c r="Q16" s="10"/>
-      <c r="R16" s="10"/>
-      <c r="S16" s="10"/>
-      <c r="T16" s="10"/>
-      <c r="U16" s="10"/>
-      <c r="V16" s="10"/>
-      <c r="W16" s="10"/>
-      <c r="X16" s="10"/>
-      <c r="Y16" s="10"/>
-      <c r="Z16" s="10"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="2"/>
+      <c r="R16" s="2"/>
+      <c r="S16" s="2"/>
+      <c r="T16" s="2"/>
+      <c r="U16" s="2"/>
+      <c r="V16" s="2"/>
+      <c r="W16" s="2"/>
+      <c r="X16" s="2"/>
+      <c r="Y16" s="2"/>
+      <c r="Z16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" s="17" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="D17" s="19" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
+        <v>36</v>
+      </c>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
       <c r="I17" s="18"/>
-      <c r="J17" s="10"/>
-      <c r="K17" s="12"/>
-      <c r="L17" s="10"/>
-      <c r="M17" s="10"/>
-      <c r="N17" s="10"/>
-      <c r="O17" s="10"/>
-      <c r="P17" s="10"/>
-      <c r="Q17" s="10"/>
-      <c r="R17" s="10"/>
-      <c r="S17" s="10"/>
-      <c r="T17" s="10"/>
-      <c r="U17" s="10"/>
-      <c r="V17" s="10"/>
-      <c r="W17" s="10"/>
-      <c r="X17" s="10"/>
-      <c r="Y17" s="10"/>
-      <c r="Z17" s="10"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" s="2"/>
+      <c r="Q17" s="2"/>
+      <c r="R17" s="2"/>
+      <c r="S17" s="2"/>
+      <c r="T17" s="2"/>
+      <c r="U17" s="2"/>
+      <c r="V17" s="2"/>
+      <c r="W17" s="2"/>
+      <c r="X17" s="2"/>
+      <c r="Y17" s="2"/>
+      <c r="Z17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" s="17" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>121</v>
-      </c>
-      <c r="E18" s="8"/>
+        <v>111</v>
+      </c>
+      <c r="E18" s="3"/>
       <c r="F18" s="20" t="s">
-        <v>122</v>
-      </c>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
+        <v>112</v>
+      </c>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
       <c r="I18" s="18"/>
-      <c r="J18" s="10"/>
-      <c r="K18" s="10"/>
-      <c r="L18" s="10"/>
-      <c r="M18" s="10"/>
-      <c r="N18" s="10"/>
-      <c r="O18" s="10"/>
-      <c r="P18" s="10"/>
-      <c r="Q18" s="10"/>
-      <c r="R18" s="10"/>
-      <c r="S18" s="10"/>
-      <c r="T18" s="10"/>
-      <c r="U18" s="10"/>
-      <c r="V18" s="10"/>
-      <c r="W18" s="10"/>
-      <c r="X18" s="10"/>
-      <c r="Y18" s="10"/>
-      <c r="Z18" s="10"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" s="2"/>
+      <c r="Q18" s="2"/>
+      <c r="R18" s="2"/>
+      <c r="S18" s="2"/>
+      <c r="T18" s="2"/>
+      <c r="U18" s="2"/>
+      <c r="V18" s="2"/>
+      <c r="W18" s="2"/>
+      <c r="X18" s="2"/>
+      <c r="Y18" s="2"/>
+      <c r="Z18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>114</v>
+      </c>
+      <c r="D19" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="B19" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="C19" s="17" t="s">
-        <v>124</v>
-      </c>
-      <c r="D19" s="17" t="s">
-        <v>125</v>
-      </c>
       <c r="E19" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="F19" s="10"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="10"/>
-      <c r="I19" s="8"/>
-      <c r="J19" s="10"/>
-      <c r="K19" s="12"/>
-      <c r="L19" s="10"/>
-      <c r="M19" s="10"/>
-      <c r="N19" s="10"/>
-      <c r="O19" s="10"/>
-      <c r="P19" s="10"/>
-      <c r="Q19" s="10"/>
-      <c r="R19" s="10"/>
-      <c r="S19" s="10"/>
-      <c r="T19" s="10"/>
-      <c r="U19" s="10"/>
-      <c r="V19" s="10"/>
-      <c r="W19" s="10"/>
-      <c r="X19" s="10"/>
-      <c r="Y19" s="10"/>
-      <c r="Z19" s="10"/>
+        <v>36</v>
+      </c>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="7"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" s="2"/>
+      <c r="Q19" s="2"/>
+      <c r="R19" s="2"/>
+      <c r="S19" s="2"/>
+      <c r="T19" s="2"/>
+      <c r="U19" s="2"/>
+      <c r="V19" s="2"/>
+      <c r="W19" s="2"/>
+      <c r="X19" s="2"/>
+      <c r="Y19" s="2"/>
+      <c r="Z19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" s="17" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>128</v>
-      </c>
-      <c r="E20" s="8"/>
+        <v>118</v>
+      </c>
+      <c r="E20" s="3"/>
       <c r="F20" s="20" t="s">
-        <v>129</v>
-      </c>
-      <c r="G20" s="10"/>
-      <c r="H20" s="10"/>
-      <c r="I20" s="10"/>
-      <c r="J20" s="10"/>
-      <c r="K20" s="12"/>
-      <c r="L20" s="10"/>
-      <c r="M20" s="10"/>
-      <c r="N20" s="10"/>
-      <c r="O20" s="10"/>
-      <c r="P20" s="10"/>
-      <c r="Q20" s="10"/>
-      <c r="R20" s="10"/>
-      <c r="S20" s="10"/>
-      <c r="T20" s="10"/>
-      <c r="U20" s="10"/>
-      <c r="V20" s="10"/>
-      <c r="W20" s="10"/>
-      <c r="X20" s="10"/>
-      <c r="Y20" s="10"/>
-      <c r="Z20" s="10"/>
+        <v>119</v>
+      </c>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="7"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" s="2"/>
+      <c r="Q20" s="2"/>
+      <c r="R20" s="2"/>
+      <c r="S20" s="2"/>
+      <c r="T20" s="2"/>
+      <c r="U20" s="2"/>
+      <c r="V20" s="2"/>
+      <c r="W20" s="2"/>
+      <c r="X20" s="2"/>
+      <c r="Y20" s="2"/>
+      <c r="Z20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" s="21" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B21" s="22" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>131</v>
-      </c>
-      <c r="D21" s="21" t="s">
-        <v>132</v>
+        <v>121</v>
+      </c>
+      <c r="D21" s="23" t="s">
+        <v>122</v>
       </c>
       <c r="E21" s="21"/>
-      <c r="F21" s="23"/>
-      <c r="G21" s="24"/>
-      <c r="H21" s="24"/>
-      <c r="I21" s="24"/>
-      <c r="J21" s="24"/>
-      <c r="K21" s="24"/>
-      <c r="L21" s="24"/>
-      <c r="M21" s="24"/>
-      <c r="N21" s="24"/>
-      <c r="O21" s="24"/>
-      <c r="P21" s="24"/>
-      <c r="Q21" s="24"/>
-      <c r="R21" s="24"/>
-      <c r="S21" s="24"/>
-      <c r="T21" s="24"/>
-      <c r="U21" s="24"/>
-      <c r="V21" s="24"/>
-      <c r="W21" s="24"/>
-      <c r="X21" s="24"/>
-      <c r="Y21" s="24"/>
-      <c r="Z21" s="24"/>
+      <c r="F21" s="24" t="s">
+        <v>119</v>
+      </c>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4"/>
+      <c r="K21" s="4"/>
+      <c r="L21" s="4"/>
+      <c r="M21" s="4"/>
+      <c r="N21" s="4"/>
+      <c r="O21" s="4"/>
+      <c r="P21" s="4"/>
+      <c r="Q21" s="4"/>
+      <c r="R21" s="4"/>
+      <c r="S21" s="4"/>
+      <c r="T21" s="4"/>
+      <c r="U21" s="4"/>
+      <c r="V21" s="4"/>
+      <c r="W21" s="4"/>
+      <c r="X21" s="4"/>
+      <c r="Y21" s="4"/>
+      <c r="Z21" s="4"/>
     </row>
     <row r="22">
       <c r="A22" s="17" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>136</v>
-      </c>
-      <c r="F22" s="23"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="10"/>
+        <v>126</v>
+      </c>
+      <c r="F22" s="24" t="s">
+        <v>119</v>
+      </c>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
       <c r="I22" s="20"/>
       <c r="J22" s="25"/>
       <c r="K22" s="25"/>
-      <c r="L22" s="10"/>
-      <c r="M22" s="10"/>
-      <c r="N22" s="10"/>
-      <c r="O22" s="10"/>
-      <c r="P22" s="10"/>
-      <c r="Q22" s="10"/>
-      <c r="R22" s="10"/>
-      <c r="S22" s="10"/>
-      <c r="T22" s="10"/>
-      <c r="U22" s="10"/>
-      <c r="V22" s="10"/>
-      <c r="W22" s="10"/>
-      <c r="X22" s="10"/>
-      <c r="Y22" s="10"/>
-      <c r="Z22" s="10"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2"/>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" s="2"/>
+      <c r="Q22" s="2"/>
+      <c r="R22" s="2"/>
+      <c r="S22" s="2"/>
+      <c r="T22" s="2"/>
+      <c r="U22" s="2"/>
+      <c r="V22" s="2"/>
+      <c r="W22" s="2"/>
+      <c r="X22" s="2"/>
+      <c r="Y22" s="2"/>
+      <c r="Z22" s="2"/>
     </row>
     <row r="23">
       <c r="A23" s="21" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B23" s="22" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="C23" s="22" t="s">
-        <v>131</v>
-      </c>
-      <c r="D23" s="21" t="s">
-        <v>132</v>
+        <v>121</v>
+      </c>
+      <c r="D23" s="23" t="s">
+        <v>122</v>
       </c>
       <c r="E23" s="21"/>
-      <c r="F23" s="23" t="s">
-        <v>138</v>
-      </c>
-      <c r="G23" s="24"/>
-      <c r="H23" s="24"/>
-      <c r="I23" s="24"/>
-      <c r="J23" s="24"/>
-      <c r="K23" s="24"/>
-      <c r="L23" s="24"/>
-      <c r="M23" s="24"/>
-      <c r="N23" s="24"/>
-      <c r="O23" s="24"/>
-      <c r="P23" s="24"/>
-      <c r="Q23" s="24"/>
-      <c r="R23" s="24"/>
-      <c r="S23" s="24"/>
-      <c r="T23" s="24"/>
-      <c r="U23" s="24"/>
-      <c r="V23" s="24"/>
-      <c r="W23" s="24"/>
-      <c r="X23" s="24"/>
-      <c r="Y23" s="24"/>
-      <c r="Z23" s="24"/>
+      <c r="F23" s="24" t="s">
+        <v>128</v>
+      </c>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+      <c r="K23" s="4"/>
+      <c r="L23" s="4"/>
+      <c r="M23" s="4"/>
+      <c r="N23" s="4"/>
+      <c r="O23" s="4"/>
+      <c r="P23" s="4"/>
+      <c r="Q23" s="4"/>
+      <c r="R23" s="4"/>
+      <c r="S23" s="4"/>
+      <c r="T23" s="4"/>
+      <c r="U23" s="4"/>
+      <c r="V23" s="4"/>
+      <c r="W23" s="4"/>
+      <c r="X23" s="4"/>
+      <c r="Y23" s="4"/>
+      <c r="Z23" s="4"/>
     </row>
     <row r="24">
       <c r="A24" s="17" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="B24" s="17" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="E24" s="17" t="s">
-        <v>136</v>
-      </c>
-      <c r="F24" s="23" t="s">
-        <v>138</v>
-      </c>
-      <c r="G24" s="10"/>
-      <c r="H24" s="10"/>
-      <c r="I24" s="10"/>
-      <c r="J24" s="10"/>
-      <c r="K24" s="12"/>
-      <c r="L24" s="10"/>
-      <c r="M24" s="10"/>
-      <c r="N24" s="10"/>
-      <c r="O24" s="10"/>
-      <c r="P24" s="10"/>
-      <c r="Q24" s="10"/>
-      <c r="R24" s="10"/>
-      <c r="S24" s="10"/>
-      <c r="T24" s="10"/>
-      <c r="U24" s="10"/>
-      <c r="V24" s="10"/>
-      <c r="W24" s="10"/>
-      <c r="X24" s="10"/>
-      <c r="Y24" s="10"/>
-      <c r="Z24" s="10"/>
+        <v>126</v>
+      </c>
+      <c r="F24" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="7"/>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2"/>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" s="2"/>
+      <c r="Q24" s="2"/>
+      <c r="R24" s="2"/>
+      <c r="S24" s="2"/>
+      <c r="T24" s="2"/>
+      <c r="U24" s="2"/>
+      <c r="V24" s="2"/>
+      <c r="W24" s="2"/>
+      <c r="X24" s="2"/>
+      <c r="Y24" s="2"/>
+      <c r="Z24" s="2"/>
     </row>
     <row r="25">
       <c r="A25" s="17" t="s">
-        <v>89</v>
+        <v>29</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>108</v>
-      </c>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="10"/>
-      <c r="H25" s="10"/>
-      <c r="I25" s="10"/>
-      <c r="J25" s="10"/>
-      <c r="K25" s="12"/>
-      <c r="L25" s="10"/>
-      <c r="M25" s="10"/>
-      <c r="N25" s="10"/>
-      <c r="O25" s="10"/>
-      <c r="P25" s="10"/>
-      <c r="Q25" s="10"/>
-      <c r="R25" s="10"/>
-      <c r="S25" s="10"/>
-      <c r="T25" s="10"/>
-      <c r="U25" s="10"/>
-      <c r="V25" s="10"/>
-      <c r="W25" s="10"/>
-      <c r="X25" s="10"/>
-      <c r="Y25" s="10"/>
-      <c r="Z25" s="10"/>
+        <v>98</v>
+      </c>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="7"/>
+      <c r="L25" s="2"/>
+      <c r="M25" s="2"/>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
+      <c r="P25" s="2"/>
+      <c r="Q25" s="2"/>
+      <c r="R25" s="2"/>
+      <c r="S25" s="2"/>
+      <c r="T25" s="2"/>
+      <c r="U25" s="2"/>
+      <c r="V25" s="2"/>
+      <c r="W25" s="2"/>
+      <c r="X25" s="2"/>
+      <c r="Y25" s="2"/>
+      <c r="Z25" s="2"/>
     </row>
     <row r="26">
       <c r="A26" s="17" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>145</v>
-      </c>
-      <c r="E26" s="8"/>
-      <c r="F26" s="10"/>
+        <v>135</v>
+      </c>
+      <c r="E26" s="3"/>
+      <c r="F26" s="2"/>
       <c r="G26" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="H26" s="10"/>
-      <c r="I26" s="10"/>
-      <c r="J26" s="10"/>
-      <c r="K26" s="12"/>
-      <c r="L26" s="10"/>
-      <c r="M26" s="10"/>
-      <c r="N26" s="10"/>
-      <c r="O26" s="10"/>
-      <c r="P26" s="10"/>
-      <c r="Q26" s="10"/>
-      <c r="R26" s="10"/>
-      <c r="S26" s="10"/>
-      <c r="T26" s="10"/>
-      <c r="U26" s="10"/>
-      <c r="V26" s="10"/>
-      <c r="W26" s="10"/>
-      <c r="X26" s="10"/>
-      <c r="Y26" s="10"/>
-      <c r="Z26" s="10"/>
+        <v>92</v>
+      </c>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="7"/>
+      <c r="L26" s="2"/>
+      <c r="M26" s="2"/>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
+      <c r="P26" s="2"/>
+      <c r="Q26" s="2"/>
+      <c r="R26" s="2"/>
+      <c r="S26" s="2"/>
+      <c r="T26" s="2"/>
+      <c r="U26" s="2"/>
+      <c r="V26" s="2"/>
+      <c r="W26" s="2"/>
+      <c r="X26" s="2"/>
+      <c r="Y26" s="2"/>
+      <c r="Z26" s="2"/>
     </row>
     <row r="27">
       <c r="A27" s="17" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B27" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="C27" s="17" t="s">
-        <v>147</v>
+        <v>136</v>
+      </c>
+      <c r="C27" s="27" t="s">
+        <v>137</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>148</v>
-      </c>
-      <c r="E27" s="8"/>
-      <c r="F27" s="10"/>
-      <c r="G27" s="10"/>
-      <c r="H27" s="10"/>
-      <c r="I27" s="8"/>
-      <c r="J27" s="8"/>
-      <c r="K27" s="10"/>
-      <c r="L27" s="10"/>
-      <c r="M27" s="10"/>
-      <c r="N27" s="10"/>
-      <c r="O27" s="10"/>
-      <c r="P27" s="10"/>
-      <c r="Q27" s="10"/>
-      <c r="R27" s="10"/>
-      <c r="S27" s="10"/>
-      <c r="T27" s="10"/>
-      <c r="U27" s="10"/>
-      <c r="V27" s="10"/>
-      <c r="W27" s="10"/>
-      <c r="X27" s="10"/>
-      <c r="Y27" s="10"/>
-      <c r="Z27" s="10"/>
+        <v>138</v>
+      </c>
+      <c r="E27" s="3"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="3"/>
+      <c r="J27" s="3"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
+      <c r="M27" s="2"/>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
+      <c r="P27" s="2"/>
+      <c r="Q27" s="2"/>
+      <c r="R27" s="2"/>
+      <c r="S27" s="2"/>
+      <c r="T27" s="2"/>
+      <c r="U27" s="2"/>
+      <c r="V27" s="2"/>
+      <c r="W27" s="2"/>
+      <c r="X27" s="2"/>
+      <c r="Y27" s="2"/>
+      <c r="Z27" s="2"/>
     </row>
     <row r="28">
       <c r="A28" s="17" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="B28" s="17" t="s">
-        <v>143</v>
-      </c>
-      <c r="C28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="10"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="10"/>
-      <c r="I28" s="8"/>
-      <c r="J28" s="8"/>
-      <c r="K28" s="10"/>
-      <c r="L28" s="10"/>
-      <c r="M28" s="10"/>
-      <c r="N28" s="10"/>
-      <c r="O28" s="10"/>
-      <c r="P28" s="10"/>
-      <c r="Q28" s="10"/>
-      <c r="R28" s="10"/>
-      <c r="S28" s="10"/>
-      <c r="T28" s="10"/>
-      <c r="U28" s="10"/>
-      <c r="V28" s="10"/>
-      <c r="W28" s="10"/>
-      <c r="X28" s="10"/>
-      <c r="Y28" s="10"/>
-      <c r="Z28" s="10"/>
+        <v>133</v>
+      </c>
+      <c r="C28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="3"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
+      <c r="M28" s="2"/>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+      <c r="P28" s="2"/>
+      <c r="Q28" s="2"/>
+      <c r="R28" s="2"/>
+      <c r="S28" s="2"/>
+      <c r="T28" s="2"/>
+      <c r="U28" s="2"/>
+      <c r="V28" s="2"/>
+      <c r="W28" s="2"/>
+      <c r="X28" s="2"/>
+      <c r="Y28" s="2"/>
+      <c r="Z28" s="2"/>
     </row>
     <row r="29">
       <c r="A29" s="17" t="s">
-        <v>79</v>
+        <v>19</v>
       </c>
       <c r="B29" s="17" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="C29" s="17" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="E29" s="8"/>
-      <c r="F29" s="10"/>
+        <v>140</v>
+      </c>
+      <c r="E29" s="3"/>
+      <c r="F29" s="2"/>
       <c r="G29" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="H29" s="10"/>
-      <c r="I29" s="10"/>
-      <c r="J29" s="10"/>
-      <c r="K29" s="12"/>
-      <c r="L29" s="10"/>
-      <c r="M29" s="10"/>
-      <c r="N29" s="10"/>
-      <c r="O29" s="10"/>
-      <c r="P29" s="10"/>
-      <c r="Q29" s="10"/>
-      <c r="R29" s="10"/>
-      <c r="S29" s="10"/>
-      <c r="T29" s="10"/>
-      <c r="U29" s="10"/>
-      <c r="V29" s="10"/>
-      <c r="W29" s="10"/>
-      <c r="X29" s="10"/>
-      <c r="Y29" s="10"/>
-      <c r="Z29" s="10"/>
+        <v>92</v>
+      </c>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="7"/>
+      <c r="L29" s="2"/>
+      <c r="M29" s="2"/>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+      <c r="P29" s="2"/>
+      <c r="Q29" s="2"/>
+      <c r="R29" s="2"/>
+      <c r="S29" s="2"/>
+      <c r="T29" s="2"/>
+      <c r="U29" s="2"/>
+      <c r="V29" s="2"/>
+      <c r="W29" s="2"/>
+      <c r="X29" s="2"/>
+      <c r="Y29" s="2"/>
+      <c r="Z29" s="2"/>
     </row>
     <row r="30">
       <c r="A30" s="17" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B30" s="17" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="D30" s="17" t="s">
-        <v>153</v>
-      </c>
-      <c r="E30" s="8"/>
-      <c r="F30" s="10"/>
-      <c r="G30" s="10"/>
-      <c r="H30" s="10"/>
-      <c r="I30" s="10"/>
-      <c r="J30" s="10"/>
-      <c r="K30" s="12"/>
-      <c r="L30" s="10"/>
-      <c r="M30" s="10"/>
-      <c r="N30" s="10"/>
-      <c r="O30" s="10"/>
-      <c r="P30" s="10"/>
-      <c r="Q30" s="10"/>
-      <c r="R30" s="10"/>
-      <c r="S30" s="10"/>
-      <c r="T30" s="10"/>
-      <c r="U30" s="10"/>
-      <c r="V30" s="10"/>
-      <c r="W30" s="10"/>
-      <c r="X30" s="10"/>
-      <c r="Y30" s="10"/>
-      <c r="Z30" s="10"/>
+        <v>143</v>
+      </c>
+      <c r="E30" s="3"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="7"/>
+      <c r="L30" s="2"/>
+      <c r="M30" s="2"/>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+      <c r="P30" s="2"/>
+      <c r="Q30" s="2"/>
+      <c r="R30" s="2"/>
+      <c r="S30" s="2"/>
+      <c r="T30" s="2"/>
+      <c r="U30" s="2"/>
+      <c r="V30" s="2"/>
+      <c r="W30" s="2"/>
+      <c r="X30" s="2"/>
+      <c r="Y30" s="2"/>
+      <c r="Z30" s="2"/>
     </row>
     <row r="31">
       <c r="A31" s="17" t="s">
-        <v>89</v>
+        <v>29</v>
       </c>
       <c r="B31" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="C31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="10"/>
-      <c r="G31" s="10"/>
-      <c r="H31" s="10"/>
-      <c r="I31" s="10"/>
-      <c r="J31" s="10"/>
-      <c r="K31" s="10"/>
-      <c r="L31" s="10"/>
-      <c r="M31" s="10"/>
-      <c r="N31" s="10"/>
-      <c r="O31" s="10"/>
-      <c r="P31" s="10"/>
-      <c r="Q31" s="10"/>
-      <c r="R31" s="10"/>
-      <c r="S31" s="10"/>
-      <c r="T31" s="10"/>
-      <c r="U31" s="10"/>
-      <c r="V31" s="10"/>
-      <c r="W31" s="10"/>
-      <c r="X31" s="10"/>
-      <c r="Y31" s="10"/>
-      <c r="Z31" s="10"/>
+        <v>46</v>
+      </c>
+      <c r="C31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
+      <c r="L31" s="2"/>
+      <c r="M31" s="2"/>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
+      <c r="P31" s="2"/>
+      <c r="Q31" s="2"/>
+      <c r="R31" s="2"/>
+      <c r="S31" s="2"/>
+      <c r="T31" s="2"/>
+      <c r="U31" s="2"/>
+      <c r="V31" s="2"/>
+      <c r="W31" s="2"/>
+      <c r="X31" s="2"/>
+      <c r="Y31" s="2"/>
+      <c r="Z31" s="2"/>
     </row>
     <row r="32">
       <c r="A32" s="17" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="B32" s="17" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="C32" s="17" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="D32" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="E32" s="8"/>
-      <c r="F32" s="10"/>
+        <v>145</v>
+      </c>
+      <c r="E32" s="3"/>
+      <c r="F32" s="2"/>
       <c r="G32" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="H32" s="10"/>
-      <c r="I32" s="10"/>
-      <c r="J32" s="10"/>
-      <c r="K32" s="10"/>
-      <c r="L32" s="10"/>
-      <c r="M32" s="10"/>
-      <c r="N32" s="10"/>
-      <c r="O32" s="10"/>
-      <c r="P32" s="10"/>
-      <c r="Q32" s="10"/>
-      <c r="R32" s="10"/>
-      <c r="S32" s="10"/>
-      <c r="T32" s="10"/>
-      <c r="U32" s="10"/>
-      <c r="V32" s="10"/>
-      <c r="W32" s="10"/>
-      <c r="X32" s="10"/>
-      <c r="Y32" s="10"/>
-      <c r="Z32" s="10"/>
+        <v>92</v>
+      </c>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2"/>
+      <c r="L32" s="2"/>
+      <c r="M32" s="2"/>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
+      <c r="P32" s="2"/>
+      <c r="Q32" s="2"/>
+      <c r="R32" s="2"/>
+      <c r="S32" s="2"/>
+      <c r="T32" s="2"/>
+      <c r="U32" s="2"/>
+      <c r="V32" s="2"/>
+      <c r="W32" s="2"/>
+      <c r="X32" s="2"/>
+      <c r="Y32" s="2"/>
+      <c r="Z32" s="2"/>
     </row>
     <row r="33">
       <c r="A33" s="17" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B33" s="17" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="D33" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="E33" s="8"/>
-      <c r="F33" s="10"/>
-      <c r="G33" s="10"/>
-      <c r="H33" s="10"/>
-      <c r="I33" s="10"/>
-      <c r="J33" s="10"/>
-      <c r="K33" s="12"/>
-      <c r="L33" s="10"/>
-      <c r="M33" s="10"/>
-      <c r="N33" s="10"/>
-      <c r="O33" s="10"/>
-      <c r="P33" s="10"/>
-      <c r="Q33" s="10"/>
-      <c r="R33" s="10"/>
-      <c r="S33" s="10"/>
-      <c r="T33" s="10"/>
-      <c r="U33" s="10"/>
-      <c r="V33" s="10"/>
-      <c r="W33" s="10"/>
-      <c r="X33" s="10"/>
-      <c r="Y33" s="10"/>
-      <c r="Z33" s="10"/>
+        <v>148</v>
+      </c>
+      <c r="E33" s="3"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="7"/>
+      <c r="L33" s="2"/>
+      <c r="M33" s="2"/>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
+      <c r="P33" s="2"/>
+      <c r="Q33" s="2"/>
+      <c r="R33" s="2"/>
+      <c r="S33" s="2"/>
+      <c r="T33" s="2"/>
+      <c r="U33" s="2"/>
+      <c r="V33" s="2"/>
+      <c r="W33" s="2"/>
+      <c r="X33" s="2"/>
+      <c r="Y33" s="2"/>
+      <c r="Z33" s="2"/>
     </row>
     <row r="34">
       <c r="A34" s="17" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="B34" s="17" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="C34" s="17" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="D34" s="17" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="E34" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="F34" s="10"/>
-      <c r="G34" s="10"/>
-      <c r="H34" s="10"/>
-      <c r="I34" s="10"/>
-      <c r="J34" s="10"/>
-      <c r="K34" s="12"/>
-      <c r="L34" s="10"/>
-      <c r="M34" s="10"/>
-      <c r="N34" s="10"/>
-      <c r="O34" s="10"/>
-      <c r="P34" s="10"/>
-      <c r="Q34" s="10"/>
-      <c r="R34" s="10"/>
-      <c r="S34" s="10"/>
-      <c r="T34" s="10"/>
-      <c r="U34" s="10"/>
-      <c r="V34" s="10"/>
-      <c r="W34" s="10"/>
-      <c r="X34" s="10"/>
-      <c r="Y34" s="10"/>
-      <c r="Z34" s="10"/>
+        <v>36</v>
+      </c>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="7"/>
+      <c r="L34" s="2"/>
+      <c r="M34" s="2"/>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
+      <c r="P34" s="2"/>
+      <c r="Q34" s="2"/>
+      <c r="R34" s="2"/>
+      <c r="S34" s="2"/>
+      <c r="T34" s="2"/>
+      <c r="U34" s="2"/>
+      <c r="V34" s="2"/>
+      <c r="W34" s="2"/>
+      <c r="X34" s="2"/>
+      <c r="Y34" s="2"/>
+      <c r="Z34" s="2"/>
     </row>
     <row r="35">
       <c r="A35" s="17" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B35" s="17" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="C35" s="17" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="D35" s="17" t="s">
-        <v>164</v>
-      </c>
-      <c r="E35" s="8"/>
+        <v>154</v>
+      </c>
+      <c r="E35" s="3"/>
       <c r="F35" s="20" t="s">
-        <v>165</v>
-      </c>
-      <c r="G35" s="10"/>
-      <c r="H35" s="10"/>
-      <c r="I35" s="10"/>
-      <c r="J35" s="10"/>
-      <c r="K35" s="12"/>
-      <c r="L35" s="10"/>
-      <c r="M35" s="10"/>
-      <c r="N35" s="10"/>
-      <c r="O35" s="10"/>
-      <c r="P35" s="10"/>
-      <c r="Q35" s="10"/>
-      <c r="R35" s="10"/>
-      <c r="S35" s="10"/>
-      <c r="T35" s="10"/>
-      <c r="U35" s="10"/>
-      <c r="V35" s="10"/>
-      <c r="W35" s="10"/>
-      <c r="X35" s="10"/>
-      <c r="Y35" s="10"/>
-      <c r="Z35" s="10"/>
+        <v>155</v>
+      </c>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="2"/>
+      <c r="K35" s="7"/>
+      <c r="L35" s="2"/>
+      <c r="M35" s="2"/>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
+      <c r="P35" s="2"/>
+      <c r="Q35" s="2"/>
+      <c r="R35" s="2"/>
+      <c r="S35" s="2"/>
+      <c r="T35" s="2"/>
+      <c r="U35" s="2"/>
+      <c r="V35" s="2"/>
+      <c r="W35" s="2"/>
+      <c r="X35" s="2"/>
+      <c r="Y35" s="2"/>
+      <c r="Z35" s="2"/>
     </row>
     <row r="36">
       <c r="A36" s="17" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B36" s="17" t="s">
-        <v>166</v>
-      </c>
-      <c r="C36" s="8"/>
-      <c r="E36" s="10"/>
-      <c r="F36" s="10"/>
-      <c r="G36" s="10"/>
-      <c r="H36" s="10"/>
-      <c r="I36" s="10"/>
-      <c r="J36" s="10"/>
-      <c r="K36" s="10"/>
-      <c r="L36" s="10"/>
-      <c r="M36" s="10"/>
-      <c r="N36" s="10"/>
-      <c r="O36" s="10"/>
-      <c r="P36" s="10"/>
-      <c r="Q36" s="10"/>
+        <v>156</v>
+      </c>
+      <c r="C36" s="3"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="2"/>
+      <c r="L36" s="2"/>
+      <c r="M36" s="2"/>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+      <c r="P36" s="2"/>
+      <c r="Q36" s="2"/>
       <c r="R36" s="17" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="S36" s="17" t="s">
-        <v>167</v>
-      </c>
-      <c r="T36" s="10"/>
-      <c r="U36" s="10"/>
-      <c r="V36" s="10"/>
-      <c r="W36" s="10"/>
-      <c r="X36" s="10"/>
-      <c r="Y36" s="10"/>
-      <c r="Z36" s="10"/>
+        <v>157</v>
+      </c>
+      <c r="T36" s="2"/>
+      <c r="U36" s="2"/>
+      <c r="V36" s="2"/>
+      <c r="W36" s="2"/>
+      <c r="X36" s="2"/>
+      <c r="Y36" s="2"/>
+      <c r="Z36" s="2"/>
     </row>
     <row r="37">
       <c r="A37" s="20" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B37" s="17" t="s">
-        <v>168</v>
-      </c>
-      <c r="C37" s="10"/>
-      <c r="D37" s="10"/>
-      <c r="E37" s="10"/>
-      <c r="F37" s="10"/>
-      <c r="G37" s="10"/>
-      <c r="H37" s="10"/>
-      <c r="I37" s="10"/>
-      <c r="J37" s="10"/>
-      <c r="K37" s="10"/>
-      <c r="L37" s="10"/>
-      <c r="M37" s="10"/>
-      <c r="N37" s="10"/>
-      <c r="O37" s="10"/>
-      <c r="P37" s="10"/>
-      <c r="Q37" s="10"/>
+        <v>158</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="2"/>
+      <c r="K37" s="2"/>
+      <c r="L37" s="2"/>
+      <c r="M37" s="2"/>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
+      <c r="P37" s="2"/>
+      <c r="Q37" s="2"/>
       <c r="R37" s="20" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="S37" s="20" t="s">
-        <v>169</v>
-      </c>
-      <c r="T37" s="10"/>
-      <c r="U37" s="10"/>
-      <c r="V37" s="10"/>
-      <c r="W37" s="10"/>
-      <c r="X37" s="10"/>
-      <c r="Y37" s="10"/>
-      <c r="Z37" s="10"/>
+        <v>159</v>
+      </c>
+      <c r="T37" s="2"/>
+      <c r="U37" s="2"/>
+      <c r="V37" s="2"/>
+      <c r="W37" s="2"/>
+      <c r="X37" s="2"/>
+      <c r="Y37" s="2"/>
+      <c r="Z37" s="2"/>
     </row>
     <row r="38">
       <c r="A38" s="20" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B38" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="C38" s="10"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="10"/>
-      <c r="F38" s="10"/>
-      <c r="G38" s="10"/>
-      <c r="H38" s="10"/>
-      <c r="I38" s="10"/>
-      <c r="J38" s="10"/>
-      <c r="K38" s="10"/>
-      <c r="L38" s="10"/>
-      <c r="M38" s="10"/>
-      <c r="N38" s="10"/>
-      <c r="O38" s="10"/>
-      <c r="P38" s="10"/>
-      <c r="Q38" s="10"/>
+        <v>160</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="2"/>
+      <c r="K38" s="2"/>
+      <c r="L38" s="2"/>
+      <c r="M38" s="2"/>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
+      <c r="P38" s="2"/>
+      <c r="Q38" s="2"/>
       <c r="R38" s="20" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="S38" s="20" t="s">
-        <v>171</v>
-      </c>
-      <c r="T38" s="10"/>
-      <c r="U38" s="10"/>
-      <c r="V38" s="10"/>
-      <c r="W38" s="10"/>
-      <c r="X38" s="10"/>
-      <c r="Y38" s="10"/>
-      <c r="Z38" s="10"/>
+        <v>161</v>
+      </c>
+      <c r="T38" s="2"/>
+      <c r="U38" s="2"/>
+      <c r="V38" s="2"/>
+      <c r="W38" s="2"/>
+      <c r="X38" s="2"/>
+      <c r="Y38" s="2"/>
+      <c r="Z38" s="2"/>
     </row>
     <row r="39">
       <c r="A39" s="20" t="s">
-        <v>89</v>
+        <v>29</v>
       </c>
       <c r="B39" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="C39" s="10"/>
-      <c r="D39" s="10"/>
-      <c r="E39" s="10"/>
-      <c r="F39" s="10"/>
-      <c r="G39" s="10"/>
-      <c r="H39" s="10"/>
-      <c r="I39" s="10"/>
-      <c r="J39" s="10"/>
-      <c r="K39" s="10"/>
-      <c r="L39" s="10"/>
-      <c r="M39" s="10"/>
-      <c r="N39" s="10"/>
-      <c r="O39" s="10"/>
-      <c r="P39" s="10"/>
-      <c r="Q39" s="10"/>
-      <c r="R39" s="10"/>
-      <c r="S39" s="10"/>
-      <c r="T39" s="10"/>
-      <c r="U39" s="10"/>
-      <c r="V39" s="10"/>
-      <c r="W39" s="10"/>
-      <c r="X39" s="10"/>
-      <c r="Y39" s="10"/>
-      <c r="Z39" s="10"/>
+        <v>52</v>
+      </c>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="2"/>
+      <c r="K39" s="2"/>
+      <c r="L39" s="2"/>
+      <c r="M39" s="2"/>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
+      <c r="P39" s="2"/>
+      <c r="Q39" s="2"/>
+      <c r="R39" s="2"/>
+      <c r="S39" s="2"/>
+      <c r="T39" s="2"/>
+      <c r="U39" s="2"/>
+      <c r="V39" s="2"/>
+      <c r="W39" s="2"/>
+      <c r="X39" s="2"/>
+      <c r="Y39" s="2"/>
+      <c r="Z39" s="2"/>
     </row>
     <row r="40">
       <c r="A40" s="20" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="B40" s="20" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="C40" s="20" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="D40" s="20" t="s">
-        <v>174</v>
-      </c>
-      <c r="E40" s="10"/>
-      <c r="F40" s="10"/>
+        <v>164</v>
+      </c>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
       <c r="G40" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="H40" s="10"/>
-      <c r="I40" s="10"/>
-      <c r="J40" s="10"/>
-      <c r="K40" s="10"/>
-      <c r="L40" s="10"/>
-      <c r="M40" s="10"/>
-      <c r="N40" s="10"/>
-      <c r="O40" s="10"/>
-      <c r="P40" s="10"/>
-      <c r="Q40" s="10"/>
-      <c r="R40" s="10"/>
-      <c r="S40" s="10"/>
-      <c r="T40" s="10"/>
-      <c r="U40" s="10"/>
-      <c r="V40" s="10"/>
-      <c r="W40" s="10"/>
-      <c r="X40" s="10"/>
-      <c r="Y40" s="10"/>
-      <c r="Z40" s="10"/>
+        <v>92</v>
+      </c>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="2"/>
+      <c r="K40" s="2"/>
+      <c r="L40" s="2"/>
+      <c r="M40" s="2"/>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
+      <c r="P40" s="2"/>
+      <c r="Q40" s="2"/>
+      <c r="R40" s="2"/>
+      <c r="S40" s="2"/>
+      <c r="T40" s="2"/>
+      <c r="U40" s="2"/>
+      <c r="V40" s="2"/>
+      <c r="W40" s="2"/>
+      <c r="X40" s="2"/>
+      <c r="Y40" s="2"/>
+      <c r="Z40" s="2"/>
     </row>
     <row r="41">
       <c r="A41" s="20" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B41" s="20" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="C41" s="20" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="D41" s="20" t="s">
-        <v>177</v>
-      </c>
-      <c r="E41" s="10"/>
-      <c r="F41" s="10"/>
-      <c r="G41" s="10"/>
-      <c r="H41" s="10"/>
-      <c r="I41" s="10"/>
-      <c r="J41" s="10"/>
-      <c r="K41" s="10"/>
-      <c r="L41" s="10"/>
-      <c r="M41" s="10"/>
-      <c r="N41" s="10"/>
-      <c r="O41" s="10"/>
-      <c r="P41" s="10"/>
-      <c r="Q41" s="10"/>
-      <c r="R41" s="10"/>
-      <c r="S41" s="10"/>
-      <c r="T41" s="10"/>
-      <c r="U41" s="10"/>
-      <c r="V41" s="10"/>
-      <c r="W41" s="10"/>
-      <c r="X41" s="10"/>
-      <c r="Y41" s="10"/>
-      <c r="Z41" s="10"/>
+        <v>167</v>
+      </c>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="2"/>
+      <c r="K41" s="2"/>
+      <c r="L41" s="2"/>
+      <c r="M41" s="2"/>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
+      <c r="P41" s="2"/>
+      <c r="Q41" s="2"/>
+      <c r="R41" s="2"/>
+      <c r="S41" s="2"/>
+      <c r="T41" s="2"/>
+      <c r="U41" s="2"/>
+      <c r="V41" s="2"/>
+      <c r="W41" s="2"/>
+      <c r="X41" s="2"/>
+      <c r="Y41" s="2"/>
+      <c r="Z41" s="2"/>
     </row>
     <row r="42">
       <c r="A42" s="20" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B42" s="20" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="C42" s="20"/>
       <c r="D42" s="20"/>
-      <c r="E42" s="10"/>
-      <c r="F42" s="10"/>
-      <c r="G42" s="10"/>
-      <c r="H42" s="10"/>
-      <c r="I42" s="10"/>
-      <c r="J42" s="10"/>
-      <c r="K42" s="10"/>
-      <c r="L42" s="10"/>
-      <c r="M42" s="10"/>
-      <c r="N42" s="10"/>
-      <c r="O42" s="10"/>
-      <c r="P42" s="10"/>
-      <c r="Q42" s="10"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="2"/>
+      <c r="K42" s="2"/>
+      <c r="L42" s="2"/>
+      <c r="M42" s="2"/>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
+      <c r="P42" s="2"/>
+      <c r="Q42" s="2"/>
       <c r="R42" s="20" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="S42" s="20" t="s">
-        <v>179</v>
-      </c>
-      <c r="T42" s="10"/>
-      <c r="U42" s="10"/>
-      <c r="V42" s="10"/>
-      <c r="W42" s="10"/>
-      <c r="X42" s="10"/>
-      <c r="Y42" s="10"/>
-      <c r="Z42" s="10"/>
+        <v>169</v>
+      </c>
+      <c r="T42" s="2"/>
+      <c r="U42" s="2"/>
+      <c r="V42" s="2"/>
+      <c r="W42" s="2"/>
+      <c r="X42" s="2"/>
+      <c r="Y42" s="2"/>
+      <c r="Z42" s="2"/>
     </row>
     <row r="43">
       <c r="A43" s="20" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B43" s="20" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="C43" s="20"/>
       <c r="D43" s="20"/>
-      <c r="E43" s="10"/>
-      <c r="F43" s="10"/>
-      <c r="G43" s="10"/>
-      <c r="H43" s="10"/>
-      <c r="I43" s="10"/>
-      <c r="J43" s="10"/>
-      <c r="K43" s="10"/>
-      <c r="L43" s="10"/>
-      <c r="M43" s="10"/>
-      <c r="N43" s="10"/>
-      <c r="O43" s="10"/>
-      <c r="P43" s="10"/>
-      <c r="Q43" s="10"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="2"/>
+      <c r="K43" s="2"/>
+      <c r="L43" s="2"/>
+      <c r="M43" s="2"/>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
+      <c r="P43" s="2"/>
+      <c r="Q43" s="2"/>
       <c r="R43" s="20" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="S43" s="20" t="s">
-        <v>181</v>
-      </c>
-      <c r="T43" s="10"/>
-      <c r="U43" s="10"/>
-      <c r="V43" s="10"/>
-      <c r="W43" s="10"/>
-      <c r="X43" s="10"/>
-      <c r="Y43" s="10"/>
-      <c r="Z43" s="10"/>
+        <v>171</v>
+      </c>
+      <c r="T43" s="2"/>
+      <c r="U43" s="2"/>
+      <c r="V43" s="2"/>
+      <c r="W43" s="2"/>
+      <c r="X43" s="2"/>
+      <c r="Y43" s="2"/>
+      <c r="Z43" s="2"/>
     </row>
     <row r="44">
       <c r="A44" s="20" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B44" s="20" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C44" s="20"/>
       <c r="D44" s="20"/>
-      <c r="E44" s="10"/>
-      <c r="F44" s="10"/>
-      <c r="G44" s="10"/>
-      <c r="H44" s="10"/>
-      <c r="I44" s="10"/>
-      <c r="J44" s="10"/>
-      <c r="K44" s="10"/>
-      <c r="L44" s="10"/>
-      <c r="M44" s="10"/>
-      <c r="N44" s="10"/>
-      <c r="O44" s="10"/>
-      <c r="P44" s="10"/>
-      <c r="Q44" s="10"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+      <c r="J44" s="2"/>
+      <c r="K44" s="2"/>
+      <c r="L44" s="2"/>
+      <c r="M44" s="2"/>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
+      <c r="P44" s="2"/>
+      <c r="Q44" s="2"/>
       <c r="R44" s="20" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="S44" s="20" t="s">
-        <v>183</v>
-      </c>
-      <c r="T44" s="10"/>
-      <c r="U44" s="10"/>
-      <c r="V44" s="10"/>
-      <c r="W44" s="10"/>
-      <c r="X44" s="10"/>
-      <c r="Y44" s="10"/>
-      <c r="Z44" s="10"/>
+        <v>173</v>
+      </c>
+      <c r="T44" s="2"/>
+      <c r="U44" s="2"/>
+      <c r="V44" s="2"/>
+      <c r="W44" s="2"/>
+      <c r="X44" s="2"/>
+      <c r="Y44" s="2"/>
+      <c r="Z44" s="2"/>
     </row>
     <row r="45">
       <c r="A45" s="20" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B45" s="20" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="C45" s="20"/>
       <c r="D45" s="20"/>
-      <c r="E45" s="10"/>
-      <c r="F45" s="10"/>
-      <c r="G45" s="10"/>
-      <c r="H45" s="10"/>
-      <c r="I45" s="10"/>
-      <c r="J45" s="10"/>
-      <c r="K45" s="10"/>
-      <c r="L45" s="10"/>
-      <c r="M45" s="10"/>
-      <c r="N45" s="10"/>
-      <c r="O45" s="10"/>
-      <c r="P45" s="10"/>
-      <c r="Q45" s="10"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="2"/>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
+      <c r="J45" s="2"/>
+      <c r="K45" s="2"/>
+      <c r="L45" s="2"/>
+      <c r="M45" s="2"/>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
+      <c r="P45" s="2"/>
+      <c r="Q45" s="2"/>
       <c r="R45" s="20" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="S45" s="20" t="s">
-        <v>185</v>
-      </c>
-      <c r="T45" s="10"/>
-      <c r="U45" s="10"/>
-      <c r="V45" s="10"/>
-      <c r="W45" s="10"/>
-      <c r="X45" s="10"/>
-      <c r="Y45" s="10"/>
-      <c r="Z45" s="10"/>
+        <v>175</v>
+      </c>
+      <c r="T45" s="2"/>
+      <c r="U45" s="2"/>
+      <c r="V45" s="2"/>
+      <c r="W45" s="2"/>
+      <c r="X45" s="2"/>
+      <c r="Y45" s="2"/>
+      <c r="Z45" s="2"/>
     </row>
     <row r="46">
       <c r="A46" s="20" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B46" s="20" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="C46" s="20"/>
       <c r="D46" s="20"/>
-      <c r="E46" s="10"/>
-      <c r="F46" s="10"/>
-      <c r="G46" s="10"/>
-      <c r="H46" s="10"/>
-      <c r="I46" s="10"/>
-      <c r="J46" s="10"/>
-      <c r="K46" s="10"/>
-      <c r="L46" s="10"/>
-      <c r="M46" s="10"/>
-      <c r="N46" s="10"/>
-      <c r="O46" s="10"/>
-      <c r="P46" s="10"/>
-      <c r="Q46" s="10"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+      <c r="J46" s="2"/>
+      <c r="K46" s="2"/>
+      <c r="L46" s="2"/>
+      <c r="M46" s="2"/>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
+      <c r="P46" s="2"/>
+      <c r="Q46" s="2"/>
       <c r="R46" s="20" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="S46" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="T46" s="10"/>
-      <c r="U46" s="10"/>
-      <c r="V46" s="10"/>
-      <c r="W46" s="10"/>
-      <c r="X46" s="10"/>
-      <c r="Y46" s="10"/>
-      <c r="Z46" s="10"/>
+        <v>177</v>
+      </c>
+      <c r="T46" s="2"/>
+      <c r="U46" s="2"/>
+      <c r="V46" s="2"/>
+      <c r="W46" s="2"/>
+      <c r="X46" s="2"/>
+      <c r="Y46" s="2"/>
+      <c r="Z46" s="2"/>
     </row>
     <row r="47">
       <c r="A47" s="20" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B47" s="20" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="C47" s="20"/>
       <c r="D47" s="20"/>
-      <c r="E47" s="10"/>
-      <c r="F47" s="10"/>
-      <c r="G47" s="10"/>
-      <c r="H47" s="10"/>
-      <c r="I47" s="10"/>
-      <c r="J47" s="10"/>
-      <c r="K47" s="10"/>
-      <c r="L47" s="10"/>
-      <c r="M47" s="10"/>
-      <c r="N47" s="10"/>
-      <c r="O47" s="10"/>
-      <c r="P47" s="10"/>
-      <c r="Q47" s="10"/>
+      <c r="E47" s="2"/>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
+      <c r="J47" s="2"/>
+      <c r="K47" s="2"/>
+      <c r="L47" s="2"/>
+      <c r="M47" s="2"/>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
+      <c r="P47" s="2"/>
+      <c r="Q47" s="2"/>
       <c r="R47" s="20" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="S47" s="20" t="s">
-        <v>189</v>
-      </c>
-      <c r="T47" s="10"/>
-      <c r="U47" s="10"/>
-      <c r="V47" s="10"/>
-      <c r="W47" s="10"/>
-      <c r="X47" s="10"/>
-      <c r="Y47" s="10"/>
-      <c r="Z47" s="10"/>
+        <v>179</v>
+      </c>
+      <c r="T47" s="2"/>
+      <c r="U47" s="2"/>
+      <c r="V47" s="2"/>
+      <c r="W47" s="2"/>
+      <c r="X47" s="2"/>
+      <c r="Y47" s="2"/>
+      <c r="Z47" s="2"/>
     </row>
     <row r="48">
       <c r="A48" s="20" t="s">
-        <v>89</v>
+        <v>29</v>
       </c>
       <c r="B48" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="C48" s="10"/>
-      <c r="D48" s="10"/>
-      <c r="E48" s="10"/>
-      <c r="F48" s="10"/>
-      <c r="G48" s="10"/>
-      <c r="H48" s="10"/>
-      <c r="I48" s="10"/>
-      <c r="J48" s="10"/>
-      <c r="K48" s="10"/>
-      <c r="L48" s="10"/>
-      <c r="M48" s="10"/>
-      <c r="N48" s="10"/>
-      <c r="O48" s="10"/>
-      <c r="P48" s="10"/>
-      <c r="Q48" s="10"/>
-      <c r="R48" s="10"/>
-      <c r="S48" s="10"/>
-      <c r="T48" s="10"/>
-      <c r="U48" s="10"/>
-      <c r="V48" s="10"/>
-      <c r="W48" s="10"/>
-      <c r="X48" s="10"/>
-      <c r="Y48" s="10"/>
-      <c r="Z48" s="10"/>
+        <v>180</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
+      <c r="J48" s="2"/>
+      <c r="K48" s="2"/>
+      <c r="L48" s="2"/>
+      <c r="M48" s="2"/>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
+      <c r="P48" s="2"/>
+      <c r="Q48" s="2"/>
+      <c r="R48" s="2"/>
+      <c r="S48" s="2"/>
+      <c r="T48" s="2"/>
+      <c r="U48" s="2"/>
+      <c r="V48" s="2"/>
+      <c r="W48" s="2"/>
+      <c r="X48" s="2"/>
+      <c r="Y48" s="2"/>
+      <c r="Z48" s="2"/>
     </row>
     <row r="49">
       <c r="A49" s="20" t="s">
-        <v>79</v>
+        <v>19</v>
       </c>
       <c r="B49" s="20" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="C49" s="20" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="D49" s="20" t="s">
-        <v>193</v>
-      </c>
-      <c r="E49" s="10"/>
+        <v>183</v>
+      </c>
+      <c r="E49" s="2"/>
       <c r="G49" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="H49" s="10"/>
-      <c r="I49" s="10"/>
-      <c r="J49" s="10"/>
-      <c r="K49" s="10"/>
-      <c r="L49" s="10"/>
-      <c r="M49" s="10"/>
-      <c r="N49" s="10"/>
-      <c r="O49" s="10"/>
-      <c r="P49" s="10"/>
-      <c r="Q49" s="10"/>
-      <c r="R49" s="10"/>
-      <c r="S49" s="10"/>
-      <c r="T49" s="10"/>
-      <c r="U49" s="10"/>
-      <c r="V49" s="10"/>
-      <c r="W49" s="10"/>
-      <c r="X49" s="10"/>
-      <c r="Y49" s="10"/>
-      <c r="Z49" s="10"/>
+        <v>92</v>
+      </c>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
+      <c r="J49" s="2"/>
+      <c r="K49" s="2"/>
+      <c r="L49" s="2"/>
+      <c r="M49" s="2"/>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
+      <c r="P49" s="2"/>
+      <c r="Q49" s="2"/>
+      <c r="R49" s="2"/>
+      <c r="S49" s="2"/>
+      <c r="T49" s="2"/>
+      <c r="U49" s="2"/>
+      <c r="V49" s="2"/>
+      <c r="W49" s="2"/>
+      <c r="X49" s="2"/>
+      <c r="Y49" s="2"/>
+      <c r="Z49" s="2"/>
     </row>
     <row r="50">
       <c r="A50" s="20" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B50" s="20" t="s">
-        <v>194</v>
-      </c>
-      <c r="C50" s="20" t="s">
-        <v>195</v>
+        <v>184</v>
+      </c>
+      <c r="C50" s="28" t="s">
+        <v>185</v>
       </c>
       <c r="D50" s="20" t="s">
-        <v>196</v>
-      </c>
-      <c r="E50" s="10"/>
-      <c r="F50" s="10"/>
-      <c r="G50" s="10"/>
-      <c r="H50" s="10"/>
-      <c r="I50" s="10"/>
-      <c r="J50" s="10"/>
-      <c r="K50" s="10"/>
-      <c r="L50" s="10"/>
-      <c r="M50" s="10"/>
-      <c r="N50" s="10"/>
-      <c r="O50" s="10"/>
-      <c r="P50" s="10"/>
-      <c r="Q50" s="10"/>
-      <c r="R50" s="10"/>
-      <c r="S50" s="10"/>
-      <c r="T50" s="10"/>
-      <c r="U50" s="10"/>
-      <c r="V50" s="10"/>
-      <c r="W50" s="10"/>
-      <c r="X50" s="10"/>
-      <c r="Y50" s="10"/>
-      <c r="Z50" s="10"/>
+        <v>186</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" s="2"/>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
+      <c r="J50" s="2"/>
+      <c r="K50" s="2"/>
+      <c r="L50" s="2"/>
+      <c r="M50" s="2"/>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
+      <c r="P50" s="2"/>
+      <c r="Q50" s="2"/>
+      <c r="R50" s="2"/>
+      <c r="S50" s="2"/>
+      <c r="T50" s="2"/>
+      <c r="U50" s="2"/>
+      <c r="V50" s="2"/>
+      <c r="W50" s="2"/>
+      <c r="X50" s="2"/>
+      <c r="Y50" s="2"/>
+      <c r="Z50" s="2"/>
     </row>
     <row r="51">
       <c r="A51" s="20" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="B51" s="20" t="s">
-        <v>191</v>
-      </c>
-      <c r="C51" s="10"/>
-      <c r="D51" s="10"/>
-      <c r="E51" s="10"/>
-      <c r="F51" s="10"/>
-      <c r="G51" s="10"/>
-      <c r="H51" s="10"/>
-      <c r="I51" s="10"/>
-      <c r="J51" s="10"/>
-      <c r="K51" s="10"/>
-      <c r="L51" s="10"/>
-      <c r="M51" s="10"/>
-      <c r="N51" s="10"/>
-      <c r="O51" s="10"/>
-      <c r="P51" s="10"/>
-      <c r="Q51" s="10"/>
-      <c r="R51" s="10"/>
-      <c r="S51" s="10"/>
-      <c r="T51" s="10"/>
-      <c r="U51" s="10"/>
-      <c r="V51" s="10"/>
-      <c r="W51" s="10"/>
-      <c r="X51" s="10"/>
-      <c r="Y51" s="10"/>
-      <c r="Z51" s="10"/>
+        <v>181</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="2"/>
+      <c r="F51" s="2"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+      <c r="J51" s="2"/>
+      <c r="K51" s="2"/>
+      <c r="L51" s="2"/>
+      <c r="M51" s="2"/>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
+      <c r="P51" s="2"/>
+      <c r="Q51" s="2"/>
+      <c r="R51" s="2"/>
+      <c r="S51" s="2"/>
+      <c r="T51" s="2"/>
+      <c r="U51" s="2"/>
+      <c r="V51" s="2"/>
+      <c r="W51" s="2"/>
+      <c r="X51" s="2"/>
+      <c r="Y51" s="2"/>
+      <c r="Z51" s="2"/>
     </row>
     <row r="52">
       <c r="A52" s="20" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="B52" s="20" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="C52" s="20" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="D52" s="20" t="s">
-        <v>199</v>
-      </c>
-      <c r="E52" s="10"/>
-      <c r="F52" s="10"/>
+        <v>189</v>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" s="2"/>
       <c r="G52" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="H52" s="10"/>
-      <c r="I52" s="10"/>
-      <c r="J52" s="10"/>
-      <c r="K52" s="10"/>
-      <c r="L52" s="10"/>
-      <c r="M52" s="10"/>
-      <c r="N52" s="10"/>
-      <c r="O52" s="10"/>
-      <c r="P52" s="10"/>
-      <c r="Q52" s="10"/>
-      <c r="R52" s="10"/>
-      <c r="S52" s="10"/>
-      <c r="T52" s="10"/>
-      <c r="U52" s="10"/>
-      <c r="V52" s="10"/>
-      <c r="W52" s="10"/>
-      <c r="X52" s="10"/>
-      <c r="Y52" s="10"/>
-      <c r="Z52" s="10"/>
+        <v>92</v>
+      </c>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+      <c r="J52" s="2"/>
+      <c r="K52" s="2"/>
+      <c r="L52" s="2"/>
+      <c r="M52" s="2"/>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
+      <c r="P52" s="2"/>
+      <c r="Q52" s="2"/>
+      <c r="R52" s="2"/>
+      <c r="S52" s="2"/>
+      <c r="T52" s="2"/>
+      <c r="U52" s="2"/>
+      <c r="V52" s="2"/>
+      <c r="W52" s="2"/>
+      <c r="X52" s="2"/>
+      <c r="Y52" s="2"/>
+      <c r="Z52" s="2"/>
     </row>
     <row r="53">
       <c r="A53" s="20" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="B53" s="20" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="C53" s="20" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="D53" s="20" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="E53" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="F53" s="10"/>
-      <c r="G53" s="10"/>
-      <c r="H53" s="10"/>
-      <c r="I53" s="10"/>
-      <c r="J53" s="10"/>
-      <c r="K53" s="10"/>
-      <c r="L53" s="10"/>
-      <c r="M53" s="10"/>
-      <c r="N53" s="10"/>
-      <c r="O53" s="10"/>
-      <c r="P53" s="10"/>
-      <c r="Q53" s="10"/>
-      <c r="R53" s="10"/>
-      <c r="S53" s="10"/>
-      <c r="T53" s="10"/>
-      <c r="U53" s="10"/>
-      <c r="V53" s="10"/>
-      <c r="W53" s="10"/>
-      <c r="X53" s="10"/>
-      <c r="Y53" s="10"/>
-      <c r="Z53" s="10"/>
+        <v>36</v>
+      </c>
+      <c r="F53" s="2"/>
+      <c r="G53" s="2"/>
+      <c r="H53" s="2"/>
+      <c r="I53" s="2"/>
+      <c r="J53" s="2"/>
+      <c r="K53" s="2"/>
+      <c r="L53" s="2"/>
+      <c r="M53" s="2"/>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
+      <c r="P53" s="2"/>
+      <c r="Q53" s="2"/>
+      <c r="R53" s="2"/>
+      <c r="S53" s="2"/>
+      <c r="T53" s="2"/>
+      <c r="U53" s="2"/>
+      <c r="V53" s="2"/>
+      <c r="W53" s="2"/>
+      <c r="X53" s="2"/>
+      <c r="Y53" s="2"/>
+      <c r="Z53" s="2"/>
     </row>
     <row r="54">
       <c r="A54" s="20" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="B54" s="20" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C54" s="20" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="D54" s="20" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="E54" s="20" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="F54" s="20" t="s">
-        <v>207</v>
-      </c>
-      <c r="G54" s="10"/>
-      <c r="H54" s="10"/>
-      <c r="I54" s="10"/>
-      <c r="J54" s="10"/>
-      <c r="K54" s="10"/>
-      <c r="L54" s="10"/>
-      <c r="M54" s="10"/>
-      <c r="N54" s="10"/>
-      <c r="O54" s="10"/>
-      <c r="P54" s="10"/>
-      <c r="Q54" s="10"/>
-      <c r="R54" s="10"/>
-      <c r="S54" s="10"/>
-      <c r="T54" s="10"/>
-      <c r="U54" s="10"/>
-      <c r="V54" s="10"/>
-      <c r="W54" s="10"/>
-      <c r="X54" s="10"/>
-      <c r="Y54" s="10"/>
-      <c r="Z54" s="10"/>
+        <v>197</v>
+      </c>
+      <c r="G54" s="2"/>
+      <c r="H54" s="2"/>
+      <c r="I54" s="2"/>
+      <c r="J54" s="2"/>
+      <c r="K54" s="2"/>
+      <c r="L54" s="2"/>
+      <c r="M54" s="2"/>
+      <c r="N54" s="2"/>
+      <c r="O54" s="2"/>
+      <c r="P54" s="2"/>
+      <c r="Q54" s="2"/>
+      <c r="R54" s="2"/>
+      <c r="S54" s="2"/>
+      <c r="T54" s="2"/>
+      <c r="U54" s="2"/>
+      <c r="V54" s="2"/>
+      <c r="W54" s="2"/>
+      <c r="X54" s="2"/>
+      <c r="Y54" s="2"/>
+      <c r="Z54" s="2"/>
     </row>
     <row r="55">
       <c r="A55" s="20" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B55" s="20" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="C55" s="20" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="D55" s="20" t="s">
-        <v>210</v>
-      </c>
-      <c r="E55" s="10"/>
+        <v>200</v>
+      </c>
+      <c r="E55" s="2"/>
       <c r="F55" s="20" t="s">
-        <v>211</v>
-      </c>
-      <c r="G55" s="10"/>
-      <c r="H55" s="10"/>
-      <c r="I55" s="10"/>
-      <c r="J55" s="10"/>
-      <c r="K55" s="10"/>
-      <c r="L55" s="10"/>
-      <c r="M55" s="10"/>
-      <c r="N55" s="10"/>
-      <c r="O55" s="10"/>
-      <c r="P55" s="10"/>
-      <c r="Q55" s="10"/>
-      <c r="R55" s="10"/>
-      <c r="S55" s="10"/>
-      <c r="T55" s="10"/>
-      <c r="U55" s="10"/>
-      <c r="V55" s="10"/>
-      <c r="W55" s="10"/>
-      <c r="X55" s="10"/>
-      <c r="Y55" s="10"/>
-      <c r="Z55" s="10"/>
+        <v>201</v>
+      </c>
+      <c r="G55" s="2"/>
+      <c r="H55" s="2"/>
+      <c r="I55" s="2"/>
+      <c r="J55" s="2"/>
+      <c r="K55" s="2"/>
+      <c r="L55" s="2"/>
+      <c r="M55" s="2"/>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
+      <c r="P55" s="2"/>
+      <c r="Q55" s="2"/>
+      <c r="R55" s="2"/>
+      <c r="S55" s="2"/>
+      <c r="T55" s="2"/>
+      <c r="U55" s="2"/>
+      <c r="V55" s="2"/>
+      <c r="W55" s="2"/>
+      <c r="X55" s="2"/>
+      <c r="Y55" s="2"/>
+      <c r="Z55" s="2"/>
     </row>
     <row r="56">
-      <c r="A56" s="20" t="s">
-        <v>103</v>
-      </c>
-      <c r="B56" s="20" t="s">
-        <v>212</v>
-      </c>
-      <c r="C56" s="20" t="s">
-        <v>213</v>
-      </c>
-      <c r="D56" s="20" t="s">
-        <v>214</v>
-      </c>
-      <c r="E56" s="10"/>
-      <c r="F56" s="10"/>
-      <c r="G56" s="10"/>
-      <c r="H56" s="10"/>
-      <c r="I56" s="10"/>
-      <c r="J56" s="10"/>
-      <c r="K56" s="10"/>
-      <c r="L56" s="10"/>
-      <c r="M56" s="10"/>
-      <c r="N56" s="10"/>
-      <c r="O56" s="10"/>
-      <c r="P56" s="10"/>
-      <c r="Q56" s="10"/>
-      <c r="R56" s="20" t="s">
-        <v>215</v>
-      </c>
-      <c r="S56" s="20" t="s">
-        <v>215</v>
-      </c>
-      <c r="T56" s="10"/>
-      <c r="U56" s="10"/>
-      <c r="V56" s="10"/>
-      <c r="W56" s="10"/>
-      <c r="X56" s="10"/>
-      <c r="Y56" s="10"/>
-      <c r="Z56" s="10"/>
+      <c r="A56" s="28" t="s">
+        <v>93</v>
+      </c>
+      <c r="B56" s="28" t="s">
+        <v>202</v>
+      </c>
+      <c r="C56" s="28" t="s">
+        <v>203</v>
+      </c>
+      <c r="D56" s="28" t="s">
+        <v>204</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" s="2"/>
+      <c r="G56" s="2"/>
+      <c r="H56" s="2"/>
+      <c r="I56" s="2"/>
+      <c r="J56" s="2"/>
+      <c r="K56" s="2"/>
+      <c r="L56" s="2"/>
+      <c r="M56" s="2"/>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
+      <c r="P56" s="2"/>
+      <c r="Q56" s="2"/>
+      <c r="R56" s="20"/>
+      <c r="S56" s="20"/>
+      <c r="T56" s="2"/>
+      <c r="U56" s="2"/>
+      <c r="V56" s="2"/>
+      <c r="W56" s="2"/>
+      <c r="X56" s="2"/>
+      <c r="Y56" s="2"/>
+      <c r="Z56" s="2"/>
     </row>
     <row r="57">
       <c r="A57" s="20" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B57" s="20" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="C57" s="20" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="D57" s="20" t="s">
-        <v>218</v>
-      </c>
-      <c r="E57" s="10"/>
-      <c r="F57" s="10"/>
-      <c r="G57" s="10"/>
-      <c r="H57" s="10"/>
-      <c r="I57" s="10"/>
-      <c r="J57" s="10"/>
-      <c r="K57" s="10"/>
-      <c r="L57" s="10"/>
-      <c r="M57" s="10"/>
-      <c r="N57" s="10"/>
-      <c r="O57" s="10"/>
-      <c r="P57" s="10"/>
-      <c r="Q57" s="10"/>
+        <v>207</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" s="2"/>
+      <c r="G57" s="2"/>
+      <c r="H57" s="2"/>
+      <c r="I57" s="2"/>
+      <c r="J57" s="2"/>
+      <c r="K57" s="2"/>
+      <c r="L57" s="2"/>
+      <c r="M57" s="2"/>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2"/>
+      <c r="P57" s="2"/>
+      <c r="Q57" s="2"/>
       <c r="R57" s="20" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="S57" s="20" t="s">
-        <v>219</v>
-      </c>
-      <c r="T57" s="10"/>
-      <c r="U57" s="10"/>
-      <c r="V57" s="10"/>
-      <c r="W57" s="10"/>
-      <c r="X57" s="10"/>
-      <c r="Y57" s="10"/>
-      <c r="Z57" s="10"/>
+        <v>208</v>
+      </c>
+      <c r="T57" s="2"/>
+      <c r="U57" s="2"/>
+      <c r="V57" s="2"/>
+      <c r="W57" s="2"/>
+      <c r="X57" s="2"/>
+      <c r="Y57" s="2"/>
+      <c r="Z57" s="2"/>
     </row>
     <row r="58">
       <c r="A58" s="20" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B58" s="20" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="C58" s="20" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="D58" s="20" t="s">
-        <v>222</v>
-      </c>
-      <c r="E58" s="10"/>
-      <c r="F58" s="10"/>
-      <c r="G58" s="10"/>
-      <c r="H58" s="10"/>
-      <c r="I58" s="10"/>
-      <c r="J58" s="10"/>
-      <c r="K58" s="10"/>
-      <c r="L58" s="10"/>
-      <c r="M58" s="10"/>
-      <c r="N58" s="10"/>
-      <c r="O58" s="10"/>
-      <c r="P58" s="10"/>
-      <c r="Q58" s="10"/>
+        <v>211</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2"/>
+      <c r="G58" s="2"/>
+      <c r="H58" s="2"/>
+      <c r="I58" s="2"/>
+      <c r="J58" s="2"/>
+      <c r="K58" s="2"/>
+      <c r="L58" s="2"/>
+      <c r="M58" s="2"/>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
+      <c r="P58" s="2"/>
+      <c r="Q58" s="2"/>
       <c r="R58" s="20" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="S58" s="20" t="s">
-        <v>223</v>
-      </c>
-      <c r="T58" s="10"/>
-      <c r="U58" s="10"/>
-      <c r="V58" s="10"/>
-      <c r="W58" s="10"/>
-      <c r="X58" s="10"/>
-      <c r="Y58" s="10"/>
-      <c r="Z58" s="10"/>
+        <v>212</v>
+      </c>
+      <c r="T58" s="2"/>
+      <c r="U58" s="2"/>
+      <c r="V58" s="2"/>
+      <c r="W58" s="2"/>
+      <c r="X58" s="2"/>
+      <c r="Y58" s="2"/>
+      <c r="Z58" s="2"/>
     </row>
     <row r="59">
       <c r="A59" s="20" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B59" s="20" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="C59" s="20" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="D59" s="20" t="s">
-        <v>226</v>
-      </c>
-      <c r="E59" s="10"/>
-      <c r="F59" s="10"/>
-      <c r="G59" s="10"/>
-      <c r="H59" s="10"/>
-      <c r="I59" s="10"/>
-      <c r="J59" s="10"/>
-      <c r="K59" s="10"/>
-      <c r="L59" s="10"/>
-      <c r="M59" s="10"/>
-      <c r="N59" s="10"/>
-      <c r="O59" s="10"/>
-      <c r="P59" s="10"/>
-      <c r="Q59" s="10"/>
+        <v>215</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" s="2"/>
+      <c r="G59" s="2"/>
+      <c r="H59" s="2"/>
+      <c r="I59" s="2"/>
+      <c r="J59" s="2"/>
+      <c r="K59" s="2"/>
+      <c r="L59" s="2"/>
+      <c r="M59" s="2"/>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
+      <c r="P59" s="2"/>
+      <c r="Q59" s="2"/>
       <c r="R59" s="20" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="S59" s="20" t="s">
-        <v>227</v>
-      </c>
-      <c r="T59" s="10"/>
-      <c r="U59" s="10"/>
-      <c r="V59" s="10"/>
-      <c r="W59" s="10"/>
-      <c r="X59" s="10"/>
-      <c r="Y59" s="10"/>
-      <c r="Z59" s="10"/>
+        <v>216</v>
+      </c>
+      <c r="T59" s="2"/>
+      <c r="U59" s="2"/>
+      <c r="V59" s="2"/>
+      <c r="W59" s="2"/>
+      <c r="X59" s="2"/>
+      <c r="Y59" s="2"/>
+      <c r="Z59" s="2"/>
     </row>
     <row r="60">
       <c r="A60" s="20" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B60" s="20" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="C60" s="20" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="D60" s="20" t="s">
-        <v>230</v>
-      </c>
-      <c r="E60" s="10"/>
-      <c r="F60" s="10"/>
-      <c r="G60" s="10"/>
-      <c r="H60" s="10"/>
-      <c r="I60" s="10"/>
-      <c r="J60" s="10"/>
-      <c r="K60" s="10"/>
-      <c r="L60" s="10"/>
-      <c r="M60" s="10"/>
-      <c r="N60" s="10"/>
-      <c r="O60" s="10"/>
-      <c r="P60" s="10"/>
-      <c r="Q60" s="10"/>
+        <v>219</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" s="2"/>
+      <c r="G60" s="2"/>
+      <c r="H60" s="2"/>
+      <c r="I60" s="2"/>
+      <c r="J60" s="2"/>
+      <c r="K60" s="2"/>
+      <c r="L60" s="2"/>
+      <c r="M60" s="2"/>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
+      <c r="P60" s="2"/>
+      <c r="Q60" s="2"/>
       <c r="R60" s="20" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="S60" s="20" t="s">
-        <v>231</v>
-      </c>
-      <c r="T60" s="10"/>
-      <c r="U60" s="10"/>
-      <c r="V60" s="10"/>
-      <c r="W60" s="10"/>
-      <c r="X60" s="10"/>
-      <c r="Y60" s="10"/>
-      <c r="Z60" s="10"/>
+        <v>220</v>
+      </c>
+      <c r="T60" s="2"/>
+      <c r="U60" s="2"/>
+      <c r="V60" s="2"/>
+      <c r="W60" s="2"/>
+      <c r="X60" s="2"/>
+      <c r="Y60" s="2"/>
+      <c r="Z60" s="2"/>
     </row>
     <row r="61">
       <c r="A61" s="20" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B61" s="20" t="s">
-        <v>232</v>
-      </c>
-      <c r="C61" s="20" t="s">
-        <v>233</v>
-      </c>
-      <c r="D61" s="20" t="s">
-        <v>234</v>
-      </c>
-      <c r="E61" s="10"/>
-      <c r="F61" s="10"/>
-      <c r="G61" s="10"/>
-      <c r="H61" s="10"/>
-      <c r="I61" s="10"/>
-      <c r="J61" s="10"/>
-      <c r="K61" s="10"/>
-      <c r="L61" s="10"/>
-      <c r="M61" s="10"/>
-      <c r="N61" s="10"/>
-      <c r="O61" s="10"/>
-      <c r="P61" s="10"/>
-      <c r="Q61" s="10"/>
+        <v>221</v>
+      </c>
+      <c r="C61" s="28" t="s">
+        <v>222</v>
+      </c>
+      <c r="D61" s="28" t="s">
+        <v>223</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" s="2"/>
+      <c r="G61" s="2"/>
+      <c r="H61" s="2"/>
+      <c r="I61" s="2"/>
+      <c r="J61" s="2"/>
+      <c r="K61" s="2"/>
+      <c r="L61" s="2"/>
+      <c r="M61" s="2"/>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
+      <c r="P61" s="2"/>
+      <c r="Q61" s="2"/>
       <c r="R61" s="20" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="S61" s="20" t="s">
-        <v>235</v>
-      </c>
-      <c r="T61" s="10"/>
-      <c r="U61" s="10"/>
-      <c r="V61" s="10"/>
-      <c r="W61" s="10"/>
-      <c r="X61" s="10"/>
-      <c r="Y61" s="10"/>
-      <c r="Z61" s="10"/>
+        <v>224</v>
+      </c>
+      <c r="T61" s="2"/>
+      <c r="U61" s="2"/>
+      <c r="V61" s="2"/>
+      <c r="W61" s="2"/>
+      <c r="X61" s="2"/>
+      <c r="Y61" s="2"/>
+      <c r="Z61" s="2"/>
     </row>
     <row r="62">
       <c r="A62" s="20" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B62" s="20" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="C62" s="20" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="D62" s="20" t="s">
-        <v>238</v>
-      </c>
-      <c r="E62" s="10"/>
-      <c r="F62" s="10"/>
-      <c r="G62" s="10"/>
-      <c r="H62" s="10"/>
-      <c r="I62" s="10"/>
-      <c r="J62" s="10"/>
-      <c r="K62" s="10"/>
-      <c r="L62" s="10"/>
-      <c r="M62" s="10"/>
-      <c r="N62" s="10"/>
-      <c r="O62" s="10"/>
-      <c r="P62" s="10"/>
-      <c r="Q62" s="10"/>
-      <c r="R62" s="10"/>
-      <c r="S62" s="10"/>
-      <c r="T62" s="10"/>
-      <c r="U62" s="10"/>
-      <c r="V62" s="10"/>
-      <c r="W62" s="10"/>
-      <c r="X62" s="10"/>
-      <c r="Y62" s="10"/>
-      <c r="Z62" s="10"/>
+        <v>227</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" s="2"/>
+      <c r="G62" s="2"/>
+      <c r="H62" s="2"/>
+      <c r="I62" s="2"/>
+      <c r="J62" s="2"/>
+      <c r="K62" s="2"/>
+      <c r="L62" s="2"/>
+      <c r="M62" s="2"/>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
+      <c r="P62" s="2"/>
+      <c r="Q62" s="2"/>
+      <c r="R62" s="20" t="s">
+        <v>228</v>
+      </c>
+      <c r="S62" s="20" t="s">
+        <v>228</v>
+      </c>
+      <c r="T62" s="2"/>
+      <c r="U62" s="2"/>
+      <c r="V62" s="2"/>
+      <c r="W62" s="2"/>
+      <c r="X62" s="2"/>
+      <c r="Y62" s="2"/>
+      <c r="Z62" s="2"/>
     </row>
     <row r="63">
       <c r="A63" s="20" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="B63" s="20" t="s">
-        <v>197</v>
-      </c>
-      <c r="C63" s="10"/>
-      <c r="D63" s="10"/>
-      <c r="E63" s="10"/>
-      <c r="F63" s="10"/>
-      <c r="G63" s="10"/>
-      <c r="H63" s="10"/>
-      <c r="I63" s="10"/>
-      <c r="J63" s="10"/>
-      <c r="K63" s="10"/>
-      <c r="L63" s="10"/>
-      <c r="M63" s="10"/>
-      <c r="N63" s="10"/>
-      <c r="O63" s="10"/>
-      <c r="P63" s="10"/>
-      <c r="Q63" s="10"/>
-      <c r="R63" s="10"/>
-      <c r="S63" s="10"/>
-      <c r="T63" s="10"/>
-      <c r="U63" s="10"/>
-      <c r="V63" s="10"/>
-      <c r="W63" s="10"/>
-      <c r="X63" s="10"/>
-      <c r="Y63" s="10"/>
-      <c r="Z63" s="10"/>
+        <v>229</v>
+      </c>
+      <c r="C63" s="28" t="s">
+        <v>230</v>
+      </c>
+      <c r="D63" s="28" t="s">
+        <v>231</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" s="2"/>
+      <c r="G63" s="2"/>
+      <c r="H63" s="2"/>
+      <c r="I63" s="2"/>
+      <c r="J63" s="2"/>
+      <c r="K63" s="2"/>
+      <c r="L63" s="2"/>
+      <c r="M63" s="2"/>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
+      <c r="P63" s="2"/>
+      <c r="Q63" s="2"/>
+      <c r="R63" s="2"/>
+      <c r="S63" s="2"/>
+      <c r="T63" s="2"/>
+      <c r="U63" s="2"/>
+      <c r="V63" s="2"/>
+      <c r="W63" s="2"/>
+      <c r="X63" s="2"/>
+      <c r="Y63" s="2"/>
+      <c r="Z63" s="2"/>
     </row>
     <row r="64">
       <c r="A64" s="20" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="B64" s="20" t="s">
-        <v>239</v>
-      </c>
-      <c r="C64" s="20" t="s">
-        <v>240</v>
-      </c>
-      <c r="D64" s="20" t="s">
-        <v>241</v>
-      </c>
-      <c r="E64" s="10"/>
-      <c r="F64" s="10"/>
-      <c r="G64" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="H64" s="10"/>
-      <c r="I64" s="10"/>
-      <c r="J64" s="10"/>
-      <c r="K64" s="10"/>
-      <c r="L64" s="10"/>
-      <c r="M64" s="10"/>
-      <c r="N64" s="10"/>
-      <c r="O64" s="10"/>
-      <c r="P64" s="10"/>
-      <c r="Q64" s="10"/>
-      <c r="R64" s="10"/>
-      <c r="S64" s="10"/>
-      <c r="T64" s="10"/>
-      <c r="U64" s="10"/>
-      <c r="V64" s="10"/>
-      <c r="W64" s="10"/>
-      <c r="X64" s="10"/>
-      <c r="Y64" s="10"/>
-      <c r="Z64" s="10"/>
+        <v>187</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" s="2"/>
+      <c r="E64" s="2"/>
+      <c r="F64" s="2"/>
+      <c r="G64" s="2"/>
+      <c r="H64" s="2"/>
+      <c r="I64" s="2"/>
+      <c r="J64" s="2"/>
+      <c r="K64" s="2"/>
+      <c r="L64" s="2"/>
+      <c r="M64" s="2"/>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
+      <c r="P64" s="2"/>
+      <c r="Q64" s="2"/>
+      <c r="R64" s="2"/>
+      <c r="S64" s="2"/>
+      <c r="T64" s="2"/>
+      <c r="U64" s="2"/>
+      <c r="V64" s="2"/>
+      <c r="W64" s="2"/>
+      <c r="X64" s="2"/>
+      <c r="Y64" s="2"/>
+      <c r="Z64" s="2"/>
     </row>
     <row r="65">
       <c r="A65" s="20" t="s">
-        <v>242</v>
+        <v>19</v>
       </c>
       <c r="B65" s="20" t="s">
-        <v>40</v>
+        <v>232</v>
       </c>
       <c r="C65" s="20" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="D65" s="20" t="s">
-        <v>244</v>
-      </c>
-      <c r="E65" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="F65" s="10"/>
-      <c r="G65" s="10"/>
-      <c r="H65" s="10"/>
-      <c r="I65" s="20" t="s">
-        <v>245</v>
-      </c>
-      <c r="J65" s="25" t="s">
-        <v>246</v>
-      </c>
-      <c r="K65" s="25" t="s">
-        <v>247</v>
-      </c>
-      <c r="L65" s="10"/>
-      <c r="M65" s="10"/>
-      <c r="N65" s="10"/>
-      <c r="O65" s="10"/>
-      <c r="P65" s="10"/>
-      <c r="Q65" s="10"/>
-      <c r="R65" s="10"/>
-      <c r="S65" s="10"/>
-      <c r="T65" s="10"/>
-      <c r="U65" s="10"/>
-      <c r="V65" s="10"/>
-      <c r="W65" s="10"/>
-      <c r="X65" s="10"/>
-      <c r="Y65" s="10"/>
-      <c r="Z65" s="10"/>
+        <v>234</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" s="2"/>
+      <c r="G65" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="H65" s="2"/>
+      <c r="I65" s="2"/>
+      <c r="J65" s="2"/>
+      <c r="K65" s="2"/>
+      <c r="L65" s="2"/>
+      <c r="M65" s="2"/>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
+      <c r="P65" s="2"/>
+      <c r="Q65" s="2"/>
+      <c r="R65" s="2"/>
+      <c r="S65" s="2"/>
+      <c r="T65" s="2"/>
+      <c r="U65" s="2"/>
+      <c r="V65" s="2"/>
+      <c r="W65" s="2"/>
+      <c r="X65" s="2"/>
+      <c r="Y65" s="2"/>
+      <c r="Z65" s="2"/>
     </row>
     <row r="66">
       <c r="A66" s="20" t="s">
-        <v>115</v>
+        <v>235</v>
       </c>
       <c r="B66" s="20" t="s">
-        <v>248</v>
+        <v>60</v>
       </c>
       <c r="C66" s="20" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="D66" s="20" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="E66" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="F66" s="20"/>
-      <c r="G66" s="10"/>
-      <c r="H66" s="10"/>
-      <c r="I66" s="10"/>
-      <c r="J66" s="10"/>
-      <c r="K66" s="10"/>
-      <c r="L66" s="10"/>
-      <c r="M66" s="10"/>
-      <c r="N66" s="10"/>
-      <c r="O66" s="10"/>
-      <c r="P66" s="10"/>
-      <c r="Q66" s="10"/>
-      <c r="R66" s="10"/>
-      <c r="S66" s="10"/>
-      <c r="T66" s="10"/>
-      <c r="U66" s="10"/>
-      <c r="V66" s="10"/>
-      <c r="W66" s="10"/>
-      <c r="X66" s="10"/>
-      <c r="Y66" s="10"/>
-      <c r="Z66" s="10"/>
+        <v>36</v>
+      </c>
+      <c r="F66" s="2"/>
+      <c r="G66" s="2"/>
+      <c r="H66" s="2"/>
+      <c r="I66" s="20" t="s">
+        <v>238</v>
+      </c>
+      <c r="J66" s="25" t="s">
+        <v>239</v>
+      </c>
+      <c r="K66" s="25" t="s">
+        <v>240</v>
+      </c>
+      <c r="L66" s="2"/>
+      <c r="M66" s="2"/>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
+      <c r="P66" s="2"/>
+      <c r="Q66" s="2"/>
+      <c r="R66" s="2"/>
+      <c r="S66" s="2"/>
+      <c r="T66" s="2"/>
+      <c r="U66" s="2"/>
+      <c r="V66" s="2"/>
+      <c r="W66" s="2"/>
+      <c r="X66" s="2"/>
+      <c r="Y66" s="2"/>
+      <c r="Z66" s="2"/>
     </row>
     <row r="67">
       <c r="A67" s="20" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B67" s="20" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="C67" s="20" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="D67" s="20" t="s">
-        <v>253</v>
-      </c>
-      <c r="E67" s="10"/>
-      <c r="F67" s="10"/>
-      <c r="G67" s="10"/>
-      <c r="H67" s="10"/>
-      <c r="I67" s="10"/>
-      <c r="J67" s="10"/>
-      <c r="K67" s="10"/>
-      <c r="L67" s="10"/>
-      <c r="M67" s="10"/>
-      <c r="N67" s="10"/>
-      <c r="O67" s="10"/>
-      <c r="P67" s="10"/>
-      <c r="Q67" s="10"/>
-      <c r="R67" s="10"/>
-      <c r="S67" s="10"/>
-      <c r="T67" s="10"/>
-      <c r="U67" s="10"/>
-      <c r="V67" s="10"/>
-      <c r="W67" s="10"/>
-      <c r="X67" s="10"/>
-      <c r="Y67" s="10"/>
-      <c r="Z67" s="10"/>
+        <v>243</v>
+      </c>
+      <c r="E67" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="F67" s="20"/>
+      <c r="G67" s="2"/>
+      <c r="H67" s="2"/>
+      <c r="I67" s="2"/>
+      <c r="J67" s="2"/>
+      <c r="K67" s="2"/>
+      <c r="L67" s="2"/>
+      <c r="M67" s="2"/>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
+      <c r="P67" s="2"/>
+      <c r="Q67" s="2"/>
+      <c r="R67" s="2"/>
+      <c r="S67" s="2"/>
+      <c r="T67" s="2"/>
+      <c r="U67" s="2"/>
+      <c r="V67" s="2"/>
+      <c r="W67" s="2"/>
+      <c r="X67" s="2"/>
+      <c r="Y67" s="2"/>
+      <c r="Z67" s="2"/>
     </row>
     <row r="68">
       <c r="A68" s="20" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="B68" s="20" t="s">
-        <v>239</v>
-      </c>
-      <c r="C68" s="20"/>
-      <c r="D68" s="20"/>
-      <c r="E68" s="10"/>
-      <c r="F68" s="10"/>
-      <c r="G68" s="20"/>
-      <c r="H68" s="10"/>
-      <c r="I68" s="10"/>
-      <c r="J68" s="10"/>
-      <c r="K68" s="10"/>
-      <c r="L68" s="10"/>
-      <c r="M68" s="10"/>
-      <c r="N68" s="10"/>
-      <c r="O68" s="10"/>
-      <c r="P68" s="10"/>
-      <c r="Q68" s="10"/>
-      <c r="R68" s="10"/>
-      <c r="S68" s="10"/>
-      <c r="T68" s="10"/>
-      <c r="U68" s="10"/>
-      <c r="V68" s="10"/>
-      <c r="W68" s="10"/>
-      <c r="X68" s="10"/>
-      <c r="Y68" s="10"/>
-      <c r="Z68" s="10"/>
+        <v>244</v>
+      </c>
+      <c r="C68" s="28" t="s">
+        <v>245</v>
+      </c>
+      <c r="D68" s="20" t="s">
+        <v>246</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" s="2"/>
+      <c r="G68" s="2"/>
+      <c r="H68" s="2"/>
+      <c r="I68" s="2"/>
+      <c r="J68" s="2"/>
+      <c r="K68" s="2"/>
+      <c r="L68" s="2"/>
+      <c r="M68" s="2"/>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
+      <c r="P68" s="2"/>
+      <c r="Q68" s="2"/>
+      <c r="R68" s="2"/>
+      <c r="S68" s="2"/>
+      <c r="T68" s="2"/>
+      <c r="U68" s="2"/>
+      <c r="V68" s="2"/>
+      <c r="W68" s="2"/>
+      <c r="X68" s="2"/>
+      <c r="Y68" s="2"/>
+      <c r="Z68" s="2"/>
     </row>
     <row r="69">
       <c r="A69" s="20" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B69" s="20" t="s">
-        <v>254</v>
-      </c>
-      <c r="C69" s="20" t="s">
-        <v>255</v>
-      </c>
-      <c r="D69" s="20" t="s">
-        <v>256</v>
-      </c>
-      <c r="E69" s="10"/>
-      <c r="F69" s="10"/>
-      <c r="G69" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="H69" s="10"/>
-      <c r="I69" s="10"/>
-      <c r="J69" s="10"/>
-      <c r="K69" s="10"/>
-      <c r="L69" s="10"/>
-      <c r="M69" s="10"/>
-      <c r="N69" s="10"/>
-      <c r="O69" s="10"/>
-      <c r="P69" s="10"/>
-      <c r="Q69" s="10"/>
-      <c r="R69" s="10"/>
-      <c r="S69" s="10"/>
-      <c r="T69" s="10"/>
-      <c r="U69" s="10"/>
-      <c r="V69" s="10"/>
-      <c r="W69" s="10"/>
-      <c r="X69" s="10"/>
-      <c r="Y69" s="10"/>
-      <c r="Z69" s="10"/>
+        <v>232</v>
+      </c>
+      <c r="C69" s="20"/>
+      <c r="D69" s="20"/>
+      <c r="E69" s="2"/>
+      <c r="F69" s="2"/>
+      <c r="G69" s="20"/>
+      <c r="H69" s="2"/>
+      <c r="I69" s="2"/>
+      <c r="J69" s="2"/>
+      <c r="K69" s="2"/>
+      <c r="L69" s="2"/>
+      <c r="M69" s="2"/>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
+      <c r="P69" s="2"/>
+      <c r="Q69" s="2"/>
+      <c r="R69" s="2"/>
+      <c r="S69" s="2"/>
+      <c r="T69" s="2"/>
+      <c r="U69" s="2"/>
+      <c r="V69" s="2"/>
+      <c r="W69" s="2"/>
+      <c r="X69" s="2"/>
+      <c r="Y69" s="2"/>
+      <c r="Z69" s="2"/>
     </row>
     <row r="70">
       <c r="A70" s="20" t="s">
-        <v>200</v>
+        <v>88</v>
       </c>
       <c r="B70" s="20" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="C70" s="20" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="D70" s="20" t="s">
-        <v>259</v>
-      </c>
-      <c r="E70" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="F70" s="10"/>
-      <c r="G70" s="10"/>
-      <c r="H70" s="10"/>
-      <c r="I70" s="10"/>
-      <c r="J70" s="10"/>
-      <c r="K70" s="10"/>
-      <c r="L70" s="10"/>
-      <c r="M70" s="10"/>
-      <c r="N70" s="10"/>
-      <c r="O70" s="10"/>
-      <c r="P70" s="10"/>
-      <c r="Q70" s="10"/>
-      <c r="R70" s="10"/>
-      <c r="S70" s="10"/>
-      <c r="T70" s="10"/>
-      <c r="U70" s="10"/>
-      <c r="V70" s="10"/>
-      <c r="W70" s="10"/>
-      <c r="X70" s="10"/>
-      <c r="Y70" s="10"/>
-      <c r="Z70" s="10"/>
+        <v>249</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" s="2"/>
+      <c r="G70" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="H70" s="2"/>
+      <c r="I70" s="2"/>
+      <c r="J70" s="2"/>
+      <c r="K70" s="2"/>
+      <c r="L70" s="2"/>
+      <c r="M70" s="2"/>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
+      <c r="P70" s="2"/>
+      <c r="Q70" s="2"/>
+      <c r="R70" s="2"/>
+      <c r="S70" s="2"/>
+      <c r="T70" s="2"/>
+      <c r="U70" s="2"/>
+      <c r="V70" s="2"/>
+      <c r="W70" s="2"/>
+      <c r="X70" s="2"/>
+      <c r="Y70" s="2"/>
+      <c r="Z70" s="2"/>
     </row>
     <row r="71">
       <c r="A71" s="20" t="s">
-        <v>115</v>
+        <v>190</v>
       </c>
       <c r="B71" s="20" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="C71" s="20" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="D71" s="20" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="E71" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="F71" s="10"/>
-      <c r="G71" s="10"/>
-      <c r="H71" s="10"/>
-      <c r="I71" s="10"/>
-      <c r="J71" s="10"/>
-      <c r="K71" s="10"/>
-      <c r="L71" s="10"/>
-      <c r="M71" s="10"/>
-      <c r="N71" s="10"/>
-      <c r="O71" s="10"/>
-      <c r="P71" s="10"/>
-      <c r="Q71" s="10"/>
-      <c r="R71" s="10"/>
-      <c r="S71" s="10"/>
-      <c r="T71" s="10"/>
-      <c r="U71" s="10"/>
-      <c r="V71" s="10"/>
-      <c r="W71" s="10"/>
-      <c r="X71" s="10"/>
-      <c r="Y71" s="10"/>
-      <c r="Z71" s="10"/>
+        <v>36</v>
+      </c>
+      <c r="F71" s="2"/>
+      <c r="G71" s="2"/>
+      <c r="H71" s="2"/>
+      <c r="I71" s="2"/>
+      <c r="J71" s="2"/>
+      <c r="K71" s="2"/>
+      <c r="L71" s="2"/>
+      <c r="M71" s="2"/>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
+      <c r="P71" s="2"/>
+      <c r="Q71" s="2"/>
+      <c r="R71" s="2"/>
+      <c r="S71" s="2"/>
+      <c r="T71" s="2"/>
+      <c r="U71" s="2"/>
+      <c r="V71" s="2"/>
+      <c r="W71" s="2"/>
+      <c r="X71" s="2"/>
+      <c r="Y71" s="2"/>
+      <c r="Z71" s="2"/>
     </row>
     <row r="72">
       <c r="A72" s="20" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B72" s="20" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="C72" s="20" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="D72" s="20" t="s">
-        <v>265</v>
-      </c>
-      <c r="E72" s="10"/>
-      <c r="F72" s="10"/>
-      <c r="G72" s="10"/>
-      <c r="H72" s="10"/>
-      <c r="I72" s="10"/>
-      <c r="J72" s="10"/>
-      <c r="K72" s="10"/>
-      <c r="L72" s="10"/>
-      <c r="M72" s="10"/>
-      <c r="N72" s="10"/>
-      <c r="O72" s="10"/>
-      <c r="P72" s="10"/>
-      <c r="Q72" s="10"/>
-      <c r="R72" s="10"/>
-      <c r="S72" s="10"/>
-      <c r="T72" s="10"/>
-      <c r="U72" s="10"/>
-      <c r="V72" s="10"/>
-      <c r="W72" s="10"/>
-      <c r="X72" s="10"/>
-      <c r="Y72" s="10"/>
-      <c r="Z72" s="10"/>
+        <v>255</v>
+      </c>
+      <c r="E72" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="F72" s="2"/>
+      <c r="G72" s="2"/>
+      <c r="H72" s="2"/>
+      <c r="I72" s="2"/>
+      <c r="J72" s="2"/>
+      <c r="K72" s="2"/>
+      <c r="L72" s="2"/>
+      <c r="M72" s="2"/>
+      <c r="N72" s="2"/>
+      <c r="O72" s="2"/>
+      <c r="P72" s="2"/>
+      <c r="Q72" s="2"/>
+      <c r="R72" s="2"/>
+      <c r="S72" s="2"/>
+      <c r="T72" s="2"/>
+      <c r="U72" s="2"/>
+      <c r="V72" s="2"/>
+      <c r="W72" s="2"/>
+      <c r="X72" s="2"/>
+      <c r="Y72" s="2"/>
+      <c r="Z72" s="2"/>
     </row>
     <row r="73">
       <c r="A73" s="20" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="B73" s="20" t="s">
-        <v>254</v>
-      </c>
-      <c r="C73" s="10"/>
-      <c r="D73" s="10"/>
-      <c r="E73" s="10"/>
-      <c r="F73" s="10"/>
-      <c r="G73" s="10"/>
-      <c r="H73" s="10"/>
-      <c r="I73" s="10"/>
-      <c r="J73" s="10"/>
-      <c r="K73" s="10"/>
-      <c r="L73" s="10"/>
-      <c r="M73" s="10"/>
-      <c r="N73" s="10"/>
-      <c r="O73" s="10"/>
-      <c r="P73" s="10"/>
-      <c r="Q73" s="10"/>
-      <c r="R73" s="10"/>
-      <c r="S73" s="10"/>
-      <c r="T73" s="10"/>
-      <c r="U73" s="10"/>
-      <c r="V73" s="10"/>
-      <c r="W73" s="10"/>
-      <c r="X73" s="10"/>
-      <c r="Y73" s="10"/>
-      <c r="Z73" s="10"/>
+        <v>256</v>
+      </c>
+      <c r="C73" s="20" t="s">
+        <v>257</v>
+      </c>
+      <c r="D73" s="20" t="s">
+        <v>258</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" s="2"/>
+      <c r="G73" s="2"/>
+      <c r="H73" s="2"/>
+      <c r="I73" s="2"/>
+      <c r="J73" s="2"/>
+      <c r="K73" s="2"/>
+      <c r="L73" s="2"/>
+      <c r="M73" s="2"/>
+      <c r="N73" s="2"/>
+      <c r="O73" s="2"/>
+      <c r="P73" s="2"/>
+      <c r="Q73" s="2"/>
+      <c r="R73" s="2"/>
+      <c r="S73" s="2"/>
+      <c r="T73" s="2"/>
+      <c r="U73" s="2"/>
+      <c r="V73" s="2"/>
+      <c r="W73" s="2"/>
+      <c r="X73" s="2"/>
+      <c r="Y73" s="2"/>
+      <c r="Z73" s="2"/>
     </row>
     <row r="74">
-      <c r="A74" s="2"/>
-      <c r="B74" s="2"/>
+      <c r="A74" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="B74" s="20" t="s">
+        <v>247</v>
+      </c>
       <c r="C74" s="2"/>
       <c r="D74" s="2"/>
       <c r="E74" s="2"/>
@@ -30535,6 +30583,34 @@
       <c r="Y1022" s="2"/>
       <c r="Z1022" s="2"/>
     </row>
+    <row r="1023">
+      <c r="A1023" s="2"/>
+      <c r="B1023" s="2"/>
+      <c r="C1023" s="2"/>
+      <c r="D1023" s="2"/>
+      <c r="E1023" s="2"/>
+      <c r="F1023" s="2"/>
+      <c r="G1023" s="2"/>
+      <c r="H1023" s="2"/>
+      <c r="I1023" s="2"/>
+      <c r="J1023" s="2"/>
+      <c r="K1023" s="2"/>
+      <c r="L1023" s="2"/>
+      <c r="M1023" s="2"/>
+      <c r="N1023" s="2"/>
+      <c r="O1023" s="2"/>
+      <c r="P1023" s="2"/>
+      <c r="Q1023" s="2"/>
+      <c r="R1023" s="2"/>
+      <c r="S1023" s="2"/>
+      <c r="T1023" s="2"/>
+      <c r="U1023" s="2"/>
+      <c r="V1023" s="2"/>
+      <c r="W1023" s="2"/>
+      <c r="X1023" s="2"/>
+      <c r="Y1023" s="2"/>
+      <c r="Z1023" s="2"/>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="C28:D28"/>
@@ -30553,17 +30629,17 @@
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.75"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>10</v>
+      <c r="A1" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>3</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -30589,227 +30665,227 @@
       <c r="Z1" s="2"/>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>18</v>
+      <c r="A2" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>21</v>
+      <c r="A3" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>25</v>
+      <c r="A4" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>28</v>
+      <c r="A5" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>31</v>
+      <c r="A6" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>34</v>
+      <c r="A7" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>37</v>
+      <c r="A8" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" s="7" t="s">
+      <c r="A9" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="11" t="s">
         <v>39</v>
       </c>
+      <c r="C9" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>43</v>
+      <c r="A10" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>46</v>
+      <c r="A11" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>49</v>
+      <c r="A12" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>52</v>
+      <c r="A13" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>55</v>
+      <c r="A14" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>58</v>
+      <c r="A15" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C16" s="7" t="s">
+      <c r="A16" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="D16" s="7" t="s">
-        <v>61</v>
+      <c r="B16" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>63</v>
+      <c r="A17" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -30825,82 +30901,82 @@
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.75"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-      <c r="W1" s="1"/>
-      <c r="X1" s="1"/>
-      <c r="Y1" s="1"/>
-      <c r="Z1" s="1"/>
+      <c r="A1" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
+      <c r="P1" s="4"/>
+      <c r="Q1" s="4"/>
+      <c r="R1" s="4"/>
+      <c r="S1" s="4"/>
+      <c r="T1" s="4"/>
+      <c r="U1" s="4"/>
+      <c r="V1" s="4"/>
+      <c r="W1" s="4"/>
+      <c r="X1" s="4"/>
+      <c r="Y1" s="4"/>
+      <c r="Z1" s="4"/>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="6">
+      <c r="A2" s="22" t="s">
+        <v>265</v>
+      </c>
+      <c r="B2" s="22" t="s">
+        <v>266</v>
+      </c>
+      <c r="C2" s="29">
         <v>43596.0</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1"/>
-      <c r="Q2" s="1"/>
-      <c r="R2" s="1"/>
-      <c r="S2" s="1"/>
-      <c r="T2" s="1"/>
-      <c r="U2" s="1"/>
-      <c r="V2" s="1"/>
-      <c r="W2" s="1"/>
-      <c r="X2" s="1"/>
-      <c r="Y2" s="1"/>
-      <c r="Z2" s="1"/>
+      <c r="D2" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
+      <c r="S2" s="4"/>
+      <c r="T2" s="4"/>
+      <c r="U2" s="4"/>
+      <c r="V2" s="4"/>
+      <c r="W2" s="4"/>
+      <c r="X2" s="4"/>
+      <c r="Y2" s="4"/>
+      <c r="Z2" s="4"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/forms/app/covid_education.xlsx
+++ b/forms/app/covid_education.xlsx
@@ -1,14 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\D-tree\config-dtree-newrepo\config-dtree\forms\app\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6620"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="survey" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="choices" sheetId="2" r:id="rId5"/>
-    <sheet state="visible" name="settings" sheetId="3" r:id="rId6"/>
+    <sheet name="survey" sheetId="1" r:id="rId1"/>
+    <sheet name="choices" sheetId="2" r:id="rId2"/>
+    <sheet name="settings" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="162913" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
@@ -989,58 +997,66 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
   </numFmts>
   <fonts count="10">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF1D1C1D"/>
       <name val="Slack-Lato"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Sans"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF3C4043"/>
       <name val="Roboto"/>
     </font>
     <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
-    <font/>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1056,7 +1072,13 @@
     </fill>
   </fills>
   <borders count="3">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -1067,6 +1089,8 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1081,127 +1105,69 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="33">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1391,22 +1357,25 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.75"/>
+  <dimension ref="A1:Z1033"/>
+  <sheetFormatPr defaultColWidth="14.40625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="2" width="23.57"/>
-    <col customWidth="1" min="3" max="3" width="286.71"/>
-    <col customWidth="1" min="4" max="26" width="23.57"/>
+    <col min="1" max="2" width="23.54296875" customWidth="1"/>
+    <col min="3" max="3" width="286.6796875" customWidth="1"/>
+    <col min="4" max="26" width="23.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:26" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1472,7 +1441,7 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:26" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>19</v>
       </c>
@@ -1509,7 +1478,7 @@
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
     </row>
-    <row r="3">
+    <row r="3" spans="1:26" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>19</v>
       </c>
@@ -1543,7 +1512,7 @@
       <c r="Y3" s="1"/>
       <c r="Z3" s="1"/>
     </row>
-    <row r="4">
+    <row r="4" spans="1:26" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>23</v>
       </c>
@@ -1577,7 +1546,7 @@
       <c r="Y4" s="1"/>
       <c r="Z4" s="1"/>
     </row>
-    <row r="5">
+    <row r="5" spans="1:26" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>23</v>
       </c>
@@ -1611,7 +1580,7 @@
       <c r="Y5" s="1"/>
       <c r="Z5" s="1"/>
     </row>
-    <row r="6">
+    <row r="6" spans="1:26" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>23</v>
       </c>
@@ -1645,7 +1614,7 @@
       <c r="Y6" s="1"/>
       <c r="Z6" s="1"/>
     </row>
-    <row r="7">
+    <row r="7" spans="1:26" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>29</v>
       </c>
@@ -1677,7 +1646,7 @@
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
     </row>
-    <row r="8">
+    <row r="8" spans="1:26" ht="15.75" customHeight="1">
       <c r="A8" s="6" t="s">
         <v>19</v>
       </c>
@@ -1711,7 +1680,7 @@
       <c r="Y8" s="1"/>
       <c r="Z8" s="1"/>
     </row>
-    <row r="9">
+    <row r="9" spans="1:26" ht="15.75" customHeight="1">
       <c r="A9" s="6" t="s">
         <v>31</v>
       </c>
@@ -1747,7 +1716,7 @@
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
     </row>
-    <row r="10">
+    <row r="10" spans="1:26" ht="15.75" customHeight="1">
       <c r="A10" s="6" t="s">
         <v>29</v>
       </c>
@@ -1779,7 +1748,7 @@
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
     </row>
-    <row r="11">
+    <row r="11" spans="1:26" ht="15.75" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>29</v>
       </c>
@@ -1811,7 +1780,7 @@
       <c r="Y11" s="1"/>
       <c r="Z11" s="1"/>
     </row>
-    <row r="12">
+    <row r="12" spans="1:26" ht="15.75" customHeight="1">
       <c r="A12" s="1" t="s">
         <v>34</v>
       </c>
@@ -1847,7 +1816,7 @@
       <c r="Y12" s="1"/>
       <c r="Z12" s="1"/>
     </row>
-    <row r="13">
+    <row r="13" spans="1:26" ht="15.75" customHeight="1">
       <c r="A13" s="1" t="s">
         <v>34</v>
       </c>
@@ -1883,7 +1852,7 @@
       <c r="Y13" s="1"/>
       <c r="Z13" s="1"/>
     </row>
-    <row r="14">
+    <row r="14" spans="1:26" ht="15.75" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>34</v>
       </c>
@@ -1919,7 +1888,7 @@
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
     </row>
-    <row r="15">
+    <row r="15" spans="1:26" ht="15.75" customHeight="1">
       <c r="A15" s="2" t="s">
         <v>42</v>
       </c>
@@ -1951,7 +1920,7 @@
       <c r="Y15" s="9"/>
       <c r="Z15" s="9"/>
     </row>
-    <row r="16">
+    <row r="16" spans="1:26" ht="15.75" customHeight="1">
       <c r="A16" s="2" t="s">
         <v>43</v>
       </c>
@@ -1983,7 +1952,7 @@
       <c r="Y16" s="9"/>
       <c r="Z16" s="9"/>
     </row>
-    <row r="17">
+    <row r="17" spans="1:26" ht="15.75" customHeight="1">
       <c r="A17" s="12" t="s">
         <v>44</v>
       </c>
@@ -2021,7 +1990,7 @@
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
     </row>
-    <row r="18">
+    <row r="18" spans="1:26" ht="15.75" customHeight="1">
       <c r="A18" s="12" t="s">
         <v>49</v>
       </c>
@@ -2057,7 +2026,7 @@
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
     </row>
-    <row r="19">
+    <row r="19" spans="1:26" ht="15.75" customHeight="1">
       <c r="A19" s="12" t="s">
         <v>53</v>
       </c>
@@ -2089,7 +2058,7 @@
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
     </row>
-    <row r="20">
+    <row r="20" spans="1:26" ht="15.75" customHeight="1">
       <c r="A20" s="2" t="s">
         <v>19</v>
       </c>
@@ -2126,7 +2095,7 @@
       <c r="Y20" s="1"/>
       <c r="Z20" s="1"/>
     </row>
-    <row r="21">
+    <row r="21" spans="1:26" ht="15.75" customHeight="1">
       <c r="A21" s="16" t="s">
         <v>49</v>
       </c>
@@ -2162,7 +2131,7 @@
       <c r="Y21" s="1"/>
       <c r="Z21" s="1"/>
     </row>
-    <row r="22">
+    <row r="22" spans="1:26" ht="14.75">
       <c r="A22" s="16" t="s">
         <v>61</v>
       </c>
@@ -2200,7 +2169,7 @@
       <c r="Y22" s="1"/>
       <c r="Z22" s="1"/>
     </row>
-    <row r="23">
+    <row r="23" spans="1:26" ht="13">
       <c r="A23" s="16" t="s">
         <v>49</v>
       </c>
@@ -2238,7 +2207,7 @@
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
     </row>
-    <row r="24">
+    <row r="24" spans="1:26" ht="13">
       <c r="A24" s="16" t="s">
         <v>61</v>
       </c>
@@ -2276,7 +2245,7 @@
       <c r="Y24" s="1"/>
       <c r="Z24" s="1"/>
     </row>
-    <row r="25">
+    <row r="25" spans="1:26" ht="13">
       <c r="A25" s="16" t="s">
         <v>49</v>
       </c>
@@ -2314,7 +2283,7 @@
       <c r="Y25" s="1"/>
       <c r="Z25" s="1"/>
     </row>
-    <row r="26">
+    <row r="26" spans="1:26" ht="13">
       <c r="A26" s="20" t="s">
         <v>49</v>
       </c>
@@ -2352,7 +2321,7 @@
       <c r="Y26" s="3"/>
       <c r="Z26" s="3"/>
     </row>
-    <row r="27">
+    <row r="27" spans="1:26" ht="13">
       <c r="A27" s="16" t="s">
         <v>80</v>
       </c>
@@ -2392,7 +2361,7 @@
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
     </row>
-    <row r="28">
+    <row r="28" spans="1:26" ht="13">
       <c r="A28" s="20" t="s">
         <v>49</v>
       </c>
@@ -2430,7 +2399,7 @@
       <c r="Y28" s="3"/>
       <c r="Z28" s="3"/>
     </row>
-    <row r="29">
+    <row r="29" spans="1:26" ht="13">
       <c r="A29" s="16" t="s">
         <v>87</v>
       </c>
@@ -2470,7 +2439,7 @@
       <c r="Y29" s="1"/>
       <c r="Z29" s="1"/>
     </row>
-    <row r="30">
+    <row r="30" spans="1:26" ht="13">
       <c r="A30" s="16" t="s">
         <v>29</v>
       </c>
@@ -2502,7 +2471,7 @@
       <c r="Y30" s="1"/>
       <c r="Z30" s="1"/>
     </row>
-    <row r="31">
+    <row r="31" spans="1:26" ht="13">
       <c r="A31" s="16" t="s">
         <v>44</v>
       </c>
@@ -2540,7 +2509,7 @@
       <c r="Y31" s="1"/>
       <c r="Z31" s="1"/>
     </row>
-    <row r="32">
+    <row r="32" spans="1:26" ht="14.25">
       <c r="A32" s="16" t="s">
         <v>49</v>
       </c>
@@ -2576,14 +2545,15 @@
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
     </row>
-    <row r="33">
+    <row r="33" spans="1:26" ht="13">
       <c r="A33" s="16" t="s">
         <v>53</v>
       </c>
       <c r="B33" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C33" s="2"/>
+      <c r="C33" s="31"/>
+      <c r="D33" s="32"/>
       <c r="E33" s="2"/>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
@@ -2607,7 +2577,7 @@
       <c r="Y33" s="1"/>
       <c r="Z33" s="1"/>
     </row>
-    <row r="34">
+    <row r="34" spans="1:26" ht="13">
       <c r="A34" s="16" t="s">
         <v>19</v>
       </c>
@@ -2645,7 +2615,7 @@
       <c r="Y34" s="1"/>
       <c r="Z34" s="1"/>
     </row>
-    <row r="35">
+    <row r="35" spans="1:26" ht="13">
       <c r="A35" s="16" t="s">
         <v>49</v>
       </c>
@@ -2681,14 +2651,14 @@
       <c r="Y35" s="1"/>
       <c r="Z35" s="1"/>
     </row>
-    <row r="36">
+    <row r="36" spans="1:26" ht="13">
       <c r="A36" s="16" t="s">
         <v>29</v>
       </c>
       <c r="B36" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="C36" s="2"/>
+      <c r="C36" s="16"/>
       <c r="E36" s="2"/>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
@@ -2712,7 +2682,7 @@
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
     </row>
-    <row r="37">
+    <row r="37" spans="1:26" ht="13">
       <c r="A37" s="16" t="s">
         <v>44</v>
       </c>
@@ -2750,7 +2720,7 @@
       <c r="Y37" s="1"/>
       <c r="Z37" s="1"/>
     </row>
-    <row r="38">
+    <row r="38" spans="1:26" ht="13">
       <c r="A38" s="16" t="s">
         <v>49</v>
       </c>
@@ -2786,7 +2756,7 @@
       <c r="Y38" s="1"/>
       <c r="Z38" s="1"/>
     </row>
-    <row r="39">
+    <row r="39" spans="1:26" ht="13">
       <c r="A39" s="16" t="s">
         <v>61</v>
       </c>
@@ -2824,7 +2794,7 @@
       <c r="Y39" s="1"/>
       <c r="Z39" s="1"/>
     </row>
-    <row r="40">
+    <row r="40" spans="1:26" ht="13">
       <c r="A40" s="16" t="s">
         <v>49</v>
       </c>
@@ -2862,14 +2832,15 @@
       <c r="Y40" s="1"/>
       <c r="Z40" s="1"/>
     </row>
-    <row r="41">
+    <row r="41" spans="1:26" ht="13">
       <c r="A41" s="16" t="s">
         <v>49</v>
       </c>
       <c r="B41" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="C41" s="2"/>
+      <c r="C41" s="31"/>
+      <c r="D41" s="32"/>
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
@@ -2897,7 +2868,7 @@
       <c r="Y41" s="1"/>
       <c r="Z41" s="1"/>
     </row>
-    <row r="42">
+    <row r="42" spans="1:26" ht="13">
       <c r="A42" s="19" t="s">
         <v>49</v>
       </c>
@@ -2933,7 +2904,7 @@
       <c r="Y42" s="1"/>
       <c r="Z42" s="1"/>
     </row>
-    <row r="43">
+    <row r="43" spans="1:26" ht="13">
       <c r="A43" s="19" t="s">
         <v>49</v>
       </c>
@@ -2969,7 +2940,7 @@
       <c r="Y43" s="1"/>
       <c r="Z43" s="1"/>
     </row>
-    <row r="44">
+    <row r="44" spans="1:26" ht="13">
       <c r="A44" s="19" t="s">
         <v>29</v>
       </c>
@@ -3001,7 +2972,7 @@
       <c r="Y44" s="1"/>
       <c r="Z44" s="1"/>
     </row>
-    <row r="45">
+    <row r="45" spans="1:26" ht="13">
       <c r="A45" s="19" t="s">
         <v>44</v>
       </c>
@@ -3039,7 +3010,7 @@
       <c r="Y45" s="1"/>
       <c r="Z45" s="1"/>
     </row>
-    <row r="46">
+    <row r="46" spans="1:26" ht="13">
       <c r="A46" s="19" t="s">
         <v>49</v>
       </c>
@@ -3075,7 +3046,7 @@
       <c r="Y46" s="1"/>
       <c r="Z46" s="1"/>
     </row>
-    <row r="47">
+    <row r="47" spans="1:26" ht="13">
       <c r="A47" s="19" t="s">
         <v>49</v>
       </c>
@@ -3111,7 +3082,7 @@
       <c r="Y47" s="1"/>
       <c r="Z47" s="1"/>
     </row>
-    <row r="48">
+    <row r="48" spans="1:26" ht="13">
       <c r="A48" s="19" t="s">
         <v>49</v>
       </c>
@@ -3147,7 +3118,7 @@
       <c r="Y48" s="1"/>
       <c r="Z48" s="1"/>
     </row>
-    <row r="49">
+    <row r="49" spans="1:26" ht="13">
       <c r="A49" s="19" t="s">
         <v>49</v>
       </c>
@@ -3183,7 +3154,7 @@
       <c r="Y49" s="1"/>
       <c r="Z49" s="1"/>
     </row>
-    <row r="50">
+    <row r="50" spans="1:26" ht="13">
       <c r="A50" s="19" t="s">
         <v>49</v>
       </c>
@@ -3219,7 +3190,7 @@
       <c r="Y50" s="1"/>
       <c r="Z50" s="1"/>
     </row>
-    <row r="51">
+    <row r="51" spans="1:26" ht="13">
       <c r="A51" s="19" t="s">
         <v>49</v>
       </c>
@@ -3255,7 +3226,7 @@
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
     </row>
-    <row r="52">
+    <row r="52" spans="1:26" ht="13">
       <c r="A52" s="19" t="s">
         <v>49</v>
       </c>
@@ -3291,7 +3262,7 @@
       <c r="Y52" s="1"/>
       <c r="Z52" s="1"/>
     </row>
-    <row r="53">
+    <row r="53" spans="1:26" ht="13">
       <c r="A53" s="19" t="s">
         <v>29</v>
       </c>
@@ -3323,7 +3294,7 @@
       <c r="Y53" s="1"/>
       <c r="Z53" s="1"/>
     </row>
-    <row r="54">
+    <row r="54" spans="1:26" ht="13">
       <c r="A54" s="19" t="s">
         <v>19</v>
       </c>
@@ -3360,7 +3331,7 @@
       <c r="Y54" s="1"/>
       <c r="Z54" s="1"/>
     </row>
-    <row r="55">
+    <row r="55" spans="1:26" ht="13">
       <c r="A55" s="19" t="s">
         <v>49</v>
       </c>
@@ -3396,7 +3367,7 @@
       <c r="Y55" s="1"/>
       <c r="Z55" s="1"/>
     </row>
-    <row r="56">
+    <row r="56" spans="1:26" ht="13">
       <c r="A56" s="19" t="s">
         <v>53</v>
       </c>
@@ -3428,7 +3399,7 @@
       <c r="Y56" s="1"/>
       <c r="Z56" s="1"/>
     </row>
-    <row r="57">
+    <row r="57" spans="1:26" ht="13">
       <c r="A57" s="19" t="s">
         <v>44</v>
       </c>
@@ -3466,7 +3437,7 @@
       <c r="Y57" s="1"/>
       <c r="Z57" s="1"/>
     </row>
-    <row r="58">
+    <row r="58" spans="1:26" ht="13">
       <c r="A58" s="19" t="s">
         <v>150</v>
       </c>
@@ -3504,7 +3475,7 @@
       <c r="Y58" s="1"/>
       <c r="Z58" s="1"/>
     </row>
-    <row r="59">
+    <row r="59" spans="1:26" ht="13">
       <c r="A59" s="19" t="s">
         <v>61</v>
       </c>
@@ -3544,7 +3515,7 @@
       <c r="Y59" s="1"/>
       <c r="Z59" s="1"/>
     </row>
-    <row r="60">
+    <row r="60" spans="1:26" ht="13">
       <c r="A60" s="19" t="s">
         <v>49</v>
       </c>
@@ -3582,7 +3553,7 @@
       <c r="Y60" s="1"/>
       <c r="Z60" s="1"/>
     </row>
-    <row r="61">
+    <row r="61" spans="1:26" ht="13">
       <c r="A61" s="19" t="s">
         <v>49</v>
       </c>
@@ -3618,7 +3589,7 @@
       <c r="Y61" s="1"/>
       <c r="Z61" s="1"/>
     </row>
-    <row r="62">
+    <row r="62" spans="1:26" ht="13">
       <c r="A62" s="19" t="s">
         <v>49</v>
       </c>
@@ -3658,7 +3629,7 @@
       <c r="Y62" s="1"/>
       <c r="Z62" s="1"/>
     </row>
-    <row r="63">
+    <row r="63" spans="1:26" ht="13">
       <c r="A63" s="19" t="s">
         <v>49</v>
       </c>
@@ -3698,7 +3669,7 @@
       <c r="Y63" s="1"/>
       <c r="Z63" s="1"/>
     </row>
-    <row r="64">
+    <row r="64" spans="1:26" ht="13">
       <c r="A64" s="19" t="s">
         <v>49</v>
       </c>
@@ -3738,7 +3709,7 @@
       <c r="Y64" s="1"/>
       <c r="Z64" s="1"/>
     </row>
-    <row r="65">
+    <row r="65" spans="1:26" ht="13">
       <c r="A65" s="19" t="s">
         <v>49</v>
       </c>
@@ -3778,7 +3749,7 @@
       <c r="Y65" s="1"/>
       <c r="Z65" s="1"/>
     </row>
-    <row r="66">
+    <row r="66" spans="1:26" ht="13">
       <c r="A66" s="19" t="s">
         <v>49</v>
       </c>
@@ -3818,7 +3789,7 @@
       <c r="Y66" s="1"/>
       <c r="Z66" s="1"/>
     </row>
-    <row r="67">
+    <row r="67" spans="1:26" ht="13">
       <c r="A67" s="19" t="s">
         <v>49</v>
       </c>
@@ -3858,7 +3829,7 @@
       <c r="Y67" s="1"/>
       <c r="Z67" s="1"/>
     </row>
-    <row r="68">
+    <row r="68" spans="1:26" ht="13">
       <c r="A68" s="19" t="s">
         <v>49</v>
       </c>
@@ -3894,7 +3865,7 @@
       <c r="Y68" s="1"/>
       <c r="Z68" s="1"/>
     </row>
-    <row r="69">
+    <row r="69" spans="1:26" ht="13">
       <c r="A69" s="19" t="s">
         <v>53</v>
       </c>
@@ -3926,7 +3897,7 @@
       <c r="Y69" s="1"/>
       <c r="Z69" s="1"/>
     </row>
-    <row r="70">
+    <row r="70" spans="1:26" ht="13">
       <c r="A70" s="19" t="s">
         <v>19</v>
       </c>
@@ -3964,7 +3935,7 @@
       <c r="Y70" s="1"/>
       <c r="Z70" s="1"/>
     </row>
-    <row r="71">
+    <row r="71" spans="1:26" ht="13">
       <c r="A71" s="19" t="s">
         <v>61</v>
       </c>
@@ -4002,7 +3973,7 @@
       <c r="Y71" s="1"/>
       <c r="Z71" s="1"/>
     </row>
-    <row r="72">
+    <row r="72" spans="1:26" ht="13">
       <c r="A72" s="7" t="s">
         <v>197</v>
       </c>
@@ -4040,7 +4011,7 @@
       <c r="Y72" s="1"/>
       <c r="Z72" s="1"/>
     </row>
-    <row r="73">
+    <row r="73" spans="1:26" ht="13">
       <c r="A73" s="7" t="s">
         <v>49</v>
       </c>
@@ -4076,7 +4047,7 @@
       <c r="Y73" s="1"/>
       <c r="Z73" s="1"/>
     </row>
-    <row r="74">
+    <row r="74" spans="1:26" ht="13">
       <c r="A74" s="7" t="s">
         <v>29</v>
       </c>
@@ -4108,7 +4079,7 @@
       <c r="Y74" s="1"/>
       <c r="Z74" s="1"/>
     </row>
-    <row r="75">
+    <row r="75" spans="1:26" ht="13">
       <c r="A75" s="19" t="s">
         <v>19</v>
       </c>
@@ -4146,7 +4117,7 @@
       <c r="Y75" s="1"/>
       <c r="Z75" s="1"/>
     </row>
-    <row r="76">
+    <row r="76" spans="1:26" ht="13">
       <c r="A76" s="19" t="s">
         <v>207</v>
       </c>
@@ -4190,7 +4161,7 @@
       <c r="Y76" s="1"/>
       <c r="Z76" s="1"/>
     </row>
-    <row r="77">
+    <row r="77" spans="1:26" ht="13">
       <c r="A77" s="19" t="s">
         <v>61</v>
       </c>
@@ -4228,7 +4199,7 @@
       <c r="Y77" s="1"/>
       <c r="Z77" s="1"/>
     </row>
-    <row r="78">
+    <row r="78" spans="1:26" ht="13">
       <c r="A78" s="19" t="s">
         <v>49</v>
       </c>
@@ -4264,7 +4235,7 @@
       <c r="Y78" s="1"/>
       <c r="Z78" s="1"/>
     </row>
-    <row r="79">
+    <row r="79" spans="1:26" ht="13">
       <c r="A79" s="19" t="s">
         <v>53</v>
       </c>
@@ -4296,7 +4267,7 @@
       <c r="Y79" s="1"/>
       <c r="Z79" s="1"/>
     </row>
-    <row r="80">
+    <row r="80" spans="1:26" ht="13">
       <c r="A80" s="19" t="s">
         <v>44</v>
       </c>
@@ -4334,7 +4305,7 @@
       <c r="Y80" s="1"/>
       <c r="Z80" s="1"/>
     </row>
-    <row r="81">
+    <row r="81" spans="1:26" ht="13">
       <c r="A81" s="19" t="s">
         <v>150</v>
       </c>
@@ -4372,7 +4343,7 @@
       <c r="Y81" s="1"/>
       <c r="Z81" s="1"/>
     </row>
-    <row r="82">
+    <row r="82" spans="1:26" ht="13">
       <c r="A82" s="19" t="s">
         <v>61</v>
       </c>
@@ -4410,7 +4381,7 @@
       <c r="Y82" s="1"/>
       <c r="Z82" s="1"/>
     </row>
-    <row r="83">
+    <row r="83" spans="1:26" ht="13">
       <c r="A83" s="19" t="s">
         <v>49</v>
       </c>
@@ -4446,7 +4417,7 @@
       <c r="Y83" s="1"/>
       <c r="Z83" s="1"/>
     </row>
-    <row r="84">
+    <row r="84" spans="1:26" ht="13">
       <c r="A84" s="19" t="s">
         <v>53</v>
       </c>
@@ -4478,7 +4449,7 @@
       <c r="Y84" s="1"/>
       <c r="Z84" s="1"/>
     </row>
-    <row r="85">
+    <row r="85" spans="1:26" ht="13">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -4506,7 +4477,7 @@
       <c r="Y85" s="1"/>
       <c r="Z85" s="1"/>
     </row>
-    <row r="86">
+    <row r="86" spans="1:26" ht="13">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -4534,7 +4505,7 @@
       <c r="Y86" s="1"/>
       <c r="Z86" s="1"/>
     </row>
-    <row r="87">
+    <row r="87" spans="1:26" ht="13">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -4562,7 +4533,7 @@
       <c r="Y87" s="1"/>
       <c r="Z87" s="1"/>
     </row>
-    <row r="88">
+    <row r="88" spans="1:26" ht="13">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -4590,7 +4561,7 @@
       <c r="Y88" s="1"/>
       <c r="Z88" s="1"/>
     </row>
-    <row r="89">
+    <row r="89" spans="1:26" ht="13">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -4618,7 +4589,7 @@
       <c r="Y89" s="1"/>
       <c r="Z89" s="1"/>
     </row>
-    <row r="90">
+    <row r="90" spans="1:26" ht="13">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -4646,7 +4617,7 @@
       <c r="Y90" s="1"/>
       <c r="Z90" s="1"/>
     </row>
-    <row r="91">
+    <row r="91" spans="1:26" ht="13">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -4674,7 +4645,7 @@
       <c r="Y91" s="1"/>
       <c r="Z91" s="1"/>
     </row>
-    <row r="92">
+    <row r="92" spans="1:26" ht="13">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -4702,7 +4673,7 @@
       <c r="Y92" s="1"/>
       <c r="Z92" s="1"/>
     </row>
-    <row r="93">
+    <row r="93" spans="1:26" ht="13">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -4730,7 +4701,7 @@
       <c r="Y93" s="1"/>
       <c r="Z93" s="1"/>
     </row>
-    <row r="94">
+    <row r="94" spans="1:26" ht="13">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -4758,7 +4729,7 @@
       <c r="Y94" s="1"/>
       <c r="Z94" s="1"/>
     </row>
-    <row r="95">
+    <row r="95" spans="1:26" ht="13">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -4786,7 +4757,7 @@
       <c r="Y95" s="1"/>
       <c r="Z95" s="1"/>
     </row>
-    <row r="96">
+    <row r="96" spans="1:26" ht="13">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -4814,7 +4785,7 @@
       <c r="Y96" s="1"/>
       <c r="Z96" s="1"/>
     </row>
-    <row r="97">
+    <row r="97" spans="1:26" ht="13">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -4842,7 +4813,7 @@
       <c r="Y97" s="1"/>
       <c r="Z97" s="1"/>
     </row>
-    <row r="98">
+    <row r="98" spans="1:26" ht="13">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -4870,7 +4841,7 @@
       <c r="Y98" s="1"/>
       <c r="Z98" s="1"/>
     </row>
-    <row r="99">
+    <row r="99" spans="1:26" ht="13">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -4898,7 +4869,7 @@
       <c r="Y99" s="1"/>
       <c r="Z99" s="1"/>
     </row>
-    <row r="100">
+    <row r="100" spans="1:26" ht="13">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -4926,7 +4897,7 @@
       <c r="Y100" s="1"/>
       <c r="Z100" s="1"/>
     </row>
-    <row r="101">
+    <row r="101" spans="1:26" ht="13">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -4954,7 +4925,7 @@
       <c r="Y101" s="1"/>
       <c r="Z101" s="1"/>
     </row>
-    <row r="102">
+    <row r="102" spans="1:26" ht="13">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -4982,7 +4953,7 @@
       <c r="Y102" s="1"/>
       <c r="Z102" s="1"/>
     </row>
-    <row r="103">
+    <row r="103" spans="1:26" ht="13">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -5010,7 +4981,7 @@
       <c r="Y103" s="1"/>
       <c r="Z103" s="1"/>
     </row>
-    <row r="104">
+    <row r="104" spans="1:26" ht="13">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -5038,7 +5009,7 @@
       <c r="Y104" s="1"/>
       <c r="Z104" s="1"/>
     </row>
-    <row r="105">
+    <row r="105" spans="1:26" ht="13">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -5066,7 +5037,7 @@
       <c r="Y105" s="1"/>
       <c r="Z105" s="1"/>
     </row>
-    <row r="106">
+    <row r="106" spans="1:26" ht="13">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -5094,7 +5065,7 @@
       <c r="Y106" s="1"/>
       <c r="Z106" s="1"/>
     </row>
-    <row r="107">
+    <row r="107" spans="1:26" ht="13">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -5122,7 +5093,7 @@
       <c r="Y107" s="1"/>
       <c r="Z107" s="1"/>
     </row>
-    <row r="108">
+    <row r="108" spans="1:26" ht="13">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -5150,7 +5121,7 @@
       <c r="Y108" s="1"/>
       <c r="Z108" s="1"/>
     </row>
-    <row r="109">
+    <row r="109" spans="1:26" ht="13">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -5178,7 +5149,7 @@
       <c r="Y109" s="1"/>
       <c r="Z109" s="1"/>
     </row>
-    <row r="110">
+    <row r="110" spans="1:26" ht="13">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -5206,7 +5177,7 @@
       <c r="Y110" s="1"/>
       <c r="Z110" s="1"/>
     </row>
-    <row r="111">
+    <row r="111" spans="1:26" ht="13">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -5234,7 +5205,7 @@
       <c r="Y111" s="1"/>
       <c r="Z111" s="1"/>
     </row>
-    <row r="112">
+    <row r="112" spans="1:26" ht="13">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -5262,7 +5233,7 @@
       <c r="Y112" s="1"/>
       <c r="Z112" s="1"/>
     </row>
-    <row r="113">
+    <row r="113" spans="1:26" ht="13">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -5290,7 +5261,7 @@
       <c r="Y113" s="1"/>
       <c r="Z113" s="1"/>
     </row>
-    <row r="114">
+    <row r="114" spans="1:26" ht="13">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -5318,7 +5289,7 @@
       <c r="Y114" s="1"/>
       <c r="Z114" s="1"/>
     </row>
-    <row r="115">
+    <row r="115" spans="1:26" ht="13">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -5346,7 +5317,7 @@
       <c r="Y115" s="1"/>
       <c r="Z115" s="1"/>
     </row>
-    <row r="116">
+    <row r="116" spans="1:26" ht="13">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -5374,7 +5345,7 @@
       <c r="Y116" s="1"/>
       <c r="Z116" s="1"/>
     </row>
-    <row r="117">
+    <row r="117" spans="1:26" ht="13">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -5402,7 +5373,7 @@
       <c r="Y117" s="1"/>
       <c r="Z117" s="1"/>
     </row>
-    <row r="118">
+    <row r="118" spans="1:26" ht="13">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -5430,7 +5401,7 @@
       <c r="Y118" s="1"/>
       <c r="Z118" s="1"/>
     </row>
-    <row r="119">
+    <row r="119" spans="1:26" ht="13">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -5458,7 +5429,7 @@
       <c r="Y119" s="1"/>
       <c r="Z119" s="1"/>
     </row>
-    <row r="120">
+    <row r="120" spans="1:26" ht="13">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -5486,7 +5457,7 @@
       <c r="Y120" s="1"/>
       <c r="Z120" s="1"/>
     </row>
-    <row r="121">
+    <row r="121" spans="1:26" ht="13">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -5514,7 +5485,7 @@
       <c r="Y121" s="1"/>
       <c r="Z121" s="1"/>
     </row>
-    <row r="122">
+    <row r="122" spans="1:26" ht="13">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -5542,7 +5513,7 @@
       <c r="Y122" s="1"/>
       <c r="Z122" s="1"/>
     </row>
-    <row r="123">
+    <row r="123" spans="1:26" ht="13">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -5570,7 +5541,7 @@
       <c r="Y123" s="1"/>
       <c r="Z123" s="1"/>
     </row>
-    <row r="124">
+    <row r="124" spans="1:26" ht="13">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -5598,7 +5569,7 @@
       <c r="Y124" s="1"/>
       <c r="Z124" s="1"/>
     </row>
-    <row r="125">
+    <row r="125" spans="1:26" ht="13">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -5626,7 +5597,7 @@
       <c r="Y125" s="1"/>
       <c r="Z125" s="1"/>
     </row>
-    <row r="126">
+    <row r="126" spans="1:26" ht="13">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -5654,7 +5625,7 @@
       <c r="Y126" s="1"/>
       <c r="Z126" s="1"/>
     </row>
-    <row r="127">
+    <row r="127" spans="1:26" ht="13">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -5682,7 +5653,7 @@
       <c r="Y127" s="1"/>
       <c r="Z127" s="1"/>
     </row>
-    <row r="128">
+    <row r="128" spans="1:26" ht="13">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -5710,7 +5681,7 @@
       <c r="Y128" s="1"/>
       <c r="Z128" s="1"/>
     </row>
-    <row r="129">
+    <row r="129" spans="1:26" ht="13">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -5738,7 +5709,7 @@
       <c r="Y129" s="1"/>
       <c r="Z129" s="1"/>
     </row>
-    <row r="130">
+    <row r="130" spans="1:26" ht="13">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -5766,7 +5737,7 @@
       <c r="Y130" s="1"/>
       <c r="Z130" s="1"/>
     </row>
-    <row r="131">
+    <row r="131" spans="1:26" ht="13">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -5794,7 +5765,7 @@
       <c r="Y131" s="1"/>
       <c r="Z131" s="1"/>
     </row>
-    <row r="132">
+    <row r="132" spans="1:26" ht="13">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -5822,7 +5793,7 @@
       <c r="Y132" s="1"/>
       <c r="Z132" s="1"/>
     </row>
-    <row r="133">
+    <row r="133" spans="1:26" ht="13">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -5850,7 +5821,7 @@
       <c r="Y133" s="1"/>
       <c r="Z133" s="1"/>
     </row>
-    <row r="134">
+    <row r="134" spans="1:26" ht="13">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -5878,7 +5849,7 @@
       <c r="Y134" s="1"/>
       <c r="Z134" s="1"/>
     </row>
-    <row r="135">
+    <row r="135" spans="1:26" ht="13">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -5906,7 +5877,7 @@
       <c r="Y135" s="1"/>
       <c r="Z135" s="1"/>
     </row>
-    <row r="136">
+    <row r="136" spans="1:26" ht="13">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -5934,7 +5905,7 @@
       <c r="Y136" s="1"/>
       <c r="Z136" s="1"/>
     </row>
-    <row r="137">
+    <row r="137" spans="1:26" ht="13">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -5962,7 +5933,7 @@
       <c r="Y137" s="1"/>
       <c r="Z137" s="1"/>
     </row>
-    <row r="138">
+    <row r="138" spans="1:26" ht="13">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -5990,7 +5961,7 @@
       <c r="Y138" s="1"/>
       <c r="Z138" s="1"/>
     </row>
-    <row r="139">
+    <row r="139" spans="1:26" ht="13">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -6018,7 +5989,7 @@
       <c r="Y139" s="1"/>
       <c r="Z139" s="1"/>
     </row>
-    <row r="140">
+    <row r="140" spans="1:26" ht="13">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -6046,7 +6017,7 @@
       <c r="Y140" s="1"/>
       <c r="Z140" s="1"/>
     </row>
-    <row r="141">
+    <row r="141" spans="1:26" ht="13">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -6074,7 +6045,7 @@
       <c r="Y141" s="1"/>
       <c r="Z141" s="1"/>
     </row>
-    <row r="142">
+    <row r="142" spans="1:26" ht="13">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
@@ -6102,7 +6073,7 @@
       <c r="Y142" s="1"/>
       <c r="Z142" s="1"/>
     </row>
-    <row r="143">
+    <row r="143" spans="1:26" ht="13">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
@@ -6130,7 +6101,7 @@
       <c r="Y143" s="1"/>
       <c r="Z143" s="1"/>
     </row>
-    <row r="144">
+    <row r="144" spans="1:26" ht="13">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -6158,7 +6129,7 @@
       <c r="Y144" s="1"/>
       <c r="Z144" s="1"/>
     </row>
-    <row r="145">
+    <row r="145" spans="1:26" ht="13">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
@@ -6186,7 +6157,7 @@
       <c r="Y145" s="1"/>
       <c r="Z145" s="1"/>
     </row>
-    <row r="146">
+    <row r="146" spans="1:26" ht="13">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
@@ -6214,7 +6185,7 @@
       <c r="Y146" s="1"/>
       <c r="Z146" s="1"/>
     </row>
-    <row r="147">
+    <row r="147" spans="1:26" ht="13">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
@@ -6242,7 +6213,7 @@
       <c r="Y147" s="1"/>
       <c r="Z147" s="1"/>
     </row>
-    <row r="148">
+    <row r="148" spans="1:26" ht="13">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
@@ -6270,7 +6241,7 @@
       <c r="Y148" s="1"/>
       <c r="Z148" s="1"/>
     </row>
-    <row r="149">
+    <row r="149" spans="1:26" ht="13">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -6298,7 +6269,7 @@
       <c r="Y149" s="1"/>
       <c r="Z149" s="1"/>
     </row>
-    <row r="150">
+    <row r="150" spans="1:26" ht="13">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -6326,7 +6297,7 @@
       <c r="Y150" s="1"/>
       <c r="Z150" s="1"/>
     </row>
-    <row r="151">
+    <row r="151" spans="1:26" ht="13">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -6354,7 +6325,7 @@
       <c r="Y151" s="1"/>
       <c r="Z151" s="1"/>
     </row>
-    <row r="152">
+    <row r="152" spans="1:26" ht="13">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -6382,7 +6353,7 @@
       <c r="Y152" s="1"/>
       <c r="Z152" s="1"/>
     </row>
-    <row r="153">
+    <row r="153" spans="1:26" ht="13">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -6410,7 +6381,7 @@
       <c r="Y153" s="1"/>
       <c r="Z153" s="1"/>
     </row>
-    <row r="154">
+    <row r="154" spans="1:26" ht="13">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -6438,7 +6409,7 @@
       <c r="Y154" s="1"/>
       <c r="Z154" s="1"/>
     </row>
-    <row r="155">
+    <row r="155" spans="1:26" ht="13">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -6466,7 +6437,7 @@
       <c r="Y155" s="1"/>
       <c r="Z155" s="1"/>
     </row>
-    <row r="156">
+    <row r="156" spans="1:26" ht="13">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -6494,7 +6465,7 @@
       <c r="Y156" s="1"/>
       <c r="Z156" s="1"/>
     </row>
-    <row r="157">
+    <row r="157" spans="1:26" ht="13">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -6522,7 +6493,7 @@
       <c r="Y157" s="1"/>
       <c r="Z157" s="1"/>
     </row>
-    <row r="158">
+    <row r="158" spans="1:26" ht="13">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -6550,7 +6521,7 @@
       <c r="Y158" s="1"/>
       <c r="Z158" s="1"/>
     </row>
-    <row r="159">
+    <row r="159" spans="1:26" ht="13">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
@@ -6578,7 +6549,7 @@
       <c r="Y159" s="1"/>
       <c r="Z159" s="1"/>
     </row>
-    <row r="160">
+    <row r="160" spans="1:26" ht="13">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -6606,7 +6577,7 @@
       <c r="Y160" s="1"/>
       <c r="Z160" s="1"/>
     </row>
-    <row r="161">
+    <row r="161" spans="1:26" ht="13">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -6634,7 +6605,7 @@
       <c r="Y161" s="1"/>
       <c r="Z161" s="1"/>
     </row>
-    <row r="162">
+    <row r="162" spans="1:26" ht="13">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -6662,7 +6633,7 @@
       <c r="Y162" s="1"/>
       <c r="Z162" s="1"/>
     </row>
-    <row r="163">
+    <row r="163" spans="1:26" ht="13">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -6690,7 +6661,7 @@
       <c r="Y163" s="1"/>
       <c r="Z163" s="1"/>
     </row>
-    <row r="164">
+    <row r="164" spans="1:26" ht="13">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -6718,7 +6689,7 @@
       <c r="Y164" s="1"/>
       <c r="Z164" s="1"/>
     </row>
-    <row r="165">
+    <row r="165" spans="1:26" ht="13">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
@@ -6746,7 +6717,7 @@
       <c r="Y165" s="1"/>
       <c r="Z165" s="1"/>
     </row>
-    <row r="166">
+    <row r="166" spans="1:26" ht="13">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
@@ -6774,7 +6745,7 @@
       <c r="Y166" s="1"/>
       <c r="Z166" s="1"/>
     </row>
-    <row r="167">
+    <row r="167" spans="1:26" ht="13">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
@@ -6802,7 +6773,7 @@
       <c r="Y167" s="1"/>
       <c r="Z167" s="1"/>
     </row>
-    <row r="168">
+    <row r="168" spans="1:26" ht="13">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
@@ -6830,7 +6801,7 @@
       <c r="Y168" s="1"/>
       <c r="Z168" s="1"/>
     </row>
-    <row r="169">
+    <row r="169" spans="1:26" ht="13">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -6858,7 +6829,7 @@
       <c r="Y169" s="1"/>
       <c r="Z169" s="1"/>
     </row>
-    <row r="170">
+    <row r="170" spans="1:26" ht="13">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
@@ -6886,7 +6857,7 @@
       <c r="Y170" s="1"/>
       <c r="Z170" s="1"/>
     </row>
-    <row r="171">
+    <row r="171" spans="1:26" ht="13">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
@@ -6914,7 +6885,7 @@
       <c r="Y171" s="1"/>
       <c r="Z171" s="1"/>
     </row>
-    <row r="172">
+    <row r="172" spans="1:26" ht="13">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
@@ -6942,7 +6913,7 @@
       <c r="Y172" s="1"/>
       <c r="Z172" s="1"/>
     </row>
-    <row r="173">
+    <row r="173" spans="1:26" ht="13">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
@@ -6970,7 +6941,7 @@
       <c r="Y173" s="1"/>
       <c r="Z173" s="1"/>
     </row>
-    <row r="174">
+    <row r="174" spans="1:26" ht="13">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -6998,7 +6969,7 @@
       <c r="Y174" s="1"/>
       <c r="Z174" s="1"/>
     </row>
-    <row r="175">
+    <row r="175" spans="1:26" ht="13">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
@@ -7026,7 +6997,7 @@
       <c r="Y175" s="1"/>
       <c r="Z175" s="1"/>
     </row>
-    <row r="176">
+    <row r="176" spans="1:26" ht="13">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -7054,7 +7025,7 @@
       <c r="Y176" s="1"/>
       <c r="Z176" s="1"/>
     </row>
-    <row r="177">
+    <row r="177" spans="1:26" ht="13">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
@@ -7082,7 +7053,7 @@
       <c r="Y177" s="1"/>
       <c r="Z177" s="1"/>
     </row>
-    <row r="178">
+    <row r="178" spans="1:26" ht="13">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -7110,7 +7081,7 @@
       <c r="Y178" s="1"/>
       <c r="Z178" s="1"/>
     </row>
-    <row r="179">
+    <row r="179" spans="1:26" ht="13">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
@@ -7138,7 +7109,7 @@
       <c r="Y179" s="1"/>
       <c r="Z179" s="1"/>
     </row>
-    <row r="180">
+    <row r="180" spans="1:26" ht="13">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -7166,7 +7137,7 @@
       <c r="Y180" s="1"/>
       <c r="Z180" s="1"/>
     </row>
-    <row r="181">
+    <row r="181" spans="1:26" ht="13">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
@@ -7194,7 +7165,7 @@
       <c r="Y181" s="1"/>
       <c r="Z181" s="1"/>
     </row>
-    <row r="182">
+    <row r="182" spans="1:26" ht="13">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -7222,7 +7193,7 @@
       <c r="Y182" s="1"/>
       <c r="Z182" s="1"/>
     </row>
-    <row r="183">
+    <row r="183" spans="1:26" ht="13">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
@@ -7250,7 +7221,7 @@
       <c r="Y183" s="1"/>
       <c r="Z183" s="1"/>
     </row>
-    <row r="184">
+    <row r="184" spans="1:26" ht="13">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -7278,7 +7249,7 @@
       <c r="Y184" s="1"/>
       <c r="Z184" s="1"/>
     </row>
-    <row r="185">
+    <row r="185" spans="1:26" ht="13">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -7306,7 +7277,7 @@
       <c r="Y185" s="1"/>
       <c r="Z185" s="1"/>
     </row>
-    <row r="186">
+    <row r="186" spans="1:26" ht="13">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
@@ -7334,7 +7305,7 @@
       <c r="Y186" s="1"/>
       <c r="Z186" s="1"/>
     </row>
-    <row r="187">
+    <row r="187" spans="1:26" ht="13">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
@@ -7362,7 +7333,7 @@
       <c r="Y187" s="1"/>
       <c r="Z187" s="1"/>
     </row>
-    <row r="188">
+    <row r="188" spans="1:26" ht="13">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
@@ -7390,7 +7361,7 @@
       <c r="Y188" s="1"/>
       <c r="Z188" s="1"/>
     </row>
-    <row r="189">
+    <row r="189" spans="1:26" ht="13">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -7418,7 +7389,7 @@
       <c r="Y189" s="1"/>
       <c r="Z189" s="1"/>
     </row>
-    <row r="190">
+    <row r="190" spans="1:26" ht="13">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
@@ -7446,7 +7417,7 @@
       <c r="Y190" s="1"/>
       <c r="Z190" s="1"/>
     </row>
-    <row r="191">
+    <row r="191" spans="1:26" ht="13">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -7474,7 +7445,7 @@
       <c r="Y191" s="1"/>
       <c r="Z191" s="1"/>
     </row>
-    <row r="192">
+    <row r="192" spans="1:26" ht="13">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
@@ -7502,7 +7473,7 @@
       <c r="Y192" s="1"/>
       <c r="Z192" s="1"/>
     </row>
-    <row r="193">
+    <row r="193" spans="1:26" ht="13">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
@@ -7530,7 +7501,7 @@
       <c r="Y193" s="1"/>
       <c r="Z193" s="1"/>
     </row>
-    <row r="194">
+    <row r="194" spans="1:26" ht="13">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
@@ -7558,7 +7529,7 @@
       <c r="Y194" s="1"/>
       <c r="Z194" s="1"/>
     </row>
-    <row r="195">
+    <row r="195" spans="1:26" ht="13">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
@@ -7586,7 +7557,7 @@
       <c r="Y195" s="1"/>
       <c r="Z195" s="1"/>
     </row>
-    <row r="196">
+    <row r="196" spans="1:26" ht="13">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
@@ -7614,7 +7585,7 @@
       <c r="Y196" s="1"/>
       <c r="Z196" s="1"/>
     </row>
-    <row r="197">
+    <row r="197" spans="1:26" ht="13">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
@@ -7642,7 +7613,7 @@
       <c r="Y197" s="1"/>
       <c r="Z197" s="1"/>
     </row>
-    <row r="198">
+    <row r="198" spans="1:26" ht="13">
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
@@ -7670,7 +7641,7 @@
       <c r="Y198" s="1"/>
       <c r="Z198" s="1"/>
     </row>
-    <row r="199">
+    <row r="199" spans="1:26" ht="13">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
@@ -7698,7 +7669,7 @@
       <c r="Y199" s="1"/>
       <c r="Z199" s="1"/>
     </row>
-    <row r="200">
+    <row r="200" spans="1:26" ht="13">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
@@ -7726,7 +7697,7 @@
       <c r="Y200" s="1"/>
       <c r="Z200" s="1"/>
     </row>
-    <row r="201">
+    <row r="201" spans="1:26" ht="13">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
@@ -7754,7 +7725,7 @@
       <c r="Y201" s="1"/>
       <c r="Z201" s="1"/>
     </row>
-    <row r="202">
+    <row r="202" spans="1:26" ht="13">
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
@@ -7782,7 +7753,7 @@
       <c r="Y202" s="1"/>
       <c r="Z202" s="1"/>
     </row>
-    <row r="203">
+    <row r="203" spans="1:26" ht="13">
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
@@ -7810,7 +7781,7 @@
       <c r="Y203" s="1"/>
       <c r="Z203" s="1"/>
     </row>
-    <row r="204">
+    <row r="204" spans="1:26" ht="13">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
@@ -7838,7 +7809,7 @@
       <c r="Y204" s="1"/>
       <c r="Z204" s="1"/>
     </row>
-    <row r="205">
+    <row r="205" spans="1:26" ht="13">
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
@@ -7866,7 +7837,7 @@
       <c r="Y205" s="1"/>
       <c r="Z205" s="1"/>
     </row>
-    <row r="206">
+    <row r="206" spans="1:26" ht="13">
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
@@ -7894,7 +7865,7 @@
       <c r="Y206" s="1"/>
       <c r="Z206" s="1"/>
     </row>
-    <row r="207">
+    <row r="207" spans="1:26" ht="13">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
@@ -7922,7 +7893,7 @@
       <c r="Y207" s="1"/>
       <c r="Z207" s="1"/>
     </row>
-    <row r="208">
+    <row r="208" spans="1:26" ht="13">
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
@@ -7950,7 +7921,7 @@
       <c r="Y208" s="1"/>
       <c r="Z208" s="1"/>
     </row>
-    <row r="209">
+    <row r="209" spans="1:26" ht="13">
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
@@ -7978,7 +7949,7 @@
       <c r="Y209" s="1"/>
       <c r="Z209" s="1"/>
     </row>
-    <row r="210">
+    <row r="210" spans="1:26" ht="13">
       <c r="A210" s="1"/>
       <c r="B210" s="1"/>
       <c r="C210" s="1"/>
@@ -8006,7 +7977,7 @@
       <c r="Y210" s="1"/>
       <c r="Z210" s="1"/>
     </row>
-    <row r="211">
+    <row r="211" spans="1:26" ht="13">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
@@ -8034,7 +8005,7 @@
       <c r="Y211" s="1"/>
       <c r="Z211" s="1"/>
     </row>
-    <row r="212">
+    <row r="212" spans="1:26" ht="13">
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
       <c r="C212" s="1"/>
@@ -8062,7 +8033,7 @@
       <c r="Y212" s="1"/>
       <c r="Z212" s="1"/>
     </row>
-    <row r="213">
+    <row r="213" spans="1:26" ht="13">
       <c r="A213" s="1"/>
       <c r="B213" s="1"/>
       <c r="C213" s="1"/>
@@ -8090,7 +8061,7 @@
       <c r="Y213" s="1"/>
       <c r="Z213" s="1"/>
     </row>
-    <row r="214">
+    <row r="214" spans="1:26" ht="13">
       <c r="A214" s="1"/>
       <c r="B214" s="1"/>
       <c r="C214" s="1"/>
@@ -8118,7 +8089,7 @@
       <c r="Y214" s="1"/>
       <c r="Z214" s="1"/>
     </row>
-    <row r="215">
+    <row r="215" spans="1:26" ht="13">
       <c r="A215" s="1"/>
       <c r="B215" s="1"/>
       <c r="C215" s="1"/>
@@ -8146,7 +8117,7 @@
       <c r="Y215" s="1"/>
       <c r="Z215" s="1"/>
     </row>
-    <row r="216">
+    <row r="216" spans="1:26" ht="13">
       <c r="A216" s="1"/>
       <c r="B216" s="1"/>
       <c r="C216" s="1"/>
@@ -8174,7 +8145,7 @@
       <c r="Y216" s="1"/>
       <c r="Z216" s="1"/>
     </row>
-    <row r="217">
+    <row r="217" spans="1:26" ht="13">
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
       <c r="C217" s="1"/>
@@ -8202,7 +8173,7 @@
       <c r="Y217" s="1"/>
       <c r="Z217" s="1"/>
     </row>
-    <row r="218">
+    <row r="218" spans="1:26" ht="13">
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="1"/>
@@ -8230,7 +8201,7 @@
       <c r="Y218" s="1"/>
       <c r="Z218" s="1"/>
     </row>
-    <row r="219">
+    <row r="219" spans="1:26" ht="13">
       <c r="A219" s="1"/>
       <c r="B219" s="1"/>
       <c r="C219" s="1"/>
@@ -8258,7 +8229,7 @@
       <c r="Y219" s="1"/>
       <c r="Z219" s="1"/>
     </row>
-    <row r="220">
+    <row r="220" spans="1:26" ht="13">
       <c r="A220" s="1"/>
       <c r="B220" s="1"/>
       <c r="C220" s="1"/>
@@ -8286,7 +8257,7 @@
       <c r="Y220" s="1"/>
       <c r="Z220" s="1"/>
     </row>
-    <row r="221">
+    <row r="221" spans="1:26" ht="13">
       <c r="A221" s="1"/>
       <c r="B221" s="1"/>
       <c r="C221" s="1"/>
@@ -8314,7 +8285,7 @@
       <c r="Y221" s="1"/>
       <c r="Z221" s="1"/>
     </row>
-    <row r="222">
+    <row r="222" spans="1:26" ht="13">
       <c r="A222" s="1"/>
       <c r="B222" s="1"/>
       <c r="C222" s="1"/>
@@ -8342,7 +8313,7 @@
       <c r="Y222" s="1"/>
       <c r="Z222" s="1"/>
     </row>
-    <row r="223">
+    <row r="223" spans="1:26" ht="13">
       <c r="A223" s="1"/>
       <c r="B223" s="1"/>
       <c r="C223" s="1"/>
@@ -8370,7 +8341,7 @@
       <c r="Y223" s="1"/>
       <c r="Z223" s="1"/>
     </row>
-    <row r="224">
+    <row r="224" spans="1:26" ht="13">
       <c r="A224" s="1"/>
       <c r="B224" s="1"/>
       <c r="C224" s="1"/>
@@ -8398,7 +8369,7 @@
       <c r="Y224" s="1"/>
       <c r="Z224" s="1"/>
     </row>
-    <row r="225">
+    <row r="225" spans="1:26" ht="13">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="C225" s="1"/>
@@ -8426,7 +8397,7 @@
       <c r="Y225" s="1"/>
       <c r="Z225" s="1"/>
     </row>
-    <row r="226">
+    <row r="226" spans="1:26" ht="13">
       <c r="A226" s="1"/>
       <c r="B226" s="1"/>
       <c r="C226" s="1"/>
@@ -8454,7 +8425,7 @@
       <c r="Y226" s="1"/>
       <c r="Z226" s="1"/>
     </row>
-    <row r="227">
+    <row r="227" spans="1:26" ht="13">
       <c r="A227" s="1"/>
       <c r="B227" s="1"/>
       <c r="C227" s="1"/>
@@ -8482,7 +8453,7 @@
       <c r="Y227" s="1"/>
       <c r="Z227" s="1"/>
     </row>
-    <row r="228">
+    <row r="228" spans="1:26" ht="13">
       <c r="A228" s="1"/>
       <c r="B228" s="1"/>
       <c r="C228" s="1"/>
@@ -8510,7 +8481,7 @@
       <c r="Y228" s="1"/>
       <c r="Z228" s="1"/>
     </row>
-    <row r="229">
+    <row r="229" spans="1:26" ht="13">
       <c r="A229" s="1"/>
       <c r="B229" s="1"/>
       <c r="C229" s="1"/>
@@ -8538,7 +8509,7 @@
       <c r="Y229" s="1"/>
       <c r="Z229" s="1"/>
     </row>
-    <row r="230">
+    <row r="230" spans="1:26" ht="13">
       <c r="A230" s="1"/>
       <c r="B230" s="1"/>
       <c r="C230" s="1"/>
@@ -8566,7 +8537,7 @@
       <c r="Y230" s="1"/>
       <c r="Z230" s="1"/>
     </row>
-    <row r="231">
+    <row r="231" spans="1:26" ht="13">
       <c r="A231" s="1"/>
       <c r="B231" s="1"/>
       <c r="C231" s="1"/>
@@ -8594,7 +8565,7 @@
       <c r="Y231" s="1"/>
       <c r="Z231" s="1"/>
     </row>
-    <row r="232">
+    <row r="232" spans="1:26" ht="13">
       <c r="A232" s="1"/>
       <c r="B232" s="1"/>
       <c r="C232" s="1"/>
@@ -8622,7 +8593,7 @@
       <c r="Y232" s="1"/>
       <c r="Z232" s="1"/>
     </row>
-    <row r="233">
+    <row r="233" spans="1:26" ht="13">
       <c r="A233" s="1"/>
       <c r="B233" s="1"/>
       <c r="C233" s="1"/>
@@ -8650,7 +8621,7 @@
       <c r="Y233" s="1"/>
       <c r="Z233" s="1"/>
     </row>
-    <row r="234">
+    <row r="234" spans="1:26" ht="13">
       <c r="A234" s="1"/>
       <c r="B234" s="1"/>
       <c r="C234" s="1"/>
@@ -8678,7 +8649,7 @@
       <c r="Y234" s="1"/>
       <c r="Z234" s="1"/>
     </row>
-    <row r="235">
+    <row r="235" spans="1:26" ht="13">
       <c r="A235" s="1"/>
       <c r="B235" s="1"/>
       <c r="C235" s="1"/>
@@ -8706,7 +8677,7 @@
       <c r="Y235" s="1"/>
       <c r="Z235" s="1"/>
     </row>
-    <row r="236">
+    <row r="236" spans="1:26" ht="13">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
@@ -8734,7 +8705,7 @@
       <c r="Y236" s="1"/>
       <c r="Z236" s="1"/>
     </row>
-    <row r="237">
+    <row r="237" spans="1:26" ht="13">
       <c r="A237" s="1"/>
       <c r="B237" s="1"/>
       <c r="C237" s="1"/>
@@ -8762,7 +8733,7 @@
       <c r="Y237" s="1"/>
       <c r="Z237" s="1"/>
     </row>
-    <row r="238">
+    <row r="238" spans="1:26" ht="13">
       <c r="A238" s="1"/>
       <c r="B238" s="1"/>
       <c r="C238" s="1"/>
@@ -8790,7 +8761,7 @@
       <c r="Y238" s="1"/>
       <c r="Z238" s="1"/>
     </row>
-    <row r="239">
+    <row r="239" spans="1:26" ht="13">
       <c r="A239" s="1"/>
       <c r="B239" s="1"/>
       <c r="C239" s="1"/>
@@ -8818,7 +8789,7 @@
       <c r="Y239" s="1"/>
       <c r="Z239" s="1"/>
     </row>
-    <row r="240">
+    <row r="240" spans="1:26" ht="13">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
@@ -8846,7 +8817,7 @@
       <c r="Y240" s="1"/>
       <c r="Z240" s="1"/>
     </row>
-    <row r="241">
+    <row r="241" spans="1:26" ht="13">
       <c r="A241" s="1"/>
       <c r="B241" s="1"/>
       <c r="C241" s="1"/>
@@ -8874,7 +8845,7 @@
       <c r="Y241" s="1"/>
       <c r="Z241" s="1"/>
     </row>
-    <row r="242">
+    <row r="242" spans="1:26" ht="13">
       <c r="A242" s="1"/>
       <c r="B242" s="1"/>
       <c r="C242" s="1"/>
@@ -8902,7 +8873,7 @@
       <c r="Y242" s="1"/>
       <c r="Z242" s="1"/>
     </row>
-    <row r="243">
+    <row r="243" spans="1:26" ht="13">
       <c r="A243" s="1"/>
       <c r="B243" s="1"/>
       <c r="C243" s="1"/>
@@ -8930,7 +8901,7 @@
       <c r="Y243" s="1"/>
       <c r="Z243" s="1"/>
     </row>
-    <row r="244">
+    <row r="244" spans="1:26" ht="13">
       <c r="A244" s="1"/>
       <c r="B244" s="1"/>
       <c r="C244" s="1"/>
@@ -8958,7 +8929,7 @@
       <c r="Y244" s="1"/>
       <c r="Z244" s="1"/>
     </row>
-    <row r="245">
+    <row r="245" spans="1:26" ht="13">
       <c r="A245" s="1"/>
       <c r="B245" s="1"/>
       <c r="C245" s="1"/>
@@ -8986,7 +8957,7 @@
       <c r="Y245" s="1"/>
       <c r="Z245" s="1"/>
     </row>
-    <row r="246">
+    <row r="246" spans="1:26" ht="13">
       <c r="A246" s="1"/>
       <c r="B246" s="1"/>
       <c r="C246" s="1"/>
@@ -9014,7 +8985,7 @@
       <c r="Y246" s="1"/>
       <c r="Z246" s="1"/>
     </row>
-    <row r="247">
+    <row r="247" spans="1:26" ht="13">
       <c r="A247" s="1"/>
       <c r="B247" s="1"/>
       <c r="C247" s="1"/>
@@ -9042,7 +9013,7 @@
       <c r="Y247" s="1"/>
       <c r="Z247" s="1"/>
     </row>
-    <row r="248">
+    <row r="248" spans="1:26" ht="13">
       <c r="A248" s="1"/>
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
@@ -9070,7 +9041,7 @@
       <c r="Y248" s="1"/>
       <c r="Z248" s="1"/>
     </row>
-    <row r="249">
+    <row r="249" spans="1:26" ht="13">
       <c r="A249" s="1"/>
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
@@ -9098,7 +9069,7 @@
       <c r="Y249" s="1"/>
       <c r="Z249" s="1"/>
     </row>
-    <row r="250">
+    <row r="250" spans="1:26" ht="13">
       <c r="A250" s="1"/>
       <c r="B250" s="1"/>
       <c r="C250" s="1"/>
@@ -9126,7 +9097,7 @@
       <c r="Y250" s="1"/>
       <c r="Z250" s="1"/>
     </row>
-    <row r="251">
+    <row r="251" spans="1:26" ht="13">
       <c r="A251" s="1"/>
       <c r="B251" s="1"/>
       <c r="C251" s="1"/>
@@ -9154,7 +9125,7 @@
       <c r="Y251" s="1"/>
       <c r="Z251" s="1"/>
     </row>
-    <row r="252">
+    <row r="252" spans="1:26" ht="13">
       <c r="A252" s="1"/>
       <c r="B252" s="1"/>
       <c r="C252" s="1"/>
@@ -9182,7 +9153,7 @@
       <c r="Y252" s="1"/>
       <c r="Z252" s="1"/>
     </row>
-    <row r="253">
+    <row r="253" spans="1:26" ht="13">
       <c r="A253" s="1"/>
       <c r="B253" s="1"/>
       <c r="C253" s="1"/>
@@ -9210,7 +9181,7 @@
       <c r="Y253" s="1"/>
       <c r="Z253" s="1"/>
     </row>
-    <row r="254">
+    <row r="254" spans="1:26" ht="13">
       <c r="A254" s="1"/>
       <c r="B254" s="1"/>
       <c r="C254" s="1"/>
@@ -9238,7 +9209,7 @@
       <c r="Y254" s="1"/>
       <c r="Z254" s="1"/>
     </row>
-    <row r="255">
+    <row r="255" spans="1:26" ht="13">
       <c r="A255" s="1"/>
       <c r="B255" s="1"/>
       <c r="C255" s="1"/>
@@ -9266,7 +9237,7 @@
       <c r="Y255" s="1"/>
       <c r="Z255" s="1"/>
     </row>
-    <row r="256">
+    <row r="256" spans="1:26" ht="13">
       <c r="A256" s="1"/>
       <c r="B256" s="1"/>
       <c r="C256" s="1"/>
@@ -9294,7 +9265,7 @@
       <c r="Y256" s="1"/>
       <c r="Z256" s="1"/>
     </row>
-    <row r="257">
+    <row r="257" spans="1:26" ht="13">
       <c r="A257" s="1"/>
       <c r="B257" s="1"/>
       <c r="C257" s="1"/>
@@ -9322,7 +9293,7 @@
       <c r="Y257" s="1"/>
       <c r="Z257" s="1"/>
     </row>
-    <row r="258">
+    <row r="258" spans="1:26" ht="13">
       <c r="A258" s="1"/>
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
@@ -9350,7 +9321,7 @@
       <c r="Y258" s="1"/>
       <c r="Z258" s="1"/>
     </row>
-    <row r="259">
+    <row r="259" spans="1:26" ht="13">
       <c r="A259" s="1"/>
       <c r="B259" s="1"/>
       <c r="C259" s="1"/>
@@ -9378,7 +9349,7 @@
       <c r="Y259" s="1"/>
       <c r="Z259" s="1"/>
     </row>
-    <row r="260">
+    <row r="260" spans="1:26" ht="13">
       <c r="A260" s="1"/>
       <c r="B260" s="1"/>
       <c r="C260" s="1"/>
@@ -9406,7 +9377,7 @@
       <c r="Y260" s="1"/>
       <c r="Z260" s="1"/>
     </row>
-    <row r="261">
+    <row r="261" spans="1:26" ht="13">
       <c r="A261" s="1"/>
       <c r="B261" s="1"/>
       <c r="C261" s="1"/>
@@ -9434,7 +9405,7 @@
       <c r="Y261" s="1"/>
       <c r="Z261" s="1"/>
     </row>
-    <row r="262">
+    <row r="262" spans="1:26" ht="13">
       <c r="A262" s="1"/>
       <c r="B262" s="1"/>
       <c r="C262" s="1"/>
@@ -9462,7 +9433,7 @@
       <c r="Y262" s="1"/>
       <c r="Z262" s="1"/>
     </row>
-    <row r="263">
+    <row r="263" spans="1:26" ht="13">
       <c r="A263" s="1"/>
       <c r="B263" s="1"/>
       <c r="C263" s="1"/>
@@ -9490,7 +9461,7 @@
       <c r="Y263" s="1"/>
       <c r="Z263" s="1"/>
     </row>
-    <row r="264">
+    <row r="264" spans="1:26" ht="13">
       <c r="A264" s="1"/>
       <c r="B264" s="1"/>
       <c r="C264" s="1"/>
@@ -9518,7 +9489,7 @@
       <c r="Y264" s="1"/>
       <c r="Z264" s="1"/>
     </row>
-    <row r="265">
+    <row r="265" spans="1:26" ht="13">
       <c r="A265" s="1"/>
       <c r="B265" s="1"/>
       <c r="C265" s="1"/>
@@ -9546,7 +9517,7 @@
       <c r="Y265" s="1"/>
       <c r="Z265" s="1"/>
     </row>
-    <row r="266">
+    <row r="266" spans="1:26" ht="13">
       <c r="A266" s="1"/>
       <c r="B266" s="1"/>
       <c r="C266" s="1"/>
@@ -9574,7 +9545,7 @@
       <c r="Y266" s="1"/>
       <c r="Z266" s="1"/>
     </row>
-    <row r="267">
+    <row r="267" spans="1:26" ht="13">
       <c r="A267" s="1"/>
       <c r="B267" s="1"/>
       <c r="C267" s="1"/>
@@ -9602,7 +9573,7 @@
       <c r="Y267" s="1"/>
       <c r="Z267" s="1"/>
     </row>
-    <row r="268">
+    <row r="268" spans="1:26" ht="13">
       <c r="A268" s="1"/>
       <c r="B268" s="1"/>
       <c r="C268" s="1"/>
@@ -9630,7 +9601,7 @@
       <c r="Y268" s="1"/>
       <c r="Z268" s="1"/>
     </row>
-    <row r="269">
+    <row r="269" spans="1:26" ht="13">
       <c r="A269" s="1"/>
       <c r="B269" s="1"/>
       <c r="C269" s="1"/>
@@ -9658,7 +9629,7 @@
       <c r="Y269" s="1"/>
       <c r="Z269" s="1"/>
     </row>
-    <row r="270">
+    <row r="270" spans="1:26" ht="13">
       <c r="A270" s="1"/>
       <c r="B270" s="1"/>
       <c r="C270" s="1"/>
@@ -9686,7 +9657,7 @@
       <c r="Y270" s="1"/>
       <c r="Z270" s="1"/>
     </row>
-    <row r="271">
+    <row r="271" spans="1:26" ht="13">
       <c r="A271" s="1"/>
       <c r="B271" s="1"/>
       <c r="C271" s="1"/>
@@ -9714,7 +9685,7 @@
       <c r="Y271" s="1"/>
       <c r="Z271" s="1"/>
     </row>
-    <row r="272">
+    <row r="272" spans="1:26" ht="13">
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
@@ -9742,7 +9713,7 @@
       <c r="Y272" s="1"/>
       <c r="Z272" s="1"/>
     </row>
-    <row r="273">
+    <row r="273" spans="1:26" ht="13">
       <c r="A273" s="1"/>
       <c r="B273" s="1"/>
       <c r="C273" s="1"/>
@@ -9770,7 +9741,7 @@
       <c r="Y273" s="1"/>
       <c r="Z273" s="1"/>
     </row>
-    <row r="274">
+    <row r="274" spans="1:26" ht="13">
       <c r="A274" s="1"/>
       <c r="B274" s="1"/>
       <c r="C274" s="1"/>
@@ -9798,7 +9769,7 @@
       <c r="Y274" s="1"/>
       <c r="Z274" s="1"/>
     </row>
-    <row r="275">
+    <row r="275" spans="1:26" ht="13">
       <c r="A275" s="1"/>
       <c r="B275" s="1"/>
       <c r="C275" s="1"/>
@@ -9826,7 +9797,7 @@
       <c r="Y275" s="1"/>
       <c r="Z275" s="1"/>
     </row>
-    <row r="276">
+    <row r="276" spans="1:26" ht="13">
       <c r="A276" s="1"/>
       <c r="B276" s="1"/>
       <c r="C276" s="1"/>
@@ -9854,7 +9825,7 @@
       <c r="Y276" s="1"/>
       <c r="Z276" s="1"/>
     </row>
-    <row r="277">
+    <row r="277" spans="1:26" ht="13">
       <c r="A277" s="1"/>
       <c r="B277" s="1"/>
       <c r="C277" s="1"/>
@@ -9882,7 +9853,7 @@
       <c r="Y277" s="1"/>
       <c r="Z277" s="1"/>
     </row>
-    <row r="278">
+    <row r="278" spans="1:26" ht="13">
       <c r="A278" s="1"/>
       <c r="B278" s="1"/>
       <c r="C278" s="1"/>
@@ -9910,7 +9881,7 @@
       <c r="Y278" s="1"/>
       <c r="Z278" s="1"/>
     </row>
-    <row r="279">
+    <row r="279" spans="1:26" ht="13">
       <c r="A279" s="1"/>
       <c r="B279" s="1"/>
       <c r="C279" s="1"/>
@@ -9938,7 +9909,7 @@
       <c r="Y279" s="1"/>
       <c r="Z279" s="1"/>
     </row>
-    <row r="280">
+    <row r="280" spans="1:26" ht="13">
       <c r="A280" s="1"/>
       <c r="B280" s="1"/>
       <c r="C280" s="1"/>
@@ -9966,7 +9937,7 @@
       <c r="Y280" s="1"/>
       <c r="Z280" s="1"/>
     </row>
-    <row r="281">
+    <row r="281" spans="1:26" ht="13">
       <c r="A281" s="1"/>
       <c r="B281" s="1"/>
       <c r="C281" s="1"/>
@@ -9994,7 +9965,7 @@
       <c r="Y281" s="1"/>
       <c r="Z281" s="1"/>
     </row>
-    <row r="282">
+    <row r="282" spans="1:26" ht="13">
       <c r="A282" s="1"/>
       <c r="B282" s="1"/>
       <c r="C282" s="1"/>
@@ -10022,7 +9993,7 @@
       <c r="Y282" s="1"/>
       <c r="Z282" s="1"/>
     </row>
-    <row r="283">
+    <row r="283" spans="1:26" ht="13">
       <c r="A283" s="1"/>
       <c r="B283" s="1"/>
       <c r="C283" s="1"/>
@@ -10050,7 +10021,7 @@
       <c r="Y283" s="1"/>
       <c r="Z283" s="1"/>
     </row>
-    <row r="284">
+    <row r="284" spans="1:26" ht="13">
       <c r="A284" s="1"/>
       <c r="B284" s="1"/>
       <c r="C284" s="1"/>
@@ -10078,7 +10049,7 @@
       <c r="Y284" s="1"/>
       <c r="Z284" s="1"/>
     </row>
-    <row r="285">
+    <row r="285" spans="1:26" ht="13">
       <c r="A285" s="1"/>
       <c r="B285" s="1"/>
       <c r="C285" s="1"/>
@@ -10106,7 +10077,7 @@
       <c r="Y285" s="1"/>
       <c r="Z285" s="1"/>
     </row>
-    <row r="286">
+    <row r="286" spans="1:26" ht="13">
       <c r="A286" s="1"/>
       <c r="B286" s="1"/>
       <c r="C286" s="1"/>
@@ -10134,7 +10105,7 @@
       <c r="Y286" s="1"/>
       <c r="Z286" s="1"/>
     </row>
-    <row r="287">
+    <row r="287" spans="1:26" ht="13">
       <c r="A287" s="1"/>
       <c r="B287" s="1"/>
       <c r="C287" s="1"/>
@@ -10162,7 +10133,7 @@
       <c r="Y287" s="1"/>
       <c r="Z287" s="1"/>
     </row>
-    <row r="288">
+    <row r="288" spans="1:26" ht="13">
       <c r="A288" s="1"/>
       <c r="B288" s="1"/>
       <c r="C288" s="1"/>
@@ -10190,7 +10161,7 @@
       <c r="Y288" s="1"/>
       <c r="Z288" s="1"/>
     </row>
-    <row r="289">
+    <row r="289" spans="1:26" ht="13">
       <c r="A289" s="1"/>
       <c r="B289" s="1"/>
       <c r="C289" s="1"/>
@@ -10218,7 +10189,7 @@
       <c r="Y289" s="1"/>
       <c r="Z289" s="1"/>
     </row>
-    <row r="290">
+    <row r="290" spans="1:26" ht="13">
       <c r="A290" s="1"/>
       <c r="B290" s="1"/>
       <c r="C290" s="1"/>
@@ -10246,7 +10217,7 @@
       <c r="Y290" s="1"/>
       <c r="Z290" s="1"/>
     </row>
-    <row r="291">
+    <row r="291" spans="1:26" ht="13">
       <c r="A291" s="1"/>
       <c r="B291" s="1"/>
       <c r="C291" s="1"/>
@@ -10274,7 +10245,7 @@
       <c r="Y291" s="1"/>
       <c r="Z291" s="1"/>
     </row>
-    <row r="292">
+    <row r="292" spans="1:26" ht="13">
       <c r="A292" s="1"/>
       <c r="B292" s="1"/>
       <c r="C292" s="1"/>
@@ -10302,7 +10273,7 @@
       <c r="Y292" s="1"/>
       <c r="Z292" s="1"/>
     </row>
-    <row r="293">
+    <row r="293" spans="1:26" ht="13">
       <c r="A293" s="1"/>
       <c r="B293" s="1"/>
       <c r="C293" s="1"/>
@@ -10330,7 +10301,7 @@
       <c r="Y293" s="1"/>
       <c r="Z293" s="1"/>
     </row>
-    <row r="294">
+    <row r="294" spans="1:26" ht="13">
       <c r="A294" s="1"/>
       <c r="B294" s="1"/>
       <c r="C294" s="1"/>
@@ -10358,7 +10329,7 @@
       <c r="Y294" s="1"/>
       <c r="Z294" s="1"/>
     </row>
-    <row r="295">
+    <row r="295" spans="1:26" ht="13">
       <c r="A295" s="1"/>
       <c r="B295" s="1"/>
       <c r="C295" s="1"/>
@@ -10386,7 +10357,7 @@
       <c r="Y295" s="1"/>
       <c r="Z295" s="1"/>
     </row>
-    <row r="296">
+    <row r="296" spans="1:26" ht="13">
       <c r="A296" s="1"/>
       <c r="B296" s="1"/>
       <c r="C296" s="1"/>
@@ -10414,7 +10385,7 @@
       <c r="Y296" s="1"/>
       <c r="Z296" s="1"/>
     </row>
-    <row r="297">
+    <row r="297" spans="1:26" ht="13">
       <c r="A297" s="1"/>
       <c r="B297" s="1"/>
       <c r="C297" s="1"/>
@@ -10442,7 +10413,7 @@
       <c r="Y297" s="1"/>
       <c r="Z297" s="1"/>
     </row>
-    <row r="298">
+    <row r="298" spans="1:26" ht="13">
       <c r="A298" s="1"/>
       <c r="B298" s="1"/>
       <c r="C298" s="1"/>
@@ -10470,7 +10441,7 @@
       <c r="Y298" s="1"/>
       <c r="Z298" s="1"/>
     </row>
-    <row r="299">
+    <row r="299" spans="1:26" ht="13">
       <c r="A299" s="1"/>
       <c r="B299" s="1"/>
       <c r="C299" s="1"/>
@@ -10498,7 +10469,7 @@
       <c r="Y299" s="1"/>
       <c r="Z299" s="1"/>
     </row>
-    <row r="300">
+    <row r="300" spans="1:26" ht="13">
       <c r="A300" s="1"/>
       <c r="B300" s="1"/>
       <c r="C300" s="1"/>
@@ -10526,7 +10497,7 @@
       <c r="Y300" s="1"/>
       <c r="Z300" s="1"/>
     </row>
-    <row r="301">
+    <row r="301" spans="1:26" ht="13">
       <c r="A301" s="1"/>
       <c r="B301" s="1"/>
       <c r="C301" s="1"/>
@@ -10554,7 +10525,7 @@
       <c r="Y301" s="1"/>
       <c r="Z301" s="1"/>
     </row>
-    <row r="302">
+    <row r="302" spans="1:26" ht="13">
       <c r="A302" s="1"/>
       <c r="B302" s="1"/>
       <c r="C302" s="1"/>
@@ -10582,7 +10553,7 @@
       <c r="Y302" s="1"/>
       <c r="Z302" s="1"/>
     </row>
-    <row r="303">
+    <row r="303" spans="1:26" ht="13">
       <c r="A303" s="1"/>
       <c r="B303" s="1"/>
       <c r="C303" s="1"/>
@@ -10610,7 +10581,7 @@
       <c r="Y303" s="1"/>
       <c r="Z303" s="1"/>
     </row>
-    <row r="304">
+    <row r="304" spans="1:26" ht="13">
       <c r="A304" s="1"/>
       <c r="B304" s="1"/>
       <c r="C304" s="1"/>
@@ -10638,7 +10609,7 @@
       <c r="Y304" s="1"/>
       <c r="Z304" s="1"/>
     </row>
-    <row r="305">
+    <row r="305" spans="1:26" ht="13">
       <c r="A305" s="1"/>
       <c r="B305" s="1"/>
       <c r="C305" s="1"/>
@@ -10666,7 +10637,7 @@
       <c r="Y305" s="1"/>
       <c r="Z305" s="1"/>
     </row>
-    <row r="306">
+    <row r="306" spans="1:26" ht="13">
       <c r="A306" s="1"/>
       <c r="B306" s="1"/>
       <c r="C306" s="1"/>
@@ -10694,7 +10665,7 @@
       <c r="Y306" s="1"/>
       <c r="Z306" s="1"/>
     </row>
-    <row r="307">
+    <row r="307" spans="1:26" ht="13">
       <c r="A307" s="1"/>
       <c r="B307" s="1"/>
       <c r="C307" s="1"/>
@@ -10722,7 +10693,7 @@
       <c r="Y307" s="1"/>
       <c r="Z307" s="1"/>
     </row>
-    <row r="308">
+    <row r="308" spans="1:26" ht="13">
       <c r="A308" s="1"/>
       <c r="B308" s="1"/>
       <c r="C308" s="1"/>
@@ -10750,7 +10721,7 @@
       <c r="Y308" s="1"/>
       <c r="Z308" s="1"/>
     </row>
-    <row r="309">
+    <row r="309" spans="1:26" ht="13">
       <c r="A309" s="1"/>
       <c r="B309" s="1"/>
       <c r="C309" s="1"/>
@@ -10778,7 +10749,7 @@
       <c r="Y309" s="1"/>
       <c r="Z309" s="1"/>
     </row>
-    <row r="310">
+    <row r="310" spans="1:26" ht="13">
       <c r="A310" s="1"/>
       <c r="B310" s="1"/>
       <c r="C310" s="1"/>
@@ -10806,7 +10777,7 @@
       <c r="Y310" s="1"/>
       <c r="Z310" s="1"/>
     </row>
-    <row r="311">
+    <row r="311" spans="1:26" ht="13">
       <c r="A311" s="1"/>
       <c r="B311" s="1"/>
       <c r="C311" s="1"/>
@@ -10834,7 +10805,7 @@
       <c r="Y311" s="1"/>
       <c r="Z311" s="1"/>
     </row>
-    <row r="312">
+    <row r="312" spans="1:26" ht="13">
       <c r="A312" s="1"/>
       <c r="B312" s="1"/>
       <c r="C312" s="1"/>
@@ -10862,7 +10833,7 @@
       <c r="Y312" s="1"/>
       <c r="Z312" s="1"/>
     </row>
-    <row r="313">
+    <row r="313" spans="1:26" ht="13">
       <c r="A313" s="1"/>
       <c r="B313" s="1"/>
       <c r="C313" s="1"/>
@@ -10890,7 +10861,7 @@
       <c r="Y313" s="1"/>
       <c r="Z313" s="1"/>
     </row>
-    <row r="314">
+    <row r="314" spans="1:26" ht="13">
       <c r="A314" s="1"/>
       <c r="B314" s="1"/>
       <c r="C314" s="1"/>
@@ -10918,7 +10889,7 @@
       <c r="Y314" s="1"/>
       <c r="Z314" s="1"/>
     </row>
-    <row r="315">
+    <row r="315" spans="1:26" ht="13">
       <c r="A315" s="1"/>
       <c r="B315" s="1"/>
       <c r="C315" s="1"/>
@@ -10946,7 +10917,7 @@
       <c r="Y315" s="1"/>
       <c r="Z315" s="1"/>
     </row>
-    <row r="316">
+    <row r="316" spans="1:26" ht="13">
       <c r="A316" s="1"/>
       <c r="B316" s="1"/>
       <c r="C316" s="1"/>
@@ -10974,7 +10945,7 @@
       <c r="Y316" s="1"/>
       <c r="Z316" s="1"/>
     </row>
-    <row r="317">
+    <row r="317" spans="1:26" ht="13">
       <c r="A317" s="1"/>
       <c r="B317" s="1"/>
       <c r="C317" s="1"/>
@@ -11002,7 +10973,7 @@
       <c r="Y317" s="1"/>
       <c r="Z317" s="1"/>
     </row>
-    <row r="318">
+    <row r="318" spans="1:26" ht="13">
       <c r="A318" s="1"/>
       <c r="B318" s="1"/>
       <c r="C318" s="1"/>
@@ -11030,7 +11001,7 @@
       <c r="Y318" s="1"/>
       <c r="Z318" s="1"/>
     </row>
-    <row r="319">
+    <row r="319" spans="1:26" ht="13">
       <c r="A319" s="1"/>
       <c r="B319" s="1"/>
       <c r="C319" s="1"/>
@@ -11058,7 +11029,7 @@
       <c r="Y319" s="1"/>
       <c r="Z319" s="1"/>
     </row>
-    <row r="320">
+    <row r="320" spans="1:26" ht="13">
       <c r="A320" s="1"/>
       <c r="B320" s="1"/>
       <c r="C320" s="1"/>
@@ -11086,7 +11057,7 @@
       <c r="Y320" s="1"/>
       <c r="Z320" s="1"/>
     </row>
-    <row r="321">
+    <row r="321" spans="1:26" ht="13">
       <c r="A321" s="1"/>
       <c r="B321" s="1"/>
       <c r="C321" s="1"/>
@@ -11114,7 +11085,7 @@
       <c r="Y321" s="1"/>
       <c r="Z321" s="1"/>
     </row>
-    <row r="322">
+    <row r="322" spans="1:26" ht="13">
       <c r="A322" s="1"/>
       <c r="B322" s="1"/>
       <c r="C322" s="1"/>
@@ -11142,7 +11113,7 @@
       <c r="Y322" s="1"/>
       <c r="Z322" s="1"/>
     </row>
-    <row r="323">
+    <row r="323" spans="1:26" ht="13">
       <c r="A323" s="1"/>
       <c r="B323" s="1"/>
       <c r="C323" s="1"/>
@@ -11170,7 +11141,7 @@
       <c r="Y323" s="1"/>
       <c r="Z323" s="1"/>
     </row>
-    <row r="324">
+    <row r="324" spans="1:26" ht="13">
       <c r="A324" s="1"/>
       <c r="B324" s="1"/>
       <c r="C324" s="1"/>
@@ -11198,7 +11169,7 @@
       <c r="Y324" s="1"/>
       <c r="Z324" s="1"/>
     </row>
-    <row r="325">
+    <row r="325" spans="1:26" ht="13">
       <c r="A325" s="1"/>
       <c r="B325" s="1"/>
       <c r="C325" s="1"/>
@@ -11226,7 +11197,7 @@
       <c r="Y325" s="1"/>
       <c r="Z325" s="1"/>
     </row>
-    <row r="326">
+    <row r="326" spans="1:26" ht="13">
       <c r="A326" s="1"/>
       <c r="B326" s="1"/>
       <c r="C326" s="1"/>
@@ -11254,7 +11225,7 @@
       <c r="Y326" s="1"/>
       <c r="Z326" s="1"/>
     </row>
-    <row r="327">
+    <row r="327" spans="1:26" ht="13">
       <c r="A327" s="1"/>
       <c r="B327" s="1"/>
       <c r="C327" s="1"/>
@@ -11282,7 +11253,7 @@
       <c r="Y327" s="1"/>
       <c r="Z327" s="1"/>
     </row>
-    <row r="328">
+    <row r="328" spans="1:26" ht="13">
       <c r="A328" s="1"/>
       <c r="B328" s="1"/>
       <c r="C328" s="1"/>
@@ -11310,7 +11281,7 @@
       <c r="Y328" s="1"/>
       <c r="Z328" s="1"/>
     </row>
-    <row r="329">
+    <row r="329" spans="1:26" ht="13">
       <c r="A329" s="1"/>
       <c r="B329" s="1"/>
       <c r="C329" s="1"/>
@@ -11338,7 +11309,7 @@
       <c r="Y329" s="1"/>
       <c r="Z329" s="1"/>
     </row>
-    <row r="330">
+    <row r="330" spans="1:26" ht="13">
       <c r="A330" s="1"/>
       <c r="B330" s="1"/>
       <c r="C330" s="1"/>
@@ -11366,7 +11337,7 @@
       <c r="Y330" s="1"/>
       <c r="Z330" s="1"/>
     </row>
-    <row r="331">
+    <row r="331" spans="1:26" ht="13">
       <c r="A331" s="1"/>
       <c r="B331" s="1"/>
       <c r="C331" s="1"/>
@@ -11394,7 +11365,7 @@
       <c r="Y331" s="1"/>
       <c r="Z331" s="1"/>
     </row>
-    <row r="332">
+    <row r="332" spans="1:26" ht="13">
       <c r="A332" s="1"/>
       <c r="B332" s="1"/>
       <c r="C332" s="1"/>
@@ -11422,7 +11393,7 @@
       <c r="Y332" s="1"/>
       <c r="Z332" s="1"/>
     </row>
-    <row r="333">
+    <row r="333" spans="1:26" ht="13">
       <c r="A333" s="1"/>
       <c r="B333" s="1"/>
       <c r="C333" s="1"/>
@@ -11450,7 +11421,7 @@
       <c r="Y333" s="1"/>
       <c r="Z333" s="1"/>
     </row>
-    <row r="334">
+    <row r="334" spans="1:26" ht="13">
       <c r="A334" s="1"/>
       <c r="B334" s="1"/>
       <c r="C334" s="1"/>
@@ -11478,7 +11449,7 @@
       <c r="Y334" s="1"/>
       <c r="Z334" s="1"/>
     </row>
-    <row r="335">
+    <row r="335" spans="1:26" ht="13">
       <c r="A335" s="1"/>
       <c r="B335" s="1"/>
       <c r="C335" s="1"/>
@@ -11506,7 +11477,7 @@
       <c r="Y335" s="1"/>
       <c r="Z335" s="1"/>
     </row>
-    <row r="336">
+    <row r="336" spans="1:26" ht="13">
       <c r="A336" s="1"/>
       <c r="B336" s="1"/>
       <c r="C336" s="1"/>
@@ -11534,7 +11505,7 @@
       <c r="Y336" s="1"/>
       <c r="Z336" s="1"/>
     </row>
-    <row r="337">
+    <row r="337" spans="1:26" ht="13">
       <c r="A337" s="1"/>
       <c r="B337" s="1"/>
       <c r="C337" s="1"/>
@@ -11562,7 +11533,7 @@
       <c r="Y337" s="1"/>
       <c r="Z337" s="1"/>
     </row>
-    <row r="338">
+    <row r="338" spans="1:26" ht="13">
       <c r="A338" s="1"/>
       <c r="B338" s="1"/>
       <c r="C338" s="1"/>
@@ -11590,7 +11561,7 @@
       <c r="Y338" s="1"/>
       <c r="Z338" s="1"/>
     </row>
-    <row r="339">
+    <row r="339" spans="1:26" ht="13">
       <c r="A339" s="1"/>
       <c r="B339" s="1"/>
       <c r="C339" s="1"/>
@@ -11618,7 +11589,7 @@
       <c r="Y339" s="1"/>
       <c r="Z339" s="1"/>
     </row>
-    <row r="340">
+    <row r="340" spans="1:26" ht="13">
       <c r="A340" s="1"/>
       <c r="B340" s="1"/>
       <c r="C340" s="1"/>
@@ -11646,7 +11617,7 @@
       <c r="Y340" s="1"/>
       <c r="Z340" s="1"/>
     </row>
-    <row r="341">
+    <row r="341" spans="1:26" ht="13">
       <c r="A341" s="1"/>
       <c r="B341" s="1"/>
       <c r="C341" s="1"/>
@@ -11674,7 +11645,7 @@
       <c r="Y341" s="1"/>
       <c r="Z341" s="1"/>
     </row>
-    <row r="342">
+    <row r="342" spans="1:26" ht="13">
       <c r="A342" s="1"/>
       <c r="B342" s="1"/>
       <c r="C342" s="1"/>
@@ -11702,7 +11673,7 @@
       <c r="Y342" s="1"/>
       <c r="Z342" s="1"/>
     </row>
-    <row r="343">
+    <row r="343" spans="1:26" ht="13">
       <c r="A343" s="1"/>
       <c r="B343" s="1"/>
       <c r="C343" s="1"/>
@@ -11730,7 +11701,7 @@
       <c r="Y343" s="1"/>
       <c r="Z343" s="1"/>
     </row>
-    <row r="344">
+    <row r="344" spans="1:26" ht="13">
       <c r="A344" s="1"/>
       <c r="B344" s="1"/>
       <c r="C344" s="1"/>
@@ -11758,7 +11729,7 @@
       <c r="Y344" s="1"/>
       <c r="Z344" s="1"/>
     </row>
-    <row r="345">
+    <row r="345" spans="1:26" ht="13">
       <c r="A345" s="1"/>
       <c r="B345" s="1"/>
       <c r="C345" s="1"/>
@@ -11786,7 +11757,7 @@
       <c r="Y345" s="1"/>
       <c r="Z345" s="1"/>
     </row>
-    <row r="346">
+    <row r="346" spans="1:26" ht="13">
       <c r="A346" s="1"/>
       <c r="B346" s="1"/>
       <c r="C346" s="1"/>
@@ -11814,7 +11785,7 @@
       <c r="Y346" s="1"/>
       <c r="Z346" s="1"/>
     </row>
-    <row r="347">
+    <row r="347" spans="1:26" ht="13">
       <c r="A347" s="1"/>
       <c r="B347" s="1"/>
       <c r="C347" s="1"/>
@@ -11842,7 +11813,7 @@
       <c r="Y347" s="1"/>
       <c r="Z347" s="1"/>
     </row>
-    <row r="348">
+    <row r="348" spans="1:26" ht="13">
       <c r="A348" s="1"/>
       <c r="B348" s="1"/>
       <c r="C348" s="1"/>
@@ -11870,7 +11841,7 @@
       <c r="Y348" s="1"/>
       <c r="Z348" s="1"/>
     </row>
-    <row r="349">
+    <row r="349" spans="1:26" ht="13">
       <c r="A349" s="1"/>
       <c r="B349" s="1"/>
       <c r="C349" s="1"/>
@@ -11898,7 +11869,7 @@
       <c r="Y349" s="1"/>
       <c r="Z349" s="1"/>
     </row>
-    <row r="350">
+    <row r="350" spans="1:26" ht="13">
       <c r="A350" s="1"/>
       <c r="B350" s="1"/>
       <c r="C350" s="1"/>
@@ -11926,7 +11897,7 @@
       <c r="Y350" s="1"/>
       <c r="Z350" s="1"/>
     </row>
-    <row r="351">
+    <row r="351" spans="1:26" ht="13">
       <c r="A351" s="1"/>
       <c r="B351" s="1"/>
       <c r="C351" s="1"/>
@@ -11954,7 +11925,7 @@
       <c r="Y351" s="1"/>
       <c r="Z351" s="1"/>
     </row>
-    <row r="352">
+    <row r="352" spans="1:26" ht="13">
       <c r="A352" s="1"/>
       <c r="B352" s="1"/>
       <c r="C352" s="1"/>
@@ -11982,7 +11953,7 @@
       <c r="Y352" s="1"/>
       <c r="Z352" s="1"/>
     </row>
-    <row r="353">
+    <row r="353" spans="1:26" ht="13">
       <c r="A353" s="1"/>
       <c r="B353" s="1"/>
       <c r="C353" s="1"/>
@@ -12010,7 +11981,7 @@
       <c r="Y353" s="1"/>
       <c r="Z353" s="1"/>
     </row>
-    <row r="354">
+    <row r="354" spans="1:26" ht="13">
       <c r="A354" s="1"/>
       <c r="B354" s="1"/>
       <c r="C354" s="1"/>
@@ -12038,7 +12009,7 @@
       <c r="Y354" s="1"/>
       <c r="Z354" s="1"/>
     </row>
-    <row r="355">
+    <row r="355" spans="1:26" ht="13">
       <c r="A355" s="1"/>
       <c r="B355" s="1"/>
       <c r="C355" s="1"/>
@@ -12066,7 +12037,7 @@
       <c r="Y355" s="1"/>
       <c r="Z355" s="1"/>
     </row>
-    <row r="356">
+    <row r="356" spans="1:26" ht="13">
       <c r="A356" s="1"/>
       <c r="B356" s="1"/>
       <c r="C356" s="1"/>
@@ -12094,7 +12065,7 @@
       <c r="Y356" s="1"/>
       <c r="Z356" s="1"/>
     </row>
-    <row r="357">
+    <row r="357" spans="1:26" ht="13">
       <c r="A357" s="1"/>
       <c r="B357" s="1"/>
       <c r="C357" s="1"/>
@@ -12122,7 +12093,7 @@
       <c r="Y357" s="1"/>
       <c r="Z357" s="1"/>
     </row>
-    <row r="358">
+    <row r="358" spans="1:26" ht="13">
       <c r="A358" s="1"/>
       <c r="B358" s="1"/>
       <c r="C358" s="1"/>
@@ -12150,7 +12121,7 @@
       <c r="Y358" s="1"/>
       <c r="Z358" s="1"/>
     </row>
-    <row r="359">
+    <row r="359" spans="1:26" ht="13">
       <c r="A359" s="1"/>
       <c r="B359" s="1"/>
       <c r="C359" s="1"/>
@@ -12178,7 +12149,7 @@
       <c r="Y359" s="1"/>
       <c r="Z359" s="1"/>
     </row>
-    <row r="360">
+    <row r="360" spans="1:26" ht="13">
       <c r="A360" s="1"/>
       <c r="B360" s="1"/>
       <c r="C360" s="1"/>
@@ -12206,7 +12177,7 @@
       <c r="Y360" s="1"/>
       <c r="Z360" s="1"/>
     </row>
-    <row r="361">
+    <row r="361" spans="1:26" ht="13">
       <c r="A361" s="1"/>
       <c r="B361" s="1"/>
       <c r="C361" s="1"/>
@@ -12234,7 +12205,7 @@
       <c r="Y361" s="1"/>
       <c r="Z361" s="1"/>
     </row>
-    <row r="362">
+    <row r="362" spans="1:26" ht="13">
       <c r="A362" s="1"/>
       <c r="B362" s="1"/>
       <c r="C362" s="1"/>
@@ -12262,7 +12233,7 @@
       <c r="Y362" s="1"/>
       <c r="Z362" s="1"/>
     </row>
-    <row r="363">
+    <row r="363" spans="1:26" ht="13">
       <c r="A363" s="1"/>
       <c r="B363" s="1"/>
       <c r="C363" s="1"/>
@@ -12290,7 +12261,7 @@
       <c r="Y363" s="1"/>
       <c r="Z363" s="1"/>
     </row>
-    <row r="364">
+    <row r="364" spans="1:26" ht="13">
       <c r="A364" s="1"/>
       <c r="B364" s="1"/>
       <c r="C364" s="1"/>
@@ -12318,7 +12289,7 @@
       <c r="Y364" s="1"/>
       <c r="Z364" s="1"/>
     </row>
-    <row r="365">
+    <row r="365" spans="1:26" ht="13">
       <c r="A365" s="1"/>
       <c r="B365" s="1"/>
       <c r="C365" s="1"/>
@@ -12346,7 +12317,7 @@
       <c r="Y365" s="1"/>
       <c r="Z365" s="1"/>
     </row>
-    <row r="366">
+    <row r="366" spans="1:26" ht="13">
       <c r="A366" s="1"/>
       <c r="B366" s="1"/>
       <c r="C366" s="1"/>
@@ -12374,7 +12345,7 @@
       <c r="Y366" s="1"/>
       <c r="Z366" s="1"/>
     </row>
-    <row r="367">
+    <row r="367" spans="1:26" ht="13">
       <c r="A367" s="1"/>
       <c r="B367" s="1"/>
       <c r="C367" s="1"/>
@@ -12402,7 +12373,7 @@
       <c r="Y367" s="1"/>
       <c r="Z367" s="1"/>
     </row>
-    <row r="368">
+    <row r="368" spans="1:26" ht="13">
       <c r="A368" s="1"/>
       <c r="B368" s="1"/>
       <c r="C368" s="1"/>
@@ -12430,7 +12401,7 @@
       <c r="Y368" s="1"/>
       <c r="Z368" s="1"/>
     </row>
-    <row r="369">
+    <row r="369" spans="1:26" ht="13">
       <c r="A369" s="1"/>
       <c r="B369" s="1"/>
       <c r="C369" s="1"/>
@@ -12458,7 +12429,7 @@
       <c r="Y369" s="1"/>
       <c r="Z369" s="1"/>
     </row>
-    <row r="370">
+    <row r="370" spans="1:26" ht="13">
       <c r="A370" s="1"/>
       <c r="B370" s="1"/>
       <c r="C370" s="1"/>
@@ -12486,7 +12457,7 @@
       <c r="Y370" s="1"/>
       <c r="Z370" s="1"/>
     </row>
-    <row r="371">
+    <row r="371" spans="1:26" ht="13">
       <c r="A371" s="1"/>
       <c r="B371" s="1"/>
       <c r="C371" s="1"/>
@@ -12514,7 +12485,7 @@
       <c r="Y371" s="1"/>
       <c r="Z371" s="1"/>
     </row>
-    <row r="372">
+    <row r="372" spans="1:26" ht="13">
       <c r="A372" s="1"/>
       <c r="B372" s="1"/>
       <c r="C372" s="1"/>
@@ -12542,7 +12513,7 @@
       <c r="Y372" s="1"/>
       <c r="Z372" s="1"/>
     </row>
-    <row r="373">
+    <row r="373" spans="1:26" ht="13">
       <c r="A373" s="1"/>
       <c r="B373" s="1"/>
       <c r="C373" s="1"/>
@@ -12570,7 +12541,7 @@
       <c r="Y373" s="1"/>
       <c r="Z373" s="1"/>
     </row>
-    <row r="374">
+    <row r="374" spans="1:26" ht="13">
       <c r="A374" s="1"/>
       <c r="B374" s="1"/>
       <c r="C374" s="1"/>
@@ -12598,7 +12569,7 @@
       <c r="Y374" s="1"/>
       <c r="Z374" s="1"/>
     </row>
-    <row r="375">
+    <row r="375" spans="1:26" ht="13">
       <c r="A375" s="1"/>
       <c r="B375" s="1"/>
       <c r="C375" s="1"/>
@@ -12626,7 +12597,7 @@
       <c r="Y375" s="1"/>
       <c r="Z375" s="1"/>
     </row>
-    <row r="376">
+    <row r="376" spans="1:26" ht="13">
       <c r="A376" s="1"/>
       <c r="B376" s="1"/>
       <c r="C376" s="1"/>
@@ -12654,7 +12625,7 @@
       <c r="Y376" s="1"/>
       <c r="Z376" s="1"/>
     </row>
-    <row r="377">
+    <row r="377" spans="1:26" ht="13">
       <c r="A377" s="1"/>
       <c r="B377" s="1"/>
       <c r="C377" s="1"/>
@@ -12682,7 +12653,7 @@
       <c r="Y377" s="1"/>
       <c r="Z377" s="1"/>
     </row>
-    <row r="378">
+    <row r="378" spans="1:26" ht="13">
       <c r="A378" s="1"/>
       <c r="B378" s="1"/>
       <c r="C378" s="1"/>
@@ -12710,7 +12681,7 @@
       <c r="Y378" s="1"/>
       <c r="Z378" s="1"/>
     </row>
-    <row r="379">
+    <row r="379" spans="1:26" ht="13">
       <c r="A379" s="1"/>
       <c r="B379" s="1"/>
       <c r="C379" s="1"/>
@@ -12738,7 +12709,7 @@
       <c r="Y379" s="1"/>
       <c r="Z379" s="1"/>
     </row>
-    <row r="380">
+    <row r="380" spans="1:26" ht="13">
       <c r="A380" s="1"/>
       <c r="B380" s="1"/>
       <c r="C380" s="1"/>
@@ -12766,7 +12737,7 @@
       <c r="Y380" s="1"/>
       <c r="Z380" s="1"/>
     </row>
-    <row r="381">
+    <row r="381" spans="1:26" ht="13">
       <c r="A381" s="1"/>
       <c r="B381" s="1"/>
       <c r="C381" s="1"/>
@@ -12794,7 +12765,7 @@
       <c r="Y381" s="1"/>
       <c r="Z381" s="1"/>
     </row>
-    <row r="382">
+    <row r="382" spans="1:26" ht="13">
       <c r="A382" s="1"/>
       <c r="B382" s="1"/>
       <c r="C382" s="1"/>
@@ -12822,7 +12793,7 @@
       <c r="Y382" s="1"/>
       <c r="Z382" s="1"/>
     </row>
-    <row r="383">
+    <row r="383" spans="1:26" ht="13">
       <c r="A383" s="1"/>
       <c r="B383" s="1"/>
       <c r="C383" s="1"/>
@@ -12850,7 +12821,7 @@
       <c r="Y383" s="1"/>
       <c r="Z383" s="1"/>
     </row>
-    <row r="384">
+    <row r="384" spans="1:26" ht="13">
       <c r="A384" s="1"/>
       <c r="B384" s="1"/>
       <c r="C384" s="1"/>
@@ -12878,7 +12849,7 @@
       <c r="Y384" s="1"/>
       <c r="Z384" s="1"/>
     </row>
-    <row r="385">
+    <row r="385" spans="1:26" ht="13">
       <c r="A385" s="1"/>
       <c r="B385" s="1"/>
       <c r="C385" s="1"/>
@@ -12906,7 +12877,7 @@
       <c r="Y385" s="1"/>
       <c r="Z385" s="1"/>
     </row>
-    <row r="386">
+    <row r="386" spans="1:26" ht="13">
       <c r="A386" s="1"/>
       <c r="B386" s="1"/>
       <c r="C386" s="1"/>
@@ -12934,7 +12905,7 @@
       <c r="Y386" s="1"/>
       <c r="Z386" s="1"/>
     </row>
-    <row r="387">
+    <row r="387" spans="1:26" ht="13">
       <c r="A387" s="1"/>
       <c r="B387" s="1"/>
       <c r="C387" s="1"/>
@@ -12962,7 +12933,7 @@
       <c r="Y387" s="1"/>
       <c r="Z387" s="1"/>
     </row>
-    <row r="388">
+    <row r="388" spans="1:26" ht="13">
       <c r="A388" s="1"/>
       <c r="B388" s="1"/>
       <c r="C388" s="1"/>
@@ -12990,7 +12961,7 @@
       <c r="Y388" s="1"/>
       <c r="Z388" s="1"/>
     </row>
-    <row r="389">
+    <row r="389" spans="1:26" ht="13">
       <c r="A389" s="1"/>
       <c r="B389" s="1"/>
       <c r="C389" s="1"/>
@@ -13018,7 +12989,7 @@
       <c r="Y389" s="1"/>
       <c r="Z389" s="1"/>
     </row>
-    <row r="390">
+    <row r="390" spans="1:26" ht="13">
       <c r="A390" s="1"/>
       <c r="B390" s="1"/>
       <c r="C390" s="1"/>
@@ -13046,7 +13017,7 @@
       <c r="Y390" s="1"/>
       <c r="Z390" s="1"/>
     </row>
-    <row r="391">
+    <row r="391" spans="1:26" ht="13">
       <c r="A391" s="1"/>
       <c r="B391" s="1"/>
       <c r="C391" s="1"/>
@@ -13074,7 +13045,7 @@
       <c r="Y391" s="1"/>
       <c r="Z391" s="1"/>
     </row>
-    <row r="392">
+    <row r="392" spans="1:26" ht="13">
       <c r="A392" s="1"/>
       <c r="B392" s="1"/>
       <c r="C392" s="1"/>
@@ -13102,7 +13073,7 @@
       <c r="Y392" s="1"/>
       <c r="Z392" s="1"/>
     </row>
-    <row r="393">
+    <row r="393" spans="1:26" ht="13">
       <c r="A393" s="1"/>
       <c r="B393" s="1"/>
       <c r="C393" s="1"/>
@@ -13130,7 +13101,7 @@
       <c r="Y393" s="1"/>
       <c r="Z393" s="1"/>
     </row>
-    <row r="394">
+    <row r="394" spans="1:26" ht="13">
       <c r="A394" s="1"/>
       <c r="B394" s="1"/>
       <c r="C394" s="1"/>
@@ -13158,7 +13129,7 @@
       <c r="Y394" s="1"/>
       <c r="Z394" s="1"/>
     </row>
-    <row r="395">
+    <row r="395" spans="1:26" ht="13">
       <c r="A395" s="1"/>
       <c r="B395" s="1"/>
       <c r="C395" s="1"/>
@@ -13186,7 +13157,7 @@
       <c r="Y395" s="1"/>
       <c r="Z395" s="1"/>
     </row>
-    <row r="396">
+    <row r="396" spans="1:26" ht="13">
       <c r="A396" s="1"/>
       <c r="B396" s="1"/>
       <c r="C396" s="1"/>
@@ -13214,7 +13185,7 @@
       <c r="Y396" s="1"/>
       <c r="Z396" s="1"/>
     </row>
-    <row r="397">
+    <row r="397" spans="1:26" ht="13">
       <c r="A397" s="1"/>
       <c r="B397" s="1"/>
       <c r="C397" s="1"/>
@@ -13242,7 +13213,7 @@
       <c r="Y397" s="1"/>
       <c r="Z397" s="1"/>
     </row>
-    <row r="398">
+    <row r="398" spans="1:26" ht="13">
       <c r="A398" s="1"/>
       <c r="B398" s="1"/>
       <c r="C398" s="1"/>
@@ -13270,7 +13241,7 @@
       <c r="Y398" s="1"/>
       <c r="Z398" s="1"/>
     </row>
-    <row r="399">
+    <row r="399" spans="1:26" ht="13">
       <c r="A399" s="1"/>
       <c r="B399" s="1"/>
       <c r="C399" s="1"/>
@@ -13298,7 +13269,7 @@
       <c r="Y399" s="1"/>
       <c r="Z399" s="1"/>
     </row>
-    <row r="400">
+    <row r="400" spans="1:26" ht="13">
       <c r="A400" s="1"/>
       <c r="B400" s="1"/>
       <c r="C400" s="1"/>
@@ -13326,7 +13297,7 @@
       <c r="Y400" s="1"/>
       <c r="Z400" s="1"/>
     </row>
-    <row r="401">
+    <row r="401" spans="1:26" ht="13">
       <c r="A401" s="1"/>
       <c r="B401" s="1"/>
       <c r="C401" s="1"/>
@@ -13354,7 +13325,7 @@
       <c r="Y401" s="1"/>
       <c r="Z401" s="1"/>
     </row>
-    <row r="402">
+    <row r="402" spans="1:26" ht="13">
       <c r="A402" s="1"/>
       <c r="B402" s="1"/>
       <c r="C402" s="1"/>
@@ -13382,7 +13353,7 @@
       <c r="Y402" s="1"/>
       <c r="Z402" s="1"/>
     </row>
-    <row r="403">
+    <row r="403" spans="1:26" ht="13">
       <c r="A403" s="1"/>
       <c r="B403" s="1"/>
       <c r="C403" s="1"/>
@@ -13410,7 +13381,7 @@
       <c r="Y403" s="1"/>
       <c r="Z403" s="1"/>
     </row>
-    <row r="404">
+    <row r="404" spans="1:26" ht="13">
       <c r="A404" s="1"/>
       <c r="B404" s="1"/>
       <c r="C404" s="1"/>
@@ -13438,7 +13409,7 @@
       <c r="Y404" s="1"/>
       <c r="Z404" s="1"/>
     </row>
-    <row r="405">
+    <row r="405" spans="1:26" ht="13">
       <c r="A405" s="1"/>
       <c r="B405" s="1"/>
       <c r="C405" s="1"/>
@@ -13466,7 +13437,7 @@
       <c r="Y405" s="1"/>
       <c r="Z405" s="1"/>
     </row>
-    <row r="406">
+    <row r="406" spans="1:26" ht="13">
       <c r="A406" s="1"/>
       <c r="B406" s="1"/>
       <c r="C406" s="1"/>
@@ -13494,7 +13465,7 @@
       <c r="Y406" s="1"/>
       <c r="Z406" s="1"/>
     </row>
-    <row r="407">
+    <row r="407" spans="1:26" ht="13">
       <c r="A407" s="1"/>
       <c r="B407" s="1"/>
       <c r="C407" s="1"/>
@@ -13522,7 +13493,7 @@
       <c r="Y407" s="1"/>
       <c r="Z407" s="1"/>
     </row>
-    <row r="408">
+    <row r="408" spans="1:26" ht="13">
       <c r="A408" s="1"/>
       <c r="B408" s="1"/>
       <c r="C408" s="1"/>
@@ -13550,7 +13521,7 @@
       <c r="Y408" s="1"/>
       <c r="Z408" s="1"/>
     </row>
-    <row r="409">
+    <row r="409" spans="1:26" ht="13">
       <c r="A409" s="1"/>
       <c r="B409" s="1"/>
       <c r="C409" s="1"/>
@@ -13578,7 +13549,7 @@
       <c r="Y409" s="1"/>
       <c r="Z409" s="1"/>
     </row>
-    <row r="410">
+    <row r="410" spans="1:26" ht="13">
       <c r="A410" s="1"/>
       <c r="B410" s="1"/>
       <c r="C410" s="1"/>
@@ -13606,7 +13577,7 @@
       <c r="Y410" s="1"/>
       <c r="Z410" s="1"/>
     </row>
-    <row r="411">
+    <row r="411" spans="1:26" ht="13">
       <c r="A411" s="1"/>
       <c r="B411" s="1"/>
       <c r="C411" s="1"/>
@@ -13634,7 +13605,7 @@
       <c r="Y411" s="1"/>
       <c r="Z411" s="1"/>
     </row>
-    <row r="412">
+    <row r="412" spans="1:26" ht="13">
       <c r="A412" s="1"/>
       <c r="B412" s="1"/>
       <c r="C412" s="1"/>
@@ -13662,7 +13633,7 @@
       <c r="Y412" s="1"/>
       <c r="Z412" s="1"/>
     </row>
-    <row r="413">
+    <row r="413" spans="1:26" ht="13">
       <c r="A413" s="1"/>
       <c r="B413" s="1"/>
       <c r="C413" s="1"/>
@@ -13690,7 +13661,7 @@
       <c r="Y413" s="1"/>
       <c r="Z413" s="1"/>
     </row>
-    <row r="414">
+    <row r="414" spans="1:26" ht="13">
       <c r="A414" s="1"/>
       <c r="B414" s="1"/>
       <c r="C414" s="1"/>
@@ -13718,7 +13689,7 @@
       <c r="Y414" s="1"/>
       <c r="Z414" s="1"/>
     </row>
-    <row r="415">
+    <row r="415" spans="1:26" ht="13">
       <c r="A415" s="1"/>
       <c r="B415" s="1"/>
       <c r="C415" s="1"/>
@@ -13746,7 +13717,7 @@
       <c r="Y415" s="1"/>
       <c r="Z415" s="1"/>
     </row>
-    <row r="416">
+    <row r="416" spans="1:26" ht="13">
       <c r="A416" s="1"/>
       <c r="B416" s="1"/>
       <c r="C416" s="1"/>
@@ -13774,7 +13745,7 @@
       <c r="Y416" s="1"/>
       <c r="Z416" s="1"/>
     </row>
-    <row r="417">
+    <row r="417" spans="1:26" ht="13">
       <c r="A417" s="1"/>
       <c r="B417" s="1"/>
       <c r="C417" s="1"/>
@@ -13802,7 +13773,7 @@
       <c r="Y417" s="1"/>
       <c r="Z417" s="1"/>
     </row>
-    <row r="418">
+    <row r="418" spans="1:26" ht="13">
       <c r="A418" s="1"/>
       <c r="B418" s="1"/>
       <c r="C418" s="1"/>
@@ -13830,7 +13801,7 @@
       <c r="Y418" s="1"/>
       <c r="Z418" s="1"/>
     </row>
-    <row r="419">
+    <row r="419" spans="1:26" ht="13">
       <c r="A419" s="1"/>
       <c r="B419" s="1"/>
       <c r="C419" s="1"/>
@@ -13858,7 +13829,7 @@
       <c r="Y419" s="1"/>
       <c r="Z419" s="1"/>
     </row>
-    <row r="420">
+    <row r="420" spans="1:26" ht="13">
       <c r="A420" s="1"/>
       <c r="B420" s="1"/>
       <c r="C420" s="1"/>
@@ -13886,7 +13857,7 @@
       <c r="Y420" s="1"/>
       <c r="Z420" s="1"/>
     </row>
-    <row r="421">
+    <row r="421" spans="1:26" ht="13">
       <c r="A421" s="1"/>
       <c r="B421" s="1"/>
       <c r="C421" s="1"/>
@@ -13914,7 +13885,7 @@
       <c r="Y421" s="1"/>
       <c r="Z421" s="1"/>
     </row>
-    <row r="422">
+    <row r="422" spans="1:26" ht="13">
       <c r="A422" s="1"/>
       <c r="B422" s="1"/>
       <c r="C422" s="1"/>
@@ -13942,7 +13913,7 @@
       <c r="Y422" s="1"/>
       <c r="Z422" s="1"/>
     </row>
-    <row r="423">
+    <row r="423" spans="1:26" ht="13">
       <c r="A423" s="1"/>
       <c r="B423" s="1"/>
       <c r="C423" s="1"/>
@@ -13970,7 +13941,7 @@
       <c r="Y423" s="1"/>
       <c r="Z423" s="1"/>
     </row>
-    <row r="424">
+    <row r="424" spans="1:26" ht="13">
       <c r="A424" s="1"/>
       <c r="B424" s="1"/>
       <c r="C424" s="1"/>
@@ -13998,7 +13969,7 @@
       <c r="Y424" s="1"/>
       <c r="Z424" s="1"/>
     </row>
-    <row r="425">
+    <row r="425" spans="1:26" ht="13">
       <c r="A425" s="1"/>
       <c r="B425" s="1"/>
       <c r="C425" s="1"/>
@@ -14026,7 +13997,7 @@
       <c r="Y425" s="1"/>
       <c r="Z425" s="1"/>
     </row>
-    <row r="426">
+    <row r="426" spans="1:26" ht="13">
       <c r="A426" s="1"/>
       <c r="B426" s="1"/>
       <c r="C426" s="1"/>
@@ -14054,7 +14025,7 @@
       <c r="Y426" s="1"/>
       <c r="Z426" s="1"/>
     </row>
-    <row r="427">
+    <row r="427" spans="1:26" ht="13">
       <c r="A427" s="1"/>
       <c r="B427" s="1"/>
       <c r="C427" s="1"/>
@@ -14082,7 +14053,7 @@
       <c r="Y427" s="1"/>
       <c r="Z427" s="1"/>
     </row>
-    <row r="428">
+    <row r="428" spans="1:26" ht="13">
       <c r="A428" s="1"/>
       <c r="B428" s="1"/>
       <c r="C428" s="1"/>
@@ -14110,7 +14081,7 @@
       <c r="Y428" s="1"/>
       <c r="Z428" s="1"/>
     </row>
-    <row r="429">
+    <row r="429" spans="1:26" ht="13">
       <c r="A429" s="1"/>
       <c r="B429" s="1"/>
       <c r="C429" s="1"/>
@@ -14138,7 +14109,7 @@
       <c r="Y429" s="1"/>
       <c r="Z429" s="1"/>
     </row>
-    <row r="430">
+    <row r="430" spans="1:26" ht="13">
       <c r="A430" s="1"/>
       <c r="B430" s="1"/>
       <c r="C430" s="1"/>
@@ -14166,7 +14137,7 @@
       <c r="Y430" s="1"/>
       <c r="Z430" s="1"/>
     </row>
-    <row r="431">
+    <row r="431" spans="1:26" ht="13">
       <c r="A431" s="1"/>
       <c r="B431" s="1"/>
       <c r="C431" s="1"/>
@@ -14194,7 +14165,7 @@
       <c r="Y431" s="1"/>
       <c r="Z431" s="1"/>
     </row>
-    <row r="432">
+    <row r="432" spans="1:26" ht="13">
       <c r="A432" s="1"/>
       <c r="B432" s="1"/>
       <c r="C432" s="1"/>
@@ -14222,7 +14193,7 @@
       <c r="Y432" s="1"/>
       <c r="Z432" s="1"/>
     </row>
-    <row r="433">
+    <row r="433" spans="1:26" ht="13">
       <c r="A433" s="1"/>
       <c r="B433" s="1"/>
       <c r="C433" s="1"/>
@@ -14250,7 +14221,7 @@
       <c r="Y433" s="1"/>
       <c r="Z433" s="1"/>
     </row>
-    <row r="434">
+    <row r="434" spans="1:26" ht="13">
       <c r="A434" s="1"/>
       <c r="B434" s="1"/>
       <c r="C434" s="1"/>
@@ -14278,7 +14249,7 @@
       <c r="Y434" s="1"/>
       <c r="Z434" s="1"/>
     </row>
-    <row r="435">
+    <row r="435" spans="1:26" ht="13">
       <c r="A435" s="1"/>
       <c r="B435" s="1"/>
       <c r="C435" s="1"/>
@@ -14306,7 +14277,7 @@
       <c r="Y435" s="1"/>
       <c r="Z435" s="1"/>
     </row>
-    <row r="436">
+    <row r="436" spans="1:26" ht="13">
       <c r="A436" s="1"/>
       <c r="B436" s="1"/>
       <c r="C436" s="1"/>
@@ -14334,7 +14305,7 @@
       <c r="Y436" s="1"/>
       <c r="Z436" s="1"/>
     </row>
-    <row r="437">
+    <row r="437" spans="1:26" ht="13">
       <c r="A437" s="1"/>
       <c r="B437" s="1"/>
       <c r="C437" s="1"/>
@@ -14362,7 +14333,7 @@
       <c r="Y437" s="1"/>
       <c r="Z437" s="1"/>
     </row>
-    <row r="438">
+    <row r="438" spans="1:26" ht="13">
       <c r="A438" s="1"/>
       <c r="B438" s="1"/>
       <c r="C438" s="1"/>
@@ -14390,7 +14361,7 @@
       <c r="Y438" s="1"/>
       <c r="Z438" s="1"/>
     </row>
-    <row r="439">
+    <row r="439" spans="1:26" ht="13">
       <c r="A439" s="1"/>
       <c r="B439" s="1"/>
       <c r="C439" s="1"/>
@@ -14418,7 +14389,7 @@
       <c r="Y439" s="1"/>
       <c r="Z439" s="1"/>
     </row>
-    <row r="440">
+    <row r="440" spans="1:26" ht="13">
       <c r="A440" s="1"/>
       <c r="B440" s="1"/>
       <c r="C440" s="1"/>
@@ -14446,7 +14417,7 @@
       <c r="Y440" s="1"/>
       <c r="Z440" s="1"/>
     </row>
-    <row r="441">
+    <row r="441" spans="1:26" ht="13">
       <c r="A441" s="1"/>
       <c r="B441" s="1"/>
       <c r="C441" s="1"/>
@@ -14474,7 +14445,7 @@
       <c r="Y441" s="1"/>
       <c r="Z441" s="1"/>
     </row>
-    <row r="442">
+    <row r="442" spans="1:26" ht="13">
       <c r="A442" s="1"/>
       <c r="B442" s="1"/>
       <c r="C442" s="1"/>
@@ -14502,7 +14473,7 @@
       <c r="Y442" s="1"/>
       <c r="Z442" s="1"/>
     </row>
-    <row r="443">
+    <row r="443" spans="1:26" ht="13">
       <c r="A443" s="1"/>
       <c r="B443" s="1"/>
       <c r="C443" s="1"/>
@@ -14530,7 +14501,7 @@
       <c r="Y443" s="1"/>
       <c r="Z443" s="1"/>
     </row>
-    <row r="444">
+    <row r="444" spans="1:26" ht="13">
       <c r="A444" s="1"/>
       <c r="B444" s="1"/>
       <c r="C444" s="1"/>
@@ -14558,7 +14529,7 @@
       <c r="Y444" s="1"/>
       <c r="Z444" s="1"/>
     </row>
-    <row r="445">
+    <row r="445" spans="1:26" ht="13">
       <c r="A445" s="1"/>
       <c r="B445" s="1"/>
       <c r="C445" s="1"/>
@@ -14586,7 +14557,7 @@
       <c r="Y445" s="1"/>
       <c r="Z445" s="1"/>
     </row>
-    <row r="446">
+    <row r="446" spans="1:26" ht="13">
       <c r="A446" s="1"/>
       <c r="B446" s="1"/>
       <c r="C446" s="1"/>
@@ -14614,7 +14585,7 @@
       <c r="Y446" s="1"/>
       <c r="Z446" s="1"/>
     </row>
-    <row r="447">
+    <row r="447" spans="1:26" ht="13">
       <c r="A447" s="1"/>
       <c r="B447" s="1"/>
       <c r="C447" s="1"/>
@@ -14642,7 +14613,7 @@
       <c r="Y447" s="1"/>
       <c r="Z447" s="1"/>
     </row>
-    <row r="448">
+    <row r="448" spans="1:26" ht="13">
       <c r="A448" s="1"/>
       <c r="B448" s="1"/>
       <c r="C448" s="1"/>
@@ -14670,7 +14641,7 @@
       <c r="Y448" s="1"/>
       <c r="Z448" s="1"/>
     </row>
-    <row r="449">
+    <row r="449" spans="1:26" ht="13">
       <c r="A449" s="1"/>
       <c r="B449" s="1"/>
       <c r="C449" s="1"/>
@@ -14698,7 +14669,7 @@
       <c r="Y449" s="1"/>
       <c r="Z449" s="1"/>
     </row>
-    <row r="450">
+    <row r="450" spans="1:26" ht="13">
       <c r="A450" s="1"/>
       <c r="B450" s="1"/>
       <c r="C450" s="1"/>
@@ -14726,7 +14697,7 @@
       <c r="Y450" s="1"/>
       <c r="Z450" s="1"/>
     </row>
-    <row r="451">
+    <row r="451" spans="1:26" ht="13">
       <c r="A451" s="1"/>
       <c r="B451" s="1"/>
       <c r="C451" s="1"/>
@@ -14754,7 +14725,7 @@
       <c r="Y451" s="1"/>
       <c r="Z451" s="1"/>
     </row>
-    <row r="452">
+    <row r="452" spans="1:26" ht="13">
       <c r="A452" s="1"/>
       <c r="B452" s="1"/>
       <c r="C452" s="1"/>
@@ -14782,7 +14753,7 @@
       <c r="Y452" s="1"/>
       <c r="Z452" s="1"/>
     </row>
-    <row r="453">
+    <row r="453" spans="1:26" ht="13">
       <c r="A453" s="1"/>
       <c r="B453" s="1"/>
       <c r="C453" s="1"/>
@@ -14810,7 +14781,7 @@
       <c r="Y453" s="1"/>
       <c r="Z453" s="1"/>
     </row>
-    <row r="454">
+    <row r="454" spans="1:26" ht="13">
       <c r="A454" s="1"/>
       <c r="B454" s="1"/>
       <c r="C454" s="1"/>
@@ -14838,7 +14809,7 @@
       <c r="Y454" s="1"/>
       <c r="Z454" s="1"/>
     </row>
-    <row r="455">
+    <row r="455" spans="1:26" ht="13">
       <c r="A455" s="1"/>
       <c r="B455" s="1"/>
       <c r="C455" s="1"/>
@@ -14866,7 +14837,7 @@
       <c r="Y455" s="1"/>
       <c r="Z455" s="1"/>
     </row>
-    <row r="456">
+    <row r="456" spans="1:26" ht="13">
       <c r="A456" s="1"/>
       <c r="B456" s="1"/>
       <c r="C456" s="1"/>
@@ -14894,7 +14865,7 @@
       <c r="Y456" s="1"/>
       <c r="Z456" s="1"/>
     </row>
-    <row r="457">
+    <row r="457" spans="1:26" ht="13">
       <c r="A457" s="1"/>
       <c r="B457" s="1"/>
       <c r="C457" s="1"/>
@@ -14922,7 +14893,7 @@
       <c r="Y457" s="1"/>
       <c r="Z457" s="1"/>
     </row>
-    <row r="458">
+    <row r="458" spans="1:26" ht="13">
       <c r="A458" s="1"/>
       <c r="B458" s="1"/>
       <c r="C458" s="1"/>
@@ -14950,7 +14921,7 @@
       <c r="Y458" s="1"/>
       <c r="Z458" s="1"/>
     </row>
-    <row r="459">
+    <row r="459" spans="1:26" ht="13">
       <c r="A459" s="1"/>
       <c r="B459" s="1"/>
       <c r="C459" s="1"/>
@@ -14978,7 +14949,7 @@
       <c r="Y459" s="1"/>
       <c r="Z459" s="1"/>
     </row>
-    <row r="460">
+    <row r="460" spans="1:26" ht="13">
       <c r="A460" s="1"/>
       <c r="B460" s="1"/>
       <c r="C460" s="1"/>
@@ -15006,7 +14977,7 @@
       <c r="Y460" s="1"/>
       <c r="Z460" s="1"/>
     </row>
-    <row r="461">
+    <row r="461" spans="1:26" ht="13">
       <c r="A461" s="1"/>
       <c r="B461" s="1"/>
       <c r="C461" s="1"/>
@@ -15034,7 +15005,7 @@
       <c r="Y461" s="1"/>
       <c r="Z461" s="1"/>
     </row>
-    <row r="462">
+    <row r="462" spans="1:26" ht="13">
       <c r="A462" s="1"/>
       <c r="B462" s="1"/>
       <c r="C462" s="1"/>
@@ -15062,7 +15033,7 @@
       <c r="Y462" s="1"/>
       <c r="Z462" s="1"/>
     </row>
-    <row r="463">
+    <row r="463" spans="1:26" ht="13">
       <c r="A463" s="1"/>
       <c r="B463" s="1"/>
       <c r="C463" s="1"/>
@@ -15090,7 +15061,7 @@
       <c r="Y463" s="1"/>
       <c r="Z463" s="1"/>
     </row>
-    <row r="464">
+    <row r="464" spans="1:26" ht="13">
       <c r="A464" s="1"/>
       <c r="B464" s="1"/>
       <c r="C464" s="1"/>
@@ -15118,7 +15089,7 @@
       <c r="Y464" s="1"/>
       <c r="Z464" s="1"/>
     </row>
-    <row r="465">
+    <row r="465" spans="1:26" ht="13">
       <c r="A465" s="1"/>
       <c r="B465" s="1"/>
       <c r="C465" s="1"/>
@@ -15146,7 +15117,7 @@
       <c r="Y465" s="1"/>
       <c r="Z465" s="1"/>
     </row>
-    <row r="466">
+    <row r="466" spans="1:26" ht="13">
       <c r="A466" s="1"/>
       <c r="B466" s="1"/>
       <c r="C466" s="1"/>
@@ -15174,7 +15145,7 @@
       <c r="Y466" s="1"/>
       <c r="Z466" s="1"/>
     </row>
-    <row r="467">
+    <row r="467" spans="1:26" ht="13">
       <c r="A467" s="1"/>
       <c r="B467" s="1"/>
       <c r="C467" s="1"/>
@@ -15202,7 +15173,7 @@
       <c r="Y467" s="1"/>
       <c r="Z467" s="1"/>
     </row>
-    <row r="468">
+    <row r="468" spans="1:26" ht="13">
       <c r="A468" s="1"/>
       <c r="B468" s="1"/>
       <c r="C468" s="1"/>
@@ -15230,7 +15201,7 @@
       <c r="Y468" s="1"/>
       <c r="Z468" s="1"/>
     </row>
-    <row r="469">
+    <row r="469" spans="1:26" ht="13">
       <c r="A469" s="1"/>
       <c r="B469" s="1"/>
       <c r="C469" s="1"/>
@@ -15258,7 +15229,7 @@
       <c r="Y469" s="1"/>
       <c r="Z469" s="1"/>
     </row>
-    <row r="470">
+    <row r="470" spans="1:26" ht="13">
       <c r="A470" s="1"/>
       <c r="B470" s="1"/>
       <c r="C470" s="1"/>
@@ -15286,7 +15257,7 @@
       <c r="Y470" s="1"/>
       <c r="Z470" s="1"/>
     </row>
-    <row r="471">
+    <row r="471" spans="1:26" ht="13">
       <c r="A471" s="1"/>
       <c r="B471" s="1"/>
       <c r="C471" s="1"/>
@@ -15314,7 +15285,7 @@
       <c r="Y471" s="1"/>
       <c r="Z471" s="1"/>
     </row>
-    <row r="472">
+    <row r="472" spans="1:26" ht="13">
       <c r="A472" s="1"/>
       <c r="B472" s="1"/>
       <c r="C472" s="1"/>
@@ -15342,7 +15313,7 @@
       <c r="Y472" s="1"/>
       <c r="Z472" s="1"/>
     </row>
-    <row r="473">
+    <row r="473" spans="1:26" ht="13">
       <c r="A473" s="1"/>
       <c r="B473" s="1"/>
       <c r="C473" s="1"/>
@@ -15370,7 +15341,7 @@
       <c r="Y473" s="1"/>
       <c r="Z473" s="1"/>
     </row>
-    <row r="474">
+    <row r="474" spans="1:26" ht="13">
       <c r="A474" s="1"/>
       <c r="B474" s="1"/>
       <c r="C474" s="1"/>
@@ -15398,7 +15369,7 @@
       <c r="Y474" s="1"/>
       <c r="Z474" s="1"/>
     </row>
-    <row r="475">
+    <row r="475" spans="1:26" ht="13">
       <c r="A475" s="1"/>
       <c r="B475" s="1"/>
       <c r="C475" s="1"/>
@@ -15426,7 +15397,7 @@
       <c r="Y475" s="1"/>
       <c r="Z475" s="1"/>
     </row>
-    <row r="476">
+    <row r="476" spans="1:26" ht="13">
       <c r="A476" s="1"/>
       <c r="B476" s="1"/>
       <c r="C476" s="1"/>
@@ -15454,7 +15425,7 @@
       <c r="Y476" s="1"/>
       <c r="Z476" s="1"/>
     </row>
-    <row r="477">
+    <row r="477" spans="1:26" ht="13">
       <c r="A477" s="1"/>
       <c r="B477" s="1"/>
       <c r="C477" s="1"/>
@@ -15482,7 +15453,7 @@
       <c r="Y477" s="1"/>
       <c r="Z477" s="1"/>
     </row>
-    <row r="478">
+    <row r="478" spans="1:26" ht="13">
       <c r="A478" s="1"/>
       <c r="B478" s="1"/>
       <c r="C478" s="1"/>
@@ -15510,7 +15481,7 @@
       <c r="Y478" s="1"/>
       <c r="Z478" s="1"/>
     </row>
-    <row r="479">
+    <row r="479" spans="1:26" ht="13">
       <c r="A479" s="1"/>
       <c r="B479" s="1"/>
       <c r="C479" s="1"/>
@@ -15538,7 +15509,7 @@
       <c r="Y479" s="1"/>
       <c r="Z479" s="1"/>
     </row>
-    <row r="480">
+    <row r="480" spans="1:26" ht="13">
       <c r="A480" s="1"/>
       <c r="B480" s="1"/>
       <c r="C480" s="1"/>
@@ -15566,7 +15537,7 @@
       <c r="Y480" s="1"/>
       <c r="Z480" s="1"/>
     </row>
-    <row r="481">
+    <row r="481" spans="1:26" ht="13">
       <c r="A481" s="1"/>
       <c r="B481" s="1"/>
       <c r="C481" s="1"/>
@@ -15594,7 +15565,7 @@
       <c r="Y481" s="1"/>
       <c r="Z481" s="1"/>
     </row>
-    <row r="482">
+    <row r="482" spans="1:26" ht="13">
       <c r="A482" s="1"/>
       <c r="B482" s="1"/>
       <c r="C482" s="1"/>
@@ -15622,7 +15593,7 @@
       <c r="Y482" s="1"/>
       <c r="Z482" s="1"/>
     </row>
-    <row r="483">
+    <row r="483" spans="1:26" ht="13">
       <c r="A483" s="1"/>
       <c r="B483" s="1"/>
       <c r="C483" s="1"/>
@@ -15650,7 +15621,7 @@
       <c r="Y483" s="1"/>
       <c r="Z483" s="1"/>
     </row>
-    <row r="484">
+    <row r="484" spans="1:26" ht="13">
       <c r="A484" s="1"/>
       <c r="B484" s="1"/>
       <c r="C484" s="1"/>
@@ -15678,7 +15649,7 @@
       <c r="Y484" s="1"/>
       <c r="Z484" s="1"/>
     </row>
-    <row r="485">
+    <row r="485" spans="1:26" ht="13">
       <c r="A485" s="1"/>
       <c r="B485" s="1"/>
       <c r="C485" s="1"/>
@@ -15706,7 +15677,7 @@
       <c r="Y485" s="1"/>
       <c r="Z485" s="1"/>
     </row>
-    <row r="486">
+    <row r="486" spans="1:26" ht="13">
       <c r="A486" s="1"/>
       <c r="B486" s="1"/>
       <c r="C486" s="1"/>
@@ -15734,7 +15705,7 @@
       <c r="Y486" s="1"/>
       <c r="Z486" s="1"/>
     </row>
-    <row r="487">
+    <row r="487" spans="1:26" ht="13">
       <c r="A487" s="1"/>
       <c r="B487" s="1"/>
       <c r="C487" s="1"/>
@@ -15762,7 +15733,7 @@
       <c r="Y487" s="1"/>
       <c r="Z487" s="1"/>
     </row>
-    <row r="488">
+    <row r="488" spans="1:26" ht="13">
       <c r="A488" s="1"/>
       <c r="B488" s="1"/>
       <c r="C488" s="1"/>
@@ -15790,7 +15761,7 @@
       <c r="Y488" s="1"/>
       <c r="Z488" s="1"/>
     </row>
-    <row r="489">
+    <row r="489" spans="1:26" ht="13">
       <c r="A489" s="1"/>
       <c r="B489" s="1"/>
       <c r="C489" s="1"/>
@@ -15818,7 +15789,7 @@
       <c r="Y489" s="1"/>
       <c r="Z489" s="1"/>
     </row>
-    <row r="490">
+    <row r="490" spans="1:26" ht="13">
       <c r="A490" s="1"/>
       <c r="B490" s="1"/>
       <c r="C490" s="1"/>
@@ -15846,7 +15817,7 @@
       <c r="Y490" s="1"/>
       <c r="Z490" s="1"/>
     </row>
-    <row r="491">
+    <row r="491" spans="1:26" ht="13">
       <c r="A491" s="1"/>
       <c r="B491" s="1"/>
       <c r="C491" s="1"/>
@@ -15874,7 +15845,7 @@
       <c r="Y491" s="1"/>
       <c r="Z491" s="1"/>
     </row>
-    <row r="492">
+    <row r="492" spans="1:26" ht="13">
       <c r="A492" s="1"/>
       <c r="B492" s="1"/>
       <c r="C492" s="1"/>
@@ -15902,7 +15873,7 @@
       <c r="Y492" s="1"/>
       <c r="Z492" s="1"/>
     </row>
-    <row r="493">
+    <row r="493" spans="1:26" ht="13">
       <c r="A493" s="1"/>
       <c r="B493" s="1"/>
       <c r="C493" s="1"/>
@@ -15930,7 +15901,7 @@
       <c r="Y493" s="1"/>
       <c r="Z493" s="1"/>
     </row>
-    <row r="494">
+    <row r="494" spans="1:26" ht="13">
       <c r="A494" s="1"/>
       <c r="B494" s="1"/>
       <c r="C494" s="1"/>
@@ -15958,7 +15929,7 @@
       <c r="Y494" s="1"/>
       <c r="Z494" s="1"/>
     </row>
-    <row r="495">
+    <row r="495" spans="1:26" ht="13">
       <c r="A495" s="1"/>
       <c r="B495" s="1"/>
       <c r="C495" s="1"/>
@@ -15986,7 +15957,7 @@
       <c r="Y495" s="1"/>
       <c r="Z495" s="1"/>
     </row>
-    <row r="496">
+    <row r="496" spans="1:26" ht="13">
       <c r="A496" s="1"/>
       <c r="B496" s="1"/>
       <c r="C496" s="1"/>
@@ -16014,7 +15985,7 @@
       <c r="Y496" s="1"/>
       <c r="Z496" s="1"/>
     </row>
-    <row r="497">
+    <row r="497" spans="1:26" ht="13">
       <c r="A497" s="1"/>
       <c r="B497" s="1"/>
       <c r="C497" s="1"/>
@@ -16042,7 +16013,7 @@
       <c r="Y497" s="1"/>
       <c r="Z497" s="1"/>
     </row>
-    <row r="498">
+    <row r="498" spans="1:26" ht="13">
       <c r="A498" s="1"/>
       <c r="B498" s="1"/>
       <c r="C498" s="1"/>
@@ -16070,7 +16041,7 @@
       <c r="Y498" s="1"/>
       <c r="Z498" s="1"/>
     </row>
-    <row r="499">
+    <row r="499" spans="1:26" ht="13">
       <c r="A499" s="1"/>
       <c r="B499" s="1"/>
       <c r="C499" s="1"/>
@@ -16098,7 +16069,7 @@
       <c r="Y499" s="1"/>
       <c r="Z499" s="1"/>
     </row>
-    <row r="500">
+    <row r="500" spans="1:26" ht="13">
       <c r="A500" s="1"/>
       <c r="B500" s="1"/>
       <c r="C500" s="1"/>
@@ -16126,7 +16097,7 @@
       <c r="Y500" s="1"/>
       <c r="Z500" s="1"/>
     </row>
-    <row r="501">
+    <row r="501" spans="1:26" ht="13">
       <c r="A501" s="1"/>
       <c r="B501" s="1"/>
       <c r="C501" s="1"/>
@@ -16154,7 +16125,7 @@
       <c r="Y501" s="1"/>
       <c r="Z501" s="1"/>
     </row>
-    <row r="502">
+    <row r="502" spans="1:26" ht="13">
       <c r="A502" s="1"/>
       <c r="B502" s="1"/>
       <c r="C502" s="1"/>
@@ -16182,7 +16153,7 @@
       <c r="Y502" s="1"/>
       <c r="Z502" s="1"/>
     </row>
-    <row r="503">
+    <row r="503" spans="1:26" ht="13">
       <c r="A503" s="1"/>
       <c r="B503" s="1"/>
       <c r="C503" s="1"/>
@@ -16210,7 +16181,7 @@
       <c r="Y503" s="1"/>
       <c r="Z503" s="1"/>
     </row>
-    <row r="504">
+    <row r="504" spans="1:26" ht="13">
       <c r="A504" s="1"/>
       <c r="B504" s="1"/>
       <c r="C504" s="1"/>
@@ -16238,7 +16209,7 @@
       <c r="Y504" s="1"/>
       <c r="Z504" s="1"/>
     </row>
-    <row r="505">
+    <row r="505" spans="1:26" ht="13">
       <c r="A505" s="1"/>
       <c r="B505" s="1"/>
       <c r="C505" s="1"/>
@@ -16266,7 +16237,7 @@
       <c r="Y505" s="1"/>
       <c r="Z505" s="1"/>
     </row>
-    <row r="506">
+    <row r="506" spans="1:26" ht="13">
       <c r="A506" s="1"/>
       <c r="B506" s="1"/>
       <c r="C506" s="1"/>
@@ -16294,7 +16265,7 @@
       <c r="Y506" s="1"/>
       <c r="Z506" s="1"/>
     </row>
-    <row r="507">
+    <row r="507" spans="1:26" ht="13">
       <c r="A507" s="1"/>
       <c r="B507" s="1"/>
       <c r="C507" s="1"/>
@@ -16322,7 +16293,7 @@
       <c r="Y507" s="1"/>
       <c r="Z507" s="1"/>
     </row>
-    <row r="508">
+    <row r="508" spans="1:26" ht="13">
       <c r="A508" s="1"/>
       <c r="B508" s="1"/>
       <c r="C508" s="1"/>
@@ -16350,7 +16321,7 @@
       <c r="Y508" s="1"/>
       <c r="Z508" s="1"/>
     </row>
-    <row r="509">
+    <row r="509" spans="1:26" ht="13">
       <c r="A509" s="1"/>
       <c r="B509" s="1"/>
       <c r="C509" s="1"/>
@@ -16378,7 +16349,7 @@
       <c r="Y509" s="1"/>
       <c r="Z509" s="1"/>
     </row>
-    <row r="510">
+    <row r="510" spans="1:26" ht="13">
       <c r="A510" s="1"/>
       <c r="B510" s="1"/>
       <c r="C510" s="1"/>
@@ -16406,7 +16377,7 @@
       <c r="Y510" s="1"/>
       <c r="Z510" s="1"/>
     </row>
-    <row r="511">
+    <row r="511" spans="1:26" ht="13">
       <c r="A511" s="1"/>
       <c r="B511" s="1"/>
       <c r="C511" s="1"/>
@@ -16434,7 +16405,7 @@
       <c r="Y511" s="1"/>
       <c r="Z511" s="1"/>
     </row>
-    <row r="512">
+    <row r="512" spans="1:26" ht="13">
       <c r="A512" s="1"/>
       <c r="B512" s="1"/>
       <c r="C512" s="1"/>
@@ -16462,7 +16433,7 @@
       <c r="Y512" s="1"/>
       <c r="Z512" s="1"/>
     </row>
-    <row r="513">
+    <row r="513" spans="1:26" ht="13">
       <c r="A513" s="1"/>
       <c r="B513" s="1"/>
       <c r="C513" s="1"/>
@@ -16490,7 +16461,7 @@
       <c r="Y513" s="1"/>
       <c r="Z513" s="1"/>
     </row>
-    <row r="514">
+    <row r="514" spans="1:26" ht="13">
       <c r="A514" s="1"/>
       <c r="B514" s="1"/>
       <c r="C514" s="1"/>
@@ -16518,7 +16489,7 @@
       <c r="Y514" s="1"/>
       <c r="Z514" s="1"/>
     </row>
-    <row r="515">
+    <row r="515" spans="1:26" ht="13">
       <c r="A515" s="1"/>
       <c r="B515" s="1"/>
       <c r="C515" s="1"/>
@@ -16546,7 +16517,7 @@
       <c r="Y515" s="1"/>
       <c r="Z515" s="1"/>
     </row>
-    <row r="516">
+    <row r="516" spans="1:26" ht="13">
       <c r="A516" s="1"/>
       <c r="B516" s="1"/>
       <c r="C516" s="1"/>
@@ -16574,7 +16545,7 @@
       <c r="Y516" s="1"/>
       <c r="Z516" s="1"/>
     </row>
-    <row r="517">
+    <row r="517" spans="1:26" ht="13">
       <c r="A517" s="1"/>
       <c r="B517" s="1"/>
       <c r="C517" s="1"/>
@@ -16602,7 +16573,7 @@
       <c r="Y517" s="1"/>
       <c r="Z517" s="1"/>
     </row>
-    <row r="518">
+    <row r="518" spans="1:26" ht="13">
       <c r="A518" s="1"/>
       <c r="B518" s="1"/>
       <c r="C518" s="1"/>
@@ -16630,7 +16601,7 @@
       <c r="Y518" s="1"/>
       <c r="Z518" s="1"/>
     </row>
-    <row r="519">
+    <row r="519" spans="1:26" ht="13">
       <c r="A519" s="1"/>
       <c r="B519" s="1"/>
       <c r="C519" s="1"/>
@@ -16658,7 +16629,7 @@
       <c r="Y519" s="1"/>
       <c r="Z519" s="1"/>
     </row>
-    <row r="520">
+    <row r="520" spans="1:26" ht="13">
       <c r="A520" s="1"/>
       <c r="B520" s="1"/>
       <c r="C520" s="1"/>
@@ -16686,7 +16657,7 @@
       <c r="Y520" s="1"/>
       <c r="Z520" s="1"/>
     </row>
-    <row r="521">
+    <row r="521" spans="1:26" ht="13">
       <c r="A521" s="1"/>
       <c r="B521" s="1"/>
       <c r="C521" s="1"/>
@@ -16714,7 +16685,7 @@
       <c r="Y521" s="1"/>
       <c r="Z521" s="1"/>
     </row>
-    <row r="522">
+    <row r="522" spans="1:26" ht="13">
       <c r="A522" s="1"/>
       <c r="B522" s="1"/>
       <c r="C522" s="1"/>
@@ -16742,7 +16713,7 @@
       <c r="Y522" s="1"/>
       <c r="Z522" s="1"/>
     </row>
-    <row r="523">
+    <row r="523" spans="1:26" ht="13">
       <c r="A523" s="1"/>
       <c r="B523" s="1"/>
       <c r="C523" s="1"/>
@@ -16770,7 +16741,7 @@
       <c r="Y523" s="1"/>
       <c r="Z523" s="1"/>
     </row>
-    <row r="524">
+    <row r="524" spans="1:26" ht="13">
       <c r="A524" s="1"/>
       <c r="B524" s="1"/>
       <c r="C524" s="1"/>
@@ -16798,7 +16769,7 @@
       <c r="Y524" s="1"/>
       <c r="Z524" s="1"/>
     </row>
-    <row r="525">
+    <row r="525" spans="1:26" ht="13">
       <c r="A525" s="1"/>
       <c r="B525" s="1"/>
       <c r="C525" s="1"/>
@@ -16826,7 +16797,7 @@
       <c r="Y525" s="1"/>
       <c r="Z525" s="1"/>
     </row>
-    <row r="526">
+    <row r="526" spans="1:26" ht="13">
       <c r="A526" s="1"/>
       <c r="B526" s="1"/>
       <c r="C526" s="1"/>
@@ -16854,7 +16825,7 @@
       <c r="Y526" s="1"/>
       <c r="Z526" s="1"/>
     </row>
-    <row r="527">
+    <row r="527" spans="1:26" ht="13">
       <c r="A527" s="1"/>
       <c r="B527" s="1"/>
       <c r="C527" s="1"/>
@@ -16882,7 +16853,7 @@
       <c r="Y527" s="1"/>
       <c r="Z527" s="1"/>
     </row>
-    <row r="528">
+    <row r="528" spans="1:26" ht="13">
       <c r="A528" s="1"/>
       <c r="B528" s="1"/>
       <c r="C528" s="1"/>
@@ -16910,7 +16881,7 @@
       <c r="Y528" s="1"/>
       <c r="Z528" s="1"/>
     </row>
-    <row r="529">
+    <row r="529" spans="1:26" ht="13">
       <c r="A529" s="1"/>
       <c r="B529" s="1"/>
       <c r="C529" s="1"/>
@@ -16938,7 +16909,7 @@
       <c r="Y529" s="1"/>
       <c r="Z529" s="1"/>
     </row>
-    <row r="530">
+    <row r="530" spans="1:26" ht="13">
       <c r="A530" s="1"/>
       <c r="B530" s="1"/>
       <c r="C530" s="1"/>
@@ -16966,7 +16937,7 @@
       <c r="Y530" s="1"/>
       <c r="Z530" s="1"/>
     </row>
-    <row r="531">
+    <row r="531" spans="1:26" ht="13">
       <c r="A531" s="1"/>
       <c r="B531" s="1"/>
       <c r="C531" s="1"/>
@@ -16994,7 +16965,7 @@
       <c r="Y531" s="1"/>
       <c r="Z531" s="1"/>
     </row>
-    <row r="532">
+    <row r="532" spans="1:26" ht="13">
       <c r="A532" s="1"/>
       <c r="B532" s="1"/>
       <c r="C532" s="1"/>
@@ -17022,7 +16993,7 @@
       <c r="Y532" s="1"/>
       <c r="Z532" s="1"/>
     </row>
-    <row r="533">
+    <row r="533" spans="1:26" ht="13">
       <c r="A533" s="1"/>
       <c r="B533" s="1"/>
       <c r="C533" s="1"/>
@@ -17050,7 +17021,7 @@
       <c r="Y533" s="1"/>
       <c r="Z533" s="1"/>
     </row>
-    <row r="534">
+    <row r="534" spans="1:26" ht="13">
       <c r="A534" s="1"/>
       <c r="B534" s="1"/>
       <c r="C534" s="1"/>
@@ -17078,7 +17049,7 @@
       <c r="Y534" s="1"/>
       <c r="Z534" s="1"/>
     </row>
-    <row r="535">
+    <row r="535" spans="1:26" ht="13">
       <c r="A535" s="1"/>
       <c r="B535" s="1"/>
       <c r="C535" s="1"/>
@@ -17106,7 +17077,7 @@
       <c r="Y535" s="1"/>
       <c r="Z535" s="1"/>
     </row>
-    <row r="536">
+    <row r="536" spans="1:26" ht="13">
       <c r="A536" s="1"/>
       <c r="B536" s="1"/>
       <c r="C536" s="1"/>
@@ -17134,7 +17105,7 @@
       <c r="Y536" s="1"/>
       <c r="Z536" s="1"/>
     </row>
-    <row r="537">
+    <row r="537" spans="1:26" ht="13">
       <c r="A537" s="1"/>
       <c r="B537" s="1"/>
       <c r="C537" s="1"/>
@@ -17162,7 +17133,7 @@
       <c r="Y537" s="1"/>
       <c r="Z537" s="1"/>
     </row>
-    <row r="538">
+    <row r="538" spans="1:26" ht="13">
       <c r="A538" s="1"/>
       <c r="B538" s="1"/>
       <c r="C538" s="1"/>
@@ -17190,7 +17161,7 @@
       <c r="Y538" s="1"/>
       <c r="Z538" s="1"/>
     </row>
-    <row r="539">
+    <row r="539" spans="1:26" ht="13">
       <c r="A539" s="1"/>
       <c r="B539" s="1"/>
       <c r="C539" s="1"/>
@@ -17218,7 +17189,7 @@
       <c r="Y539" s="1"/>
       <c r="Z539" s="1"/>
     </row>
-    <row r="540">
+    <row r="540" spans="1:26" ht="13">
       <c r="A540" s="1"/>
       <c r="B540" s="1"/>
       <c r="C540" s="1"/>
@@ -17246,7 +17217,7 @@
       <c r="Y540" s="1"/>
       <c r="Z540" s="1"/>
     </row>
-    <row r="541">
+    <row r="541" spans="1:26" ht="13">
       <c r="A541" s="1"/>
       <c r="B541" s="1"/>
       <c r="C541" s="1"/>
@@ -17274,7 +17245,7 @@
       <c r="Y541" s="1"/>
       <c r="Z541" s="1"/>
     </row>
-    <row r="542">
+    <row r="542" spans="1:26" ht="13">
       <c r="A542" s="1"/>
       <c r="B542" s="1"/>
       <c r="C542" s="1"/>
@@ -17302,7 +17273,7 @@
       <c r="Y542" s="1"/>
       <c r="Z542" s="1"/>
     </row>
-    <row r="543">
+    <row r="543" spans="1:26" ht="13">
       <c r="A543" s="1"/>
       <c r="B543" s="1"/>
       <c r="C543" s="1"/>
@@ -17330,7 +17301,7 @@
       <c r="Y543" s="1"/>
       <c r="Z543" s="1"/>
     </row>
-    <row r="544">
+    <row r="544" spans="1:26" ht="13">
       <c r="A544" s="1"/>
       <c r="B544" s="1"/>
       <c r="C544" s="1"/>
@@ -17358,7 +17329,7 @@
       <c r="Y544" s="1"/>
       <c r="Z544" s="1"/>
     </row>
-    <row r="545">
+    <row r="545" spans="1:26" ht="13">
       <c r="A545" s="1"/>
       <c r="B545" s="1"/>
       <c r="C545" s="1"/>
@@ -17386,7 +17357,7 @@
       <c r="Y545" s="1"/>
       <c r="Z545" s="1"/>
     </row>
-    <row r="546">
+    <row r="546" spans="1:26" ht="13">
       <c r="A546" s="1"/>
       <c r="B546" s="1"/>
       <c r="C546" s="1"/>
@@ -17414,7 +17385,7 @@
       <c r="Y546" s="1"/>
       <c r="Z546" s="1"/>
     </row>
-    <row r="547">
+    <row r="547" spans="1:26" ht="13">
       <c r="A547" s="1"/>
       <c r="B547" s="1"/>
       <c r="C547" s="1"/>
@@ -17442,7 +17413,7 @@
       <c r="Y547" s="1"/>
       <c r="Z547" s="1"/>
     </row>
-    <row r="548">
+    <row r="548" spans="1:26" ht="13">
       <c r="A548" s="1"/>
       <c r="B548" s="1"/>
       <c r="C548" s="1"/>
@@ -17470,7 +17441,7 @@
       <c r="Y548" s="1"/>
       <c r="Z548" s="1"/>
     </row>
-    <row r="549">
+    <row r="549" spans="1:26" ht="13">
       <c r="A549" s="1"/>
       <c r="B549" s="1"/>
       <c r="C549" s="1"/>
@@ -17498,7 +17469,7 @@
       <c r="Y549" s="1"/>
       <c r="Z549" s="1"/>
     </row>
-    <row r="550">
+    <row r="550" spans="1:26" ht="13">
       <c r="A550" s="1"/>
       <c r="B550" s="1"/>
       <c r="C550" s="1"/>
@@ -17526,7 +17497,7 @@
       <c r="Y550" s="1"/>
       <c r="Z550" s="1"/>
     </row>
-    <row r="551">
+    <row r="551" spans="1:26" ht="13">
       <c r="A551" s="1"/>
       <c r="B551" s="1"/>
       <c r="C551" s="1"/>
@@ -17554,7 +17525,7 @@
       <c r="Y551" s="1"/>
       <c r="Z551" s="1"/>
     </row>
-    <row r="552">
+    <row r="552" spans="1:26" ht="13">
       <c r="A552" s="1"/>
       <c r="B552" s="1"/>
       <c r="C552" s="1"/>
@@ -17582,7 +17553,7 @@
       <c r="Y552" s="1"/>
       <c r="Z552" s="1"/>
     </row>
-    <row r="553">
+    <row r="553" spans="1:26" ht="13">
       <c r="A553" s="1"/>
       <c r="B553" s="1"/>
       <c r="C553" s="1"/>
@@ -17610,7 +17581,7 @@
       <c r="Y553" s="1"/>
       <c r="Z553" s="1"/>
     </row>
-    <row r="554">
+    <row r="554" spans="1:26" ht="13">
       <c r="A554" s="1"/>
       <c r="B554" s="1"/>
       <c r="C554" s="1"/>
@@ -17638,7 +17609,7 @@
       <c r="Y554" s="1"/>
       <c r="Z554" s="1"/>
     </row>
-    <row r="555">
+    <row r="555" spans="1:26" ht="13">
       <c r="A555" s="1"/>
       <c r="B555" s="1"/>
       <c r="C555" s="1"/>
@@ -17666,7 +17637,7 @@
       <c r="Y555" s="1"/>
       <c r="Z555" s="1"/>
     </row>
-    <row r="556">
+    <row r="556" spans="1:26" ht="13">
       <c r="A556" s="1"/>
       <c r="B556" s="1"/>
       <c r="C556" s="1"/>
@@ -17694,7 +17665,7 @@
       <c r="Y556" s="1"/>
       <c r="Z556" s="1"/>
     </row>
-    <row r="557">
+    <row r="557" spans="1:26" ht="13">
       <c r="A557" s="1"/>
       <c r="B557" s="1"/>
       <c r="C557" s="1"/>
@@ -17722,7 +17693,7 @@
       <c r="Y557" s="1"/>
       <c r="Z557" s="1"/>
     </row>
-    <row r="558">
+    <row r="558" spans="1:26" ht="13">
       <c r="A558" s="1"/>
       <c r="B558" s="1"/>
       <c r="C558" s="1"/>
@@ -17750,7 +17721,7 @@
       <c r="Y558" s="1"/>
       <c r="Z558" s="1"/>
     </row>
-    <row r="559">
+    <row r="559" spans="1:26" ht="13">
       <c r="A559" s="1"/>
       <c r="B559" s="1"/>
       <c r="C559" s="1"/>
@@ -17778,7 +17749,7 @@
       <c r="Y559" s="1"/>
       <c r="Z559" s="1"/>
     </row>
-    <row r="560">
+    <row r="560" spans="1:26" ht="13">
       <c r="A560" s="1"/>
       <c r="B560" s="1"/>
       <c r="C560" s="1"/>
@@ -17806,7 +17777,7 @@
       <c r="Y560" s="1"/>
       <c r="Z560" s="1"/>
     </row>
-    <row r="561">
+    <row r="561" spans="1:26" ht="13">
       <c r="A561" s="1"/>
       <c r="B561" s="1"/>
       <c r="C561" s="1"/>
@@ -17834,7 +17805,7 @@
       <c r="Y561" s="1"/>
       <c r="Z561" s="1"/>
     </row>
-    <row r="562">
+    <row r="562" spans="1:26" ht="13">
       <c r="A562" s="1"/>
       <c r="B562" s="1"/>
       <c r="C562" s="1"/>
@@ -17862,7 +17833,7 @@
       <c r="Y562" s="1"/>
       <c r="Z562" s="1"/>
     </row>
-    <row r="563">
+    <row r="563" spans="1:26" ht="13">
       <c r="A563" s="1"/>
       <c r="B563" s="1"/>
       <c r="C563" s="1"/>
@@ -17890,7 +17861,7 @@
       <c r="Y563" s="1"/>
       <c r="Z563" s="1"/>
     </row>
-    <row r="564">
+    <row r="564" spans="1:26" ht="13">
       <c r="A564" s="1"/>
       <c r="B564" s="1"/>
       <c r="C564" s="1"/>
@@ -17918,7 +17889,7 @@
       <c r="Y564" s="1"/>
       <c r="Z564" s="1"/>
     </row>
-    <row r="565">
+    <row r="565" spans="1:26" ht="13">
       <c r="A565" s="1"/>
       <c r="B565" s="1"/>
       <c r="C565" s="1"/>
@@ -17946,7 +17917,7 @@
       <c r="Y565" s="1"/>
       <c r="Z565" s="1"/>
     </row>
-    <row r="566">
+    <row r="566" spans="1:26" ht="13">
       <c r="A566" s="1"/>
       <c r="B566" s="1"/>
       <c r="C566" s="1"/>
@@ -17974,7 +17945,7 @@
       <c r="Y566" s="1"/>
       <c r="Z566" s="1"/>
     </row>
-    <row r="567">
+    <row r="567" spans="1:26" ht="13">
       <c r="A567" s="1"/>
       <c r="B567" s="1"/>
       <c r="C567" s="1"/>
@@ -18002,7 +17973,7 @@
       <c r="Y567" s="1"/>
       <c r="Z567" s="1"/>
     </row>
-    <row r="568">
+    <row r="568" spans="1:26" ht="13">
       <c r="A568" s="1"/>
       <c r="B568" s="1"/>
       <c r="C568" s="1"/>
@@ -18030,7 +18001,7 @@
       <c r="Y568" s="1"/>
       <c r="Z568" s="1"/>
     </row>
-    <row r="569">
+    <row r="569" spans="1:26" ht="13">
       <c r="A569" s="1"/>
       <c r="B569" s="1"/>
       <c r="C569" s="1"/>
@@ -18058,7 +18029,7 @@
       <c r="Y569" s="1"/>
       <c r="Z569" s="1"/>
     </row>
-    <row r="570">
+    <row r="570" spans="1:26" ht="13">
       <c r="A570" s="1"/>
       <c r="B570" s="1"/>
       <c r="C570" s="1"/>
@@ -18086,7 +18057,7 @@
       <c r="Y570" s="1"/>
       <c r="Z570" s="1"/>
     </row>
-    <row r="571">
+    <row r="571" spans="1:26" ht="13">
       <c r="A571" s="1"/>
       <c r="B571" s="1"/>
       <c r="C571" s="1"/>
@@ -18114,7 +18085,7 @@
       <c r="Y571" s="1"/>
       <c r="Z571" s="1"/>
     </row>
-    <row r="572">
+    <row r="572" spans="1:26" ht="13">
       <c r="A572" s="1"/>
       <c r="B572" s="1"/>
       <c r="C572" s="1"/>
@@ -18142,7 +18113,7 @@
       <c r="Y572" s="1"/>
       <c r="Z572" s="1"/>
     </row>
-    <row r="573">
+    <row r="573" spans="1:26" ht="13">
       <c r="A573" s="1"/>
       <c r="B573" s="1"/>
       <c r="C573" s="1"/>
@@ -18170,7 +18141,7 @@
       <c r="Y573" s="1"/>
       <c r="Z573" s="1"/>
     </row>
-    <row r="574">
+    <row r="574" spans="1:26" ht="13">
       <c r="A574" s="1"/>
       <c r="B574" s="1"/>
       <c r="C574" s="1"/>
@@ -18198,7 +18169,7 @@
       <c r="Y574" s="1"/>
       <c r="Z574" s="1"/>
     </row>
-    <row r="575">
+    <row r="575" spans="1:26" ht="13">
       <c r="A575" s="1"/>
       <c r="B575" s="1"/>
       <c r="C575" s="1"/>
@@ -18226,7 +18197,7 @@
       <c r="Y575" s="1"/>
       <c r="Z575" s="1"/>
     </row>
-    <row r="576">
+    <row r="576" spans="1:26" ht="13">
       <c r="A576" s="1"/>
       <c r="B576" s="1"/>
       <c r="C576" s="1"/>
@@ -18254,7 +18225,7 @@
       <c r="Y576" s="1"/>
       <c r="Z576" s="1"/>
     </row>
-    <row r="577">
+    <row r="577" spans="1:26" ht="13">
       <c r="A577" s="1"/>
       <c r="B577" s="1"/>
       <c r="C577" s="1"/>
@@ -18282,7 +18253,7 @@
       <c r="Y577" s="1"/>
       <c r="Z577" s="1"/>
     </row>
-    <row r="578">
+    <row r="578" spans="1:26" ht="13">
       <c r="A578" s="1"/>
       <c r="B578" s="1"/>
       <c r="C578" s="1"/>
@@ -18310,7 +18281,7 @@
       <c r="Y578" s="1"/>
       <c r="Z578" s="1"/>
     </row>
-    <row r="579">
+    <row r="579" spans="1:26" ht="13">
       <c r="A579" s="1"/>
       <c r="B579" s="1"/>
       <c r="C579" s="1"/>
@@ -18338,7 +18309,7 @@
       <c r="Y579" s="1"/>
       <c r="Z579" s="1"/>
     </row>
-    <row r="580">
+    <row r="580" spans="1:26" ht="13">
       <c r="A580" s="1"/>
       <c r="B580" s="1"/>
       <c r="C580" s="1"/>
@@ -18366,7 +18337,7 @@
       <c r="Y580" s="1"/>
       <c r="Z580" s="1"/>
     </row>
-    <row r="581">
+    <row r="581" spans="1:26" ht="13">
       <c r="A581" s="1"/>
       <c r="B581" s="1"/>
       <c r="C581" s="1"/>
@@ -18394,7 +18365,7 @@
       <c r="Y581" s="1"/>
       <c r="Z581" s="1"/>
     </row>
-    <row r="582">
+    <row r="582" spans="1:26" ht="13">
       <c r="A582" s="1"/>
       <c r="B582" s="1"/>
       <c r="C582" s="1"/>
@@ -18422,7 +18393,7 @@
       <c r="Y582" s="1"/>
       <c r="Z582" s="1"/>
     </row>
-    <row r="583">
+    <row r="583" spans="1:26" ht="13">
       <c r="A583" s="1"/>
       <c r="B583" s="1"/>
       <c r="C583" s="1"/>
@@ -18450,7 +18421,7 @@
       <c r="Y583" s="1"/>
       <c r="Z583" s="1"/>
     </row>
-    <row r="584">
+    <row r="584" spans="1:26" ht="13">
       <c r="A584" s="1"/>
       <c r="B584" s="1"/>
       <c r="C584" s="1"/>
@@ -18478,7 +18449,7 @@
       <c r="Y584" s="1"/>
       <c r="Z584" s="1"/>
     </row>
-    <row r="585">
+    <row r="585" spans="1:26" ht="13">
       <c r="A585" s="1"/>
       <c r="B585" s="1"/>
       <c r="C585" s="1"/>
@@ -18506,7 +18477,7 @@
       <c r="Y585" s="1"/>
       <c r="Z585" s="1"/>
     </row>
-    <row r="586">
+    <row r="586" spans="1:26" ht="13">
       <c r="A586" s="1"/>
       <c r="B586" s="1"/>
       <c r="C586" s="1"/>
@@ -18534,7 +18505,7 @@
       <c r="Y586" s="1"/>
       <c r="Z586" s="1"/>
     </row>
-    <row r="587">
+    <row r="587" spans="1:26" ht="13">
       <c r="A587" s="1"/>
       <c r="B587" s="1"/>
       <c r="C587" s="1"/>
@@ -18562,7 +18533,7 @@
       <c r="Y587" s="1"/>
       <c r="Z587" s="1"/>
     </row>
-    <row r="588">
+    <row r="588" spans="1:26" ht="13">
       <c r="A588" s="1"/>
       <c r="B588" s="1"/>
       <c r="C588" s="1"/>
@@ -18590,7 +18561,7 @@
       <c r="Y588" s="1"/>
       <c r="Z588" s="1"/>
     </row>
-    <row r="589">
+    <row r="589" spans="1:26" ht="13">
       <c r="A589" s="1"/>
       <c r="B589" s="1"/>
       <c r="C589" s="1"/>
@@ -18618,7 +18589,7 @@
       <c r="Y589" s="1"/>
       <c r="Z589" s="1"/>
     </row>
-    <row r="590">
+    <row r="590" spans="1:26" ht="13">
       <c r="A590" s="1"/>
       <c r="B590" s="1"/>
       <c r="C590" s="1"/>
@@ -18646,7 +18617,7 @@
       <c r="Y590" s="1"/>
       <c r="Z590" s="1"/>
     </row>
-    <row r="591">
+    <row r="591" spans="1:26" ht="13">
       <c r="A591" s="1"/>
       <c r="B591" s="1"/>
       <c r="C591" s="1"/>
@@ -18674,7 +18645,7 @@
       <c r="Y591" s="1"/>
       <c r="Z591" s="1"/>
     </row>
-    <row r="592">
+    <row r="592" spans="1:26" ht="13">
       <c r="A592" s="1"/>
       <c r="B592" s="1"/>
       <c r="C592" s="1"/>
@@ -18702,7 +18673,7 @@
       <c r="Y592" s="1"/>
       <c r="Z592" s="1"/>
     </row>
-    <row r="593">
+    <row r="593" spans="1:26" ht="13">
       <c r="A593" s="1"/>
       <c r="B593" s="1"/>
       <c r="C593" s="1"/>
@@ -18730,7 +18701,7 @@
       <c r="Y593" s="1"/>
       <c r="Z593" s="1"/>
     </row>
-    <row r="594">
+    <row r="594" spans="1:26" ht="13">
       <c r="A594" s="1"/>
       <c r="B594" s="1"/>
       <c r="C594" s="1"/>
@@ -18758,7 +18729,7 @@
       <c r="Y594" s="1"/>
       <c r="Z594" s="1"/>
     </row>
-    <row r="595">
+    <row r="595" spans="1:26" ht="13">
       <c r="A595" s="1"/>
       <c r="B595" s="1"/>
       <c r="C595" s="1"/>
@@ -18786,7 +18757,7 @@
       <c r="Y595" s="1"/>
       <c r="Z595" s="1"/>
     </row>
-    <row r="596">
+    <row r="596" spans="1:26" ht="13">
       <c r="A596" s="1"/>
       <c r="B596" s="1"/>
       <c r="C596" s="1"/>
@@ -18814,7 +18785,7 @@
       <c r="Y596" s="1"/>
       <c r="Z596" s="1"/>
     </row>
-    <row r="597">
+    <row r="597" spans="1:26" ht="13">
       <c r="A597" s="1"/>
       <c r="B597" s="1"/>
       <c r="C597" s="1"/>
@@ -18842,7 +18813,7 @@
       <c r="Y597" s="1"/>
       <c r="Z597" s="1"/>
     </row>
-    <row r="598">
+    <row r="598" spans="1:26" ht="13">
       <c r="A598" s="1"/>
       <c r="B598" s="1"/>
       <c r="C598" s="1"/>
@@ -18870,7 +18841,7 @@
       <c r="Y598" s="1"/>
       <c r="Z598" s="1"/>
     </row>
-    <row r="599">
+    <row r="599" spans="1:26" ht="13">
       <c r="A599" s="1"/>
       <c r="B599" s="1"/>
       <c r="C599" s="1"/>
@@ -18898,7 +18869,7 @@
       <c r="Y599" s="1"/>
       <c r="Z599" s="1"/>
     </row>
-    <row r="600">
+    <row r="600" spans="1:26" ht="13">
       <c r="A600" s="1"/>
       <c r="B600" s="1"/>
       <c r="C600" s="1"/>
@@ -18926,7 +18897,7 @@
       <c r="Y600" s="1"/>
       <c r="Z600" s="1"/>
     </row>
-    <row r="601">
+    <row r="601" spans="1:26" ht="13">
       <c r="A601" s="1"/>
       <c r="B601" s="1"/>
       <c r="C601" s="1"/>
@@ -18954,7 +18925,7 @@
       <c r="Y601" s="1"/>
       <c r="Z601" s="1"/>
     </row>
-    <row r="602">
+    <row r="602" spans="1:26" ht="13">
       <c r="A602" s="1"/>
       <c r="B602" s="1"/>
       <c r="C602" s="1"/>
@@ -18982,7 +18953,7 @@
       <c r="Y602" s="1"/>
       <c r="Z602" s="1"/>
     </row>
-    <row r="603">
+    <row r="603" spans="1:26" ht="13">
       <c r="A603" s="1"/>
       <c r="B603" s="1"/>
       <c r="C603" s="1"/>
@@ -19010,7 +18981,7 @@
       <c r="Y603" s="1"/>
       <c r="Z603" s="1"/>
     </row>
-    <row r="604">
+    <row r="604" spans="1:26" ht="13">
       <c r="A604" s="1"/>
       <c r="B604" s="1"/>
       <c r="C604" s="1"/>
@@ -19038,7 +19009,7 @@
       <c r="Y604" s="1"/>
       <c r="Z604" s="1"/>
     </row>
-    <row r="605">
+    <row r="605" spans="1:26" ht="13">
       <c r="A605" s="1"/>
       <c r="B605" s="1"/>
       <c r="C605" s="1"/>
@@ -19066,7 +19037,7 @@
       <c r="Y605" s="1"/>
       <c r="Z605" s="1"/>
     </row>
-    <row r="606">
+    <row r="606" spans="1:26" ht="13">
       <c r="A606" s="1"/>
       <c r="B606" s="1"/>
       <c r="C606" s="1"/>
@@ -19094,7 +19065,7 @@
       <c r="Y606" s="1"/>
       <c r="Z606" s="1"/>
     </row>
-    <row r="607">
+    <row r="607" spans="1:26" ht="13">
       <c r="A607" s="1"/>
       <c r="B607" s="1"/>
       <c r="C607" s="1"/>
@@ -19122,7 +19093,7 @@
       <c r="Y607" s="1"/>
       <c r="Z607" s="1"/>
     </row>
-    <row r="608">
+    <row r="608" spans="1:26" ht="13">
       <c r="A608" s="1"/>
       <c r="B608" s="1"/>
       <c r="C608" s="1"/>
@@ -19150,7 +19121,7 @@
       <c r="Y608" s="1"/>
       <c r="Z608" s="1"/>
     </row>
-    <row r="609">
+    <row r="609" spans="1:26" ht="13">
       <c r="A609" s="1"/>
       <c r="B609" s="1"/>
       <c r="C609" s="1"/>
@@ -19178,7 +19149,7 @@
       <c r="Y609" s="1"/>
       <c r="Z609" s="1"/>
     </row>
-    <row r="610">
+    <row r="610" spans="1:26" ht="13">
       <c r="A610" s="1"/>
       <c r="B610" s="1"/>
       <c r="C610" s="1"/>
@@ -19206,7 +19177,7 @@
       <c r="Y610" s="1"/>
       <c r="Z610" s="1"/>
     </row>
-    <row r="611">
+    <row r="611" spans="1:26" ht="13">
       <c r="A611" s="1"/>
       <c r="B611" s="1"/>
       <c r="C611" s="1"/>
@@ -19234,7 +19205,7 @@
       <c r="Y611" s="1"/>
       <c r="Z611" s="1"/>
     </row>
-    <row r="612">
+    <row r="612" spans="1:26" ht="13">
       <c r="A612" s="1"/>
       <c r="B612" s="1"/>
       <c r="C612" s="1"/>
@@ -19262,7 +19233,7 @@
       <c r="Y612" s="1"/>
       <c r="Z612" s="1"/>
     </row>
-    <row r="613">
+    <row r="613" spans="1:26" ht="13">
       <c r="A613" s="1"/>
       <c r="B613" s="1"/>
       <c r="C613" s="1"/>
@@ -19290,7 +19261,7 @@
       <c r="Y613" s="1"/>
       <c r="Z613" s="1"/>
     </row>
-    <row r="614">
+    <row r="614" spans="1:26" ht="13">
       <c r="A614" s="1"/>
       <c r="B614" s="1"/>
       <c r="C614" s="1"/>
@@ -19318,7 +19289,7 @@
       <c r="Y614" s="1"/>
       <c r="Z614" s="1"/>
     </row>
-    <row r="615">
+    <row r="615" spans="1:26" ht="13">
       <c r="A615" s="1"/>
       <c r="B615" s="1"/>
       <c r="C615" s="1"/>
@@ -19346,7 +19317,7 @@
       <c r="Y615" s="1"/>
       <c r="Z615" s="1"/>
     </row>
-    <row r="616">
+    <row r="616" spans="1:26" ht="13">
       <c r="A616" s="1"/>
       <c r="B616" s="1"/>
       <c r="C616" s="1"/>
@@ -19374,7 +19345,7 @@
       <c r="Y616" s="1"/>
       <c r="Z616" s="1"/>
     </row>
-    <row r="617">
+    <row r="617" spans="1:26" ht="13">
       <c r="A617" s="1"/>
       <c r="B617" s="1"/>
       <c r="C617" s="1"/>
@@ -19402,7 +19373,7 @@
       <c r="Y617" s="1"/>
       <c r="Z617" s="1"/>
     </row>
-    <row r="618">
+    <row r="618" spans="1:26" ht="13">
       <c r="A618" s="1"/>
       <c r="B618" s="1"/>
       <c r="C618" s="1"/>
@@ -19430,7 +19401,7 @@
       <c r="Y618" s="1"/>
       <c r="Z618" s="1"/>
     </row>
-    <row r="619">
+    <row r="619" spans="1:26" ht="13">
       <c r="A619" s="1"/>
       <c r="B619" s="1"/>
       <c r="C619" s="1"/>
@@ -19458,7 +19429,7 @@
       <c r="Y619" s="1"/>
       <c r="Z619" s="1"/>
     </row>
-    <row r="620">
+    <row r="620" spans="1:26" ht="13">
       <c r="A620" s="1"/>
       <c r="B620" s="1"/>
       <c r="C620" s="1"/>
@@ -19486,7 +19457,7 @@
       <c r="Y620" s="1"/>
       <c r="Z620" s="1"/>
     </row>
-    <row r="621">
+    <row r="621" spans="1:26" ht="13">
       <c r="A621" s="1"/>
       <c r="B621" s="1"/>
       <c r="C621" s="1"/>
@@ -19514,7 +19485,7 @@
       <c r="Y621" s="1"/>
       <c r="Z621" s="1"/>
     </row>
-    <row r="622">
+    <row r="622" spans="1:26" ht="13">
       <c r="A622" s="1"/>
       <c r="B622" s="1"/>
       <c r="C622" s="1"/>
@@ -19542,7 +19513,7 @@
       <c r="Y622" s="1"/>
       <c r="Z622" s="1"/>
     </row>
-    <row r="623">
+    <row r="623" spans="1:26" ht="13">
       <c r="A623" s="1"/>
       <c r="B623" s="1"/>
       <c r="C623" s="1"/>
@@ -19570,7 +19541,7 @@
       <c r="Y623" s="1"/>
       <c r="Z623" s="1"/>
     </row>
-    <row r="624">
+    <row r="624" spans="1:26" ht="13">
       <c r="A624" s="1"/>
       <c r="B624" s="1"/>
       <c r="C624" s="1"/>
@@ -19598,7 +19569,7 @@
       <c r="Y624" s="1"/>
       <c r="Z624" s="1"/>
     </row>
-    <row r="625">
+    <row r="625" spans="1:26" ht="13">
       <c r="A625" s="1"/>
       <c r="B625" s="1"/>
       <c r="C625" s="1"/>
@@ -19626,7 +19597,7 @@
       <c r="Y625" s="1"/>
       <c r="Z625" s="1"/>
     </row>
-    <row r="626">
+    <row r="626" spans="1:26" ht="13">
       <c r="A626" s="1"/>
       <c r="B626" s="1"/>
       <c r="C626" s="1"/>
@@ -19654,7 +19625,7 @@
       <c r="Y626" s="1"/>
       <c r="Z626" s="1"/>
     </row>
-    <row r="627">
+    <row r="627" spans="1:26" ht="13">
       <c r="A627" s="1"/>
       <c r="B627" s="1"/>
       <c r="C627" s="1"/>
@@ -19682,7 +19653,7 @@
       <c r="Y627" s="1"/>
       <c r="Z627" s="1"/>
     </row>
-    <row r="628">
+    <row r="628" spans="1:26" ht="13">
       <c r="A628" s="1"/>
       <c r="B628" s="1"/>
       <c r="C628" s="1"/>
@@ -19710,7 +19681,7 @@
       <c r="Y628" s="1"/>
       <c r="Z628" s="1"/>
     </row>
-    <row r="629">
+    <row r="629" spans="1:26" ht="13">
       <c r="A629" s="1"/>
       <c r="B629" s="1"/>
       <c r="C629" s="1"/>
@@ -19738,7 +19709,7 @@
       <c r="Y629" s="1"/>
       <c r="Z629" s="1"/>
     </row>
-    <row r="630">
+    <row r="630" spans="1:26" ht="13">
       <c r="A630" s="1"/>
       <c r="B630" s="1"/>
       <c r="C630" s="1"/>
@@ -19766,7 +19737,7 @@
       <c r="Y630" s="1"/>
       <c r="Z630" s="1"/>
     </row>
-    <row r="631">
+    <row r="631" spans="1:26" ht="13">
       <c r="A631" s="1"/>
       <c r="B631" s="1"/>
       <c r="C631" s="1"/>
@@ -19794,7 +19765,7 @@
       <c r="Y631" s="1"/>
       <c r="Z631" s="1"/>
     </row>
-    <row r="632">
+    <row r="632" spans="1:26" ht="13">
       <c r="A632" s="1"/>
       <c r="B632" s="1"/>
       <c r="C632" s="1"/>
@@ -19822,7 +19793,7 @@
       <c r="Y632" s="1"/>
       <c r="Z632" s="1"/>
     </row>
-    <row r="633">
+    <row r="633" spans="1:26" ht="13">
       <c r="A633" s="1"/>
       <c r="B633" s="1"/>
       <c r="C633" s="1"/>
@@ -19850,7 +19821,7 @@
       <c r="Y633" s="1"/>
       <c r="Z633" s="1"/>
     </row>
-    <row r="634">
+    <row r="634" spans="1:26" ht="13">
       <c r="A634" s="1"/>
       <c r="B634" s="1"/>
       <c r="C634" s="1"/>
@@ -19878,7 +19849,7 @@
       <c r="Y634" s="1"/>
       <c r="Z634" s="1"/>
     </row>
-    <row r="635">
+    <row r="635" spans="1:26" ht="13">
       <c r="A635" s="1"/>
       <c r="B635" s="1"/>
       <c r="C635" s="1"/>
@@ -19906,7 +19877,7 @@
       <c r="Y635" s="1"/>
       <c r="Z635" s="1"/>
     </row>
-    <row r="636">
+    <row r="636" spans="1:26" ht="13">
       <c r="A636" s="1"/>
       <c r="B636" s="1"/>
       <c r="C636" s="1"/>
@@ -19934,7 +19905,7 @@
       <c r="Y636" s="1"/>
       <c r="Z636" s="1"/>
     </row>
-    <row r="637">
+    <row r="637" spans="1:26" ht="13">
       <c r="A637" s="1"/>
       <c r="B637" s="1"/>
       <c r="C637" s="1"/>
@@ -19962,7 +19933,7 @@
       <c r="Y637" s="1"/>
       <c r="Z637" s="1"/>
     </row>
-    <row r="638">
+    <row r="638" spans="1:26" ht="13">
       <c r="A638" s="1"/>
       <c r="B638" s="1"/>
       <c r="C638" s="1"/>
@@ -19990,7 +19961,7 @@
       <c r="Y638" s="1"/>
       <c r="Z638" s="1"/>
     </row>
-    <row r="639">
+    <row r="639" spans="1:26" ht="13">
       <c r="A639" s="1"/>
       <c r="B639" s="1"/>
       <c r="C639" s="1"/>
@@ -20018,7 +19989,7 @@
       <c r="Y639" s="1"/>
       <c r="Z639" s="1"/>
     </row>
-    <row r="640">
+    <row r="640" spans="1:26" ht="13">
       <c r="A640" s="1"/>
       <c r="B640" s="1"/>
       <c r="C640" s="1"/>
@@ -20046,7 +20017,7 @@
       <c r="Y640" s="1"/>
       <c r="Z640" s="1"/>
     </row>
-    <row r="641">
+    <row r="641" spans="1:26" ht="13">
       <c r="A641" s="1"/>
       <c r="B641" s="1"/>
       <c r="C641" s="1"/>
@@ -20074,7 +20045,7 @@
       <c r="Y641" s="1"/>
       <c r="Z641" s="1"/>
     </row>
-    <row r="642">
+    <row r="642" spans="1:26" ht="13">
       <c r="A642" s="1"/>
       <c r="B642" s="1"/>
       <c r="C642" s="1"/>
@@ -20102,7 +20073,7 @@
       <c r="Y642" s="1"/>
       <c r="Z642" s="1"/>
     </row>
-    <row r="643">
+    <row r="643" spans="1:26" ht="13">
       <c r="A643" s="1"/>
       <c r="B643" s="1"/>
       <c r="C643" s="1"/>
@@ -20130,7 +20101,7 @@
       <c r="Y643" s="1"/>
       <c r="Z643" s="1"/>
     </row>
-    <row r="644">
+    <row r="644" spans="1:26" ht="13">
       <c r="A644" s="1"/>
       <c r="B644" s="1"/>
       <c r="C644" s="1"/>
@@ -20158,7 +20129,7 @@
       <c r="Y644" s="1"/>
       <c r="Z644" s="1"/>
     </row>
-    <row r="645">
+    <row r="645" spans="1:26" ht="13">
       <c r="A645" s="1"/>
       <c r="B645" s="1"/>
       <c r="C645" s="1"/>
@@ -20186,7 +20157,7 @@
       <c r="Y645" s="1"/>
       <c r="Z645" s="1"/>
     </row>
-    <row r="646">
+    <row r="646" spans="1:26" ht="13">
       <c r="A646" s="1"/>
       <c r="B646" s="1"/>
       <c r="C646" s="1"/>
@@ -20214,7 +20185,7 @@
       <c r="Y646" s="1"/>
       <c r="Z646" s="1"/>
     </row>
-    <row r="647">
+    <row r="647" spans="1:26" ht="13">
       <c r="A647" s="1"/>
       <c r="B647" s="1"/>
       <c r="C647" s="1"/>
@@ -20242,7 +20213,7 @@
       <c r="Y647" s="1"/>
       <c r="Z647" s="1"/>
     </row>
-    <row r="648">
+    <row r="648" spans="1:26" ht="13">
       <c r="A648" s="1"/>
       <c r="B648" s="1"/>
       <c r="C648" s="1"/>
@@ -20270,7 +20241,7 @@
       <c r="Y648" s="1"/>
       <c r="Z648" s="1"/>
     </row>
-    <row r="649">
+    <row r="649" spans="1:26" ht="13">
       <c r="A649" s="1"/>
       <c r="B649" s="1"/>
       <c r="C649" s="1"/>
@@ -20298,7 +20269,7 @@
       <c r="Y649" s="1"/>
       <c r="Z649" s="1"/>
     </row>
-    <row r="650">
+    <row r="650" spans="1:26" ht="13">
       <c r="A650" s="1"/>
       <c r="B650" s="1"/>
       <c r="C650" s="1"/>
@@ -20326,7 +20297,7 @@
       <c r="Y650" s="1"/>
       <c r="Z650" s="1"/>
     </row>
-    <row r="651">
+    <row r="651" spans="1:26" ht="13">
       <c r="A651" s="1"/>
       <c r="B651" s="1"/>
       <c r="C651" s="1"/>
@@ -20354,7 +20325,7 @@
       <c r="Y651" s="1"/>
       <c r="Z651" s="1"/>
     </row>
-    <row r="652">
+    <row r="652" spans="1:26" ht="13">
       <c r="A652" s="1"/>
       <c r="B652" s="1"/>
       <c r="C652" s="1"/>
@@ -20382,7 +20353,7 @@
       <c r="Y652" s="1"/>
       <c r="Z652" s="1"/>
     </row>
-    <row r="653">
+    <row r="653" spans="1:26" ht="13">
       <c r="A653" s="1"/>
       <c r="B653" s="1"/>
       <c r="C653" s="1"/>
@@ -20410,7 +20381,7 @@
       <c r="Y653" s="1"/>
       <c r="Z653" s="1"/>
     </row>
-    <row r="654">
+    <row r="654" spans="1:26" ht="13">
       <c r="A654" s="1"/>
       <c r="B654" s="1"/>
       <c r="C654" s="1"/>
@@ -20438,7 +20409,7 @@
       <c r="Y654" s="1"/>
       <c r="Z654" s="1"/>
     </row>
-    <row r="655">
+    <row r="655" spans="1:26" ht="13">
       <c r="A655" s="1"/>
       <c r="B655" s="1"/>
       <c r="C655" s="1"/>
@@ -20466,7 +20437,7 @@
       <c r="Y655" s="1"/>
       <c r="Z655" s="1"/>
     </row>
-    <row r="656">
+    <row r="656" spans="1:26" ht="13">
       <c r="A656" s="1"/>
       <c r="B656" s="1"/>
       <c r="C656" s="1"/>
@@ -20494,7 +20465,7 @@
       <c r="Y656" s="1"/>
       <c r="Z656" s="1"/>
     </row>
-    <row r="657">
+    <row r="657" spans="1:26" ht="13">
       <c r="A657" s="1"/>
       <c r="B657" s="1"/>
       <c r="C657" s="1"/>
@@ -20522,7 +20493,7 @@
       <c r="Y657" s="1"/>
       <c r="Z657" s="1"/>
     </row>
-    <row r="658">
+    <row r="658" spans="1:26" ht="13">
       <c r="A658" s="1"/>
       <c r="B658" s="1"/>
       <c r="C658" s="1"/>
@@ -20550,7 +20521,7 @@
       <c r="Y658" s="1"/>
       <c r="Z658" s="1"/>
     </row>
-    <row r="659">
+    <row r="659" spans="1:26" ht="13">
       <c r="A659" s="1"/>
       <c r="B659" s="1"/>
       <c r="C659" s="1"/>
@@ -20578,7 +20549,7 @@
       <c r="Y659" s="1"/>
       <c r="Z659" s="1"/>
     </row>
-    <row r="660">
+    <row r="660" spans="1:26" ht="13">
       <c r="A660" s="1"/>
       <c r="B660" s="1"/>
       <c r="C660" s="1"/>
@@ -20606,7 +20577,7 @@
       <c r="Y660" s="1"/>
       <c r="Z660" s="1"/>
     </row>
-    <row r="661">
+    <row r="661" spans="1:26" ht="13">
       <c r="A661" s="1"/>
       <c r="B661" s="1"/>
       <c r="C661" s="1"/>
@@ -20634,7 +20605,7 @@
       <c r="Y661" s="1"/>
       <c r="Z661" s="1"/>
     </row>
-    <row r="662">
+    <row r="662" spans="1:26" ht="13">
       <c r="A662" s="1"/>
       <c r="B662" s="1"/>
       <c r="C662" s="1"/>
@@ -20662,7 +20633,7 @@
       <c r="Y662" s="1"/>
       <c r="Z662" s="1"/>
     </row>
-    <row r="663">
+    <row r="663" spans="1:26" ht="13">
       <c r="A663" s="1"/>
       <c r="B663" s="1"/>
       <c r="C663" s="1"/>
@@ -20690,7 +20661,7 @@
       <c r="Y663" s="1"/>
       <c r="Z663" s="1"/>
     </row>
-    <row r="664">
+    <row r="664" spans="1:26" ht="13">
       <c r="A664" s="1"/>
       <c r="B664" s="1"/>
       <c r="C664" s="1"/>
@@ -20718,7 +20689,7 @@
       <c r="Y664" s="1"/>
       <c r="Z664" s="1"/>
     </row>
-    <row r="665">
+    <row r="665" spans="1:26" ht="13">
       <c r="A665" s="1"/>
       <c r="B665" s="1"/>
       <c r="C665" s="1"/>
@@ -20746,7 +20717,7 @@
       <c r="Y665" s="1"/>
       <c r="Z665" s="1"/>
     </row>
-    <row r="666">
+    <row r="666" spans="1:26" ht="13">
       <c r="A666" s="1"/>
       <c r="B666" s="1"/>
       <c r="C666" s="1"/>
@@ -20774,7 +20745,7 @@
       <c r="Y666" s="1"/>
       <c r="Z666" s="1"/>
     </row>
-    <row r="667">
+    <row r="667" spans="1:26" ht="13">
       <c r="A667" s="1"/>
       <c r="B667" s="1"/>
       <c r="C667" s="1"/>
@@ -20802,7 +20773,7 @@
       <c r="Y667" s="1"/>
       <c r="Z667" s="1"/>
     </row>
-    <row r="668">
+    <row r="668" spans="1:26" ht="13">
       <c r="A668" s="1"/>
       <c r="B668" s="1"/>
       <c r="C668" s="1"/>
@@ -20830,7 +20801,7 @@
       <c r="Y668" s="1"/>
       <c r="Z668" s="1"/>
     </row>
-    <row r="669">
+    <row r="669" spans="1:26" ht="13">
       <c r="A669" s="1"/>
       <c r="B669" s="1"/>
       <c r="C669" s="1"/>
@@ -20858,7 +20829,7 @@
       <c r="Y669" s="1"/>
       <c r="Z669" s="1"/>
     </row>
-    <row r="670">
+    <row r="670" spans="1:26" ht="13">
       <c r="A670" s="1"/>
       <c r="B670" s="1"/>
       <c r="C670" s="1"/>
@@ -20886,7 +20857,7 @@
       <c r="Y670" s="1"/>
       <c r="Z670" s="1"/>
     </row>
-    <row r="671">
+    <row r="671" spans="1:26" ht="13">
       <c r="A671" s="1"/>
       <c r="B671" s="1"/>
       <c r="C671" s="1"/>
@@ -20914,7 +20885,7 @@
       <c r="Y671" s="1"/>
       <c r="Z671" s="1"/>
     </row>
-    <row r="672">
+    <row r="672" spans="1:26" ht="13">
       <c r="A672" s="1"/>
       <c r="B672" s="1"/>
       <c r="C672" s="1"/>
@@ -20942,7 +20913,7 @@
       <c r="Y672" s="1"/>
       <c r="Z672" s="1"/>
     </row>
-    <row r="673">
+    <row r="673" spans="1:26" ht="13">
       <c r="A673" s="1"/>
       <c r="B673" s="1"/>
       <c r="C673" s="1"/>
@@ -20970,7 +20941,7 @@
       <c r="Y673" s="1"/>
       <c r="Z673" s="1"/>
     </row>
-    <row r="674">
+    <row r="674" spans="1:26" ht="13">
       <c r="A674" s="1"/>
       <c r="B674" s="1"/>
       <c r="C674" s="1"/>
@@ -20998,7 +20969,7 @@
       <c r="Y674" s="1"/>
       <c r="Z674" s="1"/>
     </row>
-    <row r="675">
+    <row r="675" spans="1:26" ht="13">
       <c r="A675" s="1"/>
       <c r="B675" s="1"/>
       <c r="C675" s="1"/>
@@ -21026,7 +20997,7 @@
       <c r="Y675" s="1"/>
       <c r="Z675" s="1"/>
     </row>
-    <row r="676">
+    <row r="676" spans="1:26" ht="13">
       <c r="A676" s="1"/>
       <c r="B676" s="1"/>
       <c r="C676" s="1"/>
@@ -21054,7 +21025,7 @@
       <c r="Y676" s="1"/>
       <c r="Z676" s="1"/>
     </row>
-    <row r="677">
+    <row r="677" spans="1:26" ht="13">
       <c r="A677" s="1"/>
       <c r="B677" s="1"/>
       <c r="C677" s="1"/>
@@ -21082,7 +21053,7 @@
       <c r="Y677" s="1"/>
       <c r="Z677" s="1"/>
     </row>
-    <row r="678">
+    <row r="678" spans="1:26" ht="13">
       <c r="A678" s="1"/>
       <c r="B678" s="1"/>
       <c r="C678" s="1"/>
@@ -21110,7 +21081,7 @@
       <c r="Y678" s="1"/>
       <c r="Z678" s="1"/>
     </row>
-    <row r="679">
+    <row r="679" spans="1:26" ht="13">
       <c r="A679" s="1"/>
       <c r="B679" s="1"/>
       <c r="C679" s="1"/>
@@ -21138,7 +21109,7 @@
       <c r="Y679" s="1"/>
       <c r="Z679" s="1"/>
     </row>
-    <row r="680">
+    <row r="680" spans="1:26" ht="13">
       <c r="A680" s="1"/>
       <c r="B680" s="1"/>
       <c r="C680" s="1"/>
@@ -21166,7 +21137,7 @@
       <c r="Y680" s="1"/>
       <c r="Z680" s="1"/>
     </row>
-    <row r="681">
+    <row r="681" spans="1:26" ht="13">
       <c r="A681" s="1"/>
       <c r="B681" s="1"/>
       <c r="C681" s="1"/>
@@ -21194,7 +21165,7 @@
       <c r="Y681" s="1"/>
       <c r="Z681" s="1"/>
     </row>
-    <row r="682">
+    <row r="682" spans="1:26" ht="13">
       <c r="A682" s="1"/>
       <c r="B682" s="1"/>
       <c r="C682" s="1"/>
@@ -21222,7 +21193,7 @@
       <c r="Y682" s="1"/>
       <c r="Z682" s="1"/>
     </row>
-    <row r="683">
+    <row r="683" spans="1:26" ht="13">
       <c r="A683" s="1"/>
       <c r="B683" s="1"/>
       <c r="C683" s="1"/>
@@ -21250,7 +21221,7 @@
       <c r="Y683" s="1"/>
       <c r="Z683" s="1"/>
     </row>
-    <row r="684">
+    <row r="684" spans="1:26" ht="13">
       <c r="A684" s="1"/>
       <c r="B684" s="1"/>
       <c r="C684" s="1"/>
@@ -21278,7 +21249,7 @@
       <c r="Y684" s="1"/>
       <c r="Z684" s="1"/>
     </row>
-    <row r="685">
+    <row r="685" spans="1:26" ht="13">
       <c r="A685" s="1"/>
       <c r="B685" s="1"/>
       <c r="C685" s="1"/>
@@ -21306,7 +21277,7 @@
       <c r="Y685" s="1"/>
       <c r="Z685" s="1"/>
     </row>
-    <row r="686">
+    <row r="686" spans="1:26" ht="13">
       <c r="A686" s="1"/>
       <c r="B686" s="1"/>
       <c r="C686" s="1"/>
@@ -21334,7 +21305,7 @@
       <c r="Y686" s="1"/>
       <c r="Z686" s="1"/>
     </row>
-    <row r="687">
+    <row r="687" spans="1:26" ht="13">
       <c r="A687" s="1"/>
       <c r="B687" s="1"/>
       <c r="C687" s="1"/>
@@ -21362,7 +21333,7 @@
       <c r="Y687" s="1"/>
       <c r="Z687" s="1"/>
     </row>
-    <row r="688">
+    <row r="688" spans="1:26" ht="13">
       <c r="A688" s="1"/>
       <c r="B688" s="1"/>
       <c r="C688" s="1"/>
@@ -21390,7 +21361,7 @@
       <c r="Y688" s="1"/>
       <c r="Z688" s="1"/>
     </row>
-    <row r="689">
+    <row r="689" spans="1:26" ht="13">
       <c r="A689" s="1"/>
       <c r="B689" s="1"/>
       <c r="C689" s="1"/>
@@ -21418,7 +21389,7 @@
       <c r="Y689" s="1"/>
       <c r="Z689" s="1"/>
     </row>
-    <row r="690">
+    <row r="690" spans="1:26" ht="13">
       <c r="A690" s="1"/>
       <c r="B690" s="1"/>
       <c r="C690" s="1"/>
@@ -21446,7 +21417,7 @@
       <c r="Y690" s="1"/>
       <c r="Z690" s="1"/>
     </row>
-    <row r="691">
+    <row r="691" spans="1:26" ht="13">
       <c r="A691" s="1"/>
       <c r="B691" s="1"/>
       <c r="C691" s="1"/>
@@ -21474,7 +21445,7 @@
       <c r="Y691" s="1"/>
       <c r="Z691" s="1"/>
     </row>
-    <row r="692">
+    <row r="692" spans="1:26" ht="13">
       <c r="A692" s="1"/>
       <c r="B692" s="1"/>
       <c r="C692" s="1"/>
@@ -21502,7 +21473,7 @@
       <c r="Y692" s="1"/>
       <c r="Z692" s="1"/>
     </row>
-    <row r="693">
+    <row r="693" spans="1:26" ht="13">
       <c r="A693" s="1"/>
       <c r="B693" s="1"/>
       <c r="C693" s="1"/>
@@ -21530,7 +21501,7 @@
       <c r="Y693" s="1"/>
       <c r="Z693" s="1"/>
     </row>
-    <row r="694">
+    <row r="694" spans="1:26" ht="13">
       <c r="A694" s="1"/>
       <c r="B694" s="1"/>
       <c r="C694" s="1"/>
@@ -21558,7 +21529,7 @@
       <c r="Y694" s="1"/>
       <c r="Z694" s="1"/>
     </row>
-    <row r="695">
+    <row r="695" spans="1:26" ht="13">
       <c r="A695" s="1"/>
       <c r="B695" s="1"/>
       <c r="C695" s="1"/>
@@ -21586,7 +21557,7 @@
       <c r="Y695" s="1"/>
       <c r="Z695" s="1"/>
     </row>
-    <row r="696">
+    <row r="696" spans="1:26" ht="13">
       <c r="A696" s="1"/>
       <c r="B696" s="1"/>
       <c r="C696" s="1"/>
@@ -21614,7 +21585,7 @@
       <c r="Y696" s="1"/>
       <c r="Z696" s="1"/>
     </row>
-    <row r="697">
+    <row r="697" spans="1:26" ht="13">
       <c r="A697" s="1"/>
       <c r="B697" s="1"/>
       <c r="C697" s="1"/>
@@ -21642,7 +21613,7 @@
       <c r="Y697" s="1"/>
       <c r="Z697" s="1"/>
     </row>
-    <row r="698">
+    <row r="698" spans="1:26" ht="13">
       <c r="A698" s="1"/>
       <c r="B698" s="1"/>
       <c r="C698" s="1"/>
@@ -21670,7 +21641,7 @@
       <c r="Y698" s="1"/>
       <c r="Z698" s="1"/>
     </row>
-    <row r="699">
+    <row r="699" spans="1:26" ht="13">
       <c r="A699" s="1"/>
       <c r="B699" s="1"/>
       <c r="C699" s="1"/>
@@ -21698,7 +21669,7 @@
       <c r="Y699" s="1"/>
       <c r="Z699" s="1"/>
     </row>
-    <row r="700">
+    <row r="700" spans="1:26" ht="13">
       <c r="A700" s="1"/>
       <c r="B700" s="1"/>
       <c r="C700" s="1"/>
@@ -21726,7 +21697,7 @@
       <c r="Y700" s="1"/>
       <c r="Z700" s="1"/>
     </row>
-    <row r="701">
+    <row r="701" spans="1:26" ht="13">
       <c r="A701" s="1"/>
       <c r="B701" s="1"/>
       <c r="C701" s="1"/>
@@ -21754,7 +21725,7 @@
       <c r="Y701" s="1"/>
       <c r="Z701" s="1"/>
     </row>
-    <row r="702">
+    <row r="702" spans="1:26" ht="13">
       <c r="A702" s="1"/>
       <c r="B702" s="1"/>
       <c r="C702" s="1"/>
@@ -21782,7 +21753,7 @@
       <c r="Y702" s="1"/>
       <c r="Z702" s="1"/>
     </row>
-    <row r="703">
+    <row r="703" spans="1:26" ht="13">
       <c r="A703" s="1"/>
       <c r="B703" s="1"/>
       <c r="C703" s="1"/>
@@ -21810,7 +21781,7 @@
       <c r="Y703" s="1"/>
       <c r="Z703" s="1"/>
     </row>
-    <row r="704">
+    <row r="704" spans="1:26" ht="13">
       <c r="A704" s="1"/>
       <c r="B704" s="1"/>
       <c r="C704" s="1"/>
@@ -21838,7 +21809,7 @@
       <c r="Y704" s="1"/>
       <c r="Z704" s="1"/>
     </row>
-    <row r="705">
+    <row r="705" spans="1:26" ht="13">
       <c r="A705" s="1"/>
       <c r="B705" s="1"/>
       <c r="C705" s="1"/>
@@ -21866,7 +21837,7 @@
       <c r="Y705" s="1"/>
       <c r="Z705" s="1"/>
     </row>
-    <row r="706">
+    <row r="706" spans="1:26" ht="13">
       <c r="A706" s="1"/>
       <c r="B706" s="1"/>
       <c r="C706" s="1"/>
@@ -21894,7 +21865,7 @@
       <c r="Y706" s="1"/>
       <c r="Z706" s="1"/>
     </row>
-    <row r="707">
+    <row r="707" spans="1:26" ht="13">
       <c r="A707" s="1"/>
       <c r="B707" s="1"/>
       <c r="C707" s="1"/>
@@ -21922,7 +21893,7 @@
       <c r="Y707" s="1"/>
       <c r="Z707" s="1"/>
     </row>
-    <row r="708">
+    <row r="708" spans="1:26" ht="13">
       <c r="A708" s="1"/>
       <c r="B708" s="1"/>
       <c r="C708" s="1"/>
@@ -21950,7 +21921,7 @@
       <c r="Y708" s="1"/>
       <c r="Z708" s="1"/>
     </row>
-    <row r="709">
+    <row r="709" spans="1:26" ht="13">
       <c r="A709" s="1"/>
       <c r="B709" s="1"/>
       <c r="C709" s="1"/>
@@ -21978,7 +21949,7 @@
       <c r="Y709" s="1"/>
       <c r="Z709" s="1"/>
     </row>
-    <row r="710">
+    <row r="710" spans="1:26" ht="13">
       <c r="A710" s="1"/>
       <c r="B710" s="1"/>
       <c r="C710" s="1"/>
@@ -22006,7 +21977,7 @@
       <c r="Y710" s="1"/>
       <c r="Z710" s="1"/>
     </row>
-    <row r="711">
+    <row r="711" spans="1:26" ht="13">
       <c r="A711" s="1"/>
       <c r="B711" s="1"/>
       <c r="C711" s="1"/>
@@ -22034,7 +22005,7 @@
       <c r="Y711" s="1"/>
       <c r="Z711" s="1"/>
     </row>
-    <row r="712">
+    <row r="712" spans="1:26" ht="13">
       <c r="A712" s="1"/>
       <c r="B712" s="1"/>
       <c r="C712" s="1"/>
@@ -22062,7 +22033,7 @@
       <c r="Y712" s="1"/>
       <c r="Z712" s="1"/>
     </row>
-    <row r="713">
+    <row r="713" spans="1:26" ht="13">
       <c r="A713" s="1"/>
       <c r="B713" s="1"/>
       <c r="C713" s="1"/>
@@ -22090,7 +22061,7 @@
       <c r="Y713" s="1"/>
       <c r="Z713" s="1"/>
     </row>
-    <row r="714">
+    <row r="714" spans="1:26" ht="13">
       <c r="A714" s="1"/>
       <c r="B714" s="1"/>
       <c r="C714" s="1"/>
@@ -22118,7 +22089,7 @@
       <c r="Y714" s="1"/>
       <c r="Z714" s="1"/>
     </row>
-    <row r="715">
+    <row r="715" spans="1:26" ht="13">
       <c r="A715" s="1"/>
       <c r="B715" s="1"/>
       <c r="C715" s="1"/>
@@ -22146,7 +22117,7 @@
       <c r="Y715" s="1"/>
       <c r="Z715" s="1"/>
     </row>
-    <row r="716">
+    <row r="716" spans="1:26" ht="13">
       <c r="A716" s="1"/>
       <c r="B716" s="1"/>
       <c r="C716" s="1"/>
@@ -22174,7 +22145,7 @@
       <c r="Y716" s="1"/>
       <c r="Z716" s="1"/>
     </row>
-    <row r="717">
+    <row r="717" spans="1:26" ht="13">
       <c r="A717" s="1"/>
       <c r="B717" s="1"/>
       <c r="C717" s="1"/>
@@ -22202,7 +22173,7 @@
       <c r="Y717" s="1"/>
       <c r="Z717" s="1"/>
     </row>
-    <row r="718">
+    <row r="718" spans="1:26" ht="13">
       <c r="A718" s="1"/>
       <c r="B718" s="1"/>
       <c r="C718" s="1"/>
@@ -22230,7 +22201,7 @@
       <c r="Y718" s="1"/>
       <c r="Z718" s="1"/>
     </row>
-    <row r="719">
+    <row r="719" spans="1:26" ht="13">
       <c r="A719" s="1"/>
       <c r="B719" s="1"/>
       <c r="C719" s="1"/>
@@ -22258,7 +22229,7 @@
       <c r="Y719" s="1"/>
       <c r="Z719" s="1"/>
     </row>
-    <row r="720">
+    <row r="720" spans="1:26" ht="13">
       <c r="A720" s="1"/>
       <c r="B720" s="1"/>
       <c r="C720" s="1"/>
@@ -22286,7 +22257,7 @@
       <c r="Y720" s="1"/>
       <c r="Z720" s="1"/>
     </row>
-    <row r="721">
+    <row r="721" spans="1:26" ht="13">
       <c r="A721" s="1"/>
       <c r="B721" s="1"/>
       <c r="C721" s="1"/>
@@ -22314,7 +22285,7 @@
       <c r="Y721" s="1"/>
       <c r="Z721" s="1"/>
     </row>
-    <row r="722">
+    <row r="722" spans="1:26" ht="13">
       <c r="A722" s="1"/>
       <c r="B722" s="1"/>
       <c r="C722" s="1"/>
@@ -22342,7 +22313,7 @@
       <c r="Y722" s="1"/>
       <c r="Z722" s="1"/>
     </row>
-    <row r="723">
+    <row r="723" spans="1:26" ht="13">
       <c r="A723" s="1"/>
       <c r="B723" s="1"/>
       <c r="C723" s="1"/>
@@ -22370,7 +22341,7 @@
       <c r="Y723" s="1"/>
       <c r="Z723" s="1"/>
     </row>
-    <row r="724">
+    <row r="724" spans="1:26" ht="13">
       <c r="A724" s="1"/>
       <c r="B724" s="1"/>
       <c r="C724" s="1"/>
@@ -22398,7 +22369,7 @@
       <c r="Y724" s="1"/>
       <c r="Z724" s="1"/>
     </row>
-    <row r="725">
+    <row r="725" spans="1:26" ht="13">
       <c r="A725" s="1"/>
       <c r="B725" s="1"/>
       <c r="C725" s="1"/>
@@ -22426,7 +22397,7 @@
       <c r="Y725" s="1"/>
       <c r="Z725" s="1"/>
     </row>
-    <row r="726">
+    <row r="726" spans="1:26" ht="13">
       <c r="A726" s="1"/>
       <c r="B726" s="1"/>
       <c r="C726" s="1"/>
@@ -22454,7 +22425,7 @@
       <c r="Y726" s="1"/>
       <c r="Z726" s="1"/>
     </row>
-    <row r="727">
+    <row r="727" spans="1:26" ht="13">
       <c r="A727" s="1"/>
       <c r="B727" s="1"/>
       <c r="C727" s="1"/>
@@ -22482,7 +22453,7 @@
       <c r="Y727" s="1"/>
       <c r="Z727" s="1"/>
     </row>
-    <row r="728">
+    <row r="728" spans="1:26" ht="13">
       <c r="A728" s="1"/>
       <c r="B728" s="1"/>
       <c r="C728" s="1"/>
@@ -22510,7 +22481,7 @@
       <c r="Y728" s="1"/>
       <c r="Z728" s="1"/>
     </row>
-    <row r="729">
+    <row r="729" spans="1:26" ht="13">
       <c r="A729" s="1"/>
       <c r="B729" s="1"/>
       <c r="C729" s="1"/>
@@ -22538,7 +22509,7 @@
       <c r="Y729" s="1"/>
       <c r="Z729" s="1"/>
     </row>
-    <row r="730">
+    <row r="730" spans="1:26" ht="13">
       <c r="A730" s="1"/>
       <c r="B730" s="1"/>
       <c r="C730" s="1"/>
@@ -22566,7 +22537,7 @@
       <c r="Y730" s="1"/>
       <c r="Z730" s="1"/>
     </row>
-    <row r="731">
+    <row r="731" spans="1:26" ht="13">
       <c r="A731" s="1"/>
       <c r="B731" s="1"/>
       <c r="C731" s="1"/>
@@ -22594,7 +22565,7 @@
       <c r="Y731" s="1"/>
       <c r="Z731" s="1"/>
     </row>
-    <row r="732">
+    <row r="732" spans="1:26" ht="13">
       <c r="A732" s="1"/>
       <c r="B732" s="1"/>
       <c r="C732" s="1"/>
@@ -22622,7 +22593,7 @@
       <c r="Y732" s="1"/>
       <c r="Z732" s="1"/>
     </row>
-    <row r="733">
+    <row r="733" spans="1:26" ht="13">
       <c r="A733" s="1"/>
       <c r="B733" s="1"/>
       <c r="C733" s="1"/>
@@ -22650,7 +22621,7 @@
       <c r="Y733" s="1"/>
       <c r="Z733" s="1"/>
     </row>
-    <row r="734">
+    <row r="734" spans="1:26" ht="13">
       <c r="A734" s="1"/>
       <c r="B734" s="1"/>
       <c r="C734" s="1"/>
@@ -22678,7 +22649,7 @@
       <c r="Y734" s="1"/>
       <c r="Z734" s="1"/>
     </row>
-    <row r="735">
+    <row r="735" spans="1:26" ht="13">
       <c r="A735" s="1"/>
       <c r="B735" s="1"/>
       <c r="C735" s="1"/>
@@ -22706,7 +22677,7 @@
       <c r="Y735" s="1"/>
       <c r="Z735" s="1"/>
     </row>
-    <row r="736">
+    <row r="736" spans="1:26" ht="13">
       <c r="A736" s="1"/>
       <c r="B736" s="1"/>
       <c r="C736" s="1"/>
@@ -22734,7 +22705,7 @@
       <c r="Y736" s="1"/>
       <c r="Z736" s="1"/>
     </row>
-    <row r="737">
+    <row r="737" spans="1:26" ht="13">
       <c r="A737" s="1"/>
       <c r="B737" s="1"/>
       <c r="C737" s="1"/>
@@ -22762,7 +22733,7 @@
       <c r="Y737" s="1"/>
       <c r="Z737" s="1"/>
     </row>
-    <row r="738">
+    <row r="738" spans="1:26" ht="13">
       <c r="A738" s="1"/>
       <c r="B738" s="1"/>
       <c r="C738" s="1"/>
@@ -22790,7 +22761,7 @@
       <c r="Y738" s="1"/>
       <c r="Z738" s="1"/>
     </row>
-    <row r="739">
+    <row r="739" spans="1:26" ht="13">
       <c r="A739" s="1"/>
       <c r="B739" s="1"/>
       <c r="C739" s="1"/>
@@ -22818,7 +22789,7 @@
       <c r="Y739" s="1"/>
       <c r="Z739" s="1"/>
     </row>
-    <row r="740">
+    <row r="740" spans="1:26" ht="13">
       <c r="A740" s="1"/>
       <c r="B740" s="1"/>
       <c r="C740" s="1"/>
@@ -22846,7 +22817,7 @@
       <c r="Y740" s="1"/>
       <c r="Z740" s="1"/>
     </row>
-    <row r="741">
+    <row r="741" spans="1:26" ht="13">
       <c r="A741" s="1"/>
       <c r="B741" s="1"/>
       <c r="C741" s="1"/>
@@ -22874,7 +22845,7 @@
       <c r="Y741" s="1"/>
       <c r="Z741" s="1"/>
     </row>
-    <row r="742">
+    <row r="742" spans="1:26" ht="13">
       <c r="A742" s="1"/>
       <c r="B742" s="1"/>
       <c r="C742" s="1"/>
@@ -22902,7 +22873,7 @@
       <c r="Y742" s="1"/>
       <c r="Z742" s="1"/>
     </row>
-    <row r="743">
+    <row r="743" spans="1:26" ht="13">
       <c r="A743" s="1"/>
       <c r="B743" s="1"/>
       <c r="C743" s="1"/>
@@ -22930,7 +22901,7 @@
       <c r="Y743" s="1"/>
       <c r="Z743" s="1"/>
     </row>
-    <row r="744">
+    <row r="744" spans="1:26" ht="13">
       <c r="A744" s="1"/>
       <c r="B744" s="1"/>
       <c r="C744" s="1"/>
@@ -22958,7 +22929,7 @@
       <c r="Y744" s="1"/>
       <c r="Z744" s="1"/>
     </row>
-    <row r="745">
+    <row r="745" spans="1:26" ht="13">
       <c r="A745" s="1"/>
       <c r="B745" s="1"/>
       <c r="C745" s="1"/>
@@ -22986,7 +22957,7 @@
       <c r="Y745" s="1"/>
       <c r="Z745" s="1"/>
     </row>
-    <row r="746">
+    <row r="746" spans="1:26" ht="13">
       <c r="A746" s="1"/>
       <c r="B746" s="1"/>
       <c r="C746" s="1"/>
@@ -23014,7 +22985,7 @@
       <c r="Y746" s="1"/>
       <c r="Z746" s="1"/>
     </row>
-    <row r="747">
+    <row r="747" spans="1:26" ht="13">
       <c r="A747" s="1"/>
       <c r="B747" s="1"/>
       <c r="C747" s="1"/>
@@ -23042,7 +23013,7 @@
       <c r="Y747" s="1"/>
       <c r="Z747" s="1"/>
     </row>
-    <row r="748">
+    <row r="748" spans="1:26" ht="13">
       <c r="A748" s="1"/>
       <c r="B748" s="1"/>
       <c r="C748" s="1"/>
@@ -23070,7 +23041,7 @@
       <c r="Y748" s="1"/>
       <c r="Z748" s="1"/>
     </row>
-    <row r="749">
+    <row r="749" spans="1:26" ht="13">
       <c r="A749" s="1"/>
       <c r="B749" s="1"/>
       <c r="C749" s="1"/>
@@ -23098,7 +23069,7 @@
       <c r="Y749" s="1"/>
       <c r="Z749" s="1"/>
     </row>
-    <row r="750">
+    <row r="750" spans="1:26" ht="13">
       <c r="A750" s="1"/>
       <c r="B750" s="1"/>
       <c r="C750" s="1"/>
@@ -23126,7 +23097,7 @@
       <c r="Y750" s="1"/>
       <c r="Z750" s="1"/>
     </row>
-    <row r="751">
+    <row r="751" spans="1:26" ht="13">
       <c r="A751" s="1"/>
       <c r="B751" s="1"/>
       <c r="C751" s="1"/>
@@ -23154,7 +23125,7 @@
       <c r="Y751" s="1"/>
       <c r="Z751" s="1"/>
     </row>
-    <row r="752">
+    <row r="752" spans="1:26" ht="13">
       <c r="A752" s="1"/>
       <c r="B752" s="1"/>
       <c r="C752" s="1"/>
@@ -23182,7 +23153,7 @@
       <c r="Y752" s="1"/>
       <c r="Z752" s="1"/>
     </row>
-    <row r="753">
+    <row r="753" spans="1:26" ht="13">
       <c r="A753" s="1"/>
       <c r="B753" s="1"/>
       <c r="C753" s="1"/>
@@ -23210,7 +23181,7 @@
       <c r="Y753" s="1"/>
       <c r="Z753" s="1"/>
     </row>
-    <row r="754">
+    <row r="754" spans="1:26" ht="13">
       <c r="A754" s="1"/>
       <c r="B754" s="1"/>
       <c r="C754" s="1"/>
@@ -23238,7 +23209,7 @@
       <c r="Y754" s="1"/>
       <c r="Z754" s="1"/>
     </row>
-    <row r="755">
+    <row r="755" spans="1:26" ht="13">
       <c r="A755" s="1"/>
       <c r="B755" s="1"/>
       <c r="C755" s="1"/>
@@ -23266,7 +23237,7 @@
       <c r="Y755" s="1"/>
       <c r="Z755" s="1"/>
     </row>
-    <row r="756">
+    <row r="756" spans="1:26" ht="13">
       <c r="A756" s="1"/>
       <c r="B756" s="1"/>
       <c r="C756" s="1"/>
@@ -23294,7 +23265,7 @@
       <c r="Y756" s="1"/>
       <c r="Z756" s="1"/>
     </row>
-    <row r="757">
+    <row r="757" spans="1:26" ht="13">
       <c r="A757" s="1"/>
       <c r="B757" s="1"/>
       <c r="C757" s="1"/>
@@ -23322,7 +23293,7 @@
       <c r="Y757" s="1"/>
       <c r="Z757" s="1"/>
     </row>
-    <row r="758">
+    <row r="758" spans="1:26" ht="13">
       <c r="A758" s="1"/>
       <c r="B758" s="1"/>
       <c r="C758" s="1"/>
@@ -23350,7 +23321,7 @@
       <c r="Y758" s="1"/>
       <c r="Z758" s="1"/>
     </row>
-    <row r="759">
+    <row r="759" spans="1:26" ht="13">
       <c r="A759" s="1"/>
       <c r="B759" s="1"/>
       <c r="C759" s="1"/>
@@ -23378,7 +23349,7 @@
       <c r="Y759" s="1"/>
       <c r="Z759" s="1"/>
     </row>
-    <row r="760">
+    <row r="760" spans="1:26" ht="13">
       <c r="A760" s="1"/>
       <c r="B760" s="1"/>
       <c r="C760" s="1"/>
@@ -23406,7 +23377,7 @@
       <c r="Y760" s="1"/>
       <c r="Z760" s="1"/>
     </row>
-    <row r="761">
+    <row r="761" spans="1:26" ht="13">
       <c r="A761" s="1"/>
       <c r="B761" s="1"/>
       <c r="C761" s="1"/>
@@ -23434,7 +23405,7 @@
       <c r="Y761" s="1"/>
       <c r="Z761" s="1"/>
     </row>
-    <row r="762">
+    <row r="762" spans="1:26" ht="13">
       <c r="A762" s="1"/>
       <c r="B762" s="1"/>
       <c r="C762" s="1"/>
@@ -23462,7 +23433,7 @@
       <c r="Y762" s="1"/>
       <c r="Z762" s="1"/>
     </row>
-    <row r="763">
+    <row r="763" spans="1:26" ht="13">
       <c r="A763" s="1"/>
       <c r="B763" s="1"/>
       <c r="C763" s="1"/>
@@ -23490,7 +23461,7 @@
       <c r="Y763" s="1"/>
       <c r="Z763" s="1"/>
     </row>
-    <row r="764">
+    <row r="764" spans="1:26" ht="13">
       <c r="A764" s="1"/>
       <c r="B764" s="1"/>
       <c r="C764" s="1"/>
@@ -23518,7 +23489,7 @@
       <c r="Y764" s="1"/>
       <c r="Z764" s="1"/>
     </row>
-    <row r="765">
+    <row r="765" spans="1:26" ht="13">
       <c r="A765" s="1"/>
       <c r="B765" s="1"/>
       <c r="C765" s="1"/>
@@ -23546,7 +23517,7 @@
       <c r="Y765" s="1"/>
       <c r="Z765" s="1"/>
     </row>
-    <row r="766">
+    <row r="766" spans="1:26" ht="13">
       <c r="A766" s="1"/>
       <c r="B766" s="1"/>
       <c r="C766" s="1"/>
@@ -23574,7 +23545,7 @@
       <c r="Y766" s="1"/>
       <c r="Z766" s="1"/>
     </row>
-    <row r="767">
+    <row r="767" spans="1:26" ht="13">
       <c r="A767" s="1"/>
       <c r="B767" s="1"/>
       <c r="C767" s="1"/>
@@ -23602,7 +23573,7 @@
       <c r="Y767" s="1"/>
       <c r="Z767" s="1"/>
     </row>
-    <row r="768">
+    <row r="768" spans="1:26" ht="13">
       <c r="A768" s="1"/>
       <c r="B768" s="1"/>
       <c r="C768" s="1"/>
@@ -23630,7 +23601,7 @@
       <c r="Y768" s="1"/>
       <c r="Z768" s="1"/>
     </row>
-    <row r="769">
+    <row r="769" spans="1:26" ht="13">
       <c r="A769" s="1"/>
       <c r="B769" s="1"/>
       <c r="C769" s="1"/>
@@ -23658,7 +23629,7 @@
       <c r="Y769" s="1"/>
       <c r="Z769" s="1"/>
     </row>
-    <row r="770">
+    <row r="770" spans="1:26" ht="13">
       <c r="A770" s="1"/>
       <c r="B770" s="1"/>
       <c r="C770" s="1"/>
@@ -23686,7 +23657,7 @@
       <c r="Y770" s="1"/>
       <c r="Z770" s="1"/>
     </row>
-    <row r="771">
+    <row r="771" spans="1:26" ht="13">
       <c r="A771" s="1"/>
       <c r="B771" s="1"/>
       <c r="C771" s="1"/>
@@ -23714,7 +23685,7 @@
       <c r="Y771" s="1"/>
       <c r="Z771" s="1"/>
     </row>
-    <row r="772">
+    <row r="772" spans="1:26" ht="13">
       <c r="A772" s="1"/>
       <c r="B772" s="1"/>
       <c r="C772" s="1"/>
@@ -23742,7 +23713,7 @@
       <c r="Y772" s="1"/>
       <c r="Z772" s="1"/>
     </row>
-    <row r="773">
+    <row r="773" spans="1:26" ht="13">
       <c r="A773" s="1"/>
       <c r="B773" s="1"/>
       <c r="C773" s="1"/>
@@ -23770,7 +23741,7 @@
       <c r="Y773" s="1"/>
       <c r="Z773" s="1"/>
     </row>
-    <row r="774">
+    <row r="774" spans="1:26" ht="13">
       <c r="A774" s="1"/>
       <c r="B774" s="1"/>
       <c r="C774" s="1"/>
@@ -23798,7 +23769,7 @@
       <c r="Y774" s="1"/>
       <c r="Z774" s="1"/>
     </row>
-    <row r="775">
+    <row r="775" spans="1:26" ht="13">
       <c r="A775" s="1"/>
       <c r="B775" s="1"/>
       <c r="C775" s="1"/>
@@ -23826,7 +23797,7 @@
       <c r="Y775" s="1"/>
       <c r="Z775" s="1"/>
     </row>
-    <row r="776">
+    <row r="776" spans="1:26" ht="13">
       <c r="A776" s="1"/>
       <c r="B776" s="1"/>
       <c r="C776" s="1"/>
@@ -23854,7 +23825,7 @@
       <c r="Y776" s="1"/>
       <c r="Z776" s="1"/>
     </row>
-    <row r="777">
+    <row r="777" spans="1:26" ht="13">
       <c r="A777" s="1"/>
       <c r="B777" s="1"/>
       <c r="C777" s="1"/>
@@ -23882,7 +23853,7 @@
       <c r="Y777" s="1"/>
       <c r="Z777" s="1"/>
     </row>
-    <row r="778">
+    <row r="778" spans="1:26" ht="13">
       <c r="A778" s="1"/>
       <c r="B778" s="1"/>
       <c r="C778" s="1"/>
@@ -23910,7 +23881,7 @@
       <c r="Y778" s="1"/>
       <c r="Z778" s="1"/>
     </row>
-    <row r="779">
+    <row r="779" spans="1:26" ht="13">
       <c r="A779" s="1"/>
       <c r="B779" s="1"/>
       <c r="C779" s="1"/>
@@ -23938,7 +23909,7 @@
       <c r="Y779" s="1"/>
       <c r="Z779" s="1"/>
     </row>
-    <row r="780">
+    <row r="780" spans="1:26" ht="13">
       <c r="A780" s="1"/>
       <c r="B780" s="1"/>
       <c r="C780" s="1"/>
@@ -23966,7 +23937,7 @@
       <c r="Y780" s="1"/>
       <c r="Z780" s="1"/>
     </row>
-    <row r="781">
+    <row r="781" spans="1:26" ht="13">
       <c r="A781" s="1"/>
       <c r="B781" s="1"/>
       <c r="C781" s="1"/>
@@ -23994,7 +23965,7 @@
       <c r="Y781" s="1"/>
       <c r="Z781" s="1"/>
     </row>
-    <row r="782">
+    <row r="782" spans="1:26" ht="13">
       <c r="A782" s="1"/>
       <c r="B782" s="1"/>
       <c r="C782" s="1"/>
@@ -24022,7 +23993,7 @@
       <c r="Y782" s="1"/>
       <c r="Z782" s="1"/>
     </row>
-    <row r="783">
+    <row r="783" spans="1:26" ht="13">
       <c r="A783" s="1"/>
       <c r="B783" s="1"/>
       <c r="C783" s="1"/>
@@ -24050,7 +24021,7 @@
       <c r="Y783" s="1"/>
       <c r="Z783" s="1"/>
     </row>
-    <row r="784">
+    <row r="784" spans="1:26" ht="13">
       <c r="A784" s="1"/>
       <c r="B784" s="1"/>
       <c r="C784" s="1"/>
@@ -24078,7 +24049,7 @@
       <c r="Y784" s="1"/>
       <c r="Z784" s="1"/>
     </row>
-    <row r="785">
+    <row r="785" spans="1:26" ht="13">
       <c r="A785" s="1"/>
       <c r="B785" s="1"/>
       <c r="C785" s="1"/>
@@ -24106,7 +24077,7 @@
       <c r="Y785" s="1"/>
       <c r="Z785" s="1"/>
     </row>
-    <row r="786">
+    <row r="786" spans="1:26" ht="13">
       <c r="A786" s="1"/>
       <c r="B786" s="1"/>
       <c r="C786" s="1"/>
@@ -24134,7 +24105,7 @@
       <c r="Y786" s="1"/>
       <c r="Z786" s="1"/>
     </row>
-    <row r="787">
+    <row r="787" spans="1:26" ht="13">
       <c r="A787" s="1"/>
       <c r="B787" s="1"/>
       <c r="C787" s="1"/>
@@ -24162,7 +24133,7 @@
       <c r="Y787" s="1"/>
       <c r="Z787" s="1"/>
     </row>
-    <row r="788">
+    <row r="788" spans="1:26" ht="13">
       <c r="A788" s="1"/>
       <c r="B788" s="1"/>
       <c r="C788" s="1"/>
@@ -24190,7 +24161,7 @@
       <c r="Y788" s="1"/>
       <c r="Z788" s="1"/>
     </row>
-    <row r="789">
+    <row r="789" spans="1:26" ht="13">
       <c r="A789" s="1"/>
       <c r="B789" s="1"/>
       <c r="C789" s="1"/>
@@ -24218,7 +24189,7 @@
       <c r="Y789" s="1"/>
       <c r="Z789" s="1"/>
     </row>
-    <row r="790">
+    <row r="790" spans="1:26" ht="13">
       <c r="A790" s="1"/>
       <c r="B790" s="1"/>
       <c r="C790" s="1"/>
@@ -24246,7 +24217,7 @@
       <c r="Y790" s="1"/>
       <c r="Z790" s="1"/>
     </row>
-    <row r="791">
+    <row r="791" spans="1:26" ht="13">
       <c r="A791" s="1"/>
       <c r="B791" s="1"/>
       <c r="C791" s="1"/>
@@ -24274,7 +24245,7 @@
       <c r="Y791" s="1"/>
       <c r="Z791" s="1"/>
     </row>
-    <row r="792">
+    <row r="792" spans="1:26" ht="13">
       <c r="A792" s="1"/>
       <c r="B792" s="1"/>
       <c r="C792" s="1"/>
@@ -24302,7 +24273,7 @@
       <c r="Y792" s="1"/>
       <c r="Z792" s="1"/>
     </row>
-    <row r="793">
+    <row r="793" spans="1:26" ht="13">
       <c r="A793" s="1"/>
       <c r="B793" s="1"/>
       <c r="C793" s="1"/>
@@ -24330,7 +24301,7 @@
       <c r="Y793" s="1"/>
       <c r="Z793" s="1"/>
     </row>
-    <row r="794">
+    <row r="794" spans="1:26" ht="13">
       <c r="A794" s="1"/>
       <c r="B794" s="1"/>
       <c r="C794" s="1"/>
@@ -24358,7 +24329,7 @@
       <c r="Y794" s="1"/>
       <c r="Z794" s="1"/>
     </row>
-    <row r="795">
+    <row r="795" spans="1:26" ht="13">
       <c r="A795" s="1"/>
       <c r="B795" s="1"/>
       <c r="C795" s="1"/>
@@ -24386,7 +24357,7 @@
       <c r="Y795" s="1"/>
       <c r="Z795" s="1"/>
     </row>
-    <row r="796">
+    <row r="796" spans="1:26" ht="13">
       <c r="A796" s="1"/>
       <c r="B796" s="1"/>
       <c r="C796" s="1"/>
@@ -24414,7 +24385,7 @@
       <c r="Y796" s="1"/>
       <c r="Z796" s="1"/>
     </row>
-    <row r="797">
+    <row r="797" spans="1:26" ht="13">
       <c r="A797" s="1"/>
       <c r="B797" s="1"/>
       <c r="C797" s="1"/>
@@ -24442,7 +24413,7 @@
       <c r="Y797" s="1"/>
       <c r="Z797" s="1"/>
     </row>
-    <row r="798">
+    <row r="798" spans="1:26" ht="13">
       <c r="A798" s="1"/>
       <c r="B798" s="1"/>
       <c r="C798" s="1"/>
@@ -24470,7 +24441,7 @@
       <c r="Y798" s="1"/>
       <c r="Z798" s="1"/>
     </row>
-    <row r="799">
+    <row r="799" spans="1:26" ht="13">
       <c r="A799" s="1"/>
       <c r="B799" s="1"/>
       <c r="C799" s="1"/>
@@ -24498,7 +24469,7 @@
       <c r="Y799" s="1"/>
       <c r="Z799" s="1"/>
     </row>
-    <row r="800">
+    <row r="800" spans="1:26" ht="13">
       <c r="A800" s="1"/>
       <c r="B800" s="1"/>
       <c r="C800" s="1"/>
@@ -24526,7 +24497,7 @@
       <c r="Y800" s="1"/>
       <c r="Z800" s="1"/>
     </row>
-    <row r="801">
+    <row r="801" spans="1:26" ht="13">
       <c r="A801" s="1"/>
       <c r="B801" s="1"/>
       <c r="C801" s="1"/>
@@ -24554,7 +24525,7 @@
       <c r="Y801" s="1"/>
       <c r="Z801" s="1"/>
     </row>
-    <row r="802">
+    <row r="802" spans="1:26" ht="13">
       <c r="A802" s="1"/>
       <c r="B802" s="1"/>
       <c r="C802" s="1"/>
@@ -24582,7 +24553,7 @@
       <c r="Y802" s="1"/>
       <c r="Z802" s="1"/>
     </row>
-    <row r="803">
+    <row r="803" spans="1:26" ht="13">
       <c r="A803" s="1"/>
       <c r="B803" s="1"/>
       <c r="C803" s="1"/>
@@ -24610,7 +24581,7 @@
       <c r="Y803" s="1"/>
       <c r="Z803" s="1"/>
     </row>
-    <row r="804">
+    <row r="804" spans="1:26" ht="13">
       <c r="A804" s="1"/>
       <c r="B804" s="1"/>
       <c r="C804" s="1"/>
@@ -24638,7 +24609,7 @@
       <c r="Y804" s="1"/>
       <c r="Z804" s="1"/>
     </row>
-    <row r="805">
+    <row r="805" spans="1:26" ht="13">
       <c r="A805" s="1"/>
       <c r="B805" s="1"/>
       <c r="C805" s="1"/>
@@ -24666,7 +24637,7 @@
       <c r="Y805" s="1"/>
       <c r="Z805" s="1"/>
     </row>
-    <row r="806">
+    <row r="806" spans="1:26" ht="13">
       <c r="A806" s="1"/>
       <c r="B806" s="1"/>
       <c r="C806" s="1"/>
@@ -24694,7 +24665,7 @@
       <c r="Y806" s="1"/>
       <c r="Z806" s="1"/>
     </row>
-    <row r="807">
+    <row r="807" spans="1:26" ht="13">
       <c r="A807" s="1"/>
       <c r="B807" s="1"/>
       <c r="C807" s="1"/>
@@ -24722,7 +24693,7 @@
       <c r="Y807" s="1"/>
       <c r="Z807" s="1"/>
     </row>
-    <row r="808">
+    <row r="808" spans="1:26" ht="13">
       <c r="A808" s="1"/>
       <c r="B808" s="1"/>
       <c r="C808" s="1"/>
@@ -24750,7 +24721,7 @@
       <c r="Y808" s="1"/>
       <c r="Z808" s="1"/>
     </row>
-    <row r="809">
+    <row r="809" spans="1:26" ht="13">
       <c r="A809" s="1"/>
       <c r="B809" s="1"/>
       <c r="C809" s="1"/>
@@ -24778,7 +24749,7 @@
       <c r="Y809" s="1"/>
       <c r="Z809" s="1"/>
     </row>
-    <row r="810">
+    <row r="810" spans="1:26" ht="13">
       <c r="A810" s="1"/>
       <c r="B810" s="1"/>
       <c r="C810" s="1"/>
@@ -24806,7 +24777,7 @@
       <c r="Y810" s="1"/>
       <c r="Z810" s="1"/>
     </row>
-    <row r="811">
+    <row r="811" spans="1:26" ht="13">
       <c r="A811" s="1"/>
       <c r="B811" s="1"/>
       <c r="C811" s="1"/>
@@ -24834,7 +24805,7 @@
       <c r="Y811" s="1"/>
       <c r="Z811" s="1"/>
     </row>
-    <row r="812">
+    <row r="812" spans="1:26" ht="13">
       <c r="A812" s="1"/>
       <c r="B812" s="1"/>
       <c r="C812" s="1"/>
@@ -24862,7 +24833,7 @@
       <c r="Y812" s="1"/>
       <c r="Z812" s="1"/>
     </row>
-    <row r="813">
+    <row r="813" spans="1:26" ht="13">
       <c r="A813" s="1"/>
       <c r="B813" s="1"/>
       <c r="C813" s="1"/>
@@ -24890,7 +24861,7 @@
       <c r="Y813" s="1"/>
       <c r="Z813" s="1"/>
     </row>
-    <row r="814">
+    <row r="814" spans="1:26" ht="13">
       <c r="A814" s="1"/>
       <c r="B814" s="1"/>
       <c r="C814" s="1"/>
@@ -24918,7 +24889,7 @@
       <c r="Y814" s="1"/>
       <c r="Z814" s="1"/>
     </row>
-    <row r="815">
+    <row r="815" spans="1:26" ht="13">
       <c r="A815" s="1"/>
       <c r="B815" s="1"/>
       <c r="C815" s="1"/>
@@ -24946,7 +24917,7 @@
       <c r="Y815" s="1"/>
       <c r="Z815" s="1"/>
     </row>
-    <row r="816">
+    <row r="816" spans="1:26" ht="13">
       <c r="A816" s="1"/>
       <c r="B816" s="1"/>
       <c r="C816" s="1"/>
@@ -24974,7 +24945,7 @@
       <c r="Y816" s="1"/>
       <c r="Z816" s="1"/>
     </row>
-    <row r="817">
+    <row r="817" spans="1:26" ht="13">
       <c r="A817" s="1"/>
       <c r="B817" s="1"/>
       <c r="C817" s="1"/>
@@ -25002,7 +24973,7 @@
       <c r="Y817" s="1"/>
       <c r="Z817" s="1"/>
     </row>
-    <row r="818">
+    <row r="818" spans="1:26" ht="13">
       <c r="A818" s="1"/>
       <c r="B818" s="1"/>
       <c r="C818" s="1"/>
@@ -25030,7 +25001,7 @@
       <c r="Y818" s="1"/>
       <c r="Z818" s="1"/>
     </row>
-    <row r="819">
+    <row r="819" spans="1:26" ht="13">
       <c r="A819" s="1"/>
       <c r="B819" s="1"/>
       <c r="C819" s="1"/>
@@ -25058,7 +25029,7 @@
       <c r="Y819" s="1"/>
       <c r="Z819" s="1"/>
     </row>
-    <row r="820">
+    <row r="820" spans="1:26" ht="13">
       <c r="A820" s="1"/>
       <c r="B820" s="1"/>
       <c r="C820" s="1"/>
@@ -25086,7 +25057,7 @@
       <c r="Y820" s="1"/>
       <c r="Z820" s="1"/>
     </row>
-    <row r="821">
+    <row r="821" spans="1:26" ht="13">
       <c r="A821" s="1"/>
       <c r="B821" s="1"/>
       <c r="C821" s="1"/>
@@ -25114,7 +25085,7 @@
       <c r="Y821" s="1"/>
       <c r="Z821" s="1"/>
     </row>
-    <row r="822">
+    <row r="822" spans="1:26" ht="13">
       <c r="A822" s="1"/>
       <c r="B822" s="1"/>
       <c r="C822" s="1"/>
@@ -25142,7 +25113,7 @@
       <c r="Y822" s="1"/>
       <c r="Z822" s="1"/>
     </row>
-    <row r="823">
+    <row r="823" spans="1:26" ht="13">
       <c r="A823" s="1"/>
       <c r="B823" s="1"/>
       <c r="C823" s="1"/>
@@ -25170,7 +25141,7 @@
       <c r="Y823" s="1"/>
       <c r="Z823" s="1"/>
     </row>
-    <row r="824">
+    <row r="824" spans="1:26" ht="13">
       <c r="A824" s="1"/>
       <c r="B824" s="1"/>
       <c r="C824" s="1"/>
@@ -25198,7 +25169,7 @@
       <c r="Y824" s="1"/>
       <c r="Z824" s="1"/>
     </row>
-    <row r="825">
+    <row r="825" spans="1:26" ht="13">
       <c r="A825" s="1"/>
       <c r="B825" s="1"/>
       <c r="C825" s="1"/>
@@ -25226,7 +25197,7 @@
       <c r="Y825" s="1"/>
       <c r="Z825" s="1"/>
     </row>
-    <row r="826">
+    <row r="826" spans="1:26" ht="13">
       <c r="A826" s="1"/>
       <c r="B826" s="1"/>
       <c r="C826" s="1"/>
@@ -25254,7 +25225,7 @@
       <c r="Y826" s="1"/>
       <c r="Z826" s="1"/>
     </row>
-    <row r="827">
+    <row r="827" spans="1:26" ht="13">
       <c r="A827" s="1"/>
       <c r="B827" s="1"/>
       <c r="C827" s="1"/>
@@ -25282,7 +25253,7 @@
       <c r="Y827" s="1"/>
       <c r="Z827" s="1"/>
     </row>
-    <row r="828">
+    <row r="828" spans="1:26" ht="13">
       <c r="A828" s="1"/>
       <c r="B828" s="1"/>
       <c r="C828" s="1"/>
@@ -25310,7 +25281,7 @@
       <c r="Y828" s="1"/>
       <c r="Z828" s="1"/>
     </row>
-    <row r="829">
+    <row r="829" spans="1:26" ht="13">
       <c r="A829" s="1"/>
       <c r="B829" s="1"/>
       <c r="C829" s="1"/>
@@ -25338,7 +25309,7 @@
       <c r="Y829" s="1"/>
       <c r="Z829" s="1"/>
     </row>
-    <row r="830">
+    <row r="830" spans="1:26" ht="13">
       <c r="A830" s="1"/>
       <c r="B830" s="1"/>
       <c r="C830" s="1"/>
@@ -25366,7 +25337,7 @@
       <c r="Y830" s="1"/>
       <c r="Z830" s="1"/>
     </row>
-    <row r="831">
+    <row r="831" spans="1:26" ht="13">
       <c r="A831" s="1"/>
       <c r="B831" s="1"/>
       <c r="C831" s="1"/>
@@ -25394,7 +25365,7 @@
       <c r="Y831" s="1"/>
       <c r="Z831" s="1"/>
     </row>
-    <row r="832">
+    <row r="832" spans="1:26" ht="13">
       <c r="A832" s="1"/>
       <c r="B832" s="1"/>
       <c r="C832" s="1"/>
@@ -25422,7 +25393,7 @@
       <c r="Y832" s="1"/>
       <c r="Z832" s="1"/>
     </row>
-    <row r="833">
+    <row r="833" spans="1:26" ht="13">
       <c r="A833" s="1"/>
       <c r="B833" s="1"/>
       <c r="C833" s="1"/>
@@ -25450,7 +25421,7 @@
       <c r="Y833" s="1"/>
       <c r="Z833" s="1"/>
     </row>
-    <row r="834">
+    <row r="834" spans="1:26" ht="13">
       <c r="A834" s="1"/>
       <c r="B834" s="1"/>
       <c r="C834" s="1"/>
@@ -25478,7 +25449,7 @@
       <c r="Y834" s="1"/>
       <c r="Z834" s="1"/>
     </row>
-    <row r="835">
+    <row r="835" spans="1:26" ht="13">
       <c r="A835" s="1"/>
       <c r="B835" s="1"/>
       <c r="C835" s="1"/>
@@ -25506,7 +25477,7 @@
       <c r="Y835" s="1"/>
       <c r="Z835" s="1"/>
     </row>
-    <row r="836">
+    <row r="836" spans="1:26" ht="13">
       <c r="A836" s="1"/>
       <c r="B836" s="1"/>
       <c r="C836" s="1"/>
@@ -25534,7 +25505,7 @@
       <c r="Y836" s="1"/>
       <c r="Z836" s="1"/>
     </row>
-    <row r="837">
+    <row r="837" spans="1:26" ht="13">
       <c r="A837" s="1"/>
       <c r="B837" s="1"/>
       <c r="C837" s="1"/>
@@ -25562,7 +25533,7 @@
       <c r="Y837" s="1"/>
       <c r="Z837" s="1"/>
     </row>
-    <row r="838">
+    <row r="838" spans="1:26" ht="13">
       <c r="A838" s="1"/>
       <c r="B838" s="1"/>
       <c r="C838" s="1"/>
@@ -25590,7 +25561,7 @@
       <c r="Y838" s="1"/>
       <c r="Z838" s="1"/>
     </row>
-    <row r="839">
+    <row r="839" spans="1:26" ht="13">
       <c r="A839" s="1"/>
       <c r="B839" s="1"/>
       <c r="C839" s="1"/>
@@ -25618,7 +25589,7 @@
       <c r="Y839" s="1"/>
       <c r="Z839" s="1"/>
     </row>
-    <row r="840">
+    <row r="840" spans="1:26" ht="13">
       <c r="A840" s="1"/>
       <c r="B840" s="1"/>
       <c r="C840" s="1"/>
@@ -25646,7 +25617,7 @@
       <c r="Y840" s="1"/>
       <c r="Z840" s="1"/>
     </row>
-    <row r="841">
+    <row r="841" spans="1:26" ht="13">
       <c r="A841" s="1"/>
       <c r="B841" s="1"/>
       <c r="C841" s="1"/>
@@ -25674,7 +25645,7 @@
       <c r="Y841" s="1"/>
       <c r="Z841" s="1"/>
     </row>
-    <row r="842">
+    <row r="842" spans="1:26" ht="13">
       <c r="A842" s="1"/>
       <c r="B842" s="1"/>
       <c r="C842" s="1"/>
@@ -25702,7 +25673,7 @@
       <c r="Y842" s="1"/>
       <c r="Z842" s="1"/>
     </row>
-    <row r="843">
+    <row r="843" spans="1:26" ht="13">
       <c r="A843" s="1"/>
       <c r="B843" s="1"/>
       <c r="C843" s="1"/>
@@ -25730,7 +25701,7 @@
       <c r="Y843" s="1"/>
       <c r="Z843" s="1"/>
     </row>
-    <row r="844">
+    <row r="844" spans="1:26" ht="13">
       <c r="A844" s="1"/>
       <c r="B844" s="1"/>
       <c r="C844" s="1"/>
@@ -25758,7 +25729,7 @@
       <c r="Y844" s="1"/>
       <c r="Z844" s="1"/>
     </row>
-    <row r="845">
+    <row r="845" spans="1:26" ht="13">
       <c r="A845" s="1"/>
       <c r="B845" s="1"/>
       <c r="C845" s="1"/>
@@ -25786,7 +25757,7 @@
       <c r="Y845" s="1"/>
       <c r="Z845" s="1"/>
     </row>
-    <row r="846">
+    <row r="846" spans="1:26" ht="13">
       <c r="A846" s="1"/>
       <c r="B846" s="1"/>
       <c r="C846" s="1"/>
@@ -25814,7 +25785,7 @@
       <c r="Y846" s="1"/>
       <c r="Z846" s="1"/>
     </row>
-    <row r="847">
+    <row r="847" spans="1:26" ht="13">
       <c r="A847" s="1"/>
       <c r="B847" s="1"/>
       <c r="C847" s="1"/>
@@ -25842,7 +25813,7 @@
       <c r="Y847" s="1"/>
       <c r="Z847" s="1"/>
     </row>
-    <row r="848">
+    <row r="848" spans="1:26" ht="13">
       <c r="A848" s="1"/>
       <c r="B848" s="1"/>
       <c r="C848" s="1"/>
@@ -25870,7 +25841,7 @@
       <c r="Y848" s="1"/>
       <c r="Z848" s="1"/>
     </row>
-    <row r="849">
+    <row r="849" spans="1:26" ht="13">
       <c r="A849" s="1"/>
       <c r="B849" s="1"/>
       <c r="C849" s="1"/>
@@ -25898,7 +25869,7 @@
       <c r="Y849" s="1"/>
       <c r="Z849" s="1"/>
     </row>
-    <row r="850">
+    <row r="850" spans="1:26" ht="13">
       <c r="A850" s="1"/>
       <c r="B850" s="1"/>
       <c r="C850" s="1"/>
@@ -25926,7 +25897,7 @@
       <c r="Y850" s="1"/>
       <c r="Z850" s="1"/>
     </row>
-    <row r="851">
+    <row r="851" spans="1:26" ht="13">
       <c r="A851" s="1"/>
       <c r="B851" s="1"/>
       <c r="C851" s="1"/>
@@ -25954,7 +25925,7 @@
       <c r="Y851" s="1"/>
       <c r="Z851" s="1"/>
     </row>
-    <row r="852">
+    <row r="852" spans="1:26" ht="13">
       <c r="A852" s="1"/>
       <c r="B852" s="1"/>
       <c r="C852" s="1"/>
@@ -25982,7 +25953,7 @@
       <c r="Y852" s="1"/>
       <c r="Z852" s="1"/>
     </row>
-    <row r="853">
+    <row r="853" spans="1:26" ht="13">
       <c r="A853" s="1"/>
       <c r="B853" s="1"/>
       <c r="C853" s="1"/>
@@ -26010,7 +25981,7 @@
       <c r="Y853" s="1"/>
       <c r="Z853" s="1"/>
     </row>
-    <row r="854">
+    <row r="854" spans="1:26" ht="13">
       <c r="A854" s="1"/>
       <c r="B854" s="1"/>
       <c r="C854" s="1"/>
@@ -26038,7 +26009,7 @@
       <c r="Y854" s="1"/>
       <c r="Z854" s="1"/>
     </row>
-    <row r="855">
+    <row r="855" spans="1:26" ht="13">
       <c r="A855" s="1"/>
       <c r="B855" s="1"/>
       <c r="C855" s="1"/>
@@ -26066,7 +26037,7 @@
       <c r="Y855" s="1"/>
       <c r="Z855" s="1"/>
     </row>
-    <row r="856">
+    <row r="856" spans="1:26" ht="13">
       <c r="A856" s="1"/>
       <c r="B856" s="1"/>
       <c r="C856" s="1"/>
@@ -26094,7 +26065,7 @@
       <c r="Y856" s="1"/>
       <c r="Z856" s="1"/>
     </row>
-    <row r="857">
+    <row r="857" spans="1:26" ht="13">
       <c r="A857" s="1"/>
       <c r="B857" s="1"/>
       <c r="C857" s="1"/>
@@ -26122,7 +26093,7 @@
       <c r="Y857" s="1"/>
       <c r="Z857" s="1"/>
     </row>
-    <row r="858">
+    <row r="858" spans="1:26" ht="13">
       <c r="A858" s="1"/>
       <c r="B858" s="1"/>
       <c r="C858" s="1"/>
@@ -26150,7 +26121,7 @@
       <c r="Y858" s="1"/>
       <c r="Z858" s="1"/>
     </row>
-    <row r="859">
+    <row r="859" spans="1:26" ht="13">
       <c r="A859" s="1"/>
       <c r="B859" s="1"/>
       <c r="C859" s="1"/>
@@ -26178,7 +26149,7 @@
       <c r="Y859" s="1"/>
       <c r="Z859" s="1"/>
     </row>
-    <row r="860">
+    <row r="860" spans="1:26" ht="13">
       <c r="A860" s="1"/>
       <c r="B860" s="1"/>
       <c r="C860" s="1"/>
@@ -26206,7 +26177,7 @@
       <c r="Y860" s="1"/>
       <c r="Z860" s="1"/>
     </row>
-    <row r="861">
+    <row r="861" spans="1:26" ht="13">
       <c r="A861" s="1"/>
       <c r="B861" s="1"/>
       <c r="C861" s="1"/>
@@ -26234,7 +26205,7 @@
       <c r="Y861" s="1"/>
       <c r="Z861" s="1"/>
     </row>
-    <row r="862">
+    <row r="862" spans="1:26" ht="13">
       <c r="A862" s="1"/>
       <c r="B862" s="1"/>
       <c r="C862" s="1"/>
@@ -26262,7 +26233,7 @@
       <c r="Y862" s="1"/>
       <c r="Z862" s="1"/>
     </row>
-    <row r="863">
+    <row r="863" spans="1:26" ht="13">
       <c r="A863" s="1"/>
       <c r="B863" s="1"/>
       <c r="C863" s="1"/>
@@ -26290,7 +26261,7 @@
       <c r="Y863" s="1"/>
       <c r="Z863" s="1"/>
     </row>
-    <row r="864">
+    <row r="864" spans="1:26" ht="13">
       <c r="A864" s="1"/>
       <c r="B864" s="1"/>
       <c r="C864" s="1"/>
@@ -26318,7 +26289,7 @@
       <c r="Y864" s="1"/>
       <c r="Z864" s="1"/>
     </row>
-    <row r="865">
+    <row r="865" spans="1:26" ht="13">
       <c r="A865" s="1"/>
       <c r="B865" s="1"/>
       <c r="C865" s="1"/>
@@ -26346,7 +26317,7 @@
       <c r="Y865" s="1"/>
       <c r="Z865" s="1"/>
     </row>
-    <row r="866">
+    <row r="866" spans="1:26" ht="13">
       <c r="A866" s="1"/>
       <c r="B866" s="1"/>
       <c r="C866" s="1"/>
@@ -26374,7 +26345,7 @@
       <c r="Y866" s="1"/>
       <c r="Z866" s="1"/>
     </row>
-    <row r="867">
+    <row r="867" spans="1:26" ht="13">
       <c r="A867" s="1"/>
       <c r="B867" s="1"/>
       <c r="C867" s="1"/>
@@ -26402,7 +26373,7 @@
       <c r="Y867" s="1"/>
       <c r="Z867" s="1"/>
     </row>
-    <row r="868">
+    <row r="868" spans="1:26" ht="13">
       <c r="A868" s="1"/>
       <c r="B868" s="1"/>
       <c r="C868" s="1"/>
@@ -26430,7 +26401,7 @@
       <c r="Y868" s="1"/>
       <c r="Z868" s="1"/>
     </row>
-    <row r="869">
+    <row r="869" spans="1:26" ht="13">
       <c r="A869" s="1"/>
       <c r="B869" s="1"/>
       <c r="C869" s="1"/>
@@ -26458,7 +26429,7 @@
       <c r="Y869" s="1"/>
       <c r="Z869" s="1"/>
     </row>
-    <row r="870">
+    <row r="870" spans="1:26" ht="13">
       <c r="A870" s="1"/>
       <c r="B870" s="1"/>
       <c r="C870" s="1"/>
@@ -26486,7 +26457,7 @@
       <c r="Y870" s="1"/>
       <c r="Z870" s="1"/>
     </row>
-    <row r="871">
+    <row r="871" spans="1:26" ht="13">
       <c r="A871" s="1"/>
       <c r="B871" s="1"/>
       <c r="C871" s="1"/>
@@ -26514,7 +26485,7 @@
       <c r="Y871" s="1"/>
       <c r="Z871" s="1"/>
     </row>
-    <row r="872">
+    <row r="872" spans="1:26" ht="13">
       <c r="A872" s="1"/>
       <c r="B872" s="1"/>
       <c r="C872" s="1"/>
@@ -26542,7 +26513,7 @@
       <c r="Y872" s="1"/>
       <c r="Z872" s="1"/>
     </row>
-    <row r="873">
+    <row r="873" spans="1:26" ht="13">
       <c r="A873" s="1"/>
       <c r="B873" s="1"/>
       <c r="C873" s="1"/>
@@ -26570,7 +26541,7 @@
       <c r="Y873" s="1"/>
       <c r="Z873" s="1"/>
     </row>
-    <row r="874">
+    <row r="874" spans="1:26" ht="13">
       <c r="A874" s="1"/>
       <c r="B874" s="1"/>
       <c r="C874" s="1"/>
@@ -26598,7 +26569,7 @@
       <c r="Y874" s="1"/>
       <c r="Z874" s="1"/>
     </row>
-    <row r="875">
+    <row r="875" spans="1:26" ht="13">
       <c r="A875" s="1"/>
       <c r="B875" s="1"/>
       <c r="C875" s="1"/>
@@ -26626,7 +26597,7 @@
       <c r="Y875" s="1"/>
       <c r="Z875" s="1"/>
     </row>
-    <row r="876">
+    <row r="876" spans="1:26" ht="13">
       <c r="A876" s="1"/>
       <c r="B876" s="1"/>
       <c r="C876" s="1"/>
@@ -26654,7 +26625,7 @@
       <c r="Y876" s="1"/>
       <c r="Z876" s="1"/>
     </row>
-    <row r="877">
+    <row r="877" spans="1:26" ht="13">
       <c r="A877" s="1"/>
       <c r="B877" s="1"/>
       <c r="C877" s="1"/>
@@ -26682,7 +26653,7 @@
       <c r="Y877" s="1"/>
       <c r="Z877" s="1"/>
     </row>
-    <row r="878">
+    <row r="878" spans="1:26" ht="13">
       <c r="A878" s="1"/>
       <c r="B878" s="1"/>
       <c r="C878" s="1"/>
@@ -26710,7 +26681,7 @@
       <c r="Y878" s="1"/>
       <c r="Z878" s="1"/>
     </row>
-    <row r="879">
+    <row r="879" spans="1:26" ht="13">
       <c r="A879" s="1"/>
       <c r="B879" s="1"/>
       <c r="C879" s="1"/>
@@ -26738,7 +26709,7 @@
       <c r="Y879" s="1"/>
       <c r="Z879" s="1"/>
     </row>
-    <row r="880">
+    <row r="880" spans="1:26" ht="13">
       <c r="A880" s="1"/>
       <c r="B880" s="1"/>
       <c r="C880" s="1"/>
@@ -26766,7 +26737,7 @@
       <c r="Y880" s="1"/>
       <c r="Z880" s="1"/>
     </row>
-    <row r="881">
+    <row r="881" spans="1:26" ht="13">
       <c r="A881" s="1"/>
       <c r="B881" s="1"/>
       <c r="C881" s="1"/>
@@ -26794,7 +26765,7 @@
       <c r="Y881" s="1"/>
       <c r="Z881" s="1"/>
     </row>
-    <row r="882">
+    <row r="882" spans="1:26" ht="13">
       <c r="A882" s="1"/>
       <c r="B882" s="1"/>
       <c r="C882" s="1"/>
@@ -26822,7 +26793,7 @@
       <c r="Y882" s="1"/>
       <c r="Z882" s="1"/>
     </row>
-    <row r="883">
+    <row r="883" spans="1:26" ht="13">
       <c r="A883" s="1"/>
       <c r="B883" s="1"/>
       <c r="C883" s="1"/>
@@ -26850,7 +26821,7 @@
       <c r="Y883" s="1"/>
       <c r="Z883" s="1"/>
     </row>
-    <row r="884">
+    <row r="884" spans="1:26" ht="13">
       <c r="A884" s="1"/>
       <c r="B884" s="1"/>
       <c r="C884" s="1"/>
@@ -26878,7 +26849,7 @@
       <c r="Y884" s="1"/>
       <c r="Z884" s="1"/>
     </row>
-    <row r="885">
+    <row r="885" spans="1:26" ht="13">
       <c r="A885" s="1"/>
       <c r="B885" s="1"/>
       <c r="C885" s="1"/>
@@ -26906,7 +26877,7 @@
       <c r="Y885" s="1"/>
       <c r="Z885" s="1"/>
     </row>
-    <row r="886">
+    <row r="886" spans="1:26" ht="13">
       <c r="A886" s="1"/>
       <c r="B886" s="1"/>
       <c r="C886" s="1"/>
@@ -26934,7 +26905,7 @@
       <c r="Y886" s="1"/>
       <c r="Z886" s="1"/>
     </row>
-    <row r="887">
+    <row r="887" spans="1:26" ht="13">
       <c r="A887" s="1"/>
       <c r="B887" s="1"/>
       <c r="C887" s="1"/>
@@ -26962,7 +26933,7 @@
       <c r="Y887" s="1"/>
       <c r="Z887" s="1"/>
     </row>
-    <row r="888">
+    <row r="888" spans="1:26" ht="13">
       <c r="A888" s="1"/>
       <c r="B888" s="1"/>
       <c r="C888" s="1"/>
@@ -26990,7 +26961,7 @@
       <c r="Y888" s="1"/>
       <c r="Z888" s="1"/>
     </row>
-    <row r="889">
+    <row r="889" spans="1:26" ht="13">
       <c r="A889" s="1"/>
       <c r="B889" s="1"/>
       <c r="C889" s="1"/>
@@ -27018,7 +26989,7 @@
       <c r="Y889" s="1"/>
       <c r="Z889" s="1"/>
     </row>
-    <row r="890">
+    <row r="890" spans="1:26" ht="13">
       <c r="A890" s="1"/>
       <c r="B890" s="1"/>
       <c r="C890" s="1"/>
@@ -27046,7 +27017,7 @@
       <c r="Y890" s="1"/>
       <c r="Z890" s="1"/>
     </row>
-    <row r="891">
+    <row r="891" spans="1:26" ht="13">
       <c r="A891" s="1"/>
       <c r="B891" s="1"/>
       <c r="C891" s="1"/>
@@ -27074,7 +27045,7 @@
       <c r="Y891" s="1"/>
       <c r="Z891" s="1"/>
     </row>
-    <row r="892">
+    <row r="892" spans="1:26" ht="13">
       <c r="A892" s="1"/>
       <c r="B892" s="1"/>
       <c r="C892" s="1"/>
@@ -27102,7 +27073,7 @@
       <c r="Y892" s="1"/>
       <c r="Z892" s="1"/>
     </row>
-    <row r="893">
+    <row r="893" spans="1:26" ht="13">
       <c r="A893" s="1"/>
       <c r="B893" s="1"/>
       <c r="C893" s="1"/>
@@ -27130,7 +27101,7 @@
       <c r="Y893" s="1"/>
       <c r="Z893" s="1"/>
     </row>
-    <row r="894">
+    <row r="894" spans="1:26" ht="13">
       <c r="A894" s="1"/>
       <c r="B894" s="1"/>
       <c r="C894" s="1"/>
@@ -27158,7 +27129,7 @@
       <c r="Y894" s="1"/>
       <c r="Z894" s="1"/>
     </row>
-    <row r="895">
+    <row r="895" spans="1:26" ht="13">
       <c r="A895" s="1"/>
       <c r="B895" s="1"/>
       <c r="C895" s="1"/>
@@ -27186,7 +27157,7 @@
       <c r="Y895" s="1"/>
       <c r="Z895" s="1"/>
     </row>
-    <row r="896">
+    <row r="896" spans="1:26" ht="13">
       <c r="A896" s="1"/>
       <c r="B896" s="1"/>
       <c r="C896" s="1"/>
@@ -27214,7 +27185,7 @@
       <c r="Y896" s="1"/>
       <c r="Z896" s="1"/>
     </row>
-    <row r="897">
+    <row r="897" spans="1:26" ht="13">
       <c r="A897" s="1"/>
       <c r="B897" s="1"/>
       <c r="C897" s="1"/>
@@ -27242,7 +27213,7 @@
       <c r="Y897" s="1"/>
       <c r="Z897" s="1"/>
     </row>
-    <row r="898">
+    <row r="898" spans="1:26" ht="13">
       <c r="A898" s="1"/>
       <c r="B898" s="1"/>
       <c r="C898" s="1"/>
@@ -27270,7 +27241,7 @@
       <c r="Y898" s="1"/>
       <c r="Z898" s="1"/>
     </row>
-    <row r="899">
+    <row r="899" spans="1:26" ht="13">
       <c r="A899" s="1"/>
       <c r="B899" s="1"/>
       <c r="C899" s="1"/>
@@ -27298,7 +27269,7 @@
       <c r="Y899" s="1"/>
       <c r="Z899" s="1"/>
     </row>
-    <row r="900">
+    <row r="900" spans="1:26" ht="13">
       <c r="A900" s="1"/>
       <c r="B900" s="1"/>
       <c r="C900" s="1"/>
@@ -27326,7 +27297,7 @@
       <c r="Y900" s="1"/>
       <c r="Z900" s="1"/>
     </row>
-    <row r="901">
+    <row r="901" spans="1:26" ht="13">
       <c r="A901" s="1"/>
       <c r="B901" s="1"/>
       <c r="C901" s="1"/>
@@ -27354,7 +27325,7 @@
       <c r="Y901" s="1"/>
       <c r="Z901" s="1"/>
     </row>
-    <row r="902">
+    <row r="902" spans="1:26" ht="13">
       <c r="A902" s="1"/>
       <c r="B902" s="1"/>
       <c r="C902" s="1"/>
@@ -27382,7 +27353,7 @@
       <c r="Y902" s="1"/>
       <c r="Z902" s="1"/>
     </row>
-    <row r="903">
+    <row r="903" spans="1:26" ht="13">
       <c r="A903" s="1"/>
       <c r="B903" s="1"/>
       <c r="C903" s="1"/>
@@ -27410,7 +27381,7 @@
       <c r="Y903" s="1"/>
       <c r="Z903" s="1"/>
     </row>
-    <row r="904">
+    <row r="904" spans="1:26" ht="13">
       <c r="A904" s="1"/>
       <c r="B904" s="1"/>
       <c r="C904" s="1"/>
@@ -27438,7 +27409,7 @@
       <c r="Y904" s="1"/>
       <c r="Z904" s="1"/>
     </row>
-    <row r="905">
+    <row r="905" spans="1:26" ht="13">
       <c r="A905" s="1"/>
       <c r="B905" s="1"/>
       <c r="C905" s="1"/>
@@ -27466,7 +27437,7 @@
       <c r="Y905" s="1"/>
       <c r="Z905" s="1"/>
     </row>
-    <row r="906">
+    <row r="906" spans="1:26" ht="13">
       <c r="A906" s="1"/>
       <c r="B906" s="1"/>
       <c r="C906" s="1"/>
@@ -27494,7 +27465,7 @@
       <c r="Y906" s="1"/>
       <c r="Z906" s="1"/>
     </row>
-    <row r="907">
+    <row r="907" spans="1:26" ht="13">
       <c r="A907" s="1"/>
       <c r="B907" s="1"/>
       <c r="C907" s="1"/>
@@ -27522,7 +27493,7 @@
       <c r="Y907" s="1"/>
       <c r="Z907" s="1"/>
     </row>
-    <row r="908">
+    <row r="908" spans="1:26" ht="13">
       <c r="A908" s="1"/>
       <c r="B908" s="1"/>
       <c r="C908" s="1"/>
@@ -27550,7 +27521,7 @@
       <c r="Y908" s="1"/>
       <c r="Z908" s="1"/>
     </row>
-    <row r="909">
+    <row r="909" spans="1:26" ht="13">
       <c r="A909" s="1"/>
       <c r="B909" s="1"/>
       <c r="C909" s="1"/>
@@ -27578,7 +27549,7 @@
       <c r="Y909" s="1"/>
       <c r="Z909" s="1"/>
     </row>
-    <row r="910">
+    <row r="910" spans="1:26" ht="13">
       <c r="A910" s="1"/>
       <c r="B910" s="1"/>
       <c r="C910" s="1"/>
@@ -27606,7 +27577,7 @@
       <c r="Y910" s="1"/>
       <c r="Z910" s="1"/>
     </row>
-    <row r="911">
+    <row r="911" spans="1:26" ht="13">
       <c r="A911" s="1"/>
       <c r="B911" s="1"/>
       <c r="C911" s="1"/>
@@ -27634,7 +27605,7 @@
       <c r="Y911" s="1"/>
       <c r="Z911" s="1"/>
     </row>
-    <row r="912">
+    <row r="912" spans="1:26" ht="13">
       <c r="A912" s="1"/>
       <c r="B912" s="1"/>
       <c r="C912" s="1"/>
@@ -27662,7 +27633,7 @@
       <c r="Y912" s="1"/>
       <c r="Z912" s="1"/>
     </row>
-    <row r="913">
+    <row r="913" spans="1:26" ht="13">
       <c r="A913" s="1"/>
       <c r="B913" s="1"/>
       <c r="C913" s="1"/>
@@ -27690,7 +27661,7 @@
       <c r="Y913" s="1"/>
       <c r="Z913" s="1"/>
     </row>
-    <row r="914">
+    <row r="914" spans="1:26" ht="13">
       <c r="A914" s="1"/>
       <c r="B914" s="1"/>
       <c r="C914" s="1"/>
@@ -27718,7 +27689,7 @@
       <c r="Y914" s="1"/>
       <c r="Z914" s="1"/>
     </row>
-    <row r="915">
+    <row r="915" spans="1:26" ht="13">
       <c r="A915" s="1"/>
       <c r="B915" s="1"/>
       <c r="C915" s="1"/>
@@ -27746,7 +27717,7 @@
       <c r="Y915" s="1"/>
       <c r="Z915" s="1"/>
     </row>
-    <row r="916">
+    <row r="916" spans="1:26" ht="13">
       <c r="A916" s="1"/>
       <c r="B916" s="1"/>
       <c r="C916" s="1"/>
@@ -27774,7 +27745,7 @@
       <c r="Y916" s="1"/>
       <c r="Z916" s="1"/>
     </row>
-    <row r="917">
+    <row r="917" spans="1:26" ht="13">
       <c r="A917" s="1"/>
       <c r="B917" s="1"/>
       <c r="C917" s="1"/>
@@ -27802,7 +27773,7 @@
       <c r="Y917" s="1"/>
       <c r="Z917" s="1"/>
     </row>
-    <row r="918">
+    <row r="918" spans="1:26" ht="13">
       <c r="A918" s="1"/>
       <c r="B918" s="1"/>
       <c r="C918" s="1"/>
@@ -27830,7 +27801,7 @@
       <c r="Y918" s="1"/>
       <c r="Z918" s="1"/>
     </row>
-    <row r="919">
+    <row r="919" spans="1:26" ht="13">
       <c r="A919" s="1"/>
       <c r="B919" s="1"/>
       <c r="C919" s="1"/>
@@ -27858,7 +27829,7 @@
       <c r="Y919" s="1"/>
       <c r="Z919" s="1"/>
     </row>
-    <row r="920">
+    <row r="920" spans="1:26" ht="13">
       <c r="A920" s="1"/>
       <c r="B920" s="1"/>
       <c r="C920" s="1"/>
@@ -27886,7 +27857,7 @@
       <c r="Y920" s="1"/>
       <c r="Z920" s="1"/>
     </row>
-    <row r="921">
+    <row r="921" spans="1:26" ht="13">
       <c r="A921" s="1"/>
       <c r="B921" s="1"/>
       <c r="C921" s="1"/>
@@ -27914,7 +27885,7 @@
       <c r="Y921" s="1"/>
       <c r="Z921" s="1"/>
     </row>
-    <row r="922">
+    <row r="922" spans="1:26" ht="13">
       <c r="A922" s="1"/>
       <c r="B922" s="1"/>
       <c r="C922" s="1"/>
@@ -27942,7 +27913,7 @@
       <c r="Y922" s="1"/>
       <c r="Z922" s="1"/>
     </row>
-    <row r="923">
+    <row r="923" spans="1:26" ht="13">
       <c r="A923" s="1"/>
       <c r="B923" s="1"/>
       <c r="C923" s="1"/>
@@ -27970,7 +27941,7 @@
       <c r="Y923" s="1"/>
       <c r="Z923" s="1"/>
     </row>
-    <row r="924">
+    <row r="924" spans="1:26" ht="13">
       <c r="A924" s="1"/>
       <c r="B924" s="1"/>
       <c r="C924" s="1"/>
@@ -27998,7 +27969,7 @@
       <c r="Y924" s="1"/>
       <c r="Z924" s="1"/>
     </row>
-    <row r="925">
+    <row r="925" spans="1:26" ht="13">
       <c r="A925" s="1"/>
       <c r="B925" s="1"/>
       <c r="C925" s="1"/>
@@ -28026,7 +27997,7 @@
       <c r="Y925" s="1"/>
       <c r="Z925" s="1"/>
     </row>
-    <row r="926">
+    <row r="926" spans="1:26" ht="13">
       <c r="A926" s="1"/>
       <c r="B926" s="1"/>
       <c r="C926" s="1"/>
@@ -28054,7 +28025,7 @@
       <c r="Y926" s="1"/>
       <c r="Z926" s="1"/>
     </row>
-    <row r="927">
+    <row r="927" spans="1:26" ht="13">
       <c r="A927" s="1"/>
       <c r="B927" s="1"/>
       <c r="C927" s="1"/>
@@ -28082,7 +28053,7 @@
       <c r="Y927" s="1"/>
       <c r="Z927" s="1"/>
     </row>
-    <row r="928">
+    <row r="928" spans="1:26" ht="13">
       <c r="A928" s="1"/>
       <c r="B928" s="1"/>
       <c r="C928" s="1"/>
@@ -28110,7 +28081,7 @@
       <c r="Y928" s="1"/>
       <c r="Z928" s="1"/>
     </row>
-    <row r="929">
+    <row r="929" spans="1:26" ht="13">
       <c r="A929" s="1"/>
       <c r="B929" s="1"/>
       <c r="C929" s="1"/>
@@ -28138,7 +28109,7 @@
       <c r="Y929" s="1"/>
       <c r="Z929" s="1"/>
     </row>
-    <row r="930">
+    <row r="930" spans="1:26" ht="13">
       <c r="A930" s="1"/>
       <c r="B930" s="1"/>
       <c r="C930" s="1"/>
@@ -28166,7 +28137,7 @@
       <c r="Y930" s="1"/>
       <c r="Z930" s="1"/>
     </row>
-    <row r="931">
+    <row r="931" spans="1:26" ht="13">
       <c r="A931" s="1"/>
       <c r="B931" s="1"/>
       <c r="C931" s="1"/>
@@ -28194,7 +28165,7 @@
       <c r="Y931" s="1"/>
       <c r="Z931" s="1"/>
     </row>
-    <row r="932">
+    <row r="932" spans="1:26" ht="13">
       <c r="A932" s="1"/>
       <c r="B932" s="1"/>
       <c r="C932" s="1"/>
@@ -28222,7 +28193,7 @@
       <c r="Y932" s="1"/>
       <c r="Z932" s="1"/>
     </row>
-    <row r="933">
+    <row r="933" spans="1:26" ht="13">
       <c r="A933" s="1"/>
       <c r="B933" s="1"/>
       <c r="C933" s="1"/>
@@ -28250,7 +28221,7 @@
       <c r="Y933" s="1"/>
       <c r="Z933" s="1"/>
     </row>
-    <row r="934">
+    <row r="934" spans="1:26" ht="13">
       <c r="A934" s="1"/>
       <c r="B934" s="1"/>
       <c r="C934" s="1"/>
@@ -28278,7 +28249,7 @@
       <c r="Y934" s="1"/>
       <c r="Z934" s="1"/>
     </row>
-    <row r="935">
+    <row r="935" spans="1:26" ht="13">
       <c r="A935" s="1"/>
       <c r="B935" s="1"/>
       <c r="C935" s="1"/>
@@ -28306,7 +28277,7 @@
       <c r="Y935" s="1"/>
       <c r="Z935" s="1"/>
     </row>
-    <row r="936">
+    <row r="936" spans="1:26" ht="13">
       <c r="A936" s="1"/>
       <c r="B936" s="1"/>
       <c r="C936" s="1"/>
@@ -28334,7 +28305,7 @@
       <c r="Y936" s="1"/>
       <c r="Z936" s="1"/>
     </row>
-    <row r="937">
+    <row r="937" spans="1:26" ht="13">
       <c r="A937" s="1"/>
       <c r="B937" s="1"/>
       <c r="C937" s="1"/>
@@ -28362,7 +28333,7 @@
       <c r="Y937" s="1"/>
       <c r="Z937" s="1"/>
     </row>
-    <row r="938">
+    <row r="938" spans="1:26" ht="13">
       <c r="A938" s="1"/>
       <c r="B938" s="1"/>
       <c r="C938" s="1"/>
@@ -28390,7 +28361,7 @@
       <c r="Y938" s="1"/>
       <c r="Z938" s="1"/>
     </row>
-    <row r="939">
+    <row r="939" spans="1:26" ht="13">
       <c r="A939" s="1"/>
       <c r="B939" s="1"/>
       <c r="C939" s="1"/>
@@ -28418,7 +28389,7 @@
       <c r="Y939" s="1"/>
       <c r="Z939" s="1"/>
     </row>
-    <row r="940">
+    <row r="940" spans="1:26" ht="13">
       <c r="A940" s="1"/>
       <c r="B940" s="1"/>
       <c r="C940" s="1"/>
@@ -28446,7 +28417,7 @@
       <c r="Y940" s="1"/>
       <c r="Z940" s="1"/>
     </row>
-    <row r="941">
+    <row r="941" spans="1:26" ht="13">
       <c r="A941" s="1"/>
       <c r="B941" s="1"/>
       <c r="C941" s="1"/>
@@ -28474,7 +28445,7 @@
       <c r="Y941" s="1"/>
       <c r="Z941" s="1"/>
     </row>
-    <row r="942">
+    <row r="942" spans="1:26" ht="13">
       <c r="A942" s="1"/>
       <c r="B942" s="1"/>
       <c r="C942" s="1"/>
@@ -28502,7 +28473,7 @@
       <c r="Y942" s="1"/>
       <c r="Z942" s="1"/>
     </row>
-    <row r="943">
+    <row r="943" spans="1:26" ht="13">
       <c r="A943" s="1"/>
       <c r="B943" s="1"/>
       <c r="C943" s="1"/>
@@ -28530,7 +28501,7 @@
       <c r="Y943" s="1"/>
       <c r="Z943" s="1"/>
     </row>
-    <row r="944">
+    <row r="944" spans="1:26" ht="13">
       <c r="A944" s="1"/>
       <c r="B944" s="1"/>
       <c r="C944" s="1"/>
@@ -28558,7 +28529,7 @@
       <c r="Y944" s="1"/>
       <c r="Z944" s="1"/>
     </row>
-    <row r="945">
+    <row r="945" spans="1:26" ht="13">
       <c r="A945" s="1"/>
       <c r="B945" s="1"/>
       <c r="C945" s="1"/>
@@ -28586,7 +28557,7 @@
       <c r="Y945" s="1"/>
       <c r="Z945" s="1"/>
     </row>
-    <row r="946">
+    <row r="946" spans="1:26" ht="13">
       <c r="A946" s="1"/>
       <c r="B946" s="1"/>
       <c r="C946" s="1"/>
@@ -28614,7 +28585,7 @@
       <c r="Y946" s="1"/>
       <c r="Z946" s="1"/>
     </row>
-    <row r="947">
+    <row r="947" spans="1:26" ht="13">
       <c r="A947" s="1"/>
       <c r="B947" s="1"/>
       <c r="C947" s="1"/>
@@ -28642,7 +28613,7 @@
       <c r="Y947" s="1"/>
       <c r="Z947" s="1"/>
     </row>
-    <row r="948">
+    <row r="948" spans="1:26" ht="13">
       <c r="A948" s="1"/>
       <c r="B948" s="1"/>
       <c r="C948" s="1"/>
@@ -28670,7 +28641,7 @@
       <c r="Y948" s="1"/>
       <c r="Z948" s="1"/>
     </row>
-    <row r="949">
+    <row r="949" spans="1:26" ht="13">
       <c r="A949" s="1"/>
       <c r="B949" s="1"/>
       <c r="C949" s="1"/>
@@ -28698,7 +28669,7 @@
       <c r="Y949" s="1"/>
       <c r="Z949" s="1"/>
     </row>
-    <row r="950">
+    <row r="950" spans="1:26" ht="13">
       <c r="A950" s="1"/>
       <c r="B950" s="1"/>
       <c r="C950" s="1"/>
@@ -28726,7 +28697,7 @@
       <c r="Y950" s="1"/>
       <c r="Z950" s="1"/>
     </row>
-    <row r="951">
+    <row r="951" spans="1:26" ht="13">
       <c r="A951" s="1"/>
       <c r="B951" s="1"/>
       <c r="C951" s="1"/>
@@ -28754,7 +28725,7 @@
       <c r="Y951" s="1"/>
       <c r="Z951" s="1"/>
     </row>
-    <row r="952">
+    <row r="952" spans="1:26" ht="13">
       <c r="A952" s="1"/>
       <c r="B952" s="1"/>
       <c r="C952" s="1"/>
@@ -28782,7 +28753,7 @@
       <c r="Y952" s="1"/>
       <c r="Z952" s="1"/>
     </row>
-    <row r="953">
+    <row r="953" spans="1:26" ht="13">
       <c r="A953" s="1"/>
       <c r="B953" s="1"/>
       <c r="C953" s="1"/>
@@ -28810,7 +28781,7 @@
       <c r="Y953" s="1"/>
       <c r="Z953" s="1"/>
     </row>
-    <row r="954">
+    <row r="954" spans="1:26" ht="13">
       <c r="A954" s="1"/>
       <c r="B954" s="1"/>
       <c r="C954" s="1"/>
@@ -28838,7 +28809,7 @@
       <c r="Y954" s="1"/>
       <c r="Z954" s="1"/>
     </row>
-    <row r="955">
+    <row r="955" spans="1:26" ht="13">
       <c r="A955" s="1"/>
       <c r="B955" s="1"/>
       <c r="C955" s="1"/>
@@ -28866,7 +28837,7 @@
       <c r="Y955" s="1"/>
       <c r="Z955" s="1"/>
     </row>
-    <row r="956">
+    <row r="956" spans="1:26" ht="13">
       <c r="A956" s="1"/>
       <c r="B956" s="1"/>
       <c r="C956" s="1"/>
@@ -28894,7 +28865,7 @@
       <c r="Y956" s="1"/>
       <c r="Z956" s="1"/>
     </row>
-    <row r="957">
+    <row r="957" spans="1:26" ht="13">
       <c r="A957" s="1"/>
       <c r="B957" s="1"/>
       <c r="C957" s="1"/>
@@ -28922,7 +28893,7 @@
       <c r="Y957" s="1"/>
       <c r="Z957" s="1"/>
     </row>
-    <row r="958">
+    <row r="958" spans="1:26" ht="13">
       <c r="A958" s="1"/>
       <c r="B958" s="1"/>
       <c r="C958" s="1"/>
@@ -28950,7 +28921,7 @@
       <c r="Y958" s="1"/>
       <c r="Z958" s="1"/>
     </row>
-    <row r="959">
+    <row r="959" spans="1:26" ht="13">
       <c r="A959" s="1"/>
       <c r="B959" s="1"/>
       <c r="C959" s="1"/>
@@ -28978,7 +28949,7 @@
       <c r="Y959" s="1"/>
       <c r="Z959" s="1"/>
     </row>
-    <row r="960">
+    <row r="960" spans="1:26" ht="13">
       <c r="A960" s="1"/>
       <c r="B960" s="1"/>
       <c r="C960" s="1"/>
@@ -29006,7 +28977,7 @@
       <c r="Y960" s="1"/>
       <c r="Z960" s="1"/>
     </row>
-    <row r="961">
+    <row r="961" spans="1:26" ht="13">
       <c r="A961" s="1"/>
       <c r="B961" s="1"/>
       <c r="C961" s="1"/>
@@ -29034,7 +29005,7 @@
       <c r="Y961" s="1"/>
       <c r="Z961" s="1"/>
     </row>
-    <row r="962">
+    <row r="962" spans="1:26" ht="13">
       <c r="A962" s="1"/>
       <c r="B962" s="1"/>
       <c r="C962" s="1"/>
@@ -29062,7 +29033,7 @@
       <c r="Y962" s="1"/>
       <c r="Z962" s="1"/>
     </row>
-    <row r="963">
+    <row r="963" spans="1:26" ht="13">
       <c r="A963" s="1"/>
       <c r="B963" s="1"/>
       <c r="C963" s="1"/>
@@ -29090,7 +29061,7 @@
       <c r="Y963" s="1"/>
       <c r="Z963" s="1"/>
     </row>
-    <row r="964">
+    <row r="964" spans="1:26" ht="13">
       <c r="A964" s="1"/>
       <c r="B964" s="1"/>
       <c r="C964" s="1"/>
@@ -29118,7 +29089,7 @@
       <c r="Y964" s="1"/>
       <c r="Z964" s="1"/>
     </row>
-    <row r="965">
+    <row r="965" spans="1:26" ht="13">
       <c r="A965" s="1"/>
       <c r="B965" s="1"/>
       <c r="C965" s="1"/>
@@ -29146,7 +29117,7 @@
       <c r="Y965" s="1"/>
       <c r="Z965" s="1"/>
     </row>
-    <row r="966">
+    <row r="966" spans="1:26" ht="13">
       <c r="A966" s="1"/>
       <c r="B966" s="1"/>
       <c r="C966" s="1"/>
@@ -29174,7 +29145,7 @@
       <c r="Y966" s="1"/>
       <c r="Z966" s="1"/>
     </row>
-    <row r="967">
+    <row r="967" spans="1:26" ht="13">
       <c r="A967" s="1"/>
       <c r="B967" s="1"/>
       <c r="C967" s="1"/>
@@ -29202,7 +29173,7 @@
       <c r="Y967" s="1"/>
       <c r="Z967" s="1"/>
     </row>
-    <row r="968">
+    <row r="968" spans="1:26" ht="13">
       <c r="A968" s="1"/>
       <c r="B968" s="1"/>
       <c r="C968" s="1"/>
@@ -29230,7 +29201,7 @@
       <c r="Y968" s="1"/>
       <c r="Z968" s="1"/>
     </row>
-    <row r="969">
+    <row r="969" spans="1:26" ht="13">
       <c r="A969" s="1"/>
       <c r="B969" s="1"/>
       <c r="C969" s="1"/>
@@ -29258,7 +29229,7 @@
       <c r="Y969" s="1"/>
       <c r="Z969" s="1"/>
     </row>
-    <row r="970">
+    <row r="970" spans="1:26" ht="13">
       <c r="A970" s="1"/>
       <c r="B970" s="1"/>
       <c r="C970" s="1"/>
@@ -29286,7 +29257,7 @@
       <c r="Y970" s="1"/>
       <c r="Z970" s="1"/>
     </row>
-    <row r="971">
+    <row r="971" spans="1:26" ht="13">
       <c r="A971" s="1"/>
       <c r="B971" s="1"/>
       <c r="C971" s="1"/>
@@ -29314,7 +29285,7 @@
       <c r="Y971" s="1"/>
       <c r="Z971" s="1"/>
     </row>
-    <row r="972">
+    <row r="972" spans="1:26" ht="13">
       <c r="A972" s="1"/>
       <c r="B972" s="1"/>
       <c r="C972" s="1"/>
@@ -29342,7 +29313,7 @@
       <c r="Y972" s="1"/>
       <c r="Z972" s="1"/>
     </row>
-    <row r="973">
+    <row r="973" spans="1:26" ht="13">
       <c r="A973" s="1"/>
       <c r="B973" s="1"/>
       <c r="C973" s="1"/>
@@ -29370,7 +29341,7 @@
       <c r="Y973" s="1"/>
       <c r="Z973" s="1"/>
     </row>
-    <row r="974">
+    <row r="974" spans="1:26" ht="13">
       <c r="A974" s="1"/>
       <c r="B974" s="1"/>
       <c r="C974" s="1"/>
@@ -29398,7 +29369,7 @@
       <c r="Y974" s="1"/>
       <c r="Z974" s="1"/>
     </row>
-    <row r="975">
+    <row r="975" spans="1:26" ht="13">
       <c r="A975" s="1"/>
       <c r="B975" s="1"/>
       <c r="C975" s="1"/>
@@ -29426,7 +29397,7 @@
       <c r="Y975" s="1"/>
       <c r="Z975" s="1"/>
     </row>
-    <row r="976">
+    <row r="976" spans="1:26" ht="13">
       <c r="A976" s="1"/>
       <c r="B976" s="1"/>
       <c r="C976" s="1"/>
@@ -29454,7 +29425,7 @@
       <c r="Y976" s="1"/>
       <c r="Z976" s="1"/>
     </row>
-    <row r="977">
+    <row r="977" spans="1:26" ht="13">
       <c r="A977" s="1"/>
       <c r="B977" s="1"/>
       <c r="C977" s="1"/>
@@ -29482,7 +29453,7 @@
       <c r="Y977" s="1"/>
       <c r="Z977" s="1"/>
     </row>
-    <row r="978">
+    <row r="978" spans="1:26" ht="13">
       <c r="A978" s="1"/>
       <c r="B978" s="1"/>
       <c r="C978" s="1"/>
@@ -29510,7 +29481,7 @@
       <c r="Y978" s="1"/>
       <c r="Z978" s="1"/>
     </row>
-    <row r="979">
+    <row r="979" spans="1:26" ht="13">
       <c r="A979" s="1"/>
       <c r="B979" s="1"/>
       <c r="C979" s="1"/>
@@ -29538,7 +29509,7 @@
       <c r="Y979" s="1"/>
       <c r="Z979" s="1"/>
     </row>
-    <row r="980">
+    <row r="980" spans="1:26" ht="13">
       <c r="A980" s="1"/>
       <c r="B980" s="1"/>
       <c r="C980" s="1"/>
@@ -29566,7 +29537,7 @@
       <c r="Y980" s="1"/>
       <c r="Z980" s="1"/>
     </row>
-    <row r="981">
+    <row r="981" spans="1:26" ht="13">
       <c r="A981" s="1"/>
       <c r="B981" s="1"/>
       <c r="C981" s="1"/>
@@ -29594,7 +29565,7 @@
       <c r="Y981" s="1"/>
       <c r="Z981" s="1"/>
     </row>
-    <row r="982">
+    <row r="982" spans="1:26" ht="13">
       <c r="A982" s="1"/>
       <c r="B982" s="1"/>
       <c r="C982" s="1"/>
@@ -29622,7 +29593,7 @@
       <c r="Y982" s="1"/>
       <c r="Z982" s="1"/>
     </row>
-    <row r="983">
+    <row r="983" spans="1:26" ht="13">
       <c r="A983" s="1"/>
       <c r="B983" s="1"/>
       <c r="C983" s="1"/>
@@ -29650,7 +29621,7 @@
       <c r="Y983" s="1"/>
       <c r="Z983" s="1"/>
     </row>
-    <row r="984">
+    <row r="984" spans="1:26" ht="13">
       <c r="A984" s="1"/>
       <c r="B984" s="1"/>
       <c r="C984" s="1"/>
@@ -29678,7 +29649,7 @@
       <c r="Y984" s="1"/>
       <c r="Z984" s="1"/>
     </row>
-    <row r="985">
+    <row r="985" spans="1:26" ht="13">
       <c r="A985" s="1"/>
       <c r="B985" s="1"/>
       <c r="C985" s="1"/>
@@ -29706,7 +29677,7 @@
       <c r="Y985" s="1"/>
       <c r="Z985" s="1"/>
     </row>
-    <row r="986">
+    <row r="986" spans="1:26" ht="13">
       <c r="A986" s="1"/>
       <c r="B986" s="1"/>
       <c r="C986" s="1"/>
@@ -29734,7 +29705,7 @@
       <c r="Y986" s="1"/>
       <c r="Z986" s="1"/>
     </row>
-    <row r="987">
+    <row r="987" spans="1:26" ht="13">
       <c r="A987" s="1"/>
       <c r="B987" s="1"/>
       <c r="C987" s="1"/>
@@ -29762,7 +29733,7 @@
       <c r="Y987" s="1"/>
       <c r="Z987" s="1"/>
     </row>
-    <row r="988">
+    <row r="988" spans="1:26" ht="13">
       <c r="A988" s="1"/>
       <c r="B988" s="1"/>
       <c r="C988" s="1"/>
@@ -29790,7 +29761,7 @@
       <c r="Y988" s="1"/>
       <c r="Z988" s="1"/>
     </row>
-    <row r="989">
+    <row r="989" spans="1:26" ht="13">
       <c r="A989" s="1"/>
       <c r="B989" s="1"/>
       <c r="C989" s="1"/>
@@ -29818,7 +29789,7 @@
       <c r="Y989" s="1"/>
       <c r="Z989" s="1"/>
     </row>
-    <row r="990">
+    <row r="990" spans="1:26" ht="13">
       <c r="A990" s="1"/>
       <c r="B990" s="1"/>
       <c r="C990" s="1"/>
@@ -29846,7 +29817,7 @@
       <c r="Y990" s="1"/>
       <c r="Z990" s="1"/>
     </row>
-    <row r="991">
+    <row r="991" spans="1:26" ht="13">
       <c r="A991" s="1"/>
       <c r="B991" s="1"/>
       <c r="C991" s="1"/>
@@ -29874,7 +29845,7 @@
       <c r="Y991" s="1"/>
       <c r="Z991" s="1"/>
     </row>
-    <row r="992">
+    <row r="992" spans="1:26" ht="13">
       <c r="A992" s="1"/>
       <c r="B992" s="1"/>
       <c r="C992" s="1"/>
@@ -29902,7 +29873,7 @@
       <c r="Y992" s="1"/>
       <c r="Z992" s="1"/>
     </row>
-    <row r="993">
+    <row r="993" spans="1:26" ht="13">
       <c r="A993" s="1"/>
       <c r="B993" s="1"/>
       <c r="C993" s="1"/>
@@ -29930,7 +29901,7 @@
       <c r="Y993" s="1"/>
       <c r="Z993" s="1"/>
     </row>
-    <row r="994">
+    <row r="994" spans="1:26" ht="13">
       <c r="A994" s="1"/>
       <c r="B994" s="1"/>
       <c r="C994" s="1"/>
@@ -29958,7 +29929,7 @@
       <c r="Y994" s="1"/>
       <c r="Z994" s="1"/>
     </row>
-    <row r="995">
+    <row r="995" spans="1:26" ht="13">
       <c r="A995" s="1"/>
       <c r="B995" s="1"/>
       <c r="C995" s="1"/>
@@ -29986,7 +29957,7 @@
       <c r="Y995" s="1"/>
       <c r="Z995" s="1"/>
     </row>
-    <row r="996">
+    <row r="996" spans="1:26" ht="13">
       <c r="A996" s="1"/>
       <c r="B996" s="1"/>
       <c r="C996" s="1"/>
@@ -30014,7 +29985,7 @@
       <c r="Y996" s="1"/>
       <c r="Z996" s="1"/>
     </row>
-    <row r="997">
+    <row r="997" spans="1:26" ht="13">
       <c r="A997" s="1"/>
       <c r="B997" s="1"/>
       <c r="C997" s="1"/>
@@ -30042,7 +30013,7 @@
       <c r="Y997" s="1"/>
       <c r="Z997" s="1"/>
     </row>
-    <row r="998">
+    <row r="998" spans="1:26" ht="13">
       <c r="A998" s="1"/>
       <c r="B998" s="1"/>
       <c r="C998" s="1"/>
@@ -30070,7 +30041,7 @@
       <c r="Y998" s="1"/>
       <c r="Z998" s="1"/>
     </row>
-    <row r="999">
+    <row r="999" spans="1:26" ht="13">
       <c r="A999" s="1"/>
       <c r="B999" s="1"/>
       <c r="C999" s="1"/>
@@ -30098,7 +30069,7 @@
       <c r="Y999" s="1"/>
       <c r="Z999" s="1"/>
     </row>
-    <row r="1000">
+    <row r="1000" spans="1:26" ht="13">
       <c r="A1000" s="1"/>
       <c r="B1000" s="1"/>
       <c r="C1000" s="1"/>
@@ -30126,7 +30097,7 @@
       <c r="Y1000" s="1"/>
       <c r="Z1000" s="1"/>
     </row>
-    <row r="1001">
+    <row r="1001" spans="1:26" ht="13">
       <c r="A1001" s="1"/>
       <c r="B1001" s="1"/>
       <c r="C1001" s="1"/>
@@ -30154,7 +30125,7 @@
       <c r="Y1001" s="1"/>
       <c r="Z1001" s="1"/>
     </row>
-    <row r="1002">
+    <row r="1002" spans="1:26" ht="13">
       <c r="A1002" s="1"/>
       <c r="B1002" s="1"/>
       <c r="C1002" s="1"/>
@@ -30182,7 +30153,7 @@
       <c r="Y1002" s="1"/>
       <c r="Z1002" s="1"/>
     </row>
-    <row r="1003">
+    <row r="1003" spans="1:26" ht="13">
       <c r="A1003" s="1"/>
       <c r="B1003" s="1"/>
       <c r="C1003" s="1"/>
@@ -30210,7 +30181,7 @@
       <c r="Y1003" s="1"/>
       <c r="Z1003" s="1"/>
     </row>
-    <row r="1004">
+    <row r="1004" spans="1:26" ht="13">
       <c r="A1004" s="1"/>
       <c r="B1004" s="1"/>
       <c r="C1004" s="1"/>
@@ -30238,7 +30209,7 @@
       <c r="Y1004" s="1"/>
       <c r="Z1004" s="1"/>
     </row>
-    <row r="1005">
+    <row r="1005" spans="1:26" ht="13">
       <c r="A1005" s="1"/>
       <c r="B1005" s="1"/>
       <c r="C1005" s="1"/>
@@ -30266,7 +30237,7 @@
       <c r="Y1005" s="1"/>
       <c r="Z1005" s="1"/>
     </row>
-    <row r="1006">
+    <row r="1006" spans="1:26" ht="13">
       <c r="A1006" s="1"/>
       <c r="B1006" s="1"/>
       <c r="C1006" s="1"/>
@@ -30294,7 +30265,7 @@
       <c r="Y1006" s="1"/>
       <c r="Z1006" s="1"/>
     </row>
-    <row r="1007">
+    <row r="1007" spans="1:26" ht="13">
       <c r="A1007" s="1"/>
       <c r="B1007" s="1"/>
       <c r="C1007" s="1"/>
@@ -30322,7 +30293,7 @@
       <c r="Y1007" s="1"/>
       <c r="Z1007" s="1"/>
     </row>
-    <row r="1008">
+    <row r="1008" spans="1:26" ht="13">
       <c r="A1008" s="1"/>
       <c r="B1008" s="1"/>
       <c r="C1008" s="1"/>
@@ -30350,7 +30321,7 @@
       <c r="Y1008" s="1"/>
       <c r="Z1008" s="1"/>
     </row>
-    <row r="1009">
+    <row r="1009" spans="1:26" ht="13">
       <c r="A1009" s="1"/>
       <c r="B1009" s="1"/>
       <c r="C1009" s="1"/>
@@ -30378,7 +30349,7 @@
       <c r="Y1009" s="1"/>
       <c r="Z1009" s="1"/>
     </row>
-    <row r="1010">
+    <row r="1010" spans="1:26" ht="13">
       <c r="A1010" s="1"/>
       <c r="B1010" s="1"/>
       <c r="C1010" s="1"/>
@@ -30406,7 +30377,7 @@
       <c r="Y1010" s="1"/>
       <c r="Z1010" s="1"/>
     </row>
-    <row r="1011">
+    <row r="1011" spans="1:26" ht="13">
       <c r="A1011" s="1"/>
       <c r="B1011" s="1"/>
       <c r="C1011" s="1"/>
@@ -30434,7 +30405,7 @@
       <c r="Y1011" s="1"/>
       <c r="Z1011" s="1"/>
     </row>
-    <row r="1012">
+    <row r="1012" spans="1:26" ht="13">
       <c r="A1012" s="1"/>
       <c r="B1012" s="1"/>
       <c r="C1012" s="1"/>
@@ -30462,7 +30433,7 @@
       <c r="Y1012" s="1"/>
       <c r="Z1012" s="1"/>
     </row>
-    <row r="1013">
+    <row r="1013" spans="1:26" ht="13">
       <c r="A1013" s="1"/>
       <c r="B1013" s="1"/>
       <c r="C1013" s="1"/>
@@ -30490,7 +30461,7 @@
       <c r="Y1013" s="1"/>
       <c r="Z1013" s="1"/>
     </row>
-    <row r="1014">
+    <row r="1014" spans="1:26" ht="13">
       <c r="A1014" s="1"/>
       <c r="B1014" s="1"/>
       <c r="C1014" s="1"/>
@@ -30518,7 +30489,7 @@
       <c r="Y1014" s="1"/>
       <c r="Z1014" s="1"/>
     </row>
-    <row r="1015">
+    <row r="1015" spans="1:26" ht="13">
       <c r="A1015" s="1"/>
       <c r="B1015" s="1"/>
       <c r="C1015" s="1"/>
@@ -30546,7 +30517,7 @@
       <c r="Y1015" s="1"/>
       <c r="Z1015" s="1"/>
     </row>
-    <row r="1016">
+    <row r="1016" spans="1:26" ht="13">
       <c r="A1016" s="1"/>
       <c r="B1016" s="1"/>
       <c r="C1016" s="1"/>
@@ -30574,7 +30545,7 @@
       <c r="Y1016" s="1"/>
       <c r="Z1016" s="1"/>
     </row>
-    <row r="1017">
+    <row r="1017" spans="1:26" ht="13">
       <c r="A1017" s="1"/>
       <c r="B1017" s="1"/>
       <c r="C1017" s="1"/>
@@ -30602,7 +30573,7 @@
       <c r="Y1017" s="1"/>
       <c r="Z1017" s="1"/>
     </row>
-    <row r="1018">
+    <row r="1018" spans="1:26" ht="13">
       <c r="A1018" s="1"/>
       <c r="B1018" s="1"/>
       <c r="C1018" s="1"/>
@@ -30630,7 +30601,7 @@
       <c r="Y1018" s="1"/>
       <c r="Z1018" s="1"/>
     </row>
-    <row r="1019">
+    <row r="1019" spans="1:26" ht="13">
       <c r="A1019" s="1"/>
       <c r="B1019" s="1"/>
       <c r="C1019" s="1"/>
@@ -30658,7 +30629,7 @@
       <c r="Y1019" s="1"/>
       <c r="Z1019" s="1"/>
     </row>
-    <row r="1020">
+    <row r="1020" spans="1:26" ht="13">
       <c r="A1020" s="1"/>
       <c r="B1020" s="1"/>
       <c r="C1020" s="1"/>
@@ -30686,7 +30657,7 @@
       <c r="Y1020" s="1"/>
       <c r="Z1020" s="1"/>
     </row>
-    <row r="1021">
+    <row r="1021" spans="1:26" ht="13">
       <c r="A1021" s="1"/>
       <c r="B1021" s="1"/>
       <c r="C1021" s="1"/>
@@ -30714,7 +30685,7 @@
       <c r="Y1021" s="1"/>
       <c r="Z1021" s="1"/>
     </row>
-    <row r="1022">
+    <row r="1022" spans="1:26" ht="13">
       <c r="A1022" s="1"/>
       <c r="B1022" s="1"/>
       <c r="C1022" s="1"/>
@@ -30742,7 +30713,7 @@
       <c r="Y1022" s="1"/>
       <c r="Z1022" s="1"/>
     </row>
-    <row r="1023">
+    <row r="1023" spans="1:26" ht="13">
       <c r="A1023" s="1"/>
       <c r="B1023" s="1"/>
       <c r="C1023" s="1"/>
@@ -30770,7 +30741,7 @@
       <c r="Y1023" s="1"/>
       <c r="Z1023" s="1"/>
     </row>
-    <row r="1024">
+    <row r="1024" spans="1:26" ht="13">
       <c r="A1024" s="1"/>
       <c r="B1024" s="1"/>
       <c r="C1024" s="1"/>
@@ -30798,7 +30769,7 @@
       <c r="Y1024" s="1"/>
       <c r="Z1024" s="1"/>
     </row>
-    <row r="1025">
+    <row r="1025" spans="1:26" ht="13">
       <c r="A1025" s="1"/>
       <c r="B1025" s="1"/>
       <c r="C1025" s="1"/>
@@ -30826,7 +30797,7 @@
       <c r="Y1025" s="1"/>
       <c r="Z1025" s="1"/>
     </row>
-    <row r="1026">
+    <row r="1026" spans="1:26" ht="13">
       <c r="A1026" s="1"/>
       <c r="B1026" s="1"/>
       <c r="C1026" s="1"/>
@@ -30854,7 +30825,7 @@
       <c r="Y1026" s="1"/>
       <c r="Z1026" s="1"/>
     </row>
-    <row r="1027">
+    <row r="1027" spans="1:26" ht="13">
       <c r="A1027" s="1"/>
       <c r="B1027" s="1"/>
       <c r="C1027" s="1"/>
@@ -30882,7 +30853,7 @@
       <c r="Y1027" s="1"/>
       <c r="Z1027" s="1"/>
     </row>
-    <row r="1028">
+    <row r="1028" spans="1:26" ht="13">
       <c r="A1028" s="1"/>
       <c r="B1028" s="1"/>
       <c r="C1028" s="1"/>
@@ -30910,7 +30881,7 @@
       <c r="Y1028" s="1"/>
       <c r="Z1028" s="1"/>
     </row>
-    <row r="1029">
+    <row r="1029" spans="1:26" ht="13">
       <c r="A1029" s="1"/>
       <c r="B1029" s="1"/>
       <c r="C1029" s="1"/>
@@ -30938,7 +30909,7 @@
       <c r="Y1029" s="1"/>
       <c r="Z1029" s="1"/>
     </row>
-    <row r="1030">
+    <row r="1030" spans="1:26" ht="13">
       <c r="A1030" s="1"/>
       <c r="B1030" s="1"/>
       <c r="C1030" s="1"/>
@@ -30966,7 +30937,7 @@
       <c r="Y1030" s="1"/>
       <c r="Z1030" s="1"/>
     </row>
-    <row r="1031">
+    <row r="1031" spans="1:26" ht="13">
       <c r="A1031" s="1"/>
       <c r="B1031" s="1"/>
       <c r="C1031" s="1"/>
@@ -30994,7 +30965,7 @@
       <c r="Y1031" s="1"/>
       <c r="Z1031" s="1"/>
     </row>
-    <row r="1032">
+    <row r="1032" spans="1:26" ht="13">
       <c r="A1032" s="1"/>
       <c r="B1032" s="1"/>
       <c r="C1032" s="1"/>
@@ -31022,7 +30993,7 @@
       <c r="Y1032" s="1"/>
       <c r="Z1032" s="1"/>
     </row>
-    <row r="1033">
+    <row r="1033" spans="1:26" ht="13">
       <c r="A1033" s="1"/>
       <c r="B1033" s="1"/>
       <c r="C1033" s="1"/>
@@ -31051,28 +31022,28 @@
       <c r="Z1033" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="2">
     <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C36:D36"/>
     <mergeCell ref="C41:D41"/>
   </mergeCells>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.75"/>
+  <dimension ref="A1:Z20"/>
+  <sheetFormatPr defaultColWidth="14.40625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="15.43"/>
-    <col customWidth="1" min="2" max="2" width="18.29"/>
-    <col customWidth="1" min="3" max="3" width="52.71"/>
+    <col min="1" max="1" width="15.40625" customWidth="1"/>
+    <col min="2" max="2" width="18.26953125" customWidth="1"/>
+    <col min="3" max="3" width="52.6796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:26">
       <c r="A1" s="26" t="s">
         <v>232</v>
       </c>
@@ -31108,7 +31079,7 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:26" ht="15.75" customHeight="1">
       <c r="A2" s="28" t="s">
         <v>233</v>
       </c>
@@ -31122,7 +31093,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:26" ht="15.75" customHeight="1">
       <c r="A3" s="28" t="s">
         <v>233</v>
       </c>
@@ -31136,7 +31107,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:26" ht="15.75" customHeight="1">
       <c r="A4" s="28" t="s">
         <v>81</v>
       </c>
@@ -31150,7 +31121,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:26" ht="15.75" customHeight="1">
       <c r="A5" s="28" t="s">
         <v>81</v>
       </c>
@@ -31164,7 +31135,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:26" ht="15.75" customHeight="1">
       <c r="A6" s="28" t="s">
         <v>81</v>
       </c>
@@ -31178,7 +31149,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:26" ht="15.75" customHeight="1">
       <c r="A7" s="28" t="s">
         <v>81</v>
       </c>
@@ -31192,7 +31163,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:26" ht="15.75" customHeight="1">
       <c r="A8" s="28" t="s">
         <v>81</v>
       </c>
@@ -31206,7 +31177,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:26" ht="15.75" customHeight="1">
       <c r="A9" s="28" t="s">
         <v>81</v>
       </c>
@@ -31220,7 +31191,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:26" ht="15.75" customHeight="1">
       <c r="A10" s="28" t="s">
         <v>208</v>
       </c>
@@ -31234,7 +31205,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:26" ht="15.75" customHeight="1">
       <c r="A11" s="28" t="s">
         <v>208</v>
       </c>
@@ -31248,7 +31219,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:26" ht="15.75" customHeight="1">
       <c r="A12" s="28" t="s">
         <v>208</v>
       </c>
@@ -31262,7 +31233,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:26" ht="15.75" customHeight="1">
       <c r="A13" s="28" t="s">
         <v>208</v>
       </c>
@@ -31276,7 +31247,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:26" ht="15.75" customHeight="1">
       <c r="A14" s="28" t="s">
         <v>208</v>
       </c>
@@ -31290,7 +31261,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:26" ht="15.75" customHeight="1">
       <c r="A15" s="28" t="s">
         <v>208</v>
       </c>
@@ -31304,7 +31275,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:26" ht="15.75" customHeight="1">
       <c r="A16" s="28" t="s">
         <v>208</v>
       </c>
@@ -31318,7 +31289,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:4" ht="15.75" customHeight="1">
       <c r="A17" s="28" t="s">
         <v>208</v>
       </c>
@@ -31332,7 +31303,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:4" ht="15.75" customHeight="1">
       <c r="A18" s="28" t="s">
         <v>278</v>
       </c>
@@ -31346,7 +31317,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:4" ht="15.75" customHeight="1">
       <c r="A19" s="28" t="s">
         <v>278</v>
       </c>
@@ -31360,7 +31331,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:4" ht="13">
       <c r="A20" s="28" t="s">
         <v>278</v>
       </c>
@@ -31375,18 +31346,19 @@
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.75"/>
+  <dimension ref="A1:Z2"/>
+  <sheetFormatPr defaultColWidth="14.40625" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:26" ht="15.75" customHeight="1">
       <c r="A1" s="3" t="s">
         <v>288</v>
       </c>
@@ -31426,7 +31398,7 @@
       <c r="Y1" s="3"/>
       <c r="Z1" s="3"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:26" ht="15.75" customHeight="1">
       <c r="A2" s="21" t="s">
         <v>294</v>
       </c>
@@ -31434,7 +31406,7 @@
         <v>295</v>
       </c>
       <c r="C2" s="30">
-        <v>43596.0</v>
+        <v>43596</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>296</v>
@@ -31465,6 +31437,6 @@
       <c r="Z2" s="3"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/forms/app/covid_education.xlsx
+++ b/forms/app/covid_education.xlsx
@@ -1,27 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20377"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\D-tree\config-dtree-newrepo\config-dtree\forms\app\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70A47927-73B3-4D80-9373-690439AAA7F1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6620"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6590" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
     <sheet name="choices" sheetId="2" r:id="rId2"/>
     <sheet name="settings" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913" iterateDelta="1E-4"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="197">
   <si>
     <t>type</t>
   </si>
@@ -176,624 +177,31 @@
     <t>covid19_intro_note</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;span style="color:#f58a1f"&gt;As a CHV, you are responsible for making sure that you are providing the community with health education and services while trying to take precautions to stop the transmission of Coronavirus to one another. Therefore, make sure you consider the following while you conduct the visits:  
-•       All visits must be conducted outside the home in open space, where there is air flow and risk of spread of disease is less.
-•       You must wear a cloth mask when conducting home visits and moving through the community. If you do not have a mask, please do not make the household visit.
-•        Wash your hands with soap/sanitizer as many time as you can while at home, once you are at the client’s house and when you leave.
-•        Keep a 2 meters distance while talking to your clients.
-•        Don’t shake hands with your clients. 
-•        Avoid group gatherings.
-•        Cover your mouth with a towel or elbow when you sneeze or cough. 
-•        Do not go for a visit if you have symptoms of fever, cough or frequent sneezing.&lt;/span&gt; 
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;span style="color:#f58a1f"&gt;Kama mhudumu wa afya ya jamii, una jukumu la kuhakikisha unatoa elimu ya afya ya jamii na huduma huku ukijikinga ili kuepusha kusambaa kwa maambukizi ya korona kutoka kwa mtu mmoja kwenda kwa mwengine. Hivyo hakikisha unazingatia yafuatayo wakati ukiwa unatoa huduma:
-•         Matembeleo yote yafanye nje ya nyumba kwenye eneo la wazi, ambapo kuna mzunguko wa hewa kwa kupunguza athari za kuenea kwa maambukizi.
-•         Ni Lazima kuvaa barakoa yako muda wote unafanya matembeleo au kutembea kwenye jamii. Kama huna barakoa, tafadhali acha kufanya matembeleo.
-•        Osha mikono yako kwa maji na sabuni au kutumia vitakasa mikono mara nyingi kadiri unavyoweza ukiwa nyumbani kwako,nyumbani kwa mteja wako na pindi ukimaliza kutoa huduma. 
-•        Hakikisha kuna umbali wa mita mbili kati yako na mteja wako unayeenda kumtembelea 
-•        Pindi ukiongea na wateja wako , usishikane mikono. 
-•        Epuka mikusanyiko. 
-•        Funika mdomo wako kwa kitambaa au kiwiko unavyooenda chafya au kukohoa. 
-•        Tafadhali usiende kutoa huduma ukijihisi na dalili za homa na kukohoa na kwenda chafya kwa wingi.&lt;/span&gt; 
-</t>
-  </si>
-  <si>
     <t xml:space="preserve">end group </t>
-  </si>
-  <si>
-    <t>introductory_qns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Introduction to COVID </t>
-  </si>
-  <si>
-    <t>Muhtasari</t>
   </si>
   <si>
     <t>field-list</t>
   </si>
   <si>
-    <t>introduction</t>
-  </si>
-  <si>
-    <t>Hi, how are you? Today before we start our visit, please let’s talk a little about the coronavirus. As we know the world is now experiencing this tragedy of coronavirus and we as Zanzibarians have the disease here as well and the infection is affecting people, and it is our responsibility to protect ourselves</t>
-  </si>
-  <si>
-    <t>Habari yako, leo kabla hatujaanza tembeleo letu naomba tuzungumzie kidogo kuhusu virusi vya Korona. Kama tunavyojua dunia sasa inakabiliwa na janga hili la virusi vya Korona na sisi kama wanzanzibar huu ugonjwa umeshafika na teyari unawaathiri watu, na ni jukumu letu sote kujilinda.</t>
-  </si>
-  <si>
     <t>select_one yes_no</t>
-  </si>
-  <si>
-    <t>corona_awareness</t>
-  </si>
-  <si>
-    <t>Do you know anything about this disease?</t>
-  </si>
-  <si>
-    <t>Je unafahamu chochote kuhusu ugonjwa huu?</t>
   </si>
   <si>
     <t>yes</t>
   </si>
   <si>
-    <t>listen_to_mother</t>
-  </si>
-  <si>
-    <t>&lt;span style="color:#f58a1f"&gt;Listen to the mother talking about coronavirus and add to this description.&lt;/span&gt;</t>
-  </si>
-  <si>
-    <t>&lt;span style="color:#f58a1f"&gt;Msikilize mama akiongea kuhusu ugonjwa wa korona na baadae ongezea maelezo haya.&lt;/span&gt;</t>
-  </si>
-  <si>
-    <t>selected(${corona_awareness},"yes")</t>
-  </si>
-  <si>
-    <t>qns_from_family</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Before we start, do the householders have something specific about the Coronavirus they want to know or tell me? </t>
-  </si>
-  <si>
-    <t>Kabla hatujaanza ,Je wanakaya wana jambo mahsusi kuhusu Korona wanalotaka kujua au kuniambia?</t>
-  </si>
-  <si>
-    <t>answer_questions</t>
-  </si>
-  <si>
-    <t>&lt;span style="color:#f58a1f"&gt;Answer if you can, otherwise call 190.&lt;/span&gt;</t>
-  </si>
-  <si>
-    <t>&lt;span style="color:#f58a1f"&gt;Jibu ikiwa unaweza, vinginevyo piga simu ya 190.&lt;/span&gt;</t>
-  </si>
-  <si>
-    <t>selected(${qns_from_family},"yes")</t>
-  </si>
-  <si>
-    <t>msg_for_chv_questions</t>
-  </si>
-  <si>
-    <t>&lt;span style="display:block;color:red;font-style: italic;padding-left:1em"&gt;Don't read aloud. Fill in yourself. (CHV). &lt;/span&gt;</t>
-  </si>
-  <si>
-    <t>&lt;span style="color:red;font-style: italic"&gt;Usimsomee, jaza wewe (CHV). &lt;/span&gt;</t>
-  </si>
-  <si>
-    <t>select_multiple asked_qns</t>
-  </si>
-  <si>
     <t>asked_qns</t>
-  </si>
-  <si>
-    <t>Select all the questions which were asked by the client</t>
-  </si>
-  <si>
-    <t>Chagua masuali yote yalioulizwa na mteja.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">yes </t>
-  </si>
-  <si>
-    <t>msg_for_chv_other_qn</t>
-  </si>
-  <si>
-    <t>selected(${asked_qns},"none")</t>
   </si>
   <si>
     <t>text</t>
   </si>
   <si>
-    <t>other_question</t>
-  </si>
-  <si>
-    <t>Please list the asked questions</t>
-  </si>
-  <si>
-    <t>Tafadhali taja masuali yalioulizwa.</t>
-  </si>
-  <si>
-    <t>intro_to_corona</t>
-  </si>
-  <si>
-    <t>What is Coronavirus disease?</t>
-  </si>
-  <si>
-    <t>Ugonjwa wa  Korona ni nini?</t>
-  </si>
-  <si>
-    <t>what_is_corona</t>
-  </si>
-  <si>
-    <t>It is a viral disease caused by a new kind of Coronavirus, which is transmitted from one infected person to another. There are other coronaviruses that cause the flu, but this one is new and worse than the others.</t>
-  </si>
-  <si>
-    <t>Huu ni ugonjwa unaosababishwa na virusi vipya vya korona, ugonjwa huu unasambaa kutoka kwa mtu mmoja kwenda kwa mwengine, Kuna aina nyengine za virusi vya korona ambavyo husababisha mafua, lakini hibhivi i ni virusi vipya na hatari Zaidi kusambaa.</t>
-  </si>
-  <si>
     <t>corona_transmission</t>
-  </si>
-  <si>
-    <t>How is Corona disease transmitted?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ugonjwa wa Korona unaambukizwa vipi? </t>
-  </si>
-  <si>
-    <t>how_is_it_transmitted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• This disease is transmitted by airborne fluids when a person sneezes, coughs, talks and breathes.
-• A person can also get infections by touching infected objects and then touching their eyes, nose or mouth before washing their hands with soapy water.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Ugonjwa huu huenea kwa  majimaji yenye maambukizi yatokayo njia ya hewa pale mtu anapopiga chafya,  kukohoa, kusema na kupenga mafua.
-• Pia mtu anaweza kupata maambukizi kwa kugusa vitu vyenye maambukizi ya ugonjwa huo na baadae akagusa macho, pua au mdomo kabla ya kunawa mikono yake kwa maji ya kutiririka na sabuni.
-</t>
   </si>
   <si>
     <t>corona_symptoms</t>
   </si>
   <si>
-    <t>What are the symptoms of Corona disease?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ni zipi dalili za ugonjwa wa Korona? </t>
-  </si>
-  <si>
-    <t>what_are_corona_symptoms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-• A corona patient may take 1 to 14 days to show symptoms or signs.
-• Symptoms and signs of the disease include:
-     1.To get a high fever
-     2.Coughing
-     3.Trouble breathing
-     4.Sneezing frequently
-     5.Acquiring severe flu
-     6.Headache
-     7.Sore throat and
-     8.Not tasting or smelling
-•These symptoms are not unique, They may have other symptoms, Please contact a health professional / get to the center for more symptoms or if the condition worsens.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">•   Mgonjwa wa Korona anaweza kuchukua siku moja hadi kumi na nne (1-14) kuweza kuonesha dalili au ishara. 
-•  Dalili na ishara za ugonjwa huo ni pamoja na:
-        1. Kupata homa kali 
-        2. Kukohoa 
-        3. Kupumua kwa shida
-        4. Chafya za mara kwa mara 
-        5. Kupata mafua makali 
-        6. Kuumwa na kichwa 
-        7. Vidonda vya koo na 
-        8. Kutohisi ladha ya chakula au kutosikia harufu
-•   Dalili hizi sio za kipekee, Inaweza kuwa na dalili nyengine zaidi, Tafadhali wasiliana na mtaalamu wa afya/ fika kituoni kwa dalili  zaidi au ukiona hali inazidi kuwa mbaya.
-</t>
-  </si>
-  <si>
-    <t>has_corona</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Does anyone in this household have any of the symptoms mentioned?</t>
-  </si>
-  <si>
-    <t>Je kuna Mtu yeyote kwenye kaya hii ana dalili hizi tulizozitaja</t>
-  </si>
-  <si>
-    <t xml:space="preserve">report_client </t>
-  </si>
-  <si>
-    <t>&lt;span style="color:#f58a1f"&gt;If the client has any of the above symptoms, please report this to the district surveillance officer immediately.&lt;/span&gt;</t>
-  </si>
-  <si>
-    <t>&lt;span style="color:#f58a1f"&gt;Ikiwa mteja ana dalili zozote kati ya hizi, tafadhali toa ripoti kwa Afisa uchunguzi wa wilaya kwa haraka.&lt;/span&gt;</t>
-  </si>
-  <si>
-    <t>selected(${has_corona},"yes")</t>
-  </si>
-  <si>
-    <t>sneezing</t>
-  </si>
-  <si>
-    <t>sneezing.png</t>
-  </si>
-  <si>
-    <t>coughing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">coughing.png </t>
-  </si>
-  <si>
-    <t>headache</t>
-  </si>
-  <si>
-    <t>headache.png</t>
-  </si>
-  <si>
-    <t>corona_prevention</t>
-  </si>
-  <si>
-    <t>How will you protect yourself from Coronavirus?</t>
-  </si>
-  <si>
-    <t>Vipi utajikinga na ugonjwa wa Korona?</t>
-  </si>
-  <si>
-    <t>how_to_prevent_corona</t>
-  </si>
-  <si>
-    <t>• Wash hands with clean running water and regular soap (at least 20 seconds)
-• Avoid sitting in public gatherings and stay at a distance of one meter
-• Cover the mouth and nose with a towel, tissue or elbow when sneezing, coughing or flushing the flu
-• Avoid handshaking
-• Avoid touching your mouth, nose and eyes before washing your hands
-• Avoid unnecessary trips
-• Remember to wash hands with soap and running water before entering the home
-• Remember to wear a mask whenever you step out of your house.</t>
-  </si>
-  <si>
-    <t>•  Nawa mikono kwa  maji safi ya kutiririka na sabuni mara kwa mara(angalau kwa sekunde 20) (Wafundishe kutengeneza kibuyu chirizi kama hamna mferji)
-•  Epuka kukaa kwenye mikusanyiko ya watu na ukae umbali wa mita moja 
-•  Funika mdomo na pua kwa kitambaa, tishu au kiwiko cha mkono unapopiga chafya, kukohoa au kupenga mafua
-•  Epuka tabia ya  kupeana mikono
-•  Epuka kushika  mdomo, pua na macho kabla ya kuosha mikono
-•  Epuka safari zisizo za lazima
-•  Kumbuka kuosha mikono kwa sababuni na maji tiririka muda wote kabla ya kuingia nyumbani
-•  Kumbuka Kuvaa barakoa muda wote unapotoka nje ya nyumba yako.</t>
-  </si>
-  <si>
-    <t>hand_washing</t>
-  </si>
-  <si>
-    <t>hand_washing.png</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no_gathering </t>
-  </si>
-  <si>
-    <t>no_gathering.png</t>
-  </si>
-  <si>
-    <t>elbow_cough</t>
-  </si>
-  <si>
-    <t>elbow_cough.png</t>
-  </si>
-  <si>
-    <t>no_handshake</t>
-  </si>
-  <si>
-    <t>no_handshake.png</t>
-  </si>
-  <si>
-    <t>no_face_touch</t>
-  </si>
-  <si>
-    <t>no_face_touch.png</t>
-  </si>
-  <si>
-    <t>no_travel</t>
-  </si>
-  <si>
-    <t>no_travel.png</t>
-  </si>
-  <si>
-    <t xml:space="preserve">corona_prevention </t>
-  </si>
-  <si>
-    <t>additional_guidelines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Additional Guidelines </t>
-  </si>
-  <si>
-    <t>Maelezo Muhimu kuhusu Corona</t>
-  </si>
-  <si>
-    <t>list_of_guidelines</t>
-  </si>
-  <si>
-    <t>• Recognize that a person with a coronavirus infection can infect another person even if they have not begun to show signs and symptoms of the disease.
-•  Report promptly to community health workers (CHV) if there is a resident or you have received a visitor with symptoms of a coronavirus 
-•  Coronavirus currently has no cure or vaccine and is rapidly spreading around the world.
-•  You have a responsibility to protect yourself and others
-•  When you feel any signs or symptoms of severe cold flu stay at home and call by phone. Call at no cost: 190
-•  Also let them know about the Facebook, insta and whats apps of the health education unit of the Ministry of Health so that you can find more factual information and trends and events in the Zanzibar coronavirus epidemic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-• Tambua kuwa mtu mwenye virusi vya ugonjwa wa Korona anaweza kumuambukiza mtu mwengine hata kama hajaanza kuonyesha dalili na ishara za ugonjwa huo.
-•  Toa taarifa haraka kwa wahudumu wa afya ya jamii (CHV) ndapo kuna mkaazi au  mmepokea mgeni  ana dalili za Korona
-•  Ugonjwa wa Korona kwa sasa hauna tiba wala chanjo na unaenea kwa kasi duniani. 
-•  Una wajibu wa kujikinga na kuwakinga wengine
-•  Unapohisi dalili au ishara za ugonjwa wa mafua makali baki nyumbani na piga simu kwa kutumia namba. Piga bila gharama 190
-•  Pia naweza kuwaunga kwenye Facebook,insta na whats app za kitengo cha elimu ya kinga wizara ya afya ili muweze pata taarifa za ukweli zaidi na mwenendo na matukio ya Korona Zanzibar
-</t>
-  </si>
-  <si>
-    <t>mask_questions</t>
-  </si>
-  <si>
-    <t>Questions about the mask</t>
-  </si>
-  <si>
-    <t>Masuali kuhusu barakoa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">select_one yes_no </t>
-  </si>
-  <si>
-    <t>has_mask</t>
-  </si>
-  <si>
-    <t>Do you have a face mask (even a home made face mask) to cover mouth and face when exiting your home?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Je unayo Barakoa ( Hata ile ya kutengeneza nyumbani) kwa ajili ya kufunika mdomo na uso kila mara  unapotoka nyumbani kwako? </t>
-  </si>
-  <si>
-    <t>is_wearing</t>
-  </si>
-  <si>
-    <t>Are you wearing your mask every time you leave home?</t>
-  </si>
-  <si>
-    <t>Je umevaa barako yako  Kila muda unapotoka nyumbani?</t>
-  </si>
-  <si>
-    <t>selected(${has_mask},"yes")</t>
-  </si>
-  <si>
-    <t>not_wearing_msg</t>
-  </si>
-  <si>
-    <t>&lt;span style="color:#f58a1f"&gt;Please direct how to prepare your mask at home by following the steps:&lt;/.span&gt;</t>
-  </si>
-  <si>
-    <t>&lt;span style="color:#f58a1f"&gt;Tafadhali muelekeze Jinsi anaweza kutengeneza barako yako nyumbani kwa kufuata hatua zifuatazo: &lt;/span&gt;</t>
-  </si>
-  <si>
-    <t>selected(${is_wearing},"no")</t>
-  </si>
-  <si>
-    <t>self_made_mask_pics</t>
-  </si>
-  <si>
-    <t>This is how you can make your cloth mask at home</t>
-  </si>
-  <si>
-    <t>Jinsi ya kutengeneza barakoa yako nyumbani.</t>
-  </si>
-  <si>
-    <t>self_made_mask_pic1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fold bandana in half </t>
-  </si>
-  <si>
-    <t>Kunja leso/kitambaa kiwe nusu</t>
-  </si>
-  <si>
-    <t>self_made_mask_pic1.png</t>
-  </si>
-  <si>
-    <t>self_made_mask_pic2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fold top down, fold bottom up </t>
-  </si>
-  <si>
-    <t>Kunja sehemu ya juu kwa chini, na sehemu ya chini kwa juu</t>
-  </si>
-  <si>
-    <t>self_made_mask_pic2.png</t>
-  </si>
-  <si>
-    <t>self_made_mask_pic3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Place the rubber bands or hair tiers about 6 inches apart </t>
-  </si>
-  <si>
-    <t>Weka mpira au vibanio vya nywelekila upande kwa kuacha nafasi ya inchi 6 katikati</t>
-  </si>
-  <si>
-    <t>self_made_mask_pic3.png</t>
-  </si>
-  <si>
-    <t>self_made_mask_pic4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fold side to the middle and tuck </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kunja sehemu za mwisho/pembeni kuelekea katikati halafu shona/uibane  </t>
-  </si>
-  <si>
-    <t>self_made_mask_pic4.png</t>
-  </si>
-  <si>
-    <t>self_made_mask_pic5</t>
-  </si>
-  <si>
-    <t>Mask as seen after preparing</t>
-  </si>
-  <si>
-    <t>Muonekano wa barakoa baada ya kuiandaa</t>
-  </si>
-  <si>
-    <t>self_made_mask_pic5.png</t>
-  </si>
-  <si>
-    <t>self_made_mask_pic6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mask as seen after wearing </t>
-  </si>
-  <si>
-    <t>Muonekano wa barakoa baada ya kuvaa</t>
-  </si>
-  <si>
-    <t>self_made_mask_pic6.png</t>
-  </si>
-  <si>
-    <t>mask_importance</t>
-  </si>
-  <si>
-    <t>Remember that it is important to wear the mask to make sure they do not spread the virus to others. It is possible to spread the virus to others even if they have no symptoms at all.
-Wearing this mask will not protect you from getting sick if someone around you is sick, so it is important to maintain distance from other people and wash your hands often.Be careful and do not touch the outside or inside with your hands. Wash your hands with water and soap immediately before putting the mask on, and after taking it off. Wash your mask with soap and water daily after use.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kumbuka ni muhimu sana kuvaa barakoa kila mara unapotoka nyumbani ili kuwalinda wengine, inawezekana kabisa kuwa na ugonjwa huu na kutoonesha dalili yeyote.
-Kuvaa barakoa hakukuepushi na kupata ugonjwa endapo utakua karibu sana na mgonjwa, hivyo basi ni muhimu kuendelea kukaa umbali kutoka kwa watu wengine na kuosha mikono yako kila mara.
-Kuwa makini na kushika barakoa yako kwa ndani au nje kwa mikono. Kosha mikono yako kwa maji na sabauni mara baada ya kuvaa au kuvua barakoa, Kosha barakoa yako kwa maji na sabuni kila siku baada ya kutumia.
-</t>
-  </si>
-  <si>
-    <t>Questions about hand washing</t>
-  </si>
-  <si>
-    <t>Maswali kuhusu uoshaji wa mikono</t>
-  </si>
-  <si>
-    <t>has_infrastructure</t>
-  </si>
-  <si>
-    <t>Are there any good infrastructures on handwashing at home?</t>
-  </si>
-  <si>
-    <t>Je nyumbani kuna miundombinu mizuri kwa ajili ya kuosha mikono kwa maji tiririka?</t>
-  </si>
-  <si>
-    <t>select_one is_practicing</t>
-  </si>
-  <si>
-    <t>is_practicing</t>
-  </si>
-  <si>
-    <t>How many times do you practice handwashing at home?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Je ni mara ngapi unaosha mikono kwa maji tiririka na sabuni ukiwa nyumbani? </t>
-  </si>
-  <si>
-    <t>practice_reminder</t>
-  </si>
-  <si>
-    <t>Its important to practice hand washing every time you go outside the house to make sure you protectect yourself and other people from Corona virus.</t>
-  </si>
-  <si>
-    <t>Ni muhimu kuosha mikono kwa maji tiririka na sabuni mara kwa mara  ili kujilinda na kuwalinda wengine kutokana na ugojwa wa korona.</t>
-  </si>
-  <si>
-    <t>risks_and_directions</t>
-  </si>
-  <si>
-    <t>Questions about risks and directions to household members</t>
-  </si>
-  <si>
-    <t>Maswali kuhusu makundi hatarishi na maelekezo kwa wanakaya</t>
-  </si>
-  <si>
-    <t>select_multiple serious_diseases</t>
-  </si>
-  <si>
     <t>serious_diseases</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Is anyone in your household suffering from these serious diseases? </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Je kuna yeyote kwenye kaya yenu anasumbuliwa na magonjwa haya hatarishi? </t>
-  </si>
-  <si>
-    <t>(selected(.,"none") and count-selected(.)=1) or (not(selected(.,"none")) and count-selected(.)&gt;=1)</t>
-  </si>
-  <si>
-    <t>Cannot select "None of the above" and another option.</t>
-  </si>
-  <si>
-    <t>Huwezi kuchaguwa "Hakuna mojawapo" na chaguo jengine</t>
-  </si>
-  <si>
-    <t>age_above_50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Is someone in your household older than 50? </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Je kwenye kaya yenu kuna mtu mwenye umri Zaidi ya miaka 50? </t>
-  </si>
-  <si>
-    <t>prevention_for_elderly</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Older people and any aged people with health problems like the one I mentioned above are more at risk of getting coronavirus disease. Be more careful with them, We strongly recommend they stay home and avoid any gatherings and when they experience any symptoms please call the emergency help line as soon as possible to save their lives.</t>
-  </si>
-  <si>
-    <t>Watu  wazima na wale wenye umri mkubwa na wenye matatizo ya kiafya kama niliyotaja hapo juu wapo katika hatari zaidi ya kupata  maradhi ya korona, tuwe makini nao zaidi, Tunashauri wabaki nyumbani na waepuke mikusanyiko ya aina yeyote,na wanapopata dalili zozote tafadhali piga namba ya msaada wa dharura haraka iwezekanavyo kunusuru maisha yao.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test_understading </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Questions to test understanding</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Maswali ya kupima uelewa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">asymptomatic </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Do you think people who do not show any signs of illness such as coughing or sneezing can spread the virus / spread the disease? </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Je unadhani watu wasioonesha dalili zozote za ugonjwa kama vile kukohoa au kupiga chafya  wanaweza kusambaza virusi/kueneza ugonjwa? </t>
-  </si>
-  <si>
-    <t>infected_area</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Is it possible for a person to get infected by touching the infected area? </t>
-  </si>
-  <si>
-    <t>Je inawezekana kwa mtu kupata virusi/kuambukizwa kwa kugusa sehemu yenye virusi ?</t>
-  </si>
-  <si>
-    <t>educate_client</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The answer to both questions is Yes. People who show no signs of illness can spread the disease. It is possible for a person to get infected by touching an infected area and then touching their face. This is why it is important to always wear a mask outside of the home, and wash hands frequently with soap.
-Thank you for your attention
-</t>
-  </si>
-  <si>
-    <t>Majibu ya maswali yote mawili ni Ndio.Watu wasioonesha dalili wanaweza kueneza maambukizi. Inawezekana kwa mtu kuathirika kwa kushika sehemu yenye virusi na baadae kushika uso wake. Kwahiyo ni muhimu kuvaa barakoa muda wote unapotoka nyumbani , kuosha mikono mara kwa mara  kwa maji na sabuni.Ahsanteni kwa kunisikilia na kwa ushirikiano wenu.</t>
   </si>
   <si>
     <t>list_name</t>
@@ -993,15 +401,261 @@
   <si>
     <t>data</t>
   </si>
+  <si>
+    <t>corona_precautions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Precautions against Corona </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tahadhari juu ya Korona </t>
+  </si>
+  <si>
+    <t>does_client_take_precautions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je bado unachukua tahadhari juu ya ugonjwa wa Korona? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Are you still taking precautions against COVID ? </t>
+  </si>
+  <si>
+    <t>select_multiple precations_taken</t>
+  </si>
+  <si>
+    <t>precautions_taken</t>
+  </si>
+  <si>
+    <t>Muombe mlengwa akutajie tahadhari hizo, muhudumu (CHV) jaza kwenye kila alioitaja hapo chini.</t>
+  </si>
+  <si>
+    <t>selected(${does_client_take_precautions},"yes")</t>
+  </si>
+  <si>
+    <t>precations_taken</t>
+  </si>
+  <si>
+    <t>Nawa mikono kwa  maji safi ya kutiririka na sabuni mara kwa mara(angalau kwa sekunde 20)</t>
+  </si>
+  <si>
+    <t>Epuka kukaa kwenye mikusanyiko ya watu na ukae umbali wa mita moja</t>
+  </si>
+  <si>
+    <t>Funika mdomo na pua kwa kitambaa, tishu au kiwiko cha mkono unapopiga chafya, kukohoa au kupenga mafua.</t>
+  </si>
+  <si>
+    <t>Epuka tabia ya  kupeana mikono</t>
+  </si>
+  <si>
+    <t>Epuka kushika  mdomo, pua na macho kabla ya kuosha mikono</t>
+  </si>
+  <si>
+    <t>Epuka safari zisizo za lazima</t>
+  </si>
+  <si>
+    <t>Kumbuka kuosha mikono kwa sababuni na maji tiririka muda wote kabla ya kuingia nyumbani</t>
+  </si>
+  <si>
+    <t>Kumbuka Kuvaa barakoa muda wote unapotoka nje ya nyumba yako.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Nyengine</t>
+  </si>
+  <si>
+    <t>avoid_gathering</t>
+  </si>
+  <si>
+    <t>cover_mouth</t>
+  </si>
+  <si>
+    <t>avoid_handshake</t>
+  </si>
+  <si>
+    <t>avoid_face_touch</t>
+  </si>
+  <si>
+    <t>avoid_unnecessary_travel</t>
+  </si>
+  <si>
+    <t>regular_hand_wash</t>
+  </si>
+  <si>
+    <t>hand_wash_before_home</t>
+  </si>
+  <si>
+    <t>wear_mask</t>
+  </si>
+  <si>
+    <t>other</t>
+  </si>
+  <si>
+    <t xml:space="preserve">congratulate_client </t>
+  </si>
+  <si>
+    <t>Mpongeze mama/mlezi, vizuri, ni vyema kuendelea kuchukua tahadhari juu ya Ugonjwa wa Corona, pia amjuilishe mlengwa ugonjwa huo bado upo na unaendelea kuathiri nchi nyingi ikiwemo nchi yetu na nchi jirani.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">selected(${precautions_taken},"regular_hand_wash") or selected(${precautions_taken},"avoid_gathering") or selected(${precautions_taken},"cover_mouth") or selected(${precautions_taken},"avoid_handshake") or selected(${precautions_taken},"avoid_face_touch") or selected(${precautions_taken},"avoid_unnecessary_travel") or selected(${precautions_taken},"hand_wash_before_home") or selected(${precautions_taken},"wear_mask") or selected(${precautions_taken},"other") </t>
+  </si>
+  <si>
+    <t>read_precautions_to_client</t>
+  </si>
+  <si>
+    <t>&lt;span style="color:#f58a1f"&gt;Msomee mama/mlezi tahadhari hizi.&lt;/span&gt;
+•	Nawa mikono kwa  maji safi ya kutiririka na sabuni mara kwa mara(angalau kwa sekunde 20) (Wafundishe kutengeneza kibuyu chirizi kama hamna mferji)
+•	Epuka kukaa kwenye mikusanyiko ya watu na ukae umbali wa mita moja 
+•	Funika mdomo na pua kwa kitambaa, tishu au kiwiko cha mkono unapopiga chafya, kukohoa au kupenga mafua
+•	Epuka tabia ya  kupeana mikono
+•	Epuka kushika  mdomo, pua na macho kabla ya kuosha mikono
+•	Epuka safari zisizo za lazima
+•	Kumbuka kuosha mikono kwa sababuni na maji tiririka muda wote kabla ya kuingia nyumbani
+•	Kumbuka Kuvaa barakoa muda wote unapotoka nje ya nyumba yako.</t>
+  </si>
+  <si>
+    <t>selected(${does_client_take_precautions},"no")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">corona_signs </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Signs of Corona </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dailili za Korona </t>
+  </si>
+  <si>
+    <t>corona_signs_list</t>
+  </si>
+  <si>
+    <t>Baadhi ya dalili na ishara za ugonjwa wa korona, kwa maelezo zaidi ya dalili za ugonjwa huu tuwasiliane na madaktari wa vituo vya afya maana dalili hizo hubadilika mara kawa mara.
+• Kupata homa kali 
+• Kukohoa 
+• Kupumua kwa shida
+• Chafya za mara kwa mara 
+• Kupata mafua makali 
+• Kuumwa na kichwa 
+• Vidonda vya koo na 
+• Kutohisi ladha ya chakula au kutosikia harufu
+• Kuumwa na viungo vya mwili.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je kwenye kaya yenu kuna mtu mwenye umri zaidi ya miaka 50? </t>
+  </si>
+  <si>
+    <t>corona_education</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corona Education </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elimu juu ya Korona </t>
+  </si>
+  <si>
+    <t>source_of_corona_education</t>
+  </si>
+  <si>
+    <t xml:space="preserve">select_multiple source_of_corona_education </t>
+  </si>
+  <si>
+    <t>media_outlet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vyombo vya Habari </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Media Outlets </t>
+  </si>
+  <si>
+    <t>billboards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bill boards </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mabango barabarani </t>
+  </si>
+  <si>
+    <t>social_media</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Social Media </t>
+  </si>
+  <si>
+    <t>Mitandao ya kijamii</t>
+  </si>
+  <si>
+    <t>Nyengine</t>
+  </si>
+  <si>
+    <t>Vipeperushi</t>
+  </si>
+  <si>
+    <t>flyers</t>
+  </si>
+  <si>
+    <t>source_of_corona_education_other</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Please specify </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tafadhali taja </t>
+  </si>
+  <si>
+    <t>selected(${source_of_corona_education},"other")</t>
+  </si>
+  <si>
+    <t>vulnerable_corona_group</t>
+  </si>
+  <si>
+    <t>Makundi hatarishi na watu walio hatarini kupata maradhi ya korona.</t>
+  </si>
+  <si>
+    <t>list_of_vulnerable_group</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Watu wazima na wale wenye umri mkubwa na wenye matatizo ya kiafya kama vile
+• Magonjwa ya moyo
+• Kisukari
+• Magonjwa sugu ya kupumua
+• Saratani
+• Shinikizo la damu/presha
+• Pumu
+• Ugonjwa wa figo/ugonjwa waini
+ Wapo katika hatari zaidi ya kupata  maradhi ya korona, tuwe makini nao zaidi, Tunashauri wabaki nyumbani na waepuke mikusanyiko ya aina yeyote,na wanapopata dalili zozote waende kituo cha afya au kupiga namba ya msaada wa dharura haraka iwezekanavyo kunusuru maisha yao.</t>
+  </si>
+  <si>
+    <t>corona_signs</t>
+  </si>
+  <si>
+    <t>Je, ni wapi unapata zaidi elimu kuhusu Korona?</t>
+  </si>
+  <si>
+    <t>age_above_50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;span style="color:#f58a1f"&gt;As a CHV you should avoid spreading corona virus, therefore take below precautions while conducting visits.
+•	Conduct visits in a ventilated area, keep the distance of two meters from a client, wear mask all the time, and avoid hands shaking with a client during conducting visits.
+•	Wash your hands frequently with clean water and soap or sanitize your hands, avoid crowds and cover your mouth while sneezing or coughing.
+•	Do not go for a visit if you have symptoms of fever, cough or frequent sneezing.&lt;/span&gt; 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;span style="color:#f58a1f"&gt;Kama muhudumu wa afya kwenye jamii, epuka kusambaza maambukizi ya ugonjwa wa korona, hivyo zingatia yafuatayo wakati wa kutuo huduma.
+• Kaa mahali palipo na  mzunguko mzuri wa hewa, umbali wa mita mbili, ukiwa umevaa barakoa, pasipo kushikana mikoni na mteja wako wakati wote wa kufanya matembeleo.
+• Osha mikono yako kwa sabuni au kitakasa mikono mara kwa mara wakati wa kufanya tembeleo, epuka mikusanyiko,funika mdomo wako kwa kitambaa au kiwiko unavyooenda chafya au kukohoa,
+• Tafadhali usiende kutoa huduma ukijihisi na dalili za homa na kukohoa na kwenda chafya kwa wingi.&lt;/span&gt; 
+</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="13">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1011,15 +665,18 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1035,6 +692,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1045,10 +703,30 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1111,7 +789,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -1128,7 +806,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -1149,6 +826,20 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1363,15 +1054,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Z1033"/>
+  <dimension ref="A1:Z1035"/>
   <sheetFormatPr defaultColWidth="14.40625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="23.54296875" customWidth="1"/>
-    <col min="3" max="3" width="286.6796875" customWidth="1"/>
+    <col min="3" max="3" width="55.453125" customWidth="1"/>
     <col min="4" max="26" width="23.54296875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1997,11 +1688,11 @@
       <c r="B18" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="C18" s="14" t="s">
-        <v>51</v>
+      <c r="C18" s="39" t="s">
+        <v>195</v>
       </c>
-      <c r="D18" s="15" t="s">
-        <v>52</v>
+      <c r="D18" s="39" t="s">
+        <v>196</v>
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
@@ -2028,7 +1719,7 @@
     </row>
     <row r="19" spans="1:26" ht="15.75" customHeight="1">
       <c r="A19" s="12" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B19" s="12" t="s">
         <v>45</v>
@@ -2059,21 +1750,21 @@
       <c r="Z19" s="1"/>
     </row>
     <row r="20" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A20" s="2" t="s">
-        <v>19</v>
+      <c r="A20" s="27" t="s">
+        <v>44</v>
       </c>
-      <c r="B20" s="16" t="s">
-        <v>54</v>
+      <c r="B20" s="27" t="s">
+        <v>126</v>
       </c>
-      <c r="C20" s="16" t="s">
-        <v>55</v>
+      <c r="C20" s="31" t="s">
+        <v>127</v>
       </c>
-      <c r="D20" s="16" t="s">
-        <v>56</v>
+      <c r="D20" s="31" t="s">
+        <v>128</v>
       </c>
-      <c r="E20" s="16"/>
-      <c r="G20" s="2" t="s">
-        <v>57</v>
+      <c r="E20" s="15"/>
+      <c r="G20" s="33" t="s">
+        <v>52</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
@@ -2096,23 +1787,25 @@
       <c r="Z20" s="1"/>
     </row>
     <row r="21" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A21" s="16" t="s">
-        <v>49</v>
+      <c r="A21" s="27" t="s">
+        <v>53</v>
       </c>
-      <c r="B21" s="16" t="s">
-        <v>58</v>
+      <c r="B21" s="27" t="s">
+        <v>129</v>
       </c>
-      <c r="C21" s="16" t="s">
-        <v>59</v>
+      <c r="C21" s="27" t="s">
+        <v>131</v>
       </c>
-      <c r="D21" s="16" t="s">
-        <v>60</v>
+      <c r="D21" s="31" t="s">
+        <v>130</v>
       </c>
-      <c r="E21" s="2"/>
+      <c r="E21" s="31" t="s">
+        <v>54</v>
+      </c>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
-      <c r="I21" s="17"/>
+      <c r="I21" s="16"/>
       <c r="J21" s="1"/>
       <c r="K21" s="8"/>
       <c r="L21" s="1"/>
@@ -2132,25 +1825,25 @@
       <c r="Z21" s="1"/>
     </row>
     <row r="22" spans="1:26" ht="14.75">
-      <c r="A22" s="16" t="s">
-        <v>61</v>
+      <c r="A22" s="27" t="s">
+        <v>132</v>
       </c>
-      <c r="B22" s="16" t="s">
-        <v>62</v>
+      <c r="B22" s="27" t="s">
+        <v>133</v>
       </c>
-      <c r="C22" s="16" t="s">
-        <v>63</v>
+      <c r="C22" s="15"/>
+      <c r="D22" s="17" t="s">
+        <v>134</v>
       </c>
-      <c r="D22" s="18" t="s">
-        <v>64</v>
+      <c r="E22" s="31" t="s">
+        <v>54</v>
       </c>
-      <c r="E22" s="16" t="s">
-        <v>65</v>
+      <c r="F22" s="1" t="s">
+        <v>135</v>
       </c>
-      <c r="F22" s="1"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
-      <c r="I22" s="17"/>
+      <c r="I22" s="16"/>
       <c r="J22" s="1"/>
       <c r="K22" s="8"/>
       <c r="L22" s="1"/>
@@ -2170,25 +1863,23 @@
       <c r="Z22" s="1"/>
     </row>
     <row r="23" spans="1:26" ht="13">
-      <c r="A23" s="16" t="s">
+      <c r="A23" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="B23" s="16" t="s">
-        <v>66</v>
+      <c r="B23" s="34" t="s">
+        <v>155</v>
       </c>
-      <c r="C23" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="D23" s="16" t="s">
-        <v>68</v>
+      <c r="C23" s="15"/>
+      <c r="D23" s="33" t="s">
+        <v>156</v>
       </c>
       <c r="E23" s="2"/>
-      <c r="F23" s="19" t="s">
-        <v>69</v>
+      <c r="F23" s="34" t="s">
+        <v>157</v>
       </c>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
-      <c r="I23" s="17"/>
+      <c r="I23" s="16"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
@@ -2207,64 +1898,56 @@
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
     </row>
-    <row r="24" spans="1:26" ht="13">
-      <c r="A24" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="B24" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="C24" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="D24" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="E24" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="1"/>
-      <c r="K24" s="8"/>
-      <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
-      <c r="N24" s="1"/>
-      <c r="O24" s="1"/>
-      <c r="P24" s="1"/>
-      <c r="Q24" s="1"/>
-      <c r="R24" s="1"/>
-      <c r="S24" s="1"/>
-      <c r="T24" s="1"/>
-      <c r="U24" s="1"/>
-      <c r="V24" s="1"/>
-      <c r="W24" s="1"/>
-      <c r="X24" s="1"/>
-      <c r="Y24" s="1"/>
-      <c r="Z24" s="1"/>
-    </row>
-    <row r="25" spans="1:26" ht="13">
-      <c r="A25" s="16" t="s">
+    <row r="24" spans="1:26" s="31" customFormat="1" ht="59.5" customHeight="1">
+      <c r="A24" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="B25" s="16" t="s">
-        <v>73</v>
+      <c r="B24" s="34" t="s">
+        <v>158</v>
       </c>
-      <c r="C25" s="16" t="s">
-        <v>74</v>
+      <c r="C24" s="30"/>
+      <c r="D24" s="35" t="s">
+        <v>159</v>
       </c>
-      <c r="D25" s="16" t="s">
-        <v>75</v>
+      <c r="E24" s="30"/>
+      <c r="F24" s="34" t="s">
+        <v>160</v>
       </c>
-      <c r="E25" s="2"/>
-      <c r="F25" s="19" t="s">
-        <v>76</v>
+      <c r="G24" s="27"/>
+      <c r="H24" s="27"/>
+      <c r="I24" s="16"/>
+      <c r="J24" s="27"/>
+      <c r="K24" s="27"/>
+      <c r="L24" s="27"/>
+      <c r="M24" s="27"/>
+      <c r="N24" s="27"/>
+      <c r="O24" s="27"/>
+      <c r="P24" s="27"/>
+      <c r="Q24" s="27"/>
+      <c r="R24" s="27"/>
+      <c r="S24" s="27"/>
+      <c r="T24" s="27"/>
+      <c r="U24" s="27"/>
+      <c r="V24" s="27"/>
+      <c r="W24" s="27"/>
+      <c r="X24" s="27"/>
+      <c r="Y24" s="27"/>
+      <c r="Z24" s="27"/>
+    </row>
+    <row r="25" spans="1:26" ht="13">
+      <c r="A25" s="31" t="s">
+        <v>51</v>
       </c>
+      <c r="B25" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="C25" s="15"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="1"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
+      <c r="I25" s="2"/>
       <c r="J25" s="1"/>
       <c r="K25" s="8"/>
       <c r="L25" s="1"/>
@@ -2284,211 +1967,199 @@
       <c r="Z25" s="1"/>
     </row>
     <row r="26" spans="1:26" ht="13">
-      <c r="A26" s="20" t="s">
+      <c r="A26" s="34" t="s">
+        <v>44</v>
+      </c>
+      <c r="B26" s="34" t="s">
+        <v>161</v>
+      </c>
+      <c r="C26" s="33" t="s">
+        <v>162</v>
+      </c>
+      <c r="D26" s="33" t="s">
+        <v>163</v>
+      </c>
+      <c r="E26" s="2"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="34" t="s">
+        <v>48</v>
+      </c>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="8"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1"/>
+      <c r="N26" s="1"/>
+      <c r="O26" s="1"/>
+      <c r="P26" s="1"/>
+      <c r="Q26" s="1"/>
+      <c r="R26" s="1"/>
+      <c r="S26" s="1"/>
+      <c r="T26" s="1"/>
+      <c r="U26" s="1"/>
+      <c r="V26" s="1"/>
+      <c r="W26" s="1"/>
+      <c r="X26" s="1"/>
+      <c r="Y26" s="1"/>
+      <c r="Z26" s="1"/>
+    </row>
+    <row r="27" spans="1:26" ht="260">
+      <c r="A27" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="B26" s="21" t="s">
-        <v>77</v>
+      <c r="B27" s="34" t="s">
+        <v>164</v>
       </c>
-      <c r="C26" s="21" t="s">
-        <v>78</v>
+      <c r="C27" s="20"/>
+      <c r="D27" s="36" t="s">
+        <v>165</v>
       </c>
-      <c r="D26" s="21" t="s">
-        <v>79</v>
+      <c r="E27" s="19"/>
+      <c r="F27" s="21"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="3"/>
+      <c r="J27" s="3"/>
+      <c r="K27" s="3"/>
+      <c r="L27" s="3"/>
+      <c r="M27" s="3"/>
+      <c r="N27" s="3"/>
+      <c r="O27" s="3"/>
+      <c r="P27" s="3"/>
+      <c r="Q27" s="3"/>
+      <c r="R27" s="3"/>
+      <c r="S27" s="3"/>
+      <c r="T27" s="3"/>
+      <c r="U27" s="3"/>
+      <c r="V27" s="3"/>
+      <c r="W27" s="3"/>
+      <c r="X27" s="3"/>
+      <c r="Y27" s="3"/>
+      <c r="Z27" s="3"/>
+    </row>
+    <row r="28" spans="1:26" ht="13">
+      <c r="A28" s="34" t="s">
+        <v>53</v>
       </c>
-      <c r="E26" s="20"/>
-      <c r="F26" s="22" t="s">
-        <v>76</v>
+      <c r="B28" s="27" t="s">
+        <v>194</v>
       </c>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
-      <c r="J26" s="3"/>
-      <c r="K26" s="3"/>
-      <c r="L26" s="3"/>
-      <c r="M26" s="3"/>
-      <c r="N26" s="3"/>
-      <c r="O26" s="3"/>
-      <c r="P26" s="3"/>
-      <c r="Q26" s="3"/>
-      <c r="R26" s="3"/>
-      <c r="S26" s="3"/>
-      <c r="T26" s="3"/>
-      <c r="U26" s="3"/>
-      <c r="V26" s="3"/>
-      <c r="W26" s="3"/>
-      <c r="X26" s="3"/>
-      <c r="Y26" s="3"/>
-      <c r="Z26" s="3"/>
-    </row>
-    <row r="27" spans="1:26" ht="13">
-      <c r="A27" s="16" t="s">
-        <v>80</v>
+      <c r="C28" s="15"/>
+      <c r="D28" s="33" t="s">
+        <v>166</v>
       </c>
-      <c r="B27" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="C27" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="D27" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="E27" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="F27" s="22" t="s">
-        <v>76</v>
-      </c>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="19"/>
-      <c r="J27" s="23"/>
-      <c r="K27" s="23"/>
-      <c r="L27" s="1"/>
-      <c r="M27" s="1"/>
-      <c r="N27" s="1"/>
-      <c r="O27" s="1"/>
-      <c r="P27" s="1"/>
-      <c r="Q27" s="1"/>
-      <c r="R27" s="1"/>
-      <c r="S27" s="1"/>
-      <c r="T27" s="1"/>
-      <c r="U27" s="1"/>
-      <c r="V27" s="1"/>
-      <c r="W27" s="1"/>
-      <c r="X27" s="1"/>
-      <c r="Y27" s="1"/>
-      <c r="Z27" s="1"/>
-    </row>
-    <row r="28" spans="1:26" ht="13">
-      <c r="A28" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="B28" s="21" t="s">
-        <v>85</v>
-      </c>
-      <c r="C28" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="D28" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="E28" s="20"/>
-      <c r="F28" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
-      <c r="J28" s="3"/>
-      <c r="K28" s="3"/>
-      <c r="L28" s="3"/>
-      <c r="M28" s="3"/>
-      <c r="N28" s="3"/>
-      <c r="O28" s="3"/>
-      <c r="P28" s="3"/>
-      <c r="Q28" s="3"/>
-      <c r="R28" s="3"/>
-      <c r="S28" s="3"/>
-      <c r="T28" s="3"/>
-      <c r="U28" s="3"/>
-      <c r="V28" s="3"/>
-      <c r="W28" s="3"/>
-      <c r="X28" s="3"/>
-      <c r="Y28" s="3"/>
-      <c r="Z28" s="3"/>
-    </row>
-    <row r="29" spans="1:26" ht="13">
-      <c r="A29" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="B29" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="C29" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="D29" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="E29" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="F29" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
-      <c r="J29" s="1"/>
-      <c r="K29" s="8"/>
-      <c r="L29" s="1"/>
-      <c r="M29" s="1"/>
-      <c r="N29" s="1"/>
-      <c r="O29" s="1"/>
-      <c r="P29" s="1"/>
-      <c r="Q29" s="1"/>
-      <c r="R29" s="1"/>
-      <c r="S29" s="1"/>
-      <c r="T29" s="1"/>
-      <c r="U29" s="1"/>
-      <c r="V29" s="1"/>
-      <c r="W29" s="1"/>
-      <c r="X29" s="1"/>
-      <c r="Y29" s="1"/>
-      <c r="Z29" s="1"/>
-    </row>
-    <row r="30" spans="1:26" ht="13">
-      <c r="A30" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="B30" s="16" t="s">
+      <c r="E28" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1"/>
-      <c r="K30" s="8"/>
-      <c r="L30" s="1"/>
-      <c r="M30" s="1"/>
-      <c r="N30" s="1"/>
-      <c r="O30" s="1"/>
-      <c r="P30" s="1"/>
-      <c r="Q30" s="1"/>
-      <c r="R30" s="1"/>
-      <c r="S30" s="1"/>
-      <c r="T30" s="1"/>
-      <c r="U30" s="1"/>
-      <c r="V30" s="1"/>
-      <c r="W30" s="1"/>
-      <c r="X30" s="1"/>
-      <c r="Y30" s="1"/>
-      <c r="Z30" s="1"/>
-    </row>
-    <row r="31" spans="1:26" ht="13">
-      <c r="A31" s="16" t="s">
+      <c r="F28" s="21"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="18"/>
+      <c r="J28" s="22"/>
+      <c r="K28" s="22"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
+      <c r="O28" s="1"/>
+      <c r="P28" s="1"/>
+      <c r="Q28" s="1"/>
+      <c r="R28" s="1"/>
+      <c r="S28" s="1"/>
+      <c r="T28" s="1"/>
+      <c r="U28" s="1"/>
+      <c r="V28" s="1"/>
+      <c r="W28" s="1"/>
+      <c r="X28" s="1"/>
+      <c r="Y28" s="1"/>
+      <c r="Z28" s="1"/>
+    </row>
+    <row r="29" spans="1:26" s="31" customFormat="1" ht="13">
+      <c r="A29" s="34" t="s">
+        <v>51</v>
+      </c>
+      <c r="B29" s="34" t="s">
+        <v>192</v>
+      </c>
+      <c r="C29" s="30"/>
+      <c r="D29" s="33"/>
+      <c r="E29" s="33"/>
+      <c r="F29" s="27"/>
+      <c r="G29" s="27"/>
+      <c r="H29" s="27"/>
+      <c r="I29" s="27"/>
+      <c r="J29" s="27"/>
+      <c r="K29" s="27"/>
+      <c r="L29" s="27"/>
+      <c r="M29" s="27"/>
+      <c r="N29" s="27"/>
+      <c r="O29" s="27"/>
+      <c r="P29" s="27"/>
+      <c r="Q29" s="27"/>
+      <c r="R29" s="27"/>
+      <c r="S29" s="27"/>
+      <c r="T29" s="27"/>
+      <c r="U29" s="27"/>
+      <c r="V29" s="27"/>
+      <c r="W29" s="27"/>
+      <c r="X29" s="27"/>
+      <c r="Y29" s="27"/>
+      <c r="Z29" s="27"/>
+    </row>
+    <row r="30" spans="1:26" ht="13">
+      <c r="A30" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="B31" s="16" t="s">
-        <v>91</v>
+      <c r="B30" s="34" t="s">
+        <v>167</v>
       </c>
-      <c r="C31" s="16" t="s">
-        <v>92</v>
+      <c r="C30" s="34" t="s">
+        <v>168</v>
       </c>
-      <c r="D31" s="16" t="s">
-        <v>93</v>
+      <c r="D30" s="34" t="s">
+        <v>169</v>
       </c>
-      <c r="E31" s="2"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="19" t="s">
+      <c r="E30" s="19"/>
+      <c r="F30" s="21"/>
+      <c r="G30" s="34" t="s">
         <v>48</v>
       </c>
+      <c r="H30" s="3"/>
+      <c r="I30" s="3"/>
+      <c r="J30" s="3"/>
+      <c r="K30" s="3"/>
+      <c r="L30" s="3"/>
+      <c r="M30" s="3"/>
+      <c r="N30" s="3"/>
+      <c r="O30" s="3"/>
+      <c r="P30" s="3"/>
+      <c r="Q30" s="3"/>
+      <c r="R30" s="3"/>
+      <c r="S30" s="3"/>
+      <c r="T30" s="3"/>
+      <c r="U30" s="3"/>
+      <c r="V30" s="3"/>
+      <c r="W30" s="3"/>
+      <c r="X30" s="3"/>
+      <c r="Y30" s="3"/>
+      <c r="Z30" s="3"/>
+    </row>
+    <row r="31" spans="1:26" ht="13">
+      <c r="A31" s="34" t="s">
+        <v>171</v>
+      </c>
+      <c r="B31" s="34" t="s">
+        <v>170</v>
+      </c>
+      <c r="C31" s="15"/>
+      <c r="D31" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="E31" s="33" t="s">
+        <v>54</v>
+      </c>
+      <c r="F31" s="21"/>
+      <c r="G31" s="1"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
@@ -2509,26 +2180,30 @@
       <c r="Y31" s="1"/>
       <c r="Z31" s="1"/>
     </row>
-    <row r="32" spans="1:26" ht="14.25">
-      <c r="A32" s="16" t="s">
-        <v>49</v>
+    <row r="32" spans="1:26" ht="13">
+      <c r="A32" s="34" t="s">
+        <v>56</v>
       </c>
-      <c r="B32" s="16" t="s">
-        <v>94</v>
+      <c r="B32" s="34" t="s">
+        <v>184</v>
       </c>
-      <c r="C32" s="24" t="s">
-        <v>95</v>
+      <c r="C32" s="33" t="s">
+        <v>185</v>
       </c>
-      <c r="D32" s="16" t="s">
-        <v>96</v>
+      <c r="D32" s="33" t="s">
+        <v>186</v>
       </c>
-      <c r="E32" s="2"/>
-      <c r="F32" s="1"/>
+      <c r="E32" s="33" t="s">
+        <v>54</v>
+      </c>
+      <c r="F32" s="34" t="s">
+        <v>187</v>
+      </c>
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="2"/>
-      <c r="K32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="8"/>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
       <c r="N32" s="1"/>
@@ -2546,21 +2221,21 @@
       <c r="Z32" s="1"/>
     </row>
     <row r="33" spans="1:26" ht="13">
-      <c r="A33" s="16" t="s">
-        <v>53</v>
+      <c r="A33" s="34" t="s">
+        <v>29</v>
       </c>
-      <c r="B33" s="16" t="s">
-        <v>91</v>
+      <c r="B33" s="34" t="s">
+        <v>167</v>
       </c>
-      <c r="C33" s="31"/>
-      <c r="D33" s="32"/>
+      <c r="C33" s="15"/>
+      <c r="D33" s="15"/>
       <c r="E33" s="2"/>
       <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
+      <c r="G33" s="18"/>
       <c r="H33" s="1"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="2"/>
-      <c r="K33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="8"/>
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
       <c r="N33" s="1"/>
@@ -2577,28 +2252,26 @@
       <c r="Y33" s="1"/>
       <c r="Z33" s="1"/>
     </row>
-    <row r="34" spans="1:26" ht="13">
-      <c r="A34" s="16" t="s">
-        <v>19</v>
+    <row r="34" spans="1:26" ht="14.25">
+      <c r="A34" s="34" t="s">
+        <v>44</v>
       </c>
-      <c r="B34" s="16" t="s">
-        <v>97</v>
+      <c r="B34" s="34" t="s">
+        <v>188</v>
       </c>
-      <c r="C34" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="D34" s="16" t="s">
-        <v>99</v>
+      <c r="C34" s="23"/>
+      <c r="D34" s="33" t="s">
+        <v>189</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" s="1"/>
-      <c r="G34" s="19" t="s">
+      <c r="G34" s="34" t="s">
         <v>48</v>
       </c>
       <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
-      <c r="J34" s="1"/>
-      <c r="K34" s="8"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="1"/>
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
       <c r="N34" s="1"/>
@@ -2615,26 +2288,24 @@
       <c r="Y34" s="1"/>
       <c r="Z34" s="1"/>
     </row>
-    <row r="35" spans="1:26" ht="13">
-      <c r="A35" s="16" t="s">
+    <row r="35" spans="1:26" ht="72" customHeight="1">
+      <c r="A35" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="B35" s="16" t="s">
-        <v>100</v>
+      <c r="B35" s="34" t="s">
+        <v>190</v>
       </c>
-      <c r="C35" s="16" t="s">
-        <v>101</v>
+      <c r="C35" s="30"/>
+      <c r="D35" s="35" t="s">
+        <v>191</v>
       </c>
-      <c r="D35" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="E35" s="2"/>
+      <c r="E35" s="35"/>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
-      <c r="J35" s="1"/>
-      <c r="K35" s="8"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="2"/>
+      <c r="K35" s="1"/>
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
       <c r="N35" s="1"/>
@@ -2652,20 +2323,21 @@
       <c r="Z35" s="1"/>
     </row>
     <row r="36" spans="1:26" ht="13">
-      <c r="A36" s="16" t="s">
-        <v>29</v>
+      <c r="A36" s="34" t="s">
+        <v>51</v>
       </c>
-      <c r="B36" s="16" t="s">
-        <v>97</v>
+      <c r="B36" s="34" t="s">
+        <v>188</v>
       </c>
-      <c r="C36" s="16"/>
+      <c r="C36" s="15"/>
+      <c r="D36" s="15"/>
       <c r="E36" s="2"/>
       <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
+      <c r="G36" s="18"/>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
-      <c r="K36" s="1"/>
+      <c r="K36" s="8"/>
       <c r="L36" s="1"/>
       <c r="M36" s="1"/>
       <c r="N36" s="1"/>
@@ -2683,27 +2355,17 @@
       <c r="Z36" s="1"/>
     </row>
     <row r="37" spans="1:26" ht="13">
-      <c r="A37" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="B37" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="C37" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="D37" s="16" t="s">
-        <v>105</v>
-      </c>
+      <c r="A37" s="15"/>
+      <c r="B37" s="15"/>
+      <c r="C37" s="15"/>
+      <c r="D37" s="15"/>
       <c r="E37" s="2"/>
       <c r="F37" s="1"/>
-      <c r="G37" s="19" t="s">
-        <v>48</v>
-      </c>
+      <c r="G37" s="1"/>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
-      <c r="K37" s="1"/>
+      <c r="K37" s="8"/>
       <c r="L37" s="1"/>
       <c r="M37" s="1"/>
       <c r="N37" s="1"/>
@@ -2721,25 +2383,16 @@
       <c r="Z37" s="1"/>
     </row>
     <row r="38" spans="1:26" ht="13">
-      <c r="A38" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="B38" s="16" t="s">
-        <v>106</v>
-      </c>
-      <c r="C38" s="16" t="s">
-        <v>107</v>
-      </c>
-      <c r="D38" s="16" t="s">
-        <v>108</v>
-      </c>
+      <c r="A38" s="15"/>
+      <c r="B38" s="15"/>
+      <c r="C38" s="15"/>
       <c r="E38" s="2"/>
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
-      <c r="K38" s="8"/>
+      <c r="K38" s="1"/>
       <c r="L38" s="1"/>
       <c r="M38" s="1"/>
       <c r="N38" s="1"/>
@@ -2757,27 +2410,17 @@
       <c r="Z38" s="1"/>
     </row>
     <row r="39" spans="1:26" ht="13">
-      <c r="A39" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="B39" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="C39" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="D39" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="E39" s="16" t="s">
-        <v>65</v>
-      </c>
+      <c r="A39" s="15"/>
+      <c r="B39" s="15"/>
+      <c r="C39" s="15"/>
+      <c r="D39" s="15"/>
+      <c r="E39" s="2"/>
       <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
+      <c r="G39" s="18"/>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
-      <c r="K39" s="8"/>
+      <c r="K39" s="1"/>
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
       <c r="N39" s="1"/>
@@ -2795,22 +2438,12 @@
       <c r="Z39" s="1"/>
     </row>
     <row r="40" spans="1:26" ht="13">
-      <c r="A40" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="B40" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="C40" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="D40" s="16" t="s">
-        <v>114</v>
-      </c>
+      <c r="A40" s="15"/>
+      <c r="B40" s="15"/>
+      <c r="C40" s="15"/>
+      <c r="D40" s="15"/>
       <c r="E40" s="2"/>
-      <c r="F40" s="19" t="s">
-        <v>115</v>
-      </c>
+      <c r="F40" s="1"/>
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
@@ -2833,33 +2466,25 @@
       <c r="Z40" s="1"/>
     </row>
     <row r="41" spans="1:26" ht="13">
-      <c r="A41" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="B41" s="16" t="s">
-        <v>116</v>
-      </c>
-      <c r="C41" s="31"/>
-      <c r="D41" s="32"/>
-      <c r="E41" s="1"/>
+      <c r="A41" s="15"/>
+      <c r="B41" s="15"/>
+      <c r="C41" s="15"/>
+      <c r="D41" s="15"/>
+      <c r="E41" s="15"/>
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
-      <c r="K41" s="1"/>
+      <c r="K41" s="8"/>
       <c r="L41" s="1"/>
       <c r="M41" s="1"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
       <c r="P41" s="1"/>
       <c r="Q41" s="1"/>
-      <c r="R41" s="16" t="s">
-        <v>117</v>
-      </c>
-      <c r="S41" s="16" t="s">
-        <v>117</v>
-      </c>
+      <c r="R41" s="1"/>
+      <c r="S41" s="1"/>
       <c r="T41" s="1"/>
       <c r="U41" s="1"/>
       <c r="V41" s="1"/>
@@ -2869,33 +2494,25 @@
       <c r="Z41" s="1"/>
     </row>
     <row r="42" spans="1:26" ht="13">
-      <c r="A42" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="B42" s="16" t="s">
-        <v>118</v>
-      </c>
-      <c r="C42" s="1"/>
-      <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
-      <c r="F42" s="1"/>
+      <c r="A42" s="15"/>
+      <c r="B42" s="15"/>
+      <c r="C42" s="15"/>
+      <c r="D42" s="15"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="18"/>
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
-      <c r="K42" s="1"/>
+      <c r="K42" s="8"/>
       <c r="L42" s="1"/>
       <c r="M42" s="1"/>
       <c r="N42" s="1"/>
       <c r="O42" s="1"/>
       <c r="P42" s="1"/>
       <c r="Q42" s="1"/>
-      <c r="R42" s="19" t="s">
-        <v>119</v>
-      </c>
-      <c r="S42" s="19" t="s">
-        <v>119</v>
-      </c>
+      <c r="R42" s="1"/>
+      <c r="S42" s="1"/>
       <c r="T42" s="1"/>
       <c r="U42" s="1"/>
       <c r="V42" s="1"/>
@@ -2905,14 +2522,10 @@
       <c r="Z42" s="1"/>
     </row>
     <row r="43" spans="1:26" ht="13">
-      <c r="A43" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="B43" s="19" t="s">
-        <v>120</v>
-      </c>
-      <c r="C43" s="1"/>
-      <c r="D43" s="1"/>
+      <c r="A43" s="15"/>
+      <c r="B43" s="15"/>
+      <c r="C43" s="37"/>
+      <c r="D43" s="38"/>
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
@@ -2926,12 +2539,8 @@
       <c r="O43" s="1"/>
       <c r="P43" s="1"/>
       <c r="Q43" s="1"/>
-      <c r="R43" s="19" t="s">
-        <v>121</v>
-      </c>
-      <c r="S43" s="19" t="s">
-        <v>121</v>
-      </c>
+      <c r="R43" s="15"/>
+      <c r="S43" s="15"/>
       <c r="T43" s="1"/>
       <c r="U43" s="1"/>
       <c r="V43" s="1"/>
@@ -2941,12 +2550,8 @@
       <c r="Z43" s="1"/>
     </row>
     <row r="44" spans="1:26" ht="13">
-      <c r="A44" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="B44" s="19" t="s">
-        <v>103</v>
-      </c>
+      <c r="A44" s="18"/>
+      <c r="B44" s="15"/>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
@@ -2962,8 +2567,8 @@
       <c r="O44" s="1"/>
       <c r="P44" s="1"/>
       <c r="Q44" s="1"/>
-      <c r="R44" s="1"/>
-      <c r="S44" s="1"/>
+      <c r="R44" s="18"/>
+      <c r="S44" s="18"/>
       <c r="T44" s="1"/>
       <c r="U44" s="1"/>
       <c r="V44" s="1"/>
@@ -2973,23 +2578,13 @@
       <c r="Z44" s="1"/>
     </row>
     <row r="45" spans="1:26" ht="13">
-      <c r="A45" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="B45" s="19" t="s">
-        <v>122</v>
-      </c>
-      <c r="C45" s="19" t="s">
-        <v>123</v>
-      </c>
-      <c r="D45" s="19" t="s">
-        <v>124</v>
-      </c>
+      <c r="A45" s="18"/>
+      <c r="B45" s="18"/>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
-      <c r="G45" s="19" t="s">
-        <v>48</v>
-      </c>
+      <c r="G45" s="1"/>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
@@ -3000,8 +2595,8 @@
       <c r="O45" s="1"/>
       <c r="P45" s="1"/>
       <c r="Q45" s="1"/>
-      <c r="R45" s="1"/>
-      <c r="S45" s="1"/>
+      <c r="R45" s="18"/>
+      <c r="S45" s="18"/>
       <c r="T45" s="1"/>
       <c r="U45" s="1"/>
       <c r="V45" s="1"/>
@@ -3011,18 +2606,10 @@
       <c r="Z45" s="1"/>
     </row>
     <row r="46" spans="1:26" ht="13">
-      <c r="A46" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="B46" s="19" t="s">
-        <v>125</v>
-      </c>
-      <c r="C46" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="D46" s="19" t="s">
-        <v>127</v>
-      </c>
+      <c r="A46" s="18"/>
+      <c r="B46" s="18"/>
+      <c r="C46" s="1"/>
+      <c r="D46" s="1"/>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
@@ -3047,17 +2634,13 @@
       <c r="Z46" s="1"/>
     </row>
     <row r="47" spans="1:26" ht="13">
-      <c r="A47" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="B47" s="19" t="s">
-        <v>128</v>
-      </c>
-      <c r="C47" s="19"/>
-      <c r="D47" s="19"/>
+      <c r="A47" s="18"/>
+      <c r="B47" s="18"/>
+      <c r="C47" s="18"/>
+      <c r="D47" s="18"/>
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
-      <c r="G47" s="1"/>
+      <c r="G47" s="18"/>
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
@@ -3068,12 +2651,8 @@
       <c r="O47" s="1"/>
       <c r="P47" s="1"/>
       <c r="Q47" s="1"/>
-      <c r="R47" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="S47" s="19" t="s">
-        <v>129</v>
-      </c>
+      <c r="R47" s="1"/>
+      <c r="S47" s="1"/>
       <c r="T47" s="1"/>
       <c r="U47" s="1"/>
       <c r="V47" s="1"/>
@@ -3083,14 +2662,10 @@
       <c r="Z47" s="1"/>
     </row>
     <row r="48" spans="1:26" ht="13">
-      <c r="A48" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="B48" s="19" t="s">
-        <v>130</v>
-      </c>
-      <c r="C48" s="19"/>
-      <c r="D48" s="19"/>
+      <c r="A48" s="18"/>
+      <c r="B48" s="18"/>
+      <c r="C48" s="18"/>
+      <c r="D48" s="18"/>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
@@ -3104,12 +2679,8 @@
       <c r="O48" s="1"/>
       <c r="P48" s="1"/>
       <c r="Q48" s="1"/>
-      <c r="R48" s="19" t="s">
-        <v>131</v>
-      </c>
-      <c r="S48" s="19" t="s">
-        <v>131</v>
-      </c>
+      <c r="R48" s="1"/>
+      <c r="S48" s="1"/>
       <c r="T48" s="1"/>
       <c r="U48" s="1"/>
       <c r="V48" s="1"/>
@@ -3119,14 +2690,10 @@
       <c r="Z48" s="1"/>
     </row>
     <row r="49" spans="1:26" ht="13">
-      <c r="A49" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="B49" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="C49" s="19"/>
-      <c r="D49" s="19"/>
+      <c r="A49" s="18"/>
+      <c r="B49" s="18"/>
+      <c r="C49" s="18"/>
+      <c r="D49" s="18"/>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
@@ -3140,12 +2707,8 @@
       <c r="O49" s="1"/>
       <c r="P49" s="1"/>
       <c r="Q49" s="1"/>
-      <c r="R49" s="19" t="s">
-        <v>133</v>
-      </c>
-      <c r="S49" s="19" t="s">
-        <v>133</v>
-      </c>
+      <c r="R49" s="18"/>
+      <c r="S49" s="18"/>
       <c r="T49" s="1"/>
       <c r="U49" s="1"/>
       <c r="V49" s="1"/>
@@ -3155,14 +2718,10 @@
       <c r="Z49" s="1"/>
     </row>
     <row r="50" spans="1:26" ht="13">
-      <c r="A50" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="B50" s="19" t="s">
-        <v>134</v>
-      </c>
-      <c r="C50" s="19"/>
-      <c r="D50" s="19"/>
+      <c r="A50" s="18"/>
+      <c r="B50" s="18"/>
+      <c r="C50" s="18"/>
+      <c r="D50" s="18"/>
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
@@ -3176,12 +2735,8 @@
       <c r="O50" s="1"/>
       <c r="P50" s="1"/>
       <c r="Q50" s="1"/>
-      <c r="R50" s="19" t="s">
-        <v>135</v>
-      </c>
-      <c r="S50" s="19" t="s">
-        <v>135</v>
-      </c>
+      <c r="R50" s="18"/>
+      <c r="S50" s="18"/>
       <c r="T50" s="1"/>
       <c r="U50" s="1"/>
       <c r="V50" s="1"/>
@@ -3191,14 +2746,10 @@
       <c r="Z50" s="1"/>
     </row>
     <row r="51" spans="1:26" ht="13">
-      <c r="A51" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="B51" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="C51" s="19"/>
-      <c r="D51" s="19"/>
+      <c r="A51" s="18"/>
+      <c r="B51" s="18"/>
+      <c r="C51" s="18"/>
+      <c r="D51" s="18"/>
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
@@ -3212,12 +2763,8 @@
       <c r="O51" s="1"/>
       <c r="P51" s="1"/>
       <c r="Q51" s="1"/>
-      <c r="R51" s="19" t="s">
-        <v>137</v>
-      </c>
-      <c r="S51" s="19" t="s">
-        <v>137</v>
-      </c>
+      <c r="R51" s="18"/>
+      <c r="S51" s="18"/>
       <c r="T51" s="1"/>
       <c r="U51" s="1"/>
       <c r="V51" s="1"/>
@@ -3227,14 +2774,10 @@
       <c r="Z51" s="1"/>
     </row>
     <row r="52" spans="1:26" ht="13">
-      <c r="A52" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="B52" s="19" t="s">
-        <v>138</v>
-      </c>
-      <c r="C52" s="19"/>
-      <c r="D52" s="19"/>
+      <c r="A52" s="18"/>
+      <c r="B52" s="18"/>
+      <c r="C52" s="18"/>
+      <c r="D52" s="18"/>
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
       <c r="G52" s="1"/>
@@ -3248,12 +2791,8 @@
       <c r="O52" s="1"/>
       <c r="P52" s="1"/>
       <c r="Q52" s="1"/>
-      <c r="R52" s="19" t="s">
-        <v>139</v>
-      </c>
-      <c r="S52" s="19" t="s">
-        <v>139</v>
-      </c>
+      <c r="R52" s="18"/>
+      <c r="S52" s="18"/>
       <c r="T52" s="1"/>
       <c r="U52" s="1"/>
       <c r="V52" s="1"/>
@@ -3263,14 +2802,10 @@
       <c r="Z52" s="1"/>
     </row>
     <row r="53" spans="1:26" ht="13">
-      <c r="A53" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="B53" s="19" t="s">
-        <v>140</v>
-      </c>
-      <c r="C53" s="1"/>
-      <c r="D53" s="1"/>
+      <c r="A53" s="18"/>
+      <c r="B53" s="18"/>
+      <c r="C53" s="18"/>
+      <c r="D53" s="18"/>
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
       <c r="G53" s="1"/>
@@ -3284,8 +2819,8 @@
       <c r="O53" s="1"/>
       <c r="P53" s="1"/>
       <c r="Q53" s="1"/>
-      <c r="R53" s="1"/>
-      <c r="S53" s="1"/>
+      <c r="R53" s="18"/>
+      <c r="S53" s="18"/>
       <c r="T53" s="1"/>
       <c r="U53" s="1"/>
       <c r="V53" s="1"/>
@@ -3295,22 +2830,13 @@
       <c r="Z53" s="1"/>
     </row>
     <row r="54" spans="1:26" ht="13">
-      <c r="A54" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="B54" s="19" t="s">
-        <v>141</v>
-      </c>
-      <c r="C54" s="19" t="s">
-        <v>142</v>
-      </c>
-      <c r="D54" s="19" t="s">
-        <v>143</v>
-      </c>
+      <c r="A54" s="18"/>
+      <c r="B54" s="18"/>
+      <c r="C54" s="18"/>
+      <c r="D54" s="18"/>
       <c r="E54" s="1"/>
-      <c r="G54" s="19" t="s">
-        <v>48</v>
-      </c>
+      <c r="F54" s="1"/>
+      <c r="G54" s="1"/>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
@@ -3321,8 +2847,8 @@
       <c r="O54" s="1"/>
       <c r="P54" s="1"/>
       <c r="Q54" s="1"/>
-      <c r="R54" s="1"/>
-      <c r="S54" s="1"/>
+      <c r="R54" s="18"/>
+      <c r="S54" s="18"/>
       <c r="T54" s="1"/>
       <c r="U54" s="1"/>
       <c r="V54" s="1"/>
@@ -3332,18 +2858,10 @@
       <c r="Z54" s="1"/>
     </row>
     <row r="55" spans="1:26" ht="13">
-      <c r="A55" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="B55" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="C55" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="D55" s="19" t="s">
-        <v>146</v>
-      </c>
+      <c r="A55" s="18"/>
+      <c r="B55" s="18"/>
+      <c r="C55" s="1"/>
+      <c r="D55" s="1"/>
       <c r="E55" s="1"/>
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
@@ -3368,17 +2886,12 @@
       <c r="Z55" s="1"/>
     </row>
     <row r="56" spans="1:26" ht="13">
-      <c r="A56" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="B56" s="19" t="s">
-        <v>141</v>
-      </c>
-      <c r="C56" s="1"/>
-      <c r="D56" s="1"/>
+      <c r="A56" s="18"/>
+      <c r="B56" s="18"/>
+      <c r="C56" s="18"/>
+      <c r="D56" s="18"/>
       <c r="E56" s="1"/>
-      <c r="F56" s="1"/>
-      <c r="G56" s="1"/>
+      <c r="G56" s="18"/>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
@@ -3400,23 +2913,13 @@
       <c r="Z56" s="1"/>
     </row>
     <row r="57" spans="1:26" ht="13">
-      <c r="A57" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="B57" s="19" t="s">
-        <v>147</v>
-      </c>
-      <c r="C57" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="D57" s="19" t="s">
-        <v>149</v>
-      </c>
+      <c r="A57" s="18"/>
+      <c r="B57" s="18"/>
+      <c r="C57" s="18"/>
+      <c r="D57" s="18"/>
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
-      <c r="G57" s="19" t="s">
-        <v>48</v>
-      </c>
+      <c r="G57" s="1"/>
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
@@ -3438,21 +2941,11 @@
       <c r="Z57" s="1"/>
     </row>
     <row r="58" spans="1:26" ht="13">
-      <c r="A58" s="19" t="s">
-        <v>150</v>
-      </c>
-      <c r="B58" s="19" t="s">
-        <v>151</v>
-      </c>
-      <c r="C58" s="19" t="s">
-        <v>152</v>
-      </c>
-      <c r="D58" s="19" t="s">
-        <v>153</v>
-      </c>
-      <c r="E58" s="19" t="s">
-        <v>65</v>
-      </c>
+      <c r="A58" s="18"/>
+      <c r="B58" s="18"/>
+      <c r="C58" s="1"/>
+      <c r="D58" s="1"/>
+      <c r="E58" s="1"/>
       <c r="F58" s="1"/>
       <c r="G58" s="1"/>
       <c r="H58" s="1"/>
@@ -3476,25 +2969,13 @@
       <c r="Z58" s="1"/>
     </row>
     <row r="59" spans="1:26" ht="13">
-      <c r="A59" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="B59" s="19" t="s">
-        <v>154</v>
-      </c>
-      <c r="C59" s="19" t="s">
-        <v>155</v>
-      </c>
-      <c r="D59" s="19" t="s">
-        <v>156</v>
-      </c>
-      <c r="E59" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="F59" s="19" t="s">
-        <v>157</v>
-      </c>
-      <c r="G59" s="1"/>
+      <c r="A59" s="18"/>
+      <c r="B59" s="18"/>
+      <c r="C59" s="18"/>
+      <c r="D59" s="18"/>
+      <c r="E59" s="1"/>
+      <c r="F59" s="1"/>
+      <c r="G59" s="18"/>
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
       <c r="J59" s="1"/>
@@ -3516,22 +2997,12 @@
       <c r="Z59" s="1"/>
     </row>
     <row r="60" spans="1:26" ht="13">
-      <c r="A60" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="B60" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="C60" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="D60" s="19" t="s">
-        <v>160</v>
-      </c>
-      <c r="E60" s="1"/>
-      <c r="F60" s="19" t="s">
-        <v>161</v>
-      </c>
+      <c r="A60" s="18"/>
+      <c r="B60" s="18"/>
+      <c r="C60" s="18"/>
+      <c r="D60" s="18"/>
+      <c r="E60" s="18"/>
+      <c r="F60" s="1"/>
       <c r="G60" s="1"/>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
@@ -3554,20 +3025,12 @@
       <c r="Z60" s="1"/>
     </row>
     <row r="61" spans="1:26" ht="13">
-      <c r="A61" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="B61" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="C61" s="19" t="s">
-        <v>163</v>
-      </c>
-      <c r="D61" s="19" t="s">
-        <v>164</v>
-      </c>
-      <c r="E61" s="1"/>
-      <c r="F61" s="1"/>
+      <c r="A61" s="18"/>
+      <c r="B61" s="18"/>
+      <c r="C61" s="18"/>
+      <c r="D61" s="18"/>
+      <c r="E61" s="18"/>
+      <c r="F61" s="18"/>
       <c r="G61" s="1"/>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
@@ -3579,8 +3042,8 @@
       <c r="O61" s="1"/>
       <c r="P61" s="1"/>
       <c r="Q61" s="1"/>
-      <c r="R61" s="19"/>
-      <c r="S61" s="19"/>
+      <c r="R61" s="1"/>
+      <c r="S61" s="1"/>
       <c r="T61" s="1"/>
       <c r="U61" s="1"/>
       <c r="V61" s="1"/>
@@ -3590,20 +3053,12 @@
       <c r="Z61" s="1"/>
     </row>
     <row r="62" spans="1:26" ht="13">
-      <c r="A62" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="B62" s="19" t="s">
-        <v>165</v>
-      </c>
-      <c r="C62" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="D62" s="19" t="s">
-        <v>167</v>
-      </c>
+      <c r="A62" s="18"/>
+      <c r="B62" s="18"/>
+      <c r="C62" s="18"/>
+      <c r="D62" s="18"/>
       <c r="E62" s="1"/>
-      <c r="F62" s="1"/>
+      <c r="F62" s="18"/>
       <c r="G62" s="1"/>
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
@@ -3615,12 +3070,8 @@
       <c r="O62" s="1"/>
       <c r="P62" s="1"/>
       <c r="Q62" s="1"/>
-      <c r="R62" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="S62" s="19" t="s">
-        <v>168</v>
-      </c>
+      <c r="R62" s="1"/>
+      <c r="S62" s="1"/>
       <c r="T62" s="1"/>
       <c r="U62" s="1"/>
       <c r="V62" s="1"/>
@@ -3630,18 +3081,10 @@
       <c r="Z62" s="1"/>
     </row>
     <row r="63" spans="1:26" ht="13">
-      <c r="A63" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="B63" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="C63" s="19" t="s">
-        <v>170</v>
-      </c>
-      <c r="D63" s="19" t="s">
-        <v>171</v>
-      </c>
+      <c r="A63" s="18"/>
+      <c r="B63" s="18"/>
+      <c r="C63" s="18"/>
+      <c r="D63" s="18"/>
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
       <c r="G63" s="1"/>
@@ -3655,12 +3098,8 @@
       <c r="O63" s="1"/>
       <c r="P63" s="1"/>
       <c r="Q63" s="1"/>
-      <c r="R63" s="19" t="s">
-        <v>172</v>
-      </c>
-      <c r="S63" s="19" t="s">
-        <v>172</v>
-      </c>
+      <c r="R63" s="18"/>
+      <c r="S63" s="18"/>
       <c r="T63" s="1"/>
       <c r="U63" s="1"/>
       <c r="V63" s="1"/>
@@ -3670,18 +3109,10 @@
       <c r="Z63" s="1"/>
     </row>
     <row r="64" spans="1:26" ht="13">
-      <c r="A64" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="B64" s="19" t="s">
-        <v>173</v>
-      </c>
-      <c r="C64" s="19" t="s">
-        <v>174</v>
-      </c>
-      <c r="D64" s="19" t="s">
-        <v>175</v>
-      </c>
+      <c r="A64" s="18"/>
+      <c r="B64" s="18"/>
+      <c r="C64" s="18"/>
+      <c r="D64" s="18"/>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
@@ -3695,12 +3126,8 @@
       <c r="O64" s="1"/>
       <c r="P64" s="1"/>
       <c r="Q64" s="1"/>
-      <c r="R64" s="19" t="s">
-        <v>176</v>
-      </c>
-      <c r="S64" s="19" t="s">
-        <v>176</v>
-      </c>
+      <c r="R64" s="18"/>
+      <c r="S64" s="18"/>
       <c r="T64" s="1"/>
       <c r="U64" s="1"/>
       <c r="V64" s="1"/>
@@ -3710,18 +3137,10 @@
       <c r="Z64" s="1"/>
     </row>
     <row r="65" spans="1:26" ht="13">
-      <c r="A65" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="B65" s="19" t="s">
-        <v>177</v>
-      </c>
-      <c r="C65" s="19" t="s">
-        <v>178</v>
-      </c>
-      <c r="D65" s="19" t="s">
-        <v>179</v>
-      </c>
+      <c r="A65" s="18"/>
+      <c r="B65" s="18"/>
+      <c r="C65" s="18"/>
+      <c r="D65" s="18"/>
       <c r="E65" s="1"/>
       <c r="F65" s="1"/>
       <c r="G65" s="1"/>
@@ -3735,12 +3154,8 @@
       <c r="O65" s="1"/>
       <c r="P65" s="1"/>
       <c r="Q65" s="1"/>
-      <c r="R65" s="19" t="s">
-        <v>180</v>
-      </c>
-      <c r="S65" s="19" t="s">
-        <v>180</v>
-      </c>
+      <c r="R65" s="18"/>
+      <c r="S65" s="18"/>
       <c r="T65" s="1"/>
       <c r="U65" s="1"/>
       <c r="V65" s="1"/>
@@ -3750,18 +3165,10 @@
       <c r="Z65" s="1"/>
     </row>
     <row r="66" spans="1:26" ht="13">
-      <c r="A66" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="B66" s="19" t="s">
-        <v>181</v>
-      </c>
-      <c r="C66" s="19" t="s">
-        <v>182</v>
-      </c>
-      <c r="D66" s="19" t="s">
-        <v>183</v>
-      </c>
+      <c r="A66" s="18"/>
+      <c r="B66" s="18"/>
+      <c r="C66" s="18"/>
+      <c r="D66" s="18"/>
       <c r="E66" s="1"/>
       <c r="F66" s="1"/>
       <c r="G66" s="1"/>
@@ -3775,12 +3182,8 @@
       <c r="O66" s="1"/>
       <c r="P66" s="1"/>
       <c r="Q66" s="1"/>
-      <c r="R66" s="19" t="s">
-        <v>184</v>
-      </c>
-      <c r="S66" s="19" t="s">
-        <v>184</v>
-      </c>
+      <c r="R66" s="18"/>
+      <c r="S66" s="18"/>
       <c r="T66" s="1"/>
       <c r="U66" s="1"/>
       <c r="V66" s="1"/>
@@ -3790,18 +3193,10 @@
       <c r="Z66" s="1"/>
     </row>
     <row r="67" spans="1:26" ht="13">
-      <c r="A67" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="B67" s="19" t="s">
-        <v>185</v>
-      </c>
-      <c r="C67" s="19" t="s">
-        <v>186</v>
-      </c>
-      <c r="D67" s="19" t="s">
-        <v>187</v>
-      </c>
+      <c r="A67" s="18"/>
+      <c r="B67" s="18"/>
+      <c r="C67" s="18"/>
+      <c r="D67" s="18"/>
       <c r="E67" s="1"/>
       <c r="F67" s="1"/>
       <c r="G67" s="1"/>
@@ -3815,12 +3210,8 @@
       <c r="O67" s="1"/>
       <c r="P67" s="1"/>
       <c r="Q67" s="1"/>
-      <c r="R67" s="19" t="s">
-        <v>188</v>
-      </c>
-      <c r="S67" s="19" t="s">
-        <v>188</v>
-      </c>
+      <c r="R67" s="18"/>
+      <c r="S67" s="18"/>
       <c r="T67" s="1"/>
       <c r="U67" s="1"/>
       <c r="V67" s="1"/>
@@ -3830,18 +3221,10 @@
       <c r="Z67" s="1"/>
     </row>
     <row r="68" spans="1:26" ht="13">
-      <c r="A68" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="B68" s="19" t="s">
-        <v>189</v>
-      </c>
-      <c r="C68" s="19" t="s">
-        <v>190</v>
-      </c>
-      <c r="D68" s="19" t="s">
-        <v>191</v>
-      </c>
+      <c r="A68" s="18"/>
+      <c r="B68" s="18"/>
+      <c r="C68" s="18"/>
+      <c r="D68" s="18"/>
       <c r="E68" s="1"/>
       <c r="F68" s="1"/>
       <c r="G68" s="1"/>
@@ -3855,8 +3238,8 @@
       <c r="O68" s="1"/>
       <c r="P68" s="1"/>
       <c r="Q68" s="1"/>
-      <c r="R68" s="1"/>
-      <c r="S68" s="1"/>
+      <c r="R68" s="18"/>
+      <c r="S68" s="18"/>
       <c r="T68" s="1"/>
       <c r="U68" s="1"/>
       <c r="V68" s="1"/>
@@ -3866,14 +3249,10 @@
       <c r="Z68" s="1"/>
     </row>
     <row r="69" spans="1:26" ht="13">
-      <c r="A69" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="B69" s="19" t="s">
-        <v>147</v>
-      </c>
-      <c r="C69" s="1"/>
-      <c r="D69" s="1"/>
+      <c r="A69" s="18"/>
+      <c r="B69" s="18"/>
+      <c r="C69" s="18"/>
+      <c r="D69" s="18"/>
       <c r="E69" s="1"/>
       <c r="F69" s="1"/>
       <c r="G69" s="1"/>
@@ -3887,8 +3266,8 @@
       <c r="O69" s="1"/>
       <c r="P69" s="1"/>
       <c r="Q69" s="1"/>
-      <c r="R69" s="1"/>
-      <c r="S69" s="1"/>
+      <c r="R69" s="18"/>
+      <c r="S69" s="18"/>
       <c r="T69" s="1"/>
       <c r="U69" s="1"/>
       <c r="V69" s="1"/>
@@ -3898,23 +3277,13 @@
       <c r="Z69" s="1"/>
     </row>
     <row r="70" spans="1:26" ht="13">
-      <c r="A70" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="B70" s="19" t="s">
-        <v>128</v>
-      </c>
-      <c r="C70" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="D70" s="19" t="s">
-        <v>193</v>
-      </c>
+      <c r="A70" s="18"/>
+      <c r="B70" s="18"/>
+      <c r="C70" s="18"/>
+      <c r="D70" s="18"/>
       <c r="E70" s="1"/>
       <c r="F70" s="1"/>
-      <c r="G70" s="19" t="s">
-        <v>48</v>
-      </c>
+      <c r="G70" s="1"/>
       <c r="H70" s="1"/>
       <c r="I70" s="1"/>
       <c r="J70" s="1"/>
@@ -3936,23 +3305,13 @@
       <c r="Z70" s="1"/>
     </row>
     <row r="71" spans="1:26" ht="13">
-      <c r="A71" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="B71" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="C71" s="19" t="s">
-        <v>195</v>
-      </c>
-      <c r="D71" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="E71" s="19" t="s">
-        <v>65</v>
-      </c>
+      <c r="A71" s="18"/>
+      <c r="B71" s="18"/>
+      <c r="C71" s="1"/>
+      <c r="D71" s="1"/>
+      <c r="E71" s="1"/>
       <c r="F71" s="1"/>
-      <c r="G71" s="19"/>
+      <c r="G71" s="1"/>
       <c r="H71" s="1"/>
       <c r="I71" s="1"/>
       <c r="J71" s="1"/>
@@ -3974,27 +3333,17 @@
       <c r="Z71" s="1"/>
     </row>
     <row r="72" spans="1:26" ht="13">
-      <c r="A72" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="B72" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="C72" s="19" t="s">
-        <v>199</v>
-      </c>
-      <c r="D72" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="E72" s="7" t="s">
-        <v>65</v>
-      </c>
+      <c r="A72" s="18"/>
+      <c r="B72" s="18"/>
+      <c r="C72" s="7"/>
+      <c r="D72" s="18"/>
+      <c r="E72" s="1"/>
       <c r="F72" s="1"/>
-      <c r="G72" s="19"/>
+      <c r="G72" s="18"/>
       <c r="H72" s="1"/>
-      <c r="I72" s="7"/>
-      <c r="J72" s="25"/>
-      <c r="K72" s="25"/>
+      <c r="I72" s="1"/>
+      <c r="J72" s="1"/>
+      <c r="K72" s="1"/>
       <c r="L72" s="1"/>
       <c r="M72" s="1"/>
       <c r="N72" s="1"/>
@@ -4012,21 +3361,13 @@
       <c r="Z72" s="1"/>
     </row>
     <row r="73" spans="1:26" ht="13">
-      <c r="A73" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="B73" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="C73" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="D73" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="E73" s="1"/>
+      <c r="A73" s="18"/>
+      <c r="B73" s="7"/>
+      <c r="C73" s="18"/>
+      <c r="D73" s="7"/>
+      <c r="E73" s="18"/>
       <c r="F73" s="1"/>
-      <c r="G73" s="19"/>
+      <c r="G73" s="18"/>
       <c r="H73" s="1"/>
       <c r="I73" s="1"/>
       <c r="J73" s="1"/>
@@ -4048,21 +3389,17 @@
       <c r="Z73" s="1"/>
     </row>
     <row r="74" spans="1:26" ht="13">
-      <c r="A74" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="B74" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="C74" s="19"/>
-      <c r="D74" s="19"/>
-      <c r="E74" s="1"/>
+      <c r="A74" s="7"/>
+      <c r="B74" s="7"/>
+      <c r="C74" s="18"/>
+      <c r="D74" s="7"/>
+      <c r="E74" s="7"/>
       <c r="F74" s="1"/>
-      <c r="G74" s="19"/>
+      <c r="G74" s="18"/>
       <c r="H74" s="1"/>
-      <c r="I74" s="1"/>
-      <c r="J74" s="1"/>
-      <c r="K74" s="1"/>
+      <c r="I74" s="7"/>
+      <c r="J74" s="24"/>
+      <c r="K74" s="24"/>
       <c r="L74" s="1"/>
       <c r="M74" s="1"/>
       <c r="N74" s="1"/>
@@ -4080,23 +3417,13 @@
       <c r="Z74" s="1"/>
     </row>
     <row r="75" spans="1:26" ht="13">
-      <c r="A75" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="B75" s="19" t="s">
-        <v>204</v>
-      </c>
-      <c r="C75" s="19" t="s">
-        <v>205</v>
-      </c>
-      <c r="D75" s="19" t="s">
-        <v>206</v>
-      </c>
+      <c r="A75" s="7"/>
+      <c r="B75" s="7"/>
+      <c r="C75" s="7"/>
+      <c r="D75" s="7"/>
       <c r="E75" s="1"/>
       <c r="F75" s="1"/>
-      <c r="G75" s="19" t="s">
-        <v>48</v>
-      </c>
+      <c r="G75" s="18"/>
       <c r="H75" s="1"/>
       <c r="I75" s="1"/>
       <c r="J75" s="1"/>
@@ -4118,33 +3445,17 @@
       <c r="Z75" s="1"/>
     </row>
     <row r="76" spans="1:26" ht="13">
-      <c r="A76" s="19" t="s">
-        <v>207</v>
-      </c>
-      <c r="B76" s="19" t="s">
-        <v>208</v>
-      </c>
-      <c r="C76" s="19" t="s">
-        <v>209</v>
-      </c>
-      <c r="D76" s="19" t="s">
-        <v>210</v>
-      </c>
-      <c r="E76" s="19" t="s">
-        <v>65</v>
-      </c>
+      <c r="A76" s="7"/>
+      <c r="B76" s="7"/>
+      <c r="C76" s="18"/>
+      <c r="D76" s="18"/>
+      <c r="E76" s="1"/>
       <c r="F76" s="1"/>
-      <c r="G76" s="1"/>
+      <c r="G76" s="18"/>
       <c r="H76" s="1"/>
-      <c r="I76" s="19" t="s">
-        <v>211</v>
-      </c>
-      <c r="J76" s="23" t="s">
-        <v>212</v>
-      </c>
-      <c r="K76" s="23" t="s">
-        <v>213</v>
-      </c>
+      <c r="I76" s="1"/>
+      <c r="J76" s="1"/>
+      <c r="K76" s="1"/>
       <c r="L76" s="1"/>
       <c r="M76" s="1"/>
       <c r="N76" s="1"/>
@@ -4162,23 +3473,13 @@
       <c r="Z76" s="1"/>
     </row>
     <row r="77" spans="1:26" ht="13">
-      <c r="A77" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="B77" s="19" t="s">
-        <v>214</v>
-      </c>
-      <c r="C77" s="19" t="s">
-        <v>215</v>
-      </c>
-      <c r="D77" s="19" t="s">
-        <v>216</v>
-      </c>
-      <c r="E77" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="F77" s="19"/>
-      <c r="G77" s="1"/>
+      <c r="A77" s="18"/>
+      <c r="B77" s="18"/>
+      <c r="C77" s="18"/>
+      <c r="D77" s="18"/>
+      <c r="E77" s="1"/>
+      <c r="F77" s="1"/>
+      <c r="G77" s="18"/>
       <c r="H77" s="1"/>
       <c r="I77" s="1"/>
       <c r="J77" s="1"/>
@@ -4200,25 +3501,17 @@
       <c r="Z77" s="1"/>
     </row>
     <row r="78" spans="1:26" ht="13">
-      <c r="A78" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="B78" s="19" t="s">
-        <v>217</v>
-      </c>
-      <c r="C78" s="19" t="s">
-        <v>218</v>
-      </c>
-      <c r="D78" s="19" t="s">
-        <v>219</v>
-      </c>
-      <c r="E78" s="1"/>
+      <c r="A78" s="18"/>
+      <c r="B78" s="18"/>
+      <c r="C78" s="18"/>
+      <c r="D78" s="18"/>
+      <c r="E78" s="18"/>
       <c r="F78" s="1"/>
       <c r="G78" s="1"/>
       <c r="H78" s="1"/>
-      <c r="I78" s="1"/>
-      <c r="J78" s="1"/>
-      <c r="K78" s="1"/>
+      <c r="I78" s="18"/>
+      <c r="J78" s="22"/>
+      <c r="K78" s="22"/>
       <c r="L78" s="1"/>
       <c r="M78" s="1"/>
       <c r="N78" s="1"/>
@@ -4236,17 +3529,13 @@
       <c r="Z78" s="1"/>
     </row>
     <row r="79" spans="1:26" ht="13">
-      <c r="A79" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="B79" s="19" t="s">
-        <v>204</v>
-      </c>
-      <c r="C79" s="19"/>
-      <c r="D79" s="19"/>
-      <c r="E79" s="1"/>
-      <c r="F79" s="1"/>
-      <c r="G79" s="19"/>
+      <c r="A79" s="18"/>
+      <c r="B79" s="18"/>
+      <c r="C79" s="18"/>
+      <c r="D79" s="18"/>
+      <c r="E79" s="18"/>
+      <c r="F79" s="18"/>
+      <c r="G79" s="1"/>
       <c r="H79" s="1"/>
       <c r="I79" s="1"/>
       <c r="J79" s="1"/>
@@ -4268,23 +3557,13 @@
       <c r="Z79" s="1"/>
     </row>
     <row r="80" spans="1:26" ht="13">
-      <c r="A80" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="B80" s="19" t="s">
-        <v>220</v>
-      </c>
-      <c r="C80" s="19" t="s">
-        <v>221</v>
-      </c>
-      <c r="D80" s="19" t="s">
-        <v>222</v>
-      </c>
+      <c r="A80" s="18"/>
+      <c r="B80" s="18"/>
+      <c r="C80" s="18"/>
+      <c r="D80" s="18"/>
       <c r="E80" s="1"/>
       <c r="F80" s="1"/>
-      <c r="G80" s="19" t="s">
-        <v>48</v>
-      </c>
+      <c r="G80" s="1"/>
       <c r="H80" s="1"/>
       <c r="I80" s="1"/>
       <c r="J80" s="1"/>
@@ -4306,23 +3585,13 @@
       <c r="Z80" s="1"/>
     </row>
     <row r="81" spans="1:26" ht="13">
-      <c r="A81" s="19" t="s">
-        <v>150</v>
-      </c>
-      <c r="B81" s="19" t="s">
-        <v>223</v>
-      </c>
-      <c r="C81" s="19" t="s">
-        <v>224</v>
-      </c>
-      <c r="D81" s="19" t="s">
-        <v>225</v>
-      </c>
-      <c r="E81" s="19" t="s">
-        <v>65</v>
-      </c>
+      <c r="A81" s="18"/>
+      <c r="B81" s="18"/>
+      <c r="C81" s="18"/>
+      <c r="D81" s="18"/>
+      <c r="E81" s="1"/>
       <c r="F81" s="1"/>
-      <c r="G81" s="1"/>
+      <c r="G81" s="18"/>
       <c r="H81" s="1"/>
       <c r="I81" s="1"/>
       <c r="J81" s="1"/>
@@ -4344,23 +3613,13 @@
       <c r="Z81" s="1"/>
     </row>
     <row r="82" spans="1:26" ht="13">
-      <c r="A82" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="B82" s="19" t="s">
-        <v>226</v>
-      </c>
-      <c r="C82" s="19" t="s">
-        <v>227</v>
-      </c>
-      <c r="D82" s="19" t="s">
-        <v>228</v>
-      </c>
-      <c r="E82" s="19" t="s">
-        <v>65</v>
-      </c>
+      <c r="A82" s="18"/>
+      <c r="B82" s="18"/>
+      <c r="C82" s="18"/>
+      <c r="D82" s="18"/>
+      <c r="E82" s="1"/>
       <c r="F82" s="1"/>
-      <c r="G82" s="1"/>
+      <c r="G82" s="18"/>
       <c r="H82" s="1"/>
       <c r="I82" s="1"/>
       <c r="J82" s="1"/>
@@ -4382,19 +3641,11 @@
       <c r="Z82" s="1"/>
     </row>
     <row r="83" spans="1:26" ht="13">
-      <c r="A83" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="B83" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="C83" s="19" t="s">
-        <v>230</v>
-      </c>
-      <c r="D83" s="19" t="s">
-        <v>231</v>
-      </c>
-      <c r="E83" s="1"/>
+      <c r="A83" s="18"/>
+      <c r="B83" s="18"/>
+      <c r="C83" s="18"/>
+      <c r="D83" s="18"/>
+      <c r="E83" s="18"/>
       <c r="F83" s="1"/>
       <c r="G83" s="1"/>
       <c r="H83" s="1"/>
@@ -4418,15 +3669,11 @@
       <c r="Z83" s="1"/>
     </row>
     <row r="84" spans="1:26" ht="13">
-      <c r="A84" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="B84" s="19" t="s">
-        <v>220</v>
-      </c>
-      <c r="C84" s="1"/>
-      <c r="D84" s="1"/>
-      <c r="E84" s="1"/>
+      <c r="A84" s="18"/>
+      <c r="B84" s="18"/>
+      <c r="C84" s="18"/>
+      <c r="D84" s="18"/>
+      <c r="E84" s="18"/>
       <c r="F84" s="1"/>
       <c r="G84" s="1"/>
       <c r="H84" s="1"/>
@@ -4450,10 +3697,10 @@
       <c r="Z84" s="1"/>
     </row>
     <row r="85" spans="1:26" ht="13">
-      <c r="A85" s="1"/>
-      <c r="B85" s="1"/>
-      <c r="C85" s="1"/>
-      <c r="D85" s="1"/>
+      <c r="A85" s="18"/>
+      <c r="B85" s="18"/>
+      <c r="C85" s="18"/>
+      <c r="D85" s="18"/>
       <c r="E85" s="1"/>
       <c r="F85" s="1"/>
       <c r="G85" s="1"/>
@@ -4478,8 +3725,8 @@
       <c r="Z85" s="1"/>
     </row>
     <row r="86" spans="1:26" ht="13">
-      <c r="A86" s="1"/>
-      <c r="B86" s="1"/>
+      <c r="A86" s="18"/>
+      <c r="B86" s="18"/>
       <c r="C86" s="1"/>
       <c r="D86" s="1"/>
       <c r="E86" s="1"/>
@@ -31021,39 +30268,95 @@
       <c r="Y1033" s="1"/>
       <c r="Z1033" s="1"/>
     </row>
+    <row r="1034" spans="1:26" ht="13">
+      <c r="A1034" s="1"/>
+      <c r="B1034" s="1"/>
+      <c r="C1034" s="1"/>
+      <c r="D1034" s="1"/>
+      <c r="E1034" s="1"/>
+      <c r="F1034" s="1"/>
+      <c r="G1034" s="1"/>
+      <c r="H1034" s="1"/>
+      <c r="I1034" s="1"/>
+      <c r="J1034" s="1"/>
+      <c r="K1034" s="1"/>
+      <c r="L1034" s="1"/>
+      <c r="M1034" s="1"/>
+      <c r="N1034" s="1"/>
+      <c r="O1034" s="1"/>
+      <c r="P1034" s="1"/>
+      <c r="Q1034" s="1"/>
+      <c r="R1034" s="1"/>
+      <c r="S1034" s="1"/>
+      <c r="T1034" s="1"/>
+      <c r="U1034" s="1"/>
+      <c r="V1034" s="1"/>
+      <c r="W1034" s="1"/>
+      <c r="X1034" s="1"/>
+      <c r="Y1034" s="1"/>
+      <c r="Z1034" s="1"/>
+    </row>
+    <row r="1035" spans="1:26" ht="13">
+      <c r="A1035" s="1"/>
+      <c r="B1035" s="1"/>
+      <c r="C1035" s="1"/>
+      <c r="D1035" s="1"/>
+      <c r="E1035" s="1"/>
+      <c r="F1035" s="1"/>
+      <c r="G1035" s="1"/>
+      <c r="H1035" s="1"/>
+      <c r="I1035" s="1"/>
+      <c r="J1035" s="1"/>
+      <c r="K1035" s="1"/>
+      <c r="L1035" s="1"/>
+      <c r="M1035" s="1"/>
+      <c r="N1035" s="1"/>
+      <c r="O1035" s="1"/>
+      <c r="P1035" s="1"/>
+      <c r="Q1035" s="1"/>
+      <c r="R1035" s="1"/>
+      <c r="S1035" s="1"/>
+      <c r="T1035" s="1"/>
+      <c r="U1035" s="1"/>
+      <c r="V1035" s="1"/>
+      <c r="W1035" s="1"/>
+      <c r="X1035" s="1"/>
+      <c r="Y1035" s="1"/>
+      <c r="Z1035" s="1"/>
+    </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C41:D41"/>
+  <mergeCells count="1">
+    <mergeCell ref="C43:D43"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Z20"/>
+  <dimension ref="A1:Z34"/>
   <sheetFormatPr defaultColWidth="14.40625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="15.40625" customWidth="1"/>
     <col min="2" max="2" width="18.26953125" customWidth="1"/>
     <col min="3" max="3" width="52.6796875" customWidth="1"/>
+    <col min="4" max="4" width="90.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26">
-      <c r="A1" s="26" t="s">
-        <v>232</v>
+    <row r="1" spans="1:26" ht="15.25">
+      <c r="A1" s="25" t="s">
+        <v>60</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="27" t="s">
+      <c r="C1" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="26" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1"/>
@@ -31080,278 +30383,445 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A2" s="28" t="s">
-        <v>233</v>
+      <c r="A2" s="27" t="s">
+        <v>61</v>
       </c>
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2" s="27" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A3" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="B3" s="28" t="s">
+        <v>64</v>
+      </c>
+      <c r="C3" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="C2" s="28" t="s">
-        <v>234</v>
+      <c r="D3" s="27" t="s">
+        <v>66</v>
       </c>
-      <c r="D2" s="28" t="s">
-        <v>235</v>
+    </row>
+    <row r="4" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A4" s="27" t="s">
+        <v>55</v>
       </c>
-    </row>
-    <row r="3" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A3" s="28" t="s">
-        <v>233</v>
+      <c r="B4" s="27" t="s">
+        <v>67</v>
       </c>
-      <c r="B3" s="29" t="s">
-        <v>236</v>
+      <c r="C4" s="27" t="s">
+        <v>68</v>
       </c>
-      <c r="C3" s="28" t="s">
-        <v>237</v>
+      <c r="D4" s="27" t="s">
+        <v>69</v>
       </c>
-      <c r="D3" s="28" t="s">
-        <v>238</v>
+    </row>
+    <row r="5" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A5" s="27" t="s">
+        <v>55</v>
       </c>
-    </row>
-    <row r="4" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A4" s="28" t="s">
+      <c r="B5" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" s="27" t="s">
+        <v>70</v>
+      </c>
+      <c r="D5" s="27" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A6" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="27" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>73</v>
+      </c>
+      <c r="D6" s="27" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A7" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="D7" s="27" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A8" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="D8" s="27" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A9" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="B9" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="C9" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="B4" s="28" t="s">
-        <v>239</v>
+      <c r="D9" s="27" t="s">
+        <v>82</v>
       </c>
-      <c r="C4" s="28" t="s">
-        <v>240</v>
+    </row>
+    <row r="10" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A10" s="27" t="s">
+        <v>59</v>
       </c>
-      <c r="D4" s="28" t="s">
-        <v>241</v>
+      <c r="B10" s="27" t="s">
+        <v>83</v>
       </c>
-    </row>
-    <row r="5" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A5" s="28" t="s">
+      <c r="C10" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="D10" s="27" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A11" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11" s="27" t="s">
+        <v>86</v>
+      </c>
+      <c r="C11" s="27" t="s">
+        <v>87</v>
+      </c>
+      <c r="D11" s="27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A12" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="B12" s="27" t="s">
+        <v>89</v>
+      </c>
+      <c r="C12" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="D12" s="27" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A13" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="B13" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="C13" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="D13" s="27" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A14" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="B14" s="27" t="s">
+        <v>95</v>
+      </c>
+      <c r="C14" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="D14" s="27" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A15" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="C15" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="D15" s="27" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A16" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="B16" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="C16" s="27" t="s">
+        <v>102</v>
+      </c>
+      <c r="D16" s="27" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A17" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="B17" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="C17" s="27" t="s">
+        <v>104</v>
+      </c>
+      <c r="D17" s="27" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A18" s="27" t="s">
+        <v>106</v>
+      </c>
+      <c r="B18" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="C18" s="27" t="s">
+        <v>108</v>
+      </c>
+      <c r="D18" s="27" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A19" s="27" t="s">
+        <v>106</v>
+      </c>
+      <c r="B19" s="27" t="s">
+        <v>110</v>
+      </c>
+      <c r="C19" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="D19" s="27" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="13">
+      <c r="A20" s="27" t="s">
+        <v>106</v>
+      </c>
+      <c r="B20" s="27" t="s">
+        <v>113</v>
+      </c>
+      <c r="C20" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="D20" s="27" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A21" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="B21" s="34" t="s">
+        <v>151</v>
+      </c>
+      <c r="D21" s="32" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A22" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="B22" s="34" t="s">
+        <v>146</v>
+      </c>
+      <c r="D22" s="32" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A23" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="B23" s="34" t="s">
+        <v>147</v>
+      </c>
+      <c r="D23" s="34" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A24" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="B24" s="34" t="s">
+        <v>148</v>
+      </c>
+      <c r="D24" s="34" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A25" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="B25" s="34" t="s">
+        <v>149</v>
+      </c>
+      <c r="D25" s="34" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A26" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="B26" s="34" t="s">
+        <v>150</v>
+      </c>
+      <c r="D26" s="34" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A27" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="B27" s="34" t="s">
+        <v>152</v>
+      </c>
+      <c r="D27" s="34" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A28" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="B28" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="D28" s="35" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A29" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="B29" s="34" t="s">
+        <v>154</v>
+      </c>
+      <c r="D29" s="32" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A30" s="34" t="s">
+        <v>170</v>
+      </c>
+      <c r="B30" s="34" t="s">
+        <v>172</v>
+      </c>
+      <c r="C30" s="33" t="s">
+        <v>174</v>
+      </c>
+      <c r="D30" s="34" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A31" s="34" t="s">
+        <v>170</v>
+      </c>
+      <c r="B31" s="34" t="s">
+        <v>183</v>
+      </c>
+      <c r="D31" s="34" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A32" s="34" t="s">
+        <v>170</v>
+      </c>
+      <c r="B32" s="34" t="s">
+        <v>175</v>
+      </c>
+      <c r="C32" s="33" t="s">
+        <v>176</v>
+      </c>
+      <c r="D32" s="33" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A33" s="34" t="s">
+        <v>170</v>
+      </c>
+      <c r="B33" s="34" t="s">
+        <v>178</v>
+      </c>
+      <c r="C33" s="33" t="s">
+        <v>179</v>
+      </c>
+      <c r="D33" s="33" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A34" s="34" t="s">
+        <v>170</v>
+      </c>
+      <c r="B34" s="34" t="s">
+        <v>154</v>
+      </c>
+      <c r="C34" s="33" t="s">
         <v>81</v>
       </c>
-      <c r="B5" s="28" t="s">
-        <v>97</v>
-      </c>
-      <c r="C5" s="28" t="s">
-        <v>242</v>
-      </c>
-      <c r="D5" s="28" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="6" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A6" s="28" t="s">
-        <v>81</v>
-      </c>
-      <c r="B6" s="28" t="s">
-        <v>244</v>
-      </c>
-      <c r="C6" s="28" t="s">
-        <v>245</v>
-      </c>
-      <c r="D6" s="28" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="7" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A7" s="28" t="s">
-        <v>81</v>
-      </c>
-      <c r="B7" s="28" t="s">
-        <v>103</v>
-      </c>
-      <c r="C7" s="28" t="s">
-        <v>247</v>
-      </c>
-      <c r="D7" s="28" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A8" s="28" t="s">
-        <v>81</v>
-      </c>
-      <c r="B8" s="28" t="s">
-        <v>249</v>
-      </c>
-      <c r="C8" s="28" t="s">
-        <v>250</v>
-      </c>
-      <c r="D8" s="28" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A9" s="28" t="s">
-        <v>81</v>
-      </c>
-      <c r="B9" s="28" t="s">
-        <v>252</v>
-      </c>
-      <c r="C9" s="28" t="s">
-        <v>253</v>
-      </c>
-      <c r="D9" s="28" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A10" s="28" t="s">
-        <v>208</v>
-      </c>
-      <c r="B10" s="28" t="s">
-        <v>255</v>
-      </c>
-      <c r="C10" s="28" t="s">
-        <v>256</v>
-      </c>
-      <c r="D10" s="28" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A11" s="28" t="s">
-        <v>208</v>
-      </c>
-      <c r="B11" s="28" t="s">
-        <v>258</v>
-      </c>
-      <c r="C11" s="28" t="s">
-        <v>259</v>
-      </c>
-      <c r="D11" s="28" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="12" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A12" s="28" t="s">
-        <v>208</v>
-      </c>
-      <c r="B12" s="28" t="s">
-        <v>261</v>
-      </c>
-      <c r="C12" s="28" t="s">
-        <v>262</v>
-      </c>
-      <c r="D12" s="28" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="13" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A13" s="28" t="s">
-        <v>208</v>
-      </c>
-      <c r="B13" s="28" t="s">
-        <v>264</v>
-      </c>
-      <c r="C13" s="28" t="s">
-        <v>265</v>
-      </c>
-      <c r="D13" s="28" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="14" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A14" s="28" t="s">
-        <v>208</v>
-      </c>
-      <c r="B14" s="28" t="s">
-        <v>267</v>
-      </c>
-      <c r="C14" s="28" t="s">
-        <v>268</v>
-      </c>
-      <c r="D14" s="28" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="15" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A15" s="28" t="s">
-        <v>208</v>
-      </c>
-      <c r="B15" s="28" t="s">
-        <v>270</v>
-      </c>
-      <c r="C15" s="28" t="s">
-        <v>271</v>
-      </c>
-      <c r="D15" s="28" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="16" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A16" s="28" t="s">
-        <v>208</v>
-      </c>
-      <c r="B16" s="28" t="s">
-        <v>273</v>
-      </c>
-      <c r="C16" s="28" t="s">
-        <v>274</v>
-      </c>
-      <c r="D16" s="28" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A17" s="28" t="s">
-        <v>208</v>
-      </c>
-      <c r="B17" s="28" t="s">
-        <v>252</v>
-      </c>
-      <c r="C17" s="28" t="s">
-        <v>276</v>
-      </c>
-      <c r="D17" s="28" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A18" s="28" t="s">
-        <v>278</v>
-      </c>
-      <c r="B18" s="28" t="s">
-        <v>279</v>
-      </c>
-      <c r="C18" s="28" t="s">
-        <v>280</v>
-      </c>
-      <c r="D18" s="28" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A19" s="28" t="s">
-        <v>278</v>
-      </c>
-      <c r="B19" s="28" t="s">
-        <v>282</v>
-      </c>
-      <c r="C19" s="28" t="s">
-        <v>283</v>
-      </c>
-      <c r="D19" s="28" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="13">
-      <c r="A20" s="28" t="s">
-        <v>278</v>
-      </c>
-      <c r="B20" s="28" t="s">
-        <v>285</v>
-      </c>
-      <c r="C20" s="28" t="s">
-        <v>286</v>
-      </c>
-      <c r="D20" s="28" t="s">
-        <v>287</v>
+      <c r="D34" s="33" t="s">
+        <v>181</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -31360,22 +30830,22 @@
   <sheetData>
     <row r="1" spans="1:26" ht="15.75" customHeight="1">
       <c r="A1" s="3" t="s">
-        <v>288</v>
+        <v>116</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>289</v>
+        <v>117</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>290</v>
+        <v>118</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>291</v>
+        <v>119</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>292</v>
+        <v>120</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>293</v>
+        <v>121</v>
       </c>
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
@@ -31399,20 +30869,20 @@
       <c r="Z1" s="3"/>
     </row>
     <row r="2" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A2" s="21" t="s">
-        <v>294</v>
+      <c r="A2" s="20" t="s">
+        <v>122</v>
       </c>
-      <c r="B2" s="21" t="s">
-        <v>295</v>
+      <c r="B2" s="20" t="s">
+        <v>123</v>
       </c>
-      <c r="C2" s="30">
+      <c r="C2" s="29">
         <v>43596</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>296</v>
+        <v>124</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>297</v>
+        <v>125</v>
       </c>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
